--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:FG3"/>
+  <dimension ref="B1:FG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,6 +1672,445 @@
       </c>
       <c r="FG3">
         <f>FB3/FA3-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>22 Jul 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I4">
+        <f>C4/D4-1</f>
+        <v/>
+      </c>
+      <c r="J4">
+        <f>E4/D4-1</f>
+        <v/>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R4">
+        <f>L4/M4-1</f>
+        <v/>
+      </c>
+      <c r="S4">
+        <f>N4/M4-1</f>
+        <v/>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA4">
+        <f>U4/V4-1</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>W4/V4-1</f>
+        <v/>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <f>AD4/AE4-1</f>
+        <v/>
+      </c>
+      <c r="AK4">
+        <f>AF4/AE4-1</f>
+        <v/>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS4">
+        <f>AM4/AN4-1</f>
+        <v/>
+      </c>
+      <c r="AT4">
+        <f>AO4/AN4-1</f>
+        <v/>
+      </c>
+      <c r="AV4" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB4">
+        <f>AV4/AW4-1</f>
+        <v/>
+      </c>
+      <c r="BC4">
+        <f>AX4/AW4-1</f>
+        <v/>
+      </c>
+      <c r="BE4" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF4" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK4">
+        <f>BE4/BF4-1</f>
+        <v/>
+      </c>
+      <c r="BL4">
+        <f>BG4/BF4-1</f>
+        <v/>
+      </c>
+      <c r="BN4" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO4" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT4">
+        <f>BN4/BO4-1</f>
+        <v/>
+      </c>
+      <c r="BU4">
+        <f>BP4/BO4-1</f>
+        <v/>
+      </c>
+      <c r="BW4" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX4" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC4">
+        <f>BW4/BX4-1</f>
+        <v/>
+      </c>
+      <c r="CD4">
+        <f>BY4/BX4-1</f>
+        <v/>
+      </c>
+      <c r="CF4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL4">
+        <f>CF4/CG4-1</f>
+        <v/>
+      </c>
+      <c r="CM4">
+        <f>CH4/CG4-1</f>
+        <v/>
+      </c>
+      <c r="CO4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU4">
+        <f>CO4/CP4-1</f>
+        <v/>
+      </c>
+      <c r="CV4">
+        <f>CQ4/CP4-1</f>
+        <v/>
+      </c>
+      <c r="CX4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY4" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD4">
+        <f>CX4/CY4-1</f>
+        <v/>
+      </c>
+      <c r="DE4">
+        <f>CZ4/CY4-1</f>
+        <v/>
+      </c>
+      <c r="DG4" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH4" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM4">
+        <f>DG4/DH4-1</f>
+        <v/>
+      </c>
+      <c r="DN4">
+        <f>DI4/DH4-1</f>
+        <v/>
+      </c>
+      <c r="DP4" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ4" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV4">
+        <f>DP4/DQ4-1</f>
+        <v/>
+      </c>
+      <c r="DW4">
+        <f>DR4/DQ4-1</f>
+        <v/>
+      </c>
+      <c r="DY4" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ4" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE4">
+        <f>DY4/DZ4-1</f>
+        <v/>
+      </c>
+      <c r="EF4">
+        <f>EA4/DZ4-1</f>
+        <v/>
+      </c>
+      <c r="EH4" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI4" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN4">
+        <f>EH4/EI4-1</f>
+        <v/>
+      </c>
+      <c r="EO4">
+        <f>EJ4/EI4-1</f>
+        <v/>
+      </c>
+      <c r="EQ4" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER4" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET4" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU4" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW4">
+        <f>EQ4/ER4-1</f>
+        <v/>
+      </c>
+      <c r="EX4">
+        <f>ES4/ER4-1</f>
+        <v/>
+      </c>
+      <c r="EZ4" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA4" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF4">
+        <f>EZ4/FA4-1</f>
+        <v/>
+      </c>
+      <c r="FG4">
+        <f>FB4/FA4-1</f>
         <v/>
       </c>
     </row>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:FG4"/>
+  <dimension ref="B1:FG5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2111,6 +2111,447 @@
       </c>
       <c r="FG4">
         <f>FB4/FA4-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>22 Jul 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I5">
+        <f>C5/D5-1</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>E5/D5-1</f>
+        <v/>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R5">
+        <f>L5/M5-1</f>
+        <v/>
+      </c>
+      <c r="S5">
+        <f>N5/M5-1</f>
+        <v/>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA5">
+        <f>U5/V5-1</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>W5/V5-1</f>
+        <v/>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <f>AD5/AE5-1</f>
+        <v/>
+      </c>
+      <c r="AK5">
+        <f>AF5/AE5-1</f>
+        <v/>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS5">
+        <f>AM5/AN5-1</f>
+        <v/>
+      </c>
+      <c r="AT5">
+        <f>AO5/AN5-1</f>
+        <v/>
+      </c>
+      <c r="AV5" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB5">
+        <f>AV5/AW5-1</f>
+        <v/>
+      </c>
+      <c r="BC5">
+        <f>AX5/AW5-1</f>
+        <v/>
+      </c>
+      <c r="BE5" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF5" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK5">
+        <f>BE5/BF5-1</f>
+        <v/>
+      </c>
+      <c r="BL5">
+        <f>BG5/BF5-1</f>
+        <v/>
+      </c>
+      <c r="BN5" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO5" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT5">
+        <f>BN5/BO5-1</f>
+        <v/>
+      </c>
+      <c r="BU5">
+        <f>BP5/BO5-1</f>
+        <v/>
+      </c>
+      <c r="BW5" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX5" s="1" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC5">
+        <f>BW5/BX5-1</f>
+        <v/>
+      </c>
+      <c r="CD5">
+        <f>BY5/BX5-1</f>
+        <v/>
+      </c>
+      <c r="CF5" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG5" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL5">
+        <f>CF5/CG5-1</f>
+        <v/>
+      </c>
+      <c r="CM5">
+        <f>CH5/CG5-1</f>
+        <v/>
+      </c>
+      <c r="CO5" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CU5">
+        <f>CO5/CP5-1</f>
+        <v/>
+      </c>
+      <c r="CV5">
+        <f>CQ5/CP5-1</f>
+        <v/>
+      </c>
+      <c r="CX5" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY5" s="1" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD5">
+        <f>CX5/CY5-1</f>
+        <v/>
+      </c>
+      <c r="DE5">
+        <f>CZ5/CY5-1</f>
+        <v/>
+      </c>
+      <c r="DG5" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH5" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM5">
+        <f>DG5/DH5-1</f>
+        <v/>
+      </c>
+      <c r="DN5">
+        <f>DI5/DH5-1</f>
+        <v/>
+      </c>
+      <c r="DP5" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ5" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV5">
+        <f>DP5/DQ5-1</f>
+        <v/>
+      </c>
+      <c r="DW5">
+        <f>DR5/DQ5-1</f>
+        <v/>
+      </c>
+      <c r="DY5" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ5" s="1" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE5">
+        <f>DY5/DZ5-1</f>
+        <v/>
+      </c>
+      <c r="EF5">
+        <f>EA5/DZ5-1</f>
+        <v/>
+      </c>
+      <c r="EH5" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI5" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN5">
+        <f>EH5/EI5-1</f>
+        <v/>
+      </c>
+      <c r="EO5">
+        <f>EJ5/EI5-1</f>
+        <v/>
+      </c>
+      <c r="EQ5" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER5" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU5" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW5">
+        <f>EQ5/ER5-1</f>
+        <v/>
+      </c>
+      <c r="EX5">
+        <f>ES5/ER5-1</f>
+        <v/>
+      </c>
+      <c r="EZ5" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA5" s="1" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC5" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF5">
+        <f>EZ5/FA5-1</f>
+        <v/>
+      </c>
+      <c r="FG5">
+        <f>FB5/FA5-1</f>
         <v/>
       </c>
     </row>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG5"/>
+  <dimension ref="A1:FG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -3031,6 +3031,445 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23 Jul 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I6">
+        <f>C6/D6-1</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>E6/D6-1</f>
+        <v/>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R6">
+        <f>L6/M6-1</f>
+        <v/>
+      </c>
+      <c r="S6">
+        <f>N6/M6-1</f>
+        <v/>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA6">
+        <f>U6/V6-1</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>W6/V6-1</f>
+        <v/>
+      </c>
+      <c r="AD6" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE6" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <f>AD6/AE6-1</f>
+        <v/>
+      </c>
+      <c r="AK6">
+        <f>AF6/AE6-1</f>
+        <v/>
+      </c>
+      <c r="AM6" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN6" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS6">
+        <f>AM6/AN6-1</f>
+        <v/>
+      </c>
+      <c r="AT6">
+        <f>AO6/AN6-1</f>
+        <v/>
+      </c>
+      <c r="AV6" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW6" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB6">
+        <f>AV6/AW6-1</f>
+        <v/>
+      </c>
+      <c r="BC6">
+        <f>AX6/AW6-1</f>
+        <v/>
+      </c>
+      <c r="BE6" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF6" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK6">
+        <f>BE6/BF6-1</f>
+        <v/>
+      </c>
+      <c r="BL6">
+        <f>BG6/BF6-1</f>
+        <v/>
+      </c>
+      <c r="BN6" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO6" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT6">
+        <f>BN6/BO6-1</f>
+        <v/>
+      </c>
+      <c r="BU6">
+        <f>BP6/BO6-1</f>
+        <v/>
+      </c>
+      <c r="BW6" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX6" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC6">
+        <f>BW6/BX6-1</f>
+        <v/>
+      </c>
+      <c r="CD6">
+        <f>BY6/BX6-1</f>
+        <v/>
+      </c>
+      <c r="CF6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL6">
+        <f>CF6/CG6-1</f>
+        <v/>
+      </c>
+      <c r="CM6">
+        <f>CH6/CG6-1</f>
+        <v/>
+      </c>
+      <c r="CO6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU6">
+        <f>CO6/CP6-1</f>
+        <v/>
+      </c>
+      <c r="CV6">
+        <f>CQ6/CP6-1</f>
+        <v/>
+      </c>
+      <c r="CX6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY6" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD6">
+        <f>CX6/CY6-1</f>
+        <v/>
+      </c>
+      <c r="DE6">
+        <f>CZ6/CY6-1</f>
+        <v/>
+      </c>
+      <c r="DG6" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH6" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM6">
+        <f>DG6/DH6-1</f>
+        <v/>
+      </c>
+      <c r="DN6">
+        <f>DI6/DH6-1</f>
+        <v/>
+      </c>
+      <c r="DP6" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ6" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV6">
+        <f>DP6/DQ6-1</f>
+        <v/>
+      </c>
+      <c r="DW6">
+        <f>DR6/DQ6-1</f>
+        <v/>
+      </c>
+      <c r="DY6" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ6" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE6">
+        <f>DY6/DZ6-1</f>
+        <v/>
+      </c>
+      <c r="EF6">
+        <f>EA6/DZ6-1</f>
+        <v/>
+      </c>
+      <c r="EH6" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI6" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN6">
+        <f>EH6/EI6-1</f>
+        <v/>
+      </c>
+      <c r="EO6">
+        <f>EJ6/EI6-1</f>
+        <v/>
+      </c>
+      <c r="EQ6" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER6" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET6" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU6" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW6">
+        <f>EQ6/ER6-1</f>
+        <v/>
+      </c>
+      <c r="EX6">
+        <f>ES6/ER6-1</f>
+        <v/>
+      </c>
+      <c r="EZ6" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA6" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC6" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD6" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF6">
+        <f>EZ6/FA6-1</f>
+        <v/>
+      </c>
+      <c r="FG6">
+        <f>FB6/FA6-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG6"/>
+  <dimension ref="A1:FG7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -3470,6 +3470,447 @@
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>23 Jul 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I7">
+        <f>C7/D7-1</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>E7/D7-1</f>
+        <v/>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R7">
+        <f>L7/M7-1</f>
+        <v/>
+      </c>
+      <c r="S7">
+        <f>N7/M7-1</f>
+        <v/>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA7">
+        <f>U7/V7-1</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>W7/V7-1</f>
+        <v/>
+      </c>
+      <c r="AD7" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE7" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <f>AD7/AE7-1</f>
+        <v/>
+      </c>
+      <c r="AK7">
+        <f>AF7/AE7-1</f>
+        <v/>
+      </c>
+      <c r="AM7" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN7" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS7">
+        <f>AM7/AN7-1</f>
+        <v/>
+      </c>
+      <c r="AT7">
+        <f>AO7/AN7-1</f>
+        <v/>
+      </c>
+      <c r="AV7" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW7" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB7">
+        <f>AV7/AW7-1</f>
+        <v/>
+      </c>
+      <c r="BC7">
+        <f>AX7/AW7-1</f>
+        <v/>
+      </c>
+      <c r="BE7" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF7" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK7">
+        <f>BE7/BF7-1</f>
+        <v/>
+      </c>
+      <c r="BL7">
+        <f>BG7/BF7-1</f>
+        <v/>
+      </c>
+      <c r="BN7" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BT7">
+        <f>BN7/BO7-1</f>
+        <v/>
+      </c>
+      <c r="BU7">
+        <f>BP7/BO7-1</f>
+        <v/>
+      </c>
+      <c r="BW7" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX7" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC7">
+        <f>BW7/BX7-1</f>
+        <v/>
+      </c>
+      <c r="CD7">
+        <f>BY7/BX7-1</f>
+        <v/>
+      </c>
+      <c r="CF7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL7">
+        <f>CF7/CG7-1</f>
+        <v/>
+      </c>
+      <c r="CM7">
+        <f>CH7/CG7-1</f>
+        <v/>
+      </c>
+      <c r="CO7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU7">
+        <f>CO7/CP7-1</f>
+        <v/>
+      </c>
+      <c r="CV7">
+        <f>CQ7/CP7-1</f>
+        <v/>
+      </c>
+      <c r="CX7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY7" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD7">
+        <f>CX7/CY7-1</f>
+        <v/>
+      </c>
+      <c r="DE7">
+        <f>CZ7/CY7-1</f>
+        <v/>
+      </c>
+      <c r="DG7" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH7" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM7">
+        <f>DG7/DH7-1</f>
+        <v/>
+      </c>
+      <c r="DN7">
+        <f>DI7/DH7-1</f>
+        <v/>
+      </c>
+      <c r="DP7" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ7" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV7">
+        <f>DP7/DQ7-1</f>
+        <v/>
+      </c>
+      <c r="DW7">
+        <f>DR7/DQ7-1</f>
+        <v/>
+      </c>
+      <c r="DY7" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ7" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE7">
+        <f>DY7/DZ7-1</f>
+        <v/>
+      </c>
+      <c r="EF7">
+        <f>EA7/DZ7-1</f>
+        <v/>
+      </c>
+      <c r="EH7" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI7" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK7" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN7">
+        <f>EH7/EI7-1</f>
+        <v/>
+      </c>
+      <c r="EO7">
+        <f>EJ7/EI7-1</f>
+        <v/>
+      </c>
+      <c r="EQ7" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER7" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET7" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU7" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW7">
+        <f>EQ7/ER7-1</f>
+        <v/>
+      </c>
+      <c r="EX7">
+        <f>ES7/ER7-1</f>
+        <v/>
+      </c>
+      <c r="EZ7" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA7" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC7" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD7" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF7">
+        <f>EZ7/FA7-1</f>
+        <v/>
+      </c>
+      <c r="FG7">
+        <f>FB7/FA7-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG7"/>
+  <dimension ref="A1:FG8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -3911,6 +3911,445 @@
         <v/>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>23 Jul 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I8">
+        <f>C8/D8-1</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>E8/D8-1</f>
+        <v/>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R8">
+        <f>L8/M8-1</f>
+        <v/>
+      </c>
+      <c r="S8">
+        <f>N8/M8-1</f>
+        <v/>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA8">
+        <f>U8/V8-1</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>W8/V8-1</f>
+        <v/>
+      </c>
+      <c r="AD8" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE8" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <f>AD8/AE8-1</f>
+        <v/>
+      </c>
+      <c r="AK8">
+        <f>AF8/AE8-1</f>
+        <v/>
+      </c>
+      <c r="AM8" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN8" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS8">
+        <f>AM8/AN8-1</f>
+        <v/>
+      </c>
+      <c r="AT8">
+        <f>AO8/AN8-1</f>
+        <v/>
+      </c>
+      <c r="AV8" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW8" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB8">
+        <f>AV8/AW8-1</f>
+        <v/>
+      </c>
+      <c r="BC8">
+        <f>AX8/AW8-1</f>
+        <v/>
+      </c>
+      <c r="BE8" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF8" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK8">
+        <f>BE8/BF8-1</f>
+        <v/>
+      </c>
+      <c r="BL8">
+        <f>BG8/BF8-1</f>
+        <v/>
+      </c>
+      <c r="BN8" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO8" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT8">
+        <f>BN8/BO8-1</f>
+        <v/>
+      </c>
+      <c r="BU8">
+        <f>BP8/BO8-1</f>
+        <v/>
+      </c>
+      <c r="BW8" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX8" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC8">
+        <f>BW8/BX8-1</f>
+        <v/>
+      </c>
+      <c r="CD8">
+        <f>BY8/BX8-1</f>
+        <v/>
+      </c>
+      <c r="CF8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL8">
+        <f>CF8/CG8-1</f>
+        <v/>
+      </c>
+      <c r="CM8">
+        <f>CH8/CG8-1</f>
+        <v/>
+      </c>
+      <c r="CO8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU8">
+        <f>CO8/CP8-1</f>
+        <v/>
+      </c>
+      <c r="CV8">
+        <f>CQ8/CP8-1</f>
+        <v/>
+      </c>
+      <c r="CX8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY8" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD8">
+        <f>CX8/CY8-1</f>
+        <v/>
+      </c>
+      <c r="DE8">
+        <f>CZ8/CY8-1</f>
+        <v/>
+      </c>
+      <c r="DG8" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH8" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM8">
+        <f>DG8/DH8-1</f>
+        <v/>
+      </c>
+      <c r="DN8">
+        <f>DI8/DH8-1</f>
+        <v/>
+      </c>
+      <c r="DP8" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ8" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV8">
+        <f>DP8/DQ8-1</f>
+        <v/>
+      </c>
+      <c r="DW8">
+        <f>DR8/DQ8-1</f>
+        <v/>
+      </c>
+      <c r="DY8" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ8" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE8">
+        <f>DY8/DZ8-1</f>
+        <v/>
+      </c>
+      <c r="EF8">
+        <f>EA8/DZ8-1</f>
+        <v/>
+      </c>
+      <c r="EH8" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI8" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN8">
+        <f>EH8/EI8-1</f>
+        <v/>
+      </c>
+      <c r="EO8">
+        <f>EJ8/EI8-1</f>
+        <v/>
+      </c>
+      <c r="EQ8" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER8" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET8" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU8" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW8">
+        <f>EQ8/ER8-1</f>
+        <v/>
+      </c>
+      <c r="EX8">
+        <f>ES8/ER8-1</f>
+        <v/>
+      </c>
+      <c r="EZ8" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA8" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC8" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD8" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF8">
+        <f>EZ8/FA8-1</f>
+        <v/>
+      </c>
+      <c r="FG8">
+        <f>FB8/FA8-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG8"/>
+  <dimension ref="A1:FG9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -4350,6 +4350,447 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>24 Jul 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I9">
+        <f>C9/D9-1</f>
+        <v/>
+      </c>
+      <c r="J9">
+        <f>E9/D9-1</f>
+        <v/>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R9">
+        <f>L9/M9-1</f>
+        <v/>
+      </c>
+      <c r="S9">
+        <f>N9/M9-1</f>
+        <v/>
+      </c>
+      <c r="U9" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA9">
+        <f>U9/V9-1</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>W9/V9-1</f>
+        <v/>
+      </c>
+      <c r="AD9" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE9" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <f>AD9/AE9-1</f>
+        <v/>
+      </c>
+      <c r="AK9">
+        <f>AF9/AE9-1</f>
+        <v/>
+      </c>
+      <c r="AM9" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN9" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS9">
+        <f>AM9/AN9-1</f>
+        <v/>
+      </c>
+      <c r="AT9">
+        <f>AO9/AN9-1</f>
+        <v/>
+      </c>
+      <c r="AV9" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW9" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB9">
+        <f>AV9/AW9-1</f>
+        <v/>
+      </c>
+      <c r="BC9">
+        <f>AX9/AW9-1</f>
+        <v/>
+      </c>
+      <c r="BE9" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF9" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK9">
+        <f>BE9/BF9-1</f>
+        <v/>
+      </c>
+      <c r="BL9">
+        <f>BG9/BF9-1</f>
+        <v/>
+      </c>
+      <c r="BN9" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO9" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT9">
+        <f>BN9/BO9-1</f>
+        <v/>
+      </c>
+      <c r="BU9">
+        <f>BP9/BO9-1</f>
+        <v/>
+      </c>
+      <c r="BW9" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX9" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC9">
+        <f>BW9/BX9-1</f>
+        <v/>
+      </c>
+      <c r="CD9">
+        <f>BY9/BX9-1</f>
+        <v/>
+      </c>
+      <c r="CF9" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG9" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL9">
+        <f>CF9/CG9-1</f>
+        <v/>
+      </c>
+      <c r="CM9">
+        <f>CH9/CG9-1</f>
+        <v/>
+      </c>
+      <c r="CO9" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP9" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU9">
+        <f>CO9/CP9-1</f>
+        <v/>
+      </c>
+      <c r="CV9">
+        <f>CQ9/CP9-1</f>
+        <v/>
+      </c>
+      <c r="CX9" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DD9">
+        <f>CX9/CY9-1</f>
+        <v/>
+      </c>
+      <c r="DE9">
+        <f>CZ9/CY9-1</f>
+        <v/>
+      </c>
+      <c r="DG9" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH9" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM9">
+        <f>DG9/DH9-1</f>
+        <v/>
+      </c>
+      <c r="DN9">
+        <f>DI9/DH9-1</f>
+        <v/>
+      </c>
+      <c r="DP9" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ9" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV9">
+        <f>DP9/DQ9-1</f>
+        <v/>
+      </c>
+      <c r="DW9">
+        <f>DR9/DQ9-1</f>
+        <v/>
+      </c>
+      <c r="DY9" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ9" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE9">
+        <f>DY9/DZ9-1</f>
+        <v/>
+      </c>
+      <c r="EF9">
+        <f>EA9/DZ9-1</f>
+        <v/>
+      </c>
+      <c r="EH9" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI9" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN9">
+        <f>EH9/EI9-1</f>
+        <v/>
+      </c>
+      <c r="EO9">
+        <f>EJ9/EI9-1</f>
+        <v/>
+      </c>
+      <c r="EQ9" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER9" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET9" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU9" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW9">
+        <f>EQ9/ER9-1</f>
+        <v/>
+      </c>
+      <c r="EX9">
+        <f>ES9/ER9-1</f>
+        <v/>
+      </c>
+      <c r="EZ9" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA9" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC9" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD9" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF9">
+        <f>EZ9/FA9-1</f>
+        <v/>
+      </c>
+      <c r="FG9">
+        <f>FB9/FA9-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG9"/>
+  <dimension ref="A1:FG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -4791,6 +4791,445 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>24 Jul 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I10">
+        <f>C10/D10-1</f>
+        <v/>
+      </c>
+      <c r="J10">
+        <f>E10/D10-1</f>
+        <v/>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R10">
+        <f>L10/M10-1</f>
+        <v/>
+      </c>
+      <c r="S10">
+        <f>N10/M10-1</f>
+        <v/>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA10">
+        <f>U10/V10-1</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>W10/V10-1</f>
+        <v/>
+      </c>
+      <c r="AD10" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE10" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <f>AD10/AE10-1</f>
+        <v/>
+      </c>
+      <c r="AK10">
+        <f>AF10/AE10-1</f>
+        <v/>
+      </c>
+      <c r="AM10" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN10" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS10">
+        <f>AM10/AN10-1</f>
+        <v/>
+      </c>
+      <c r="AT10">
+        <f>AO10/AN10-1</f>
+        <v/>
+      </c>
+      <c r="AV10" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW10" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB10">
+        <f>AV10/AW10-1</f>
+        <v/>
+      </c>
+      <c r="BC10">
+        <f>AX10/AW10-1</f>
+        <v/>
+      </c>
+      <c r="BE10" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF10" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK10">
+        <f>BE10/BF10-1</f>
+        <v/>
+      </c>
+      <c r="BL10">
+        <f>BG10/BF10-1</f>
+        <v/>
+      </c>
+      <c r="BN10" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO10" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT10">
+        <f>BN10/BO10-1</f>
+        <v/>
+      </c>
+      <c r="BU10">
+        <f>BP10/BO10-1</f>
+        <v/>
+      </c>
+      <c r="BW10" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX10" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC10">
+        <f>BW10/BX10-1</f>
+        <v/>
+      </c>
+      <c r="CD10">
+        <f>BY10/BX10-1</f>
+        <v/>
+      </c>
+      <c r="CF10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL10">
+        <f>CF10/CG10-1</f>
+        <v/>
+      </c>
+      <c r="CM10">
+        <f>CH10/CG10-1</f>
+        <v/>
+      </c>
+      <c r="CO10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU10">
+        <f>CO10/CP10-1</f>
+        <v/>
+      </c>
+      <c r="CV10">
+        <f>CQ10/CP10-1</f>
+        <v/>
+      </c>
+      <c r="CX10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY10" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD10">
+        <f>CX10/CY10-1</f>
+        <v/>
+      </c>
+      <c r="DE10">
+        <f>CZ10/CY10-1</f>
+        <v/>
+      </c>
+      <c r="DG10" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH10" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM10">
+        <f>DG10/DH10-1</f>
+        <v/>
+      </c>
+      <c r="DN10">
+        <f>DI10/DH10-1</f>
+        <v/>
+      </c>
+      <c r="DP10" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ10" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV10">
+        <f>DP10/DQ10-1</f>
+        <v/>
+      </c>
+      <c r="DW10">
+        <f>DR10/DQ10-1</f>
+        <v/>
+      </c>
+      <c r="DY10" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ10" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE10">
+        <f>DY10/DZ10-1</f>
+        <v/>
+      </c>
+      <c r="EF10">
+        <f>EA10/DZ10-1</f>
+        <v/>
+      </c>
+      <c r="EH10" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI10" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN10">
+        <f>EH10/EI10-1</f>
+        <v/>
+      </c>
+      <c r="EO10">
+        <f>EJ10/EI10-1</f>
+        <v/>
+      </c>
+      <c r="EQ10" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER10" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET10" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU10" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW10">
+        <f>EQ10/ER10-1</f>
+        <v/>
+      </c>
+      <c r="EX10">
+        <f>ES10/ER10-1</f>
+        <v/>
+      </c>
+      <c r="EZ10" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA10" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC10" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD10" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF10">
+        <f>EZ10/FA10-1</f>
+        <v/>
+      </c>
+      <c r="FG10">
+        <f>FB10/FA10-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG10"/>
+  <dimension ref="A1:FG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -5230,6 +5230,445 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>24 Jul 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I11">
+        <f>C11/D11-1</f>
+        <v/>
+      </c>
+      <c r="J11">
+        <f>E11/D11-1</f>
+        <v/>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R11">
+        <f>L11/M11-1</f>
+        <v/>
+      </c>
+      <c r="S11">
+        <f>N11/M11-1</f>
+        <v/>
+      </c>
+      <c r="U11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA11">
+        <f>U11/V11-1</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>W11/V11-1</f>
+        <v/>
+      </c>
+      <c r="AD11" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE11" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <f>AD11/AE11-1</f>
+        <v/>
+      </c>
+      <c r="AK11">
+        <f>AF11/AE11-1</f>
+        <v/>
+      </c>
+      <c r="AM11" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN11" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS11">
+        <f>AM11/AN11-1</f>
+        <v/>
+      </c>
+      <c r="AT11">
+        <f>AO11/AN11-1</f>
+        <v/>
+      </c>
+      <c r="AV11" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW11" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB11">
+        <f>AV11/AW11-1</f>
+        <v/>
+      </c>
+      <c r="BC11">
+        <f>AX11/AW11-1</f>
+        <v/>
+      </c>
+      <c r="BE11" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF11" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK11">
+        <f>BE11/BF11-1</f>
+        <v/>
+      </c>
+      <c r="BL11">
+        <f>BG11/BF11-1</f>
+        <v/>
+      </c>
+      <c r="BN11" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO11" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT11">
+        <f>BN11/BO11-1</f>
+        <v/>
+      </c>
+      <c r="BU11">
+        <f>BP11/BO11-1</f>
+        <v/>
+      </c>
+      <c r="BW11" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX11" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC11">
+        <f>BW11/BX11-1</f>
+        <v/>
+      </c>
+      <c r="CD11">
+        <f>BY11/BX11-1</f>
+        <v/>
+      </c>
+      <c r="CF11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL11">
+        <f>CF11/CG11-1</f>
+        <v/>
+      </c>
+      <c r="CM11">
+        <f>CH11/CG11-1</f>
+        <v/>
+      </c>
+      <c r="CO11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU11">
+        <f>CO11/CP11-1</f>
+        <v/>
+      </c>
+      <c r="CV11">
+        <f>CQ11/CP11-1</f>
+        <v/>
+      </c>
+      <c r="CX11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY11" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA11" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB11" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD11">
+        <f>CX11/CY11-1</f>
+        <v/>
+      </c>
+      <c r="DE11">
+        <f>CZ11/CY11-1</f>
+        <v/>
+      </c>
+      <c r="DG11" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH11" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ11" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK11" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM11">
+        <f>DG11/DH11-1</f>
+        <v/>
+      </c>
+      <c r="DN11">
+        <f>DI11/DH11-1</f>
+        <v/>
+      </c>
+      <c r="DP11" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ11" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS11" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT11" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV11">
+        <f>DP11/DQ11-1</f>
+        <v/>
+      </c>
+      <c r="DW11">
+        <f>DR11/DQ11-1</f>
+        <v/>
+      </c>
+      <c r="DY11" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ11" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB11" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC11" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE11">
+        <f>DY11/DZ11-1</f>
+        <v/>
+      </c>
+      <c r="EF11">
+        <f>EA11/DZ11-1</f>
+        <v/>
+      </c>
+      <c r="EH11" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI11" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK11" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL11" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN11">
+        <f>EH11/EI11-1</f>
+        <v/>
+      </c>
+      <c r="EO11">
+        <f>EJ11/EI11-1</f>
+        <v/>
+      </c>
+      <c r="EQ11" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER11" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET11" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU11" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW11">
+        <f>EQ11/ER11-1</f>
+        <v/>
+      </c>
+      <c r="EX11">
+        <f>ES11/ER11-1</f>
+        <v/>
+      </c>
+      <c r="EZ11" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA11" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC11" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD11" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF11">
+        <f>EZ11/FA11-1</f>
+        <v/>
+      </c>
+      <c r="FG11">
+        <f>FB11/FA11-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG11"/>
+  <dimension ref="A1:FG12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -5669,6 +5669,445 @@
         <v/>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>24 Jul 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I12">
+        <f>C12/D12-1</f>
+        <v/>
+      </c>
+      <c r="J12">
+        <f>E12/D12-1</f>
+        <v/>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R12">
+        <f>L12/M12-1</f>
+        <v/>
+      </c>
+      <c r="S12">
+        <f>N12/M12-1</f>
+        <v/>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA12">
+        <f>U12/V12-1</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>W12/V12-1</f>
+        <v/>
+      </c>
+      <c r="AD12" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE12" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <f>AD12/AE12-1</f>
+        <v/>
+      </c>
+      <c r="AK12">
+        <f>AF12/AE12-1</f>
+        <v/>
+      </c>
+      <c r="AM12" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN12" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS12">
+        <f>AM12/AN12-1</f>
+        <v/>
+      </c>
+      <c r="AT12">
+        <f>AO12/AN12-1</f>
+        <v/>
+      </c>
+      <c r="AV12" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW12" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB12">
+        <f>AV12/AW12-1</f>
+        <v/>
+      </c>
+      <c r="BC12">
+        <f>AX12/AW12-1</f>
+        <v/>
+      </c>
+      <c r="BE12" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF12" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK12">
+        <f>BE12/BF12-1</f>
+        <v/>
+      </c>
+      <c r="BL12">
+        <f>BG12/BF12-1</f>
+        <v/>
+      </c>
+      <c r="BN12" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO12" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT12">
+        <f>BN12/BO12-1</f>
+        <v/>
+      </c>
+      <c r="BU12">
+        <f>BP12/BO12-1</f>
+        <v/>
+      </c>
+      <c r="BW12" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX12" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC12">
+        <f>BW12/BX12-1</f>
+        <v/>
+      </c>
+      <c r="CD12">
+        <f>BY12/BX12-1</f>
+        <v/>
+      </c>
+      <c r="CF12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL12">
+        <f>CF12/CG12-1</f>
+        <v/>
+      </c>
+      <c r="CM12">
+        <f>CH12/CG12-1</f>
+        <v/>
+      </c>
+      <c r="CO12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS12" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU12">
+        <f>CO12/CP12-1</f>
+        <v/>
+      </c>
+      <c r="CV12">
+        <f>CQ12/CP12-1</f>
+        <v/>
+      </c>
+      <c r="CX12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY12" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA12" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB12" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD12">
+        <f>CX12/CY12-1</f>
+        <v/>
+      </c>
+      <c r="DE12">
+        <f>CZ12/CY12-1</f>
+        <v/>
+      </c>
+      <c r="DG12" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH12" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ12" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK12" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM12">
+        <f>DG12/DH12-1</f>
+        <v/>
+      </c>
+      <c r="DN12">
+        <f>DI12/DH12-1</f>
+        <v/>
+      </c>
+      <c r="DP12" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ12" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS12" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT12" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV12">
+        <f>DP12/DQ12-1</f>
+        <v/>
+      </c>
+      <c r="DW12">
+        <f>DR12/DQ12-1</f>
+        <v/>
+      </c>
+      <c r="DY12" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ12" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB12" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC12" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE12">
+        <f>DY12/DZ12-1</f>
+        <v/>
+      </c>
+      <c r="EF12">
+        <f>EA12/DZ12-1</f>
+        <v/>
+      </c>
+      <c r="EH12" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI12" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK12" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL12" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN12">
+        <f>EH12/EI12-1</f>
+        <v/>
+      </c>
+      <c r="EO12">
+        <f>EJ12/EI12-1</f>
+        <v/>
+      </c>
+      <c r="EQ12" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER12" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET12" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU12" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW12">
+        <f>EQ12/ER12-1</f>
+        <v/>
+      </c>
+      <c r="EX12">
+        <f>ES12/ER12-1</f>
+        <v/>
+      </c>
+      <c r="EZ12" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA12" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC12" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD12" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF12">
+        <f>EZ12/FA12-1</f>
+        <v/>
+      </c>
+      <c r="FG12">
+        <f>FB12/FA12-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG12"/>
+  <dimension ref="A1:FG13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -6108,6 +6108,445 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>25 Jul 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I13">
+        <f>C13/D13-1</f>
+        <v/>
+      </c>
+      <c r="J13">
+        <f>E13/D13-1</f>
+        <v/>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R13">
+        <f>L13/M13-1</f>
+        <v/>
+      </c>
+      <c r="S13">
+        <f>N13/M13-1</f>
+        <v/>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA13">
+        <f>U13/V13-1</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>W13/V13-1</f>
+        <v/>
+      </c>
+      <c r="AD13" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE13" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <f>AD13/AE13-1</f>
+        <v/>
+      </c>
+      <c r="AK13">
+        <f>AF13/AE13-1</f>
+        <v/>
+      </c>
+      <c r="AM13" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN13" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS13">
+        <f>AM13/AN13-1</f>
+        <v/>
+      </c>
+      <c r="AT13">
+        <f>AO13/AN13-1</f>
+        <v/>
+      </c>
+      <c r="AV13" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW13" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB13">
+        <f>AV13/AW13-1</f>
+        <v/>
+      </c>
+      <c r="BC13">
+        <f>AX13/AW13-1</f>
+        <v/>
+      </c>
+      <c r="BE13" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF13" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK13">
+        <f>BE13/BF13-1</f>
+        <v/>
+      </c>
+      <c r="BL13">
+        <f>BG13/BF13-1</f>
+        <v/>
+      </c>
+      <c r="BN13" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO13" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT13">
+        <f>BN13/BO13-1</f>
+        <v/>
+      </c>
+      <c r="BU13">
+        <f>BP13/BO13-1</f>
+        <v/>
+      </c>
+      <c r="BW13" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX13" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC13">
+        <f>BW13/BX13-1</f>
+        <v/>
+      </c>
+      <c r="CD13">
+        <f>BY13/BX13-1</f>
+        <v/>
+      </c>
+      <c r="CF13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL13">
+        <f>CF13/CG13-1</f>
+        <v/>
+      </c>
+      <c r="CM13">
+        <f>CH13/CG13-1</f>
+        <v/>
+      </c>
+      <c r="CO13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS13" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU13">
+        <f>CO13/CP13-1</f>
+        <v/>
+      </c>
+      <c r="CV13">
+        <f>CQ13/CP13-1</f>
+        <v/>
+      </c>
+      <c r="CX13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY13" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA13" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB13" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD13">
+        <f>CX13/CY13-1</f>
+        <v/>
+      </c>
+      <c r="DE13">
+        <f>CZ13/CY13-1</f>
+        <v/>
+      </c>
+      <c r="DG13" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH13" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ13" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK13" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM13">
+        <f>DG13/DH13-1</f>
+        <v/>
+      </c>
+      <c r="DN13">
+        <f>DI13/DH13-1</f>
+        <v/>
+      </c>
+      <c r="DP13" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ13" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS13" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT13" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV13">
+        <f>DP13/DQ13-1</f>
+        <v/>
+      </c>
+      <c r="DW13">
+        <f>DR13/DQ13-1</f>
+        <v/>
+      </c>
+      <c r="DY13" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ13" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB13" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC13" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE13">
+        <f>DY13/DZ13-1</f>
+        <v/>
+      </c>
+      <c r="EF13">
+        <f>EA13/DZ13-1</f>
+        <v/>
+      </c>
+      <c r="EH13" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI13" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK13" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL13" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN13">
+        <f>EH13/EI13-1</f>
+        <v/>
+      </c>
+      <c r="EO13">
+        <f>EJ13/EI13-1</f>
+        <v/>
+      </c>
+      <c r="EQ13" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER13" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET13" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU13" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW13">
+        <f>EQ13/ER13-1</f>
+        <v/>
+      </c>
+      <c r="EX13">
+        <f>ES13/ER13-1</f>
+        <v/>
+      </c>
+      <c r="EZ13" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA13" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC13" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD13" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF13">
+        <f>EZ13/FA13-1</f>
+        <v/>
+      </c>
+      <c r="FG13">
+        <f>FB13/FA13-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG13"/>
+  <dimension ref="A1:FG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -6547,6 +6547,445 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>25 Jul 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I14">
+        <f>C14/D14-1</f>
+        <v/>
+      </c>
+      <c r="J14">
+        <f>E14/D14-1</f>
+        <v/>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R14">
+        <f>L14/M14-1</f>
+        <v/>
+      </c>
+      <c r="S14">
+        <f>N14/M14-1</f>
+        <v/>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA14">
+        <f>U14/V14-1</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>W14/V14-1</f>
+        <v/>
+      </c>
+      <c r="AD14" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE14" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <f>AD14/AE14-1</f>
+        <v/>
+      </c>
+      <c r="AK14">
+        <f>AF14/AE14-1</f>
+        <v/>
+      </c>
+      <c r="AM14" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN14" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS14">
+        <f>AM14/AN14-1</f>
+        <v/>
+      </c>
+      <c r="AT14">
+        <f>AO14/AN14-1</f>
+        <v/>
+      </c>
+      <c r="AV14" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW14" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB14">
+        <f>AV14/AW14-1</f>
+        <v/>
+      </c>
+      <c r="BC14">
+        <f>AX14/AW14-1</f>
+        <v/>
+      </c>
+      <c r="BE14" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF14" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK14">
+        <f>BE14/BF14-1</f>
+        <v/>
+      </c>
+      <c r="BL14">
+        <f>BG14/BF14-1</f>
+        <v/>
+      </c>
+      <c r="BN14" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO14" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT14">
+        <f>BN14/BO14-1</f>
+        <v/>
+      </c>
+      <c r="BU14">
+        <f>BP14/BO14-1</f>
+        <v/>
+      </c>
+      <c r="BW14" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX14" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC14">
+        <f>BW14/BX14-1</f>
+        <v/>
+      </c>
+      <c r="CD14">
+        <f>BY14/BX14-1</f>
+        <v/>
+      </c>
+      <c r="CF14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL14">
+        <f>CF14/CG14-1</f>
+        <v/>
+      </c>
+      <c r="CM14">
+        <f>CH14/CG14-1</f>
+        <v/>
+      </c>
+      <c r="CO14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS14" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU14">
+        <f>CO14/CP14-1</f>
+        <v/>
+      </c>
+      <c r="CV14">
+        <f>CQ14/CP14-1</f>
+        <v/>
+      </c>
+      <c r="CX14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY14" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA14" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB14" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD14">
+        <f>CX14/CY14-1</f>
+        <v/>
+      </c>
+      <c r="DE14">
+        <f>CZ14/CY14-1</f>
+        <v/>
+      </c>
+      <c r="DG14" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH14" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ14" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK14" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM14">
+        <f>DG14/DH14-1</f>
+        <v/>
+      </c>
+      <c r="DN14">
+        <f>DI14/DH14-1</f>
+        <v/>
+      </c>
+      <c r="DP14" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ14" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS14" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT14" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV14">
+        <f>DP14/DQ14-1</f>
+        <v/>
+      </c>
+      <c r="DW14">
+        <f>DR14/DQ14-1</f>
+        <v/>
+      </c>
+      <c r="DY14" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ14" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB14" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC14" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE14">
+        <f>DY14/DZ14-1</f>
+        <v/>
+      </c>
+      <c r="EF14">
+        <f>EA14/DZ14-1</f>
+        <v/>
+      </c>
+      <c r="EH14" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI14" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK14" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL14" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN14">
+        <f>EH14/EI14-1</f>
+        <v/>
+      </c>
+      <c r="EO14">
+        <f>EJ14/EI14-1</f>
+        <v/>
+      </c>
+      <c r="EQ14" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER14" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET14" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU14" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW14">
+        <f>EQ14/ER14-1</f>
+        <v/>
+      </c>
+      <c r="EX14">
+        <f>ES14/ER14-1</f>
+        <v/>
+      </c>
+      <c r="EZ14" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA14" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC14" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD14" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF14">
+        <f>EZ14/FA14-1</f>
+        <v/>
+      </c>
+      <c r="FG14">
+        <f>FB14/FA14-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG14"/>
+  <dimension ref="A1:FG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -6986,6 +6986,447 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>25 Jul 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I15">
+        <f>C15/D15-1</f>
+        <v/>
+      </c>
+      <c r="J15">
+        <f>E15/D15-1</f>
+        <v/>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R15">
+        <f>L15/M15-1</f>
+        <v/>
+      </c>
+      <c r="S15">
+        <f>N15/M15-1</f>
+        <v/>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA15">
+        <f>U15/V15-1</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>W15/V15-1</f>
+        <v/>
+      </c>
+      <c r="AD15" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE15" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <f>AD15/AE15-1</f>
+        <v/>
+      </c>
+      <c r="AK15">
+        <f>AF15/AE15-1</f>
+        <v/>
+      </c>
+      <c r="AM15" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN15" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS15">
+        <f>AM15/AN15-1</f>
+        <v/>
+      </c>
+      <c r="AT15">
+        <f>AO15/AN15-1</f>
+        <v/>
+      </c>
+      <c r="AV15" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW15" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB15">
+        <f>AV15/AW15-1</f>
+        <v/>
+      </c>
+      <c r="BC15">
+        <f>AX15/AW15-1</f>
+        <v/>
+      </c>
+      <c r="BE15" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF15" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK15">
+        <f>BE15/BF15-1</f>
+        <v/>
+      </c>
+      <c r="BL15">
+        <f>BG15/BF15-1</f>
+        <v/>
+      </c>
+      <c r="BN15" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO15" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT15">
+        <f>BN15/BO15-1</f>
+        <v/>
+      </c>
+      <c r="BU15">
+        <f>BP15/BO15-1</f>
+        <v/>
+      </c>
+      <c r="BW15" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX15" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC15">
+        <f>BW15/BX15-1</f>
+        <v/>
+      </c>
+      <c r="CD15">
+        <f>BY15/BX15-1</f>
+        <v/>
+      </c>
+      <c r="CF15" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CL15">
+        <f>CF15/CG15-1</f>
+        <v/>
+      </c>
+      <c r="CM15">
+        <f>CH15/CG15-1</f>
+        <v/>
+      </c>
+      <c r="CO15" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP15" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS15" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU15">
+        <f>CO15/CP15-1</f>
+        <v/>
+      </c>
+      <c r="CV15">
+        <f>CQ15/CP15-1</f>
+        <v/>
+      </c>
+      <c r="CX15" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY15" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA15" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB15" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD15">
+        <f>CX15/CY15-1</f>
+        <v/>
+      </c>
+      <c r="DE15">
+        <f>CZ15/CY15-1</f>
+        <v/>
+      </c>
+      <c r="DG15" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH15" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ15" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK15" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM15">
+        <f>DG15/DH15-1</f>
+        <v/>
+      </c>
+      <c r="DN15">
+        <f>DI15/DH15-1</f>
+        <v/>
+      </c>
+      <c r="DP15" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ15" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS15" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT15" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV15">
+        <f>DP15/DQ15-1</f>
+        <v/>
+      </c>
+      <c r="DW15">
+        <f>DR15/DQ15-1</f>
+        <v/>
+      </c>
+      <c r="DY15" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ15" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB15" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC15" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE15">
+        <f>DY15/DZ15-1</f>
+        <v/>
+      </c>
+      <c r="EF15">
+        <f>EA15/DZ15-1</f>
+        <v/>
+      </c>
+      <c r="EH15" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI15" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK15" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL15" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN15">
+        <f>EH15/EI15-1</f>
+        <v/>
+      </c>
+      <c r="EO15">
+        <f>EJ15/EI15-1</f>
+        <v/>
+      </c>
+      <c r="EQ15" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER15" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET15" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU15" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW15">
+        <f>EQ15/ER15-1</f>
+        <v/>
+      </c>
+      <c r="EX15">
+        <f>ES15/ER15-1</f>
+        <v/>
+      </c>
+      <c r="EZ15" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA15" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC15" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD15" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF15">
+        <f>EZ15/FA15-1</f>
+        <v/>
+      </c>
+      <c r="FG15">
+        <f>FB15/FA15-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG15"/>
+  <dimension ref="A1:FG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -7427,6 +7427,445 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>25 Jul 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I16">
+        <f>C16/D16-1</f>
+        <v/>
+      </c>
+      <c r="J16">
+        <f>E16/D16-1</f>
+        <v/>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R16">
+        <f>L16/M16-1</f>
+        <v/>
+      </c>
+      <c r="S16">
+        <f>N16/M16-1</f>
+        <v/>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA16">
+        <f>U16/V16-1</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>W16/V16-1</f>
+        <v/>
+      </c>
+      <c r="AD16" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE16" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <f>AD16/AE16-1</f>
+        <v/>
+      </c>
+      <c r="AK16">
+        <f>AF16/AE16-1</f>
+        <v/>
+      </c>
+      <c r="AM16" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN16" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS16">
+        <f>AM16/AN16-1</f>
+        <v/>
+      </c>
+      <c r="AT16">
+        <f>AO16/AN16-1</f>
+        <v/>
+      </c>
+      <c r="AV16" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW16" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB16">
+        <f>AV16/AW16-1</f>
+        <v/>
+      </c>
+      <c r="BC16">
+        <f>AX16/AW16-1</f>
+        <v/>
+      </c>
+      <c r="BE16" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF16" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK16">
+        <f>BE16/BF16-1</f>
+        <v/>
+      </c>
+      <c r="BL16">
+        <f>BG16/BF16-1</f>
+        <v/>
+      </c>
+      <c r="BN16" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO16" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT16">
+        <f>BN16/BO16-1</f>
+        <v/>
+      </c>
+      <c r="BU16">
+        <f>BP16/BO16-1</f>
+        <v/>
+      </c>
+      <c r="BW16" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX16" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC16">
+        <f>BW16/BX16-1</f>
+        <v/>
+      </c>
+      <c r="CD16">
+        <f>BY16/BX16-1</f>
+        <v/>
+      </c>
+      <c r="CF16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI16" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ16" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL16">
+        <f>CF16/CG16-1</f>
+        <v/>
+      </c>
+      <c r="CM16">
+        <f>CH16/CG16-1</f>
+        <v/>
+      </c>
+      <c r="CO16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS16" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU16">
+        <f>CO16/CP16-1</f>
+        <v/>
+      </c>
+      <c r="CV16">
+        <f>CQ16/CP16-1</f>
+        <v/>
+      </c>
+      <c r="CX16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY16" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA16" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB16" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD16">
+        <f>CX16/CY16-1</f>
+        <v/>
+      </c>
+      <c r="DE16">
+        <f>CZ16/CY16-1</f>
+        <v/>
+      </c>
+      <c r="DG16" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH16" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ16" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK16" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM16">
+        <f>DG16/DH16-1</f>
+        <v/>
+      </c>
+      <c r="DN16">
+        <f>DI16/DH16-1</f>
+        <v/>
+      </c>
+      <c r="DP16" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ16" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS16" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT16" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV16">
+        <f>DP16/DQ16-1</f>
+        <v/>
+      </c>
+      <c r="DW16">
+        <f>DR16/DQ16-1</f>
+        <v/>
+      </c>
+      <c r="DY16" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ16" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB16" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC16" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE16">
+        <f>DY16/DZ16-1</f>
+        <v/>
+      </c>
+      <c r="EF16">
+        <f>EA16/DZ16-1</f>
+        <v/>
+      </c>
+      <c r="EH16" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI16" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK16" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL16" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN16">
+        <f>EH16/EI16-1</f>
+        <v/>
+      </c>
+      <c r="EO16">
+        <f>EJ16/EI16-1</f>
+        <v/>
+      </c>
+      <c r="EQ16" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER16" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET16" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU16" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW16">
+        <f>EQ16/ER16-1</f>
+        <v/>
+      </c>
+      <c r="EX16">
+        <f>ES16/ER16-1</f>
+        <v/>
+      </c>
+      <c r="EZ16" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA16" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC16" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD16" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF16">
+        <f>EZ16/FA16-1</f>
+        <v/>
+      </c>
+      <c r="FG16">
+        <f>FB16/FA16-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG16"/>
+  <dimension ref="A1:FG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -7866,6 +7866,445 @@
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>26 Jul 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I17">
+        <f>C17/D17-1</f>
+        <v/>
+      </c>
+      <c r="J17">
+        <f>E17/D17-1</f>
+        <v/>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R17">
+        <f>L17/M17-1</f>
+        <v/>
+      </c>
+      <c r="S17">
+        <f>N17/M17-1</f>
+        <v/>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA17">
+        <f>U17/V17-1</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>W17/V17-1</f>
+        <v/>
+      </c>
+      <c r="AD17" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE17" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <f>AD17/AE17-1</f>
+        <v/>
+      </c>
+      <c r="AK17">
+        <f>AF17/AE17-1</f>
+        <v/>
+      </c>
+      <c r="AM17" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN17" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS17">
+        <f>AM17/AN17-1</f>
+        <v/>
+      </c>
+      <c r="AT17">
+        <f>AO17/AN17-1</f>
+        <v/>
+      </c>
+      <c r="AV17" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW17" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB17">
+        <f>AV17/AW17-1</f>
+        <v/>
+      </c>
+      <c r="BC17">
+        <f>AX17/AW17-1</f>
+        <v/>
+      </c>
+      <c r="BE17" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF17" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK17">
+        <f>BE17/BF17-1</f>
+        <v/>
+      </c>
+      <c r="BL17">
+        <f>BG17/BF17-1</f>
+        <v/>
+      </c>
+      <c r="BN17" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO17" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT17">
+        <f>BN17/BO17-1</f>
+        <v/>
+      </c>
+      <c r="BU17">
+        <f>BP17/BO17-1</f>
+        <v/>
+      </c>
+      <c r="BW17" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX17" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC17">
+        <f>BW17/BX17-1</f>
+        <v/>
+      </c>
+      <c r="CD17">
+        <f>BY17/BX17-1</f>
+        <v/>
+      </c>
+      <c r="CF17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL17">
+        <f>CF17/CG17-1</f>
+        <v/>
+      </c>
+      <c r="CM17">
+        <f>CH17/CG17-1</f>
+        <v/>
+      </c>
+      <c r="CO17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS17" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU17">
+        <f>CO17/CP17-1</f>
+        <v/>
+      </c>
+      <c r="CV17">
+        <f>CQ17/CP17-1</f>
+        <v/>
+      </c>
+      <c r="CX17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY17" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA17" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB17" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD17">
+        <f>CX17/CY17-1</f>
+        <v/>
+      </c>
+      <c r="DE17">
+        <f>CZ17/CY17-1</f>
+        <v/>
+      </c>
+      <c r="DG17" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH17" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ17" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK17" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM17">
+        <f>DG17/DH17-1</f>
+        <v/>
+      </c>
+      <c r="DN17">
+        <f>DI17/DH17-1</f>
+        <v/>
+      </c>
+      <c r="DP17" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ17" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS17" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT17" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV17">
+        <f>DP17/DQ17-1</f>
+        <v/>
+      </c>
+      <c r="DW17">
+        <f>DR17/DQ17-1</f>
+        <v/>
+      </c>
+      <c r="DY17" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ17" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB17" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC17" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE17">
+        <f>DY17/DZ17-1</f>
+        <v/>
+      </c>
+      <c r="EF17">
+        <f>EA17/DZ17-1</f>
+        <v/>
+      </c>
+      <c r="EH17" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI17" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK17" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL17" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN17">
+        <f>EH17/EI17-1</f>
+        <v/>
+      </c>
+      <c r="EO17">
+        <f>EJ17/EI17-1</f>
+        <v/>
+      </c>
+      <c r="EQ17" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER17" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET17" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU17" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW17">
+        <f>EQ17/ER17-1</f>
+        <v/>
+      </c>
+      <c r="EX17">
+        <f>ES17/ER17-1</f>
+        <v/>
+      </c>
+      <c r="EZ17" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA17" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC17" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD17" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF17">
+        <f>EZ17/FA17-1</f>
+        <v/>
+      </c>
+      <c r="FG17">
+        <f>FB17/FA17-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG17"/>
+  <dimension ref="A1:FG18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -8305,6 +8305,445 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>26 Jul 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I18">
+        <f>C18/D18-1</f>
+        <v/>
+      </c>
+      <c r="J18">
+        <f>E18/D18-1</f>
+        <v/>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R18">
+        <f>L18/M18-1</f>
+        <v/>
+      </c>
+      <c r="S18">
+        <f>N18/M18-1</f>
+        <v/>
+      </c>
+      <c r="U18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA18">
+        <f>U18/V18-1</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>W18/V18-1</f>
+        <v/>
+      </c>
+      <c r="AD18" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE18" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <f>AD18/AE18-1</f>
+        <v/>
+      </c>
+      <c r="AK18">
+        <f>AF18/AE18-1</f>
+        <v/>
+      </c>
+      <c r="AM18" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN18" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS18">
+        <f>AM18/AN18-1</f>
+        <v/>
+      </c>
+      <c r="AT18">
+        <f>AO18/AN18-1</f>
+        <v/>
+      </c>
+      <c r="AV18" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW18" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB18">
+        <f>AV18/AW18-1</f>
+        <v/>
+      </c>
+      <c r="BC18">
+        <f>AX18/AW18-1</f>
+        <v/>
+      </c>
+      <c r="BE18" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF18" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK18">
+        <f>BE18/BF18-1</f>
+        <v/>
+      </c>
+      <c r="BL18">
+        <f>BG18/BF18-1</f>
+        <v/>
+      </c>
+      <c r="BN18" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO18" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT18">
+        <f>BN18/BO18-1</f>
+        <v/>
+      </c>
+      <c r="BU18">
+        <f>BP18/BO18-1</f>
+        <v/>
+      </c>
+      <c r="BW18" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX18" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC18">
+        <f>BW18/BX18-1</f>
+        <v/>
+      </c>
+      <c r="CD18">
+        <f>BY18/BX18-1</f>
+        <v/>
+      </c>
+      <c r="CF18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ18" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL18">
+        <f>CF18/CG18-1</f>
+        <v/>
+      </c>
+      <c r="CM18">
+        <f>CH18/CG18-1</f>
+        <v/>
+      </c>
+      <c r="CO18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS18" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU18">
+        <f>CO18/CP18-1</f>
+        <v/>
+      </c>
+      <c r="CV18">
+        <f>CQ18/CP18-1</f>
+        <v/>
+      </c>
+      <c r="CX18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY18" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA18" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB18" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD18">
+        <f>CX18/CY18-1</f>
+        <v/>
+      </c>
+      <c r="DE18">
+        <f>CZ18/CY18-1</f>
+        <v/>
+      </c>
+      <c r="DG18" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH18" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ18" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK18" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM18">
+        <f>DG18/DH18-1</f>
+        <v/>
+      </c>
+      <c r="DN18">
+        <f>DI18/DH18-1</f>
+        <v/>
+      </c>
+      <c r="DP18" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ18" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS18" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT18" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV18">
+        <f>DP18/DQ18-1</f>
+        <v/>
+      </c>
+      <c r="DW18">
+        <f>DR18/DQ18-1</f>
+        <v/>
+      </c>
+      <c r="DY18" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ18" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB18" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC18" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE18">
+        <f>DY18/DZ18-1</f>
+        <v/>
+      </c>
+      <c r="EF18">
+        <f>EA18/DZ18-1</f>
+        <v/>
+      </c>
+      <c r="EH18" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI18" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK18" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL18" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN18">
+        <f>EH18/EI18-1</f>
+        <v/>
+      </c>
+      <c r="EO18">
+        <f>EJ18/EI18-1</f>
+        <v/>
+      </c>
+      <c r="EQ18" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER18" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET18" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU18" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW18">
+        <f>EQ18/ER18-1</f>
+        <v/>
+      </c>
+      <c r="EX18">
+        <f>ES18/ER18-1</f>
+        <v/>
+      </c>
+      <c r="EZ18" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA18" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC18" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD18" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF18">
+        <f>EZ18/FA18-1</f>
+        <v/>
+      </c>
+      <c r="FG18">
+        <f>FB18/FA18-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG18"/>
+  <dimension ref="A1:FG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -8744,6 +8744,445 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>26 Jul 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I19">
+        <f>C19/D19-1</f>
+        <v/>
+      </c>
+      <c r="J19">
+        <f>E19/D19-1</f>
+        <v/>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R19">
+        <f>L19/M19-1</f>
+        <v/>
+      </c>
+      <c r="S19">
+        <f>N19/M19-1</f>
+        <v/>
+      </c>
+      <c r="U19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA19">
+        <f>U19/V19-1</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>W19/V19-1</f>
+        <v/>
+      </c>
+      <c r="AD19" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE19" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <f>AD19/AE19-1</f>
+        <v/>
+      </c>
+      <c r="AK19">
+        <f>AF19/AE19-1</f>
+        <v/>
+      </c>
+      <c r="AM19" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN19" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS19">
+        <f>AM19/AN19-1</f>
+        <v/>
+      </c>
+      <c r="AT19">
+        <f>AO19/AN19-1</f>
+        <v/>
+      </c>
+      <c r="AV19" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW19" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB19">
+        <f>AV19/AW19-1</f>
+        <v/>
+      </c>
+      <c r="BC19">
+        <f>AX19/AW19-1</f>
+        <v/>
+      </c>
+      <c r="BE19" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF19" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK19">
+        <f>BE19/BF19-1</f>
+        <v/>
+      </c>
+      <c r="BL19">
+        <f>BG19/BF19-1</f>
+        <v/>
+      </c>
+      <c r="BN19" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO19" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT19">
+        <f>BN19/BO19-1</f>
+        <v/>
+      </c>
+      <c r="BU19">
+        <f>BP19/BO19-1</f>
+        <v/>
+      </c>
+      <c r="BW19" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX19" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC19">
+        <f>BW19/BX19-1</f>
+        <v/>
+      </c>
+      <c r="CD19">
+        <f>BY19/BX19-1</f>
+        <v/>
+      </c>
+      <c r="CF19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL19">
+        <f>CF19/CG19-1</f>
+        <v/>
+      </c>
+      <c r="CM19">
+        <f>CH19/CG19-1</f>
+        <v/>
+      </c>
+      <c r="CO19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU19">
+        <f>CO19/CP19-1</f>
+        <v/>
+      </c>
+      <c r="CV19">
+        <f>CQ19/CP19-1</f>
+        <v/>
+      </c>
+      <c r="CX19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY19" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA19" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB19" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD19">
+        <f>CX19/CY19-1</f>
+        <v/>
+      </c>
+      <c r="DE19">
+        <f>CZ19/CY19-1</f>
+        <v/>
+      </c>
+      <c r="DG19" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH19" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ19" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK19" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM19">
+        <f>DG19/DH19-1</f>
+        <v/>
+      </c>
+      <c r="DN19">
+        <f>DI19/DH19-1</f>
+        <v/>
+      </c>
+      <c r="DP19" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ19" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS19" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT19" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV19">
+        <f>DP19/DQ19-1</f>
+        <v/>
+      </c>
+      <c r="DW19">
+        <f>DR19/DQ19-1</f>
+        <v/>
+      </c>
+      <c r="DY19" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ19" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB19" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE19">
+        <f>DY19/DZ19-1</f>
+        <v/>
+      </c>
+      <c r="EF19">
+        <f>EA19/DZ19-1</f>
+        <v/>
+      </c>
+      <c r="EH19" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI19" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK19" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL19" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN19">
+        <f>EH19/EI19-1</f>
+        <v/>
+      </c>
+      <c r="EO19">
+        <f>EJ19/EI19-1</f>
+        <v/>
+      </c>
+      <c r="EQ19" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER19" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET19" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU19" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW19">
+        <f>EQ19/ER19-1</f>
+        <v/>
+      </c>
+      <c r="EX19">
+        <f>ES19/ER19-1</f>
+        <v/>
+      </c>
+      <c r="EZ19" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA19" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC19" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD19" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF19">
+        <f>EZ19/FA19-1</f>
+        <v/>
+      </c>
+      <c r="FG19">
+        <f>FB19/FA19-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG19"/>
+  <dimension ref="A1:FG20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -9183,6 +9183,445 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>26 Jul 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I20">
+        <f>C20/D20-1</f>
+        <v/>
+      </c>
+      <c r="J20">
+        <f>E20/D20-1</f>
+        <v/>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R20">
+        <f>L20/M20-1</f>
+        <v/>
+      </c>
+      <c r="S20">
+        <f>N20/M20-1</f>
+        <v/>
+      </c>
+      <c r="U20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA20">
+        <f>U20/V20-1</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>W20/V20-1</f>
+        <v/>
+      </c>
+      <c r="AD20" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE20" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <f>AD20/AE20-1</f>
+        <v/>
+      </c>
+      <c r="AK20">
+        <f>AF20/AE20-1</f>
+        <v/>
+      </c>
+      <c r="AM20" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN20" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS20">
+        <f>AM20/AN20-1</f>
+        <v/>
+      </c>
+      <c r="AT20">
+        <f>AO20/AN20-1</f>
+        <v/>
+      </c>
+      <c r="AV20" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW20" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB20">
+        <f>AV20/AW20-1</f>
+        <v/>
+      </c>
+      <c r="BC20">
+        <f>AX20/AW20-1</f>
+        <v/>
+      </c>
+      <c r="BE20" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF20" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK20">
+        <f>BE20/BF20-1</f>
+        <v/>
+      </c>
+      <c r="BL20">
+        <f>BG20/BF20-1</f>
+        <v/>
+      </c>
+      <c r="BN20" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO20" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT20">
+        <f>BN20/BO20-1</f>
+        <v/>
+      </c>
+      <c r="BU20">
+        <f>BP20/BO20-1</f>
+        <v/>
+      </c>
+      <c r="BW20" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX20" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC20">
+        <f>BW20/BX20-1</f>
+        <v/>
+      </c>
+      <c r="CD20">
+        <f>BY20/BX20-1</f>
+        <v/>
+      </c>
+      <c r="CF20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI20" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL20">
+        <f>CF20/CG20-1</f>
+        <v/>
+      </c>
+      <c r="CM20">
+        <f>CH20/CG20-1</f>
+        <v/>
+      </c>
+      <c r="CO20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU20">
+        <f>CO20/CP20-1</f>
+        <v/>
+      </c>
+      <c r="CV20">
+        <f>CQ20/CP20-1</f>
+        <v/>
+      </c>
+      <c r="CX20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY20" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA20" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB20" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD20">
+        <f>CX20/CY20-1</f>
+        <v/>
+      </c>
+      <c r="DE20">
+        <f>CZ20/CY20-1</f>
+        <v/>
+      </c>
+      <c r="DG20" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH20" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ20" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK20" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM20">
+        <f>DG20/DH20-1</f>
+        <v/>
+      </c>
+      <c r="DN20">
+        <f>DI20/DH20-1</f>
+        <v/>
+      </c>
+      <c r="DP20" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ20" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS20" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT20" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV20">
+        <f>DP20/DQ20-1</f>
+        <v/>
+      </c>
+      <c r="DW20">
+        <f>DR20/DQ20-1</f>
+        <v/>
+      </c>
+      <c r="DY20" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ20" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB20" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC20" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE20">
+        <f>DY20/DZ20-1</f>
+        <v/>
+      </c>
+      <c r="EF20">
+        <f>EA20/DZ20-1</f>
+        <v/>
+      </c>
+      <c r="EH20" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI20" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK20" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL20" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN20">
+        <f>EH20/EI20-1</f>
+        <v/>
+      </c>
+      <c r="EO20">
+        <f>EJ20/EI20-1</f>
+        <v/>
+      </c>
+      <c r="EQ20" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER20" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET20" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU20" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW20">
+        <f>EQ20/ER20-1</f>
+        <v/>
+      </c>
+      <c r="EX20">
+        <f>ES20/ER20-1</f>
+        <v/>
+      </c>
+      <c r="EZ20" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA20" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC20" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD20" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF20">
+        <f>EZ20/FA20-1</f>
+        <v/>
+      </c>
+      <c r="FG20">
+        <f>FB20/FA20-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG20"/>
+  <dimension ref="A1:FG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -9622,6 +9622,445 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>27 Jul 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I21">
+        <f>C21/D21-1</f>
+        <v/>
+      </c>
+      <c r="J21">
+        <f>E21/D21-1</f>
+        <v/>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R21">
+        <f>L21/M21-1</f>
+        <v/>
+      </c>
+      <c r="S21">
+        <f>N21/M21-1</f>
+        <v/>
+      </c>
+      <c r="U21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA21">
+        <f>U21/V21-1</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>W21/V21-1</f>
+        <v/>
+      </c>
+      <c r="AD21" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE21" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <f>AD21/AE21-1</f>
+        <v/>
+      </c>
+      <c r="AK21">
+        <f>AF21/AE21-1</f>
+        <v/>
+      </c>
+      <c r="AM21" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN21" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS21">
+        <f>AM21/AN21-1</f>
+        <v/>
+      </c>
+      <c r="AT21">
+        <f>AO21/AN21-1</f>
+        <v/>
+      </c>
+      <c r="AV21" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW21" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB21">
+        <f>AV21/AW21-1</f>
+        <v/>
+      </c>
+      <c r="BC21">
+        <f>AX21/AW21-1</f>
+        <v/>
+      </c>
+      <c r="BE21" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF21" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK21">
+        <f>BE21/BF21-1</f>
+        <v/>
+      </c>
+      <c r="BL21">
+        <f>BG21/BF21-1</f>
+        <v/>
+      </c>
+      <c r="BN21" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO21" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT21">
+        <f>BN21/BO21-1</f>
+        <v/>
+      </c>
+      <c r="BU21">
+        <f>BP21/BO21-1</f>
+        <v/>
+      </c>
+      <c r="BW21" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX21" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC21">
+        <f>BW21/BX21-1</f>
+        <v/>
+      </c>
+      <c r="CD21">
+        <f>BY21/BX21-1</f>
+        <v/>
+      </c>
+      <c r="CF21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ21" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL21">
+        <f>CF21/CG21-1</f>
+        <v/>
+      </c>
+      <c r="CM21">
+        <f>CH21/CG21-1</f>
+        <v/>
+      </c>
+      <c r="CO21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU21">
+        <f>CO21/CP21-1</f>
+        <v/>
+      </c>
+      <c r="CV21">
+        <f>CQ21/CP21-1</f>
+        <v/>
+      </c>
+      <c r="CX21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY21" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA21" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB21" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD21">
+        <f>CX21/CY21-1</f>
+        <v/>
+      </c>
+      <c r="DE21">
+        <f>CZ21/CY21-1</f>
+        <v/>
+      </c>
+      <c r="DG21" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH21" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ21" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK21" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM21">
+        <f>DG21/DH21-1</f>
+        <v/>
+      </c>
+      <c r="DN21">
+        <f>DI21/DH21-1</f>
+        <v/>
+      </c>
+      <c r="DP21" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ21" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS21" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT21" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV21">
+        <f>DP21/DQ21-1</f>
+        <v/>
+      </c>
+      <c r="DW21">
+        <f>DR21/DQ21-1</f>
+        <v/>
+      </c>
+      <c r="DY21" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ21" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB21" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC21" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE21">
+        <f>DY21/DZ21-1</f>
+        <v/>
+      </c>
+      <c r="EF21">
+        <f>EA21/DZ21-1</f>
+        <v/>
+      </c>
+      <c r="EH21" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI21" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK21" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL21" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN21">
+        <f>EH21/EI21-1</f>
+        <v/>
+      </c>
+      <c r="EO21">
+        <f>EJ21/EI21-1</f>
+        <v/>
+      </c>
+      <c r="EQ21" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER21" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET21" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU21" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW21">
+        <f>EQ21/ER21-1</f>
+        <v/>
+      </c>
+      <c r="EX21">
+        <f>ES21/ER21-1</f>
+        <v/>
+      </c>
+      <c r="EZ21" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA21" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC21" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD21" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF21">
+        <f>EZ21/FA21-1</f>
+        <v/>
+      </c>
+      <c r="FG21">
+        <f>FB21/FA21-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG21"/>
+  <dimension ref="A1:FG22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -10061,6 +10061,445 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>27 Jul 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I22">
+        <f>C22/D22-1</f>
+        <v/>
+      </c>
+      <c r="J22">
+        <f>E22/D22-1</f>
+        <v/>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R22">
+        <f>L22/M22-1</f>
+        <v/>
+      </c>
+      <c r="S22">
+        <f>N22/M22-1</f>
+        <v/>
+      </c>
+      <c r="U22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA22">
+        <f>U22/V22-1</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>W22/V22-1</f>
+        <v/>
+      </c>
+      <c r="AD22" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE22" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <f>AD22/AE22-1</f>
+        <v/>
+      </c>
+      <c r="AK22">
+        <f>AF22/AE22-1</f>
+        <v/>
+      </c>
+      <c r="AM22" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN22" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS22">
+        <f>AM22/AN22-1</f>
+        <v/>
+      </c>
+      <c r="AT22">
+        <f>AO22/AN22-1</f>
+        <v/>
+      </c>
+      <c r="AV22" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW22" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB22">
+        <f>AV22/AW22-1</f>
+        <v/>
+      </c>
+      <c r="BC22">
+        <f>AX22/AW22-1</f>
+        <v/>
+      </c>
+      <c r="BE22" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF22" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK22">
+        <f>BE22/BF22-1</f>
+        <v/>
+      </c>
+      <c r="BL22">
+        <f>BG22/BF22-1</f>
+        <v/>
+      </c>
+      <c r="BN22" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO22" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT22">
+        <f>BN22/BO22-1</f>
+        <v/>
+      </c>
+      <c r="BU22">
+        <f>BP22/BO22-1</f>
+        <v/>
+      </c>
+      <c r="BW22" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX22" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC22">
+        <f>BW22/BX22-1</f>
+        <v/>
+      </c>
+      <c r="CD22">
+        <f>BY22/BX22-1</f>
+        <v/>
+      </c>
+      <c r="CF22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI22" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL22">
+        <f>CF22/CG22-1</f>
+        <v/>
+      </c>
+      <c r="CM22">
+        <f>CH22/CG22-1</f>
+        <v/>
+      </c>
+      <c r="CO22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS22" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU22">
+        <f>CO22/CP22-1</f>
+        <v/>
+      </c>
+      <c r="CV22">
+        <f>CQ22/CP22-1</f>
+        <v/>
+      </c>
+      <c r="CX22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY22" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA22" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB22" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD22">
+        <f>CX22/CY22-1</f>
+        <v/>
+      </c>
+      <c r="DE22">
+        <f>CZ22/CY22-1</f>
+        <v/>
+      </c>
+      <c r="DG22" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH22" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ22" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK22" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM22">
+        <f>DG22/DH22-1</f>
+        <v/>
+      </c>
+      <c r="DN22">
+        <f>DI22/DH22-1</f>
+        <v/>
+      </c>
+      <c r="DP22" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ22" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS22" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT22" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV22">
+        <f>DP22/DQ22-1</f>
+        <v/>
+      </c>
+      <c r="DW22">
+        <f>DR22/DQ22-1</f>
+        <v/>
+      </c>
+      <c r="DY22" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ22" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB22" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC22" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE22">
+        <f>DY22/DZ22-1</f>
+        <v/>
+      </c>
+      <c r="EF22">
+        <f>EA22/DZ22-1</f>
+        <v/>
+      </c>
+      <c r="EH22" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI22" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK22" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL22" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN22">
+        <f>EH22/EI22-1</f>
+        <v/>
+      </c>
+      <c r="EO22">
+        <f>EJ22/EI22-1</f>
+        <v/>
+      </c>
+      <c r="EQ22" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER22" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET22" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU22" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW22">
+        <f>EQ22/ER22-1</f>
+        <v/>
+      </c>
+      <c r="EX22">
+        <f>ES22/ER22-1</f>
+        <v/>
+      </c>
+      <c r="EZ22" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA22" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC22" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD22" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF22">
+        <f>EZ22/FA22-1</f>
+        <v/>
+      </c>
+      <c r="FG22">
+        <f>FB22/FA22-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG22"/>
+  <dimension ref="A1:FG23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -10500,6 +10500,445 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>27 Jul 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I23">
+        <f>C23/D23-1</f>
+        <v/>
+      </c>
+      <c r="J23">
+        <f>E23/D23-1</f>
+        <v/>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R23">
+        <f>L23/M23-1</f>
+        <v/>
+      </c>
+      <c r="S23">
+        <f>N23/M23-1</f>
+        <v/>
+      </c>
+      <c r="U23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA23">
+        <f>U23/V23-1</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>W23/V23-1</f>
+        <v/>
+      </c>
+      <c r="AD23" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE23" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <f>AD23/AE23-1</f>
+        <v/>
+      </c>
+      <c r="AK23">
+        <f>AF23/AE23-1</f>
+        <v/>
+      </c>
+      <c r="AM23" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN23" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS23">
+        <f>AM23/AN23-1</f>
+        <v/>
+      </c>
+      <c r="AT23">
+        <f>AO23/AN23-1</f>
+        <v/>
+      </c>
+      <c r="AV23" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW23" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB23">
+        <f>AV23/AW23-1</f>
+        <v/>
+      </c>
+      <c r="BC23">
+        <f>AX23/AW23-1</f>
+        <v/>
+      </c>
+      <c r="BE23" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF23" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK23">
+        <f>BE23/BF23-1</f>
+        <v/>
+      </c>
+      <c r="BL23">
+        <f>BG23/BF23-1</f>
+        <v/>
+      </c>
+      <c r="BN23" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO23" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT23">
+        <f>BN23/BO23-1</f>
+        <v/>
+      </c>
+      <c r="BU23">
+        <f>BP23/BO23-1</f>
+        <v/>
+      </c>
+      <c r="BW23" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX23" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC23">
+        <f>BW23/BX23-1</f>
+        <v/>
+      </c>
+      <c r="CD23">
+        <f>BY23/BX23-1</f>
+        <v/>
+      </c>
+      <c r="CF23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI23" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ23" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL23">
+        <f>CF23/CG23-1</f>
+        <v/>
+      </c>
+      <c r="CM23">
+        <f>CH23/CG23-1</f>
+        <v/>
+      </c>
+      <c r="CO23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS23" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU23">
+        <f>CO23/CP23-1</f>
+        <v/>
+      </c>
+      <c r="CV23">
+        <f>CQ23/CP23-1</f>
+        <v/>
+      </c>
+      <c r="CX23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY23" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA23" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB23" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD23">
+        <f>CX23/CY23-1</f>
+        <v/>
+      </c>
+      <c r="DE23">
+        <f>CZ23/CY23-1</f>
+        <v/>
+      </c>
+      <c r="DG23" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH23" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ23" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK23" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM23">
+        <f>DG23/DH23-1</f>
+        <v/>
+      </c>
+      <c r="DN23">
+        <f>DI23/DH23-1</f>
+        <v/>
+      </c>
+      <c r="DP23" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ23" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS23" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT23" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV23">
+        <f>DP23/DQ23-1</f>
+        <v/>
+      </c>
+      <c r="DW23">
+        <f>DR23/DQ23-1</f>
+        <v/>
+      </c>
+      <c r="DY23" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ23" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB23" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC23" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE23">
+        <f>DY23/DZ23-1</f>
+        <v/>
+      </c>
+      <c r="EF23">
+        <f>EA23/DZ23-1</f>
+        <v/>
+      </c>
+      <c r="EH23" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI23" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK23" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL23" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN23">
+        <f>EH23/EI23-1</f>
+        <v/>
+      </c>
+      <c r="EO23">
+        <f>EJ23/EI23-1</f>
+        <v/>
+      </c>
+      <c r="EQ23" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER23" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET23" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU23" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW23">
+        <f>EQ23/ER23-1</f>
+        <v/>
+      </c>
+      <c r="EX23">
+        <f>ES23/ER23-1</f>
+        <v/>
+      </c>
+      <c r="EZ23" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA23" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC23" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD23" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF23">
+        <f>EZ23/FA23-1</f>
+        <v/>
+      </c>
+      <c r="FG23">
+        <f>FB23/FA23-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG23"/>
+  <dimension ref="A1:FG24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -10939,6 +10939,449 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>27 Jul 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I24">
+        <f>C24/D24-1</f>
+        <v/>
+      </c>
+      <c r="J24">
+        <f>E24/D24-1</f>
+        <v/>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="R24">
+        <f>L24/M24-1</f>
+        <v/>
+      </c>
+      <c r="S24">
+        <f>N24/M24-1</f>
+        <v/>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V24" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA24">
+        <f>U24/V24-1</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>W24/V24-1</f>
+        <v/>
+      </c>
+      <c r="AD24" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE24" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <f>AD24/AE24-1</f>
+        <v/>
+      </c>
+      <c r="AK24">
+        <f>AF24/AE24-1</f>
+        <v/>
+      </c>
+      <c r="AM24" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN24" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS24">
+        <f>AM24/AN24-1</f>
+        <v/>
+      </c>
+      <c r="AT24">
+        <f>AO24/AN24-1</f>
+        <v/>
+      </c>
+      <c r="AV24" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW24" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB24">
+        <f>AV24/AW24-1</f>
+        <v/>
+      </c>
+      <c r="BC24">
+        <f>AX24/AW24-1</f>
+        <v/>
+      </c>
+      <c r="BE24" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF24" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK24">
+        <f>BE24/BF24-1</f>
+        <v/>
+      </c>
+      <c r="BL24">
+        <f>BG24/BF24-1</f>
+        <v/>
+      </c>
+      <c r="BN24" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO24" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT24">
+        <f>BN24/BO24-1</f>
+        <v/>
+      </c>
+      <c r="BU24">
+        <f>BP24/BO24-1</f>
+        <v/>
+      </c>
+      <c r="BW24" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX24" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BZ24" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA24" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC24">
+        <f>BW24/BX24-1</f>
+        <v/>
+      </c>
+      <c r="CD24">
+        <f>BY24/BX24-1</f>
+        <v/>
+      </c>
+      <c r="CF24" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG24" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI24" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL24">
+        <f>CF24/CG24-1</f>
+        <v/>
+      </c>
+      <c r="CM24">
+        <f>CH24/CG24-1</f>
+        <v/>
+      </c>
+      <c r="CO24" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP24" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU24">
+        <f>CO24/CP24-1</f>
+        <v/>
+      </c>
+      <c r="CV24">
+        <f>CQ24/CP24-1</f>
+        <v/>
+      </c>
+      <c r="CX24" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY24" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA24" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB24" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD24">
+        <f>CX24/CY24-1</f>
+        <v/>
+      </c>
+      <c r="DE24">
+        <f>CZ24/CY24-1</f>
+        <v/>
+      </c>
+      <c r="DG24" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH24" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ24" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK24" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM24">
+        <f>DG24/DH24-1</f>
+        <v/>
+      </c>
+      <c r="DN24">
+        <f>DI24/DH24-1</f>
+        <v/>
+      </c>
+      <c r="DP24" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ24" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS24" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT24" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV24">
+        <f>DP24/DQ24-1</f>
+        <v/>
+      </c>
+      <c r="DW24">
+        <f>DR24/DQ24-1</f>
+        <v/>
+      </c>
+      <c r="DY24" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ24" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB24" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC24" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE24">
+        <f>DY24/DZ24-1</f>
+        <v/>
+      </c>
+      <c r="EF24">
+        <f>EA24/DZ24-1</f>
+        <v/>
+      </c>
+      <c r="EH24" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI24" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK24" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL24" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN24">
+        <f>EH24/EI24-1</f>
+        <v/>
+      </c>
+      <c r="EO24">
+        <f>EJ24/EI24-1</f>
+        <v/>
+      </c>
+      <c r="EQ24" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER24" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET24" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU24" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW24">
+        <f>EQ24/ER24-1</f>
+        <v/>
+      </c>
+      <c r="EX24">
+        <f>ES24/ER24-1</f>
+        <v/>
+      </c>
+      <c r="EZ24" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA24" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC24" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD24" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF24">
+        <f>EZ24/FA24-1</f>
+        <v/>
+      </c>
+      <c r="FG24">
+        <f>FB24/FA24-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG24"/>
+  <dimension ref="A1:FG25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -11382,6 +11382,445 @@
         <v/>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>28 Jul 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I25">
+        <f>C25/D25-1</f>
+        <v/>
+      </c>
+      <c r="J25">
+        <f>E25/D25-1</f>
+        <v/>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R25">
+        <f>L25/M25-1</f>
+        <v/>
+      </c>
+      <c r="S25">
+        <f>N25/M25-1</f>
+        <v/>
+      </c>
+      <c r="U25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA25">
+        <f>U25/V25-1</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>W25/V25-1</f>
+        <v/>
+      </c>
+      <c r="AD25" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE25" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <f>AD25/AE25-1</f>
+        <v/>
+      </c>
+      <c r="AK25">
+        <f>AF25/AE25-1</f>
+        <v/>
+      </c>
+      <c r="AM25" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN25" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS25">
+        <f>AM25/AN25-1</f>
+        <v/>
+      </c>
+      <c r="AT25">
+        <f>AO25/AN25-1</f>
+        <v/>
+      </c>
+      <c r="AV25" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW25" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB25">
+        <f>AV25/AW25-1</f>
+        <v/>
+      </c>
+      <c r="BC25">
+        <f>AX25/AW25-1</f>
+        <v/>
+      </c>
+      <c r="BE25" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF25" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK25">
+        <f>BE25/BF25-1</f>
+        <v/>
+      </c>
+      <c r="BL25">
+        <f>BG25/BF25-1</f>
+        <v/>
+      </c>
+      <c r="BN25" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO25" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT25">
+        <f>BN25/BO25-1</f>
+        <v/>
+      </c>
+      <c r="BU25">
+        <f>BP25/BO25-1</f>
+        <v/>
+      </c>
+      <c r="BW25" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX25" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ25" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA25" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC25">
+        <f>BW25/BX25-1</f>
+        <v/>
+      </c>
+      <c r="CD25">
+        <f>BY25/BX25-1</f>
+        <v/>
+      </c>
+      <c r="CF25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI25" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ25" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL25">
+        <f>CF25/CG25-1</f>
+        <v/>
+      </c>
+      <c r="CM25">
+        <f>CH25/CG25-1</f>
+        <v/>
+      </c>
+      <c r="CO25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU25">
+        <f>CO25/CP25-1</f>
+        <v/>
+      </c>
+      <c r="CV25">
+        <f>CQ25/CP25-1</f>
+        <v/>
+      </c>
+      <c r="CX25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY25" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA25" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB25" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD25">
+        <f>CX25/CY25-1</f>
+        <v/>
+      </c>
+      <c r="DE25">
+        <f>CZ25/CY25-1</f>
+        <v/>
+      </c>
+      <c r="DG25" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH25" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ25" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK25" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM25">
+        <f>DG25/DH25-1</f>
+        <v/>
+      </c>
+      <c r="DN25">
+        <f>DI25/DH25-1</f>
+        <v/>
+      </c>
+      <c r="DP25" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ25" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS25" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT25" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV25">
+        <f>DP25/DQ25-1</f>
+        <v/>
+      </c>
+      <c r="DW25">
+        <f>DR25/DQ25-1</f>
+        <v/>
+      </c>
+      <c r="DY25" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ25" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB25" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC25" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE25">
+        <f>DY25/DZ25-1</f>
+        <v/>
+      </c>
+      <c r="EF25">
+        <f>EA25/DZ25-1</f>
+        <v/>
+      </c>
+      <c r="EH25" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI25" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK25" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL25" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN25">
+        <f>EH25/EI25-1</f>
+        <v/>
+      </c>
+      <c r="EO25">
+        <f>EJ25/EI25-1</f>
+        <v/>
+      </c>
+      <c r="EQ25" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER25" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET25" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU25" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW25">
+        <f>EQ25/ER25-1</f>
+        <v/>
+      </c>
+      <c r="EX25">
+        <f>ES25/ER25-1</f>
+        <v/>
+      </c>
+      <c r="EZ25" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA25" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC25" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD25" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF25">
+        <f>EZ25/FA25-1</f>
+        <v/>
+      </c>
+      <c r="FG25">
+        <f>FB25/FA25-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG25"/>
+  <dimension ref="A1:FG26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -11821,6 +11821,445 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>28 Jul 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I26">
+        <f>C26/D26-1</f>
+        <v/>
+      </c>
+      <c r="J26">
+        <f>E26/D26-1</f>
+        <v/>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R26">
+        <f>L26/M26-1</f>
+        <v/>
+      </c>
+      <c r="S26">
+        <f>N26/M26-1</f>
+        <v/>
+      </c>
+      <c r="U26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA26">
+        <f>U26/V26-1</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>W26/V26-1</f>
+        <v/>
+      </c>
+      <c r="AD26" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE26" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <f>AD26/AE26-1</f>
+        <v/>
+      </c>
+      <c r="AK26">
+        <f>AF26/AE26-1</f>
+        <v/>
+      </c>
+      <c r="AM26" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN26" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS26">
+        <f>AM26/AN26-1</f>
+        <v/>
+      </c>
+      <c r="AT26">
+        <f>AO26/AN26-1</f>
+        <v/>
+      </c>
+      <c r="AV26" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW26" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB26">
+        <f>AV26/AW26-1</f>
+        <v/>
+      </c>
+      <c r="BC26">
+        <f>AX26/AW26-1</f>
+        <v/>
+      </c>
+      <c r="BE26" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF26" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK26">
+        <f>BE26/BF26-1</f>
+        <v/>
+      </c>
+      <c r="BL26">
+        <f>BG26/BF26-1</f>
+        <v/>
+      </c>
+      <c r="BN26" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO26" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ26" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT26">
+        <f>BN26/BO26-1</f>
+        <v/>
+      </c>
+      <c r="BU26">
+        <f>BP26/BO26-1</f>
+        <v/>
+      </c>
+      <c r="BW26" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX26" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ26" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA26" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC26">
+        <f>BW26/BX26-1</f>
+        <v/>
+      </c>
+      <c r="CD26">
+        <f>BY26/BX26-1</f>
+        <v/>
+      </c>
+      <c r="CF26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI26" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ26" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL26">
+        <f>CF26/CG26-1</f>
+        <v/>
+      </c>
+      <c r="CM26">
+        <f>CH26/CG26-1</f>
+        <v/>
+      </c>
+      <c r="CO26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS26" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU26">
+        <f>CO26/CP26-1</f>
+        <v/>
+      </c>
+      <c r="CV26">
+        <f>CQ26/CP26-1</f>
+        <v/>
+      </c>
+      <c r="CX26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY26" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA26" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB26" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD26">
+        <f>CX26/CY26-1</f>
+        <v/>
+      </c>
+      <c r="DE26">
+        <f>CZ26/CY26-1</f>
+        <v/>
+      </c>
+      <c r="DG26" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH26" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ26" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK26" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM26">
+        <f>DG26/DH26-1</f>
+        <v/>
+      </c>
+      <c r="DN26">
+        <f>DI26/DH26-1</f>
+        <v/>
+      </c>
+      <c r="DP26" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ26" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS26" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT26" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV26">
+        <f>DP26/DQ26-1</f>
+        <v/>
+      </c>
+      <c r="DW26">
+        <f>DR26/DQ26-1</f>
+        <v/>
+      </c>
+      <c r="DY26" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ26" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB26" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC26" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE26">
+        <f>DY26/DZ26-1</f>
+        <v/>
+      </c>
+      <c r="EF26">
+        <f>EA26/DZ26-1</f>
+        <v/>
+      </c>
+      <c r="EH26" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI26" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK26" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL26" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN26">
+        <f>EH26/EI26-1</f>
+        <v/>
+      </c>
+      <c r="EO26">
+        <f>EJ26/EI26-1</f>
+        <v/>
+      </c>
+      <c r="EQ26" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER26" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET26" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU26" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW26">
+        <f>EQ26/ER26-1</f>
+        <v/>
+      </c>
+      <c r="EX26">
+        <f>ES26/ER26-1</f>
+        <v/>
+      </c>
+      <c r="EZ26" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA26" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC26" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD26" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF26">
+        <f>EZ26/FA26-1</f>
+        <v/>
+      </c>
+      <c r="FG26">
+        <f>FB26/FA26-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG26"/>
+  <dimension ref="A1:FG27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -12260,6 +12260,447 @@
         <v/>
       </c>
     </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>28 Jul 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I27">
+        <f>C27/D27-1</f>
+        <v/>
+      </c>
+      <c r="J27">
+        <f>E27/D27-1</f>
+        <v/>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R27">
+        <f>L27/M27-1</f>
+        <v/>
+      </c>
+      <c r="S27">
+        <f>N27/M27-1</f>
+        <v/>
+      </c>
+      <c r="U27" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V27" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA27">
+        <f>U27/V27-1</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>W27/V27-1</f>
+        <v/>
+      </c>
+      <c r="AD27" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE27" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <f>AD27/AE27-1</f>
+        <v/>
+      </c>
+      <c r="AK27">
+        <f>AF27/AE27-1</f>
+        <v/>
+      </c>
+      <c r="AM27" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN27" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS27">
+        <f>AM27/AN27-1</f>
+        <v/>
+      </c>
+      <c r="AT27">
+        <f>AO27/AN27-1</f>
+        <v/>
+      </c>
+      <c r="AV27" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW27" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB27">
+        <f>AV27/AW27-1</f>
+        <v/>
+      </c>
+      <c r="BC27">
+        <f>AX27/AW27-1</f>
+        <v/>
+      </c>
+      <c r="BE27" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF27" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK27">
+        <f>BE27/BF27-1</f>
+        <v/>
+      </c>
+      <c r="BL27">
+        <f>BG27/BF27-1</f>
+        <v/>
+      </c>
+      <c r="BN27" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO27" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ27" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT27">
+        <f>BN27/BO27-1</f>
+        <v/>
+      </c>
+      <c r="BU27">
+        <f>BP27/BO27-1</f>
+        <v/>
+      </c>
+      <c r="BW27" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX27" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ27" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA27" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC27">
+        <f>BW27/BX27-1</f>
+        <v/>
+      </c>
+      <c r="CD27">
+        <f>BY27/BX27-1</f>
+        <v/>
+      </c>
+      <c r="CF27" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG27" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CI27" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ27" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CL27">
+        <f>CF27/CG27-1</f>
+        <v/>
+      </c>
+      <c r="CM27">
+        <f>CH27/CG27-1</f>
+        <v/>
+      </c>
+      <c r="CO27" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP27" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS27" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU27">
+        <f>CO27/CP27-1</f>
+        <v/>
+      </c>
+      <c r="CV27">
+        <f>CQ27/CP27-1</f>
+        <v/>
+      </c>
+      <c r="CX27" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY27" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA27" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB27" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD27">
+        <f>CX27/CY27-1</f>
+        <v/>
+      </c>
+      <c r="DE27">
+        <f>CZ27/CY27-1</f>
+        <v/>
+      </c>
+      <c r="DG27" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH27" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ27" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK27" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM27">
+        <f>DG27/DH27-1</f>
+        <v/>
+      </c>
+      <c r="DN27">
+        <f>DI27/DH27-1</f>
+        <v/>
+      </c>
+      <c r="DP27" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ27" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS27" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT27" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV27">
+        <f>DP27/DQ27-1</f>
+        <v/>
+      </c>
+      <c r="DW27">
+        <f>DR27/DQ27-1</f>
+        <v/>
+      </c>
+      <c r="DY27" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ27" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB27" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC27" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE27">
+        <f>DY27/DZ27-1</f>
+        <v/>
+      </c>
+      <c r="EF27">
+        <f>EA27/DZ27-1</f>
+        <v/>
+      </c>
+      <c r="EH27" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI27" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK27" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL27" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN27">
+        <f>EH27/EI27-1</f>
+        <v/>
+      </c>
+      <c r="EO27">
+        <f>EJ27/EI27-1</f>
+        <v/>
+      </c>
+      <c r="EQ27" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER27" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET27" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU27" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW27">
+        <f>EQ27/ER27-1</f>
+        <v/>
+      </c>
+      <c r="EX27">
+        <f>ES27/ER27-1</f>
+        <v/>
+      </c>
+      <c r="EZ27" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA27" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC27" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD27" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF27">
+        <f>EZ27/FA27-1</f>
+        <v/>
+      </c>
+      <c r="FG27">
+        <f>FB27/FA27-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG27"/>
+  <dimension ref="A1:FG28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -12701,6 +12701,447 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>28 Jul 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I28">
+        <f>C28/D28-1</f>
+        <v/>
+      </c>
+      <c r="J28">
+        <f>E28/D28-1</f>
+        <v/>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="R28">
+        <f>L28/M28-1</f>
+        <v/>
+      </c>
+      <c r="S28">
+        <f>N28/M28-1</f>
+        <v/>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V28" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA28">
+        <f>U28/V28-1</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>W28/V28-1</f>
+        <v/>
+      </c>
+      <c r="AD28" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE28" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <f>AD28/AE28-1</f>
+        <v/>
+      </c>
+      <c r="AK28">
+        <f>AF28/AE28-1</f>
+        <v/>
+      </c>
+      <c r="AM28" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN28" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS28">
+        <f>AM28/AN28-1</f>
+        <v/>
+      </c>
+      <c r="AT28">
+        <f>AO28/AN28-1</f>
+        <v/>
+      </c>
+      <c r="AV28" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW28" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB28">
+        <f>AV28/AW28-1</f>
+        <v/>
+      </c>
+      <c r="BC28">
+        <f>AX28/AW28-1</f>
+        <v/>
+      </c>
+      <c r="BE28" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF28" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK28">
+        <f>BE28/BF28-1</f>
+        <v/>
+      </c>
+      <c r="BL28">
+        <f>BG28/BF28-1</f>
+        <v/>
+      </c>
+      <c r="BN28" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO28" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ28" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT28">
+        <f>BN28/BO28-1</f>
+        <v/>
+      </c>
+      <c r="BU28">
+        <f>BP28/BO28-1</f>
+        <v/>
+      </c>
+      <c r="BW28" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX28" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ28" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA28" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC28">
+        <f>BW28/BX28-1</f>
+        <v/>
+      </c>
+      <c r="CD28">
+        <f>BY28/BX28-1</f>
+        <v/>
+      </c>
+      <c r="CF28" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG28" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI28" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ28" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL28">
+        <f>CF28/CG28-1</f>
+        <v/>
+      </c>
+      <c r="CM28">
+        <f>CH28/CG28-1</f>
+        <v/>
+      </c>
+      <c r="CO28" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP28" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS28" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU28">
+        <f>CO28/CP28-1</f>
+        <v/>
+      </c>
+      <c r="CV28">
+        <f>CQ28/CP28-1</f>
+        <v/>
+      </c>
+      <c r="CX28" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY28" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA28" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB28" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD28">
+        <f>CX28/CY28-1</f>
+        <v/>
+      </c>
+      <c r="DE28">
+        <f>CZ28/CY28-1</f>
+        <v/>
+      </c>
+      <c r="DG28" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH28" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ28" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK28" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM28">
+        <f>DG28/DH28-1</f>
+        <v/>
+      </c>
+      <c r="DN28">
+        <f>DI28/DH28-1</f>
+        <v/>
+      </c>
+      <c r="DP28" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ28" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS28" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT28" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV28">
+        <f>DP28/DQ28-1</f>
+        <v/>
+      </c>
+      <c r="DW28">
+        <f>DR28/DQ28-1</f>
+        <v/>
+      </c>
+      <c r="DY28" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ28" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB28" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC28" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE28">
+        <f>DY28/DZ28-1</f>
+        <v/>
+      </c>
+      <c r="EF28">
+        <f>EA28/DZ28-1</f>
+        <v/>
+      </c>
+      <c r="EH28" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI28" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK28" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL28" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN28">
+        <f>EH28/EI28-1</f>
+        <v/>
+      </c>
+      <c r="EO28">
+        <f>EJ28/EI28-1</f>
+        <v/>
+      </c>
+      <c r="EQ28" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER28" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET28" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU28" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW28">
+        <f>EQ28/ER28-1</f>
+        <v/>
+      </c>
+      <c r="EX28">
+        <f>ES28/ER28-1</f>
+        <v/>
+      </c>
+      <c r="EZ28" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA28" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC28" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD28" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF28">
+        <f>EZ28/FA28-1</f>
+        <v/>
+      </c>
+      <c r="FG28">
+        <f>FB28/FA28-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG28"/>
+  <dimension ref="A1:FG29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -13142,6 +13142,447 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>29 Jul 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I29">
+        <f>C29/D29-1</f>
+        <v/>
+      </c>
+      <c r="J29">
+        <f>E29/D29-1</f>
+        <v/>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R29">
+        <f>L29/M29-1</f>
+        <v/>
+      </c>
+      <c r="S29">
+        <f>N29/M29-1</f>
+        <v/>
+      </c>
+      <c r="U29" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V29" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA29">
+        <f>U29/V29-1</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>W29/V29-1</f>
+        <v/>
+      </c>
+      <c r="AD29" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE29" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <f>AD29/AE29-1</f>
+        <v/>
+      </c>
+      <c r="AK29">
+        <f>AF29/AE29-1</f>
+        <v/>
+      </c>
+      <c r="AM29" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN29" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS29">
+        <f>AM29/AN29-1</f>
+        <v/>
+      </c>
+      <c r="AT29">
+        <f>AO29/AN29-1</f>
+        <v/>
+      </c>
+      <c r="AV29" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW29" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB29">
+        <f>AV29/AW29-1</f>
+        <v/>
+      </c>
+      <c r="BC29">
+        <f>AX29/AW29-1</f>
+        <v/>
+      </c>
+      <c r="BE29" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF29" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK29">
+        <f>BE29/BF29-1</f>
+        <v/>
+      </c>
+      <c r="BL29">
+        <f>BG29/BF29-1</f>
+        <v/>
+      </c>
+      <c r="BN29" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO29" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ29" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT29">
+        <f>BN29/BO29-1</f>
+        <v/>
+      </c>
+      <c r="BU29">
+        <f>BP29/BO29-1</f>
+        <v/>
+      </c>
+      <c r="BW29" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX29" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ29" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA29" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC29">
+        <f>BW29/BX29-1</f>
+        <v/>
+      </c>
+      <c r="CD29">
+        <f>BY29/BX29-1</f>
+        <v/>
+      </c>
+      <c r="CF29" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG29" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI29" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ29" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL29">
+        <f>CF29/CG29-1</f>
+        <v/>
+      </c>
+      <c r="CM29">
+        <f>CH29/CG29-1</f>
+        <v/>
+      </c>
+      <c r="CO29" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP29" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS29" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU29">
+        <f>CO29/CP29-1</f>
+        <v/>
+      </c>
+      <c r="CV29">
+        <f>CQ29/CP29-1</f>
+        <v/>
+      </c>
+      <c r="CX29" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY29" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DA29" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB29" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DD29">
+        <f>CX29/CY29-1</f>
+        <v/>
+      </c>
+      <c r="DE29">
+        <f>CZ29/CY29-1</f>
+        <v/>
+      </c>
+      <c r="DG29" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH29" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ29" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK29" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM29">
+        <f>DG29/DH29-1</f>
+        <v/>
+      </c>
+      <c r="DN29">
+        <f>DI29/DH29-1</f>
+        <v/>
+      </c>
+      <c r="DP29" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ29" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS29" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT29" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV29">
+        <f>DP29/DQ29-1</f>
+        <v/>
+      </c>
+      <c r="DW29">
+        <f>DR29/DQ29-1</f>
+        <v/>
+      </c>
+      <c r="DY29" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ29" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB29" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC29" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE29">
+        <f>DY29/DZ29-1</f>
+        <v/>
+      </c>
+      <c r="EF29">
+        <f>EA29/DZ29-1</f>
+        <v/>
+      </c>
+      <c r="EH29" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI29" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK29" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL29" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN29">
+        <f>EH29/EI29-1</f>
+        <v/>
+      </c>
+      <c r="EO29">
+        <f>EJ29/EI29-1</f>
+        <v/>
+      </c>
+      <c r="EQ29" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER29" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET29" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU29" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW29">
+        <f>EQ29/ER29-1</f>
+        <v/>
+      </c>
+      <c r="EX29">
+        <f>ES29/ER29-1</f>
+        <v/>
+      </c>
+      <c r="EZ29" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA29" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC29" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD29" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF29">
+        <f>EZ29/FA29-1</f>
+        <v/>
+      </c>
+      <c r="FG29">
+        <f>FB29/FA29-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG29"/>
+  <dimension ref="A1:FG30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -13583,6 +13583,447 @@
         <v/>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>29 Jul 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I30">
+        <f>C30/D30-1</f>
+        <v/>
+      </c>
+      <c r="J30">
+        <f>E30/D30-1</f>
+        <v/>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R30">
+        <f>L30/M30-1</f>
+        <v/>
+      </c>
+      <c r="S30">
+        <f>N30/M30-1</f>
+        <v/>
+      </c>
+      <c r="U30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA30">
+        <f>U30/V30-1</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>W30/V30-1</f>
+        <v/>
+      </c>
+      <c r="AD30" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE30" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <f>AD30/AE30-1</f>
+        <v/>
+      </c>
+      <c r="AK30">
+        <f>AF30/AE30-1</f>
+        <v/>
+      </c>
+      <c r="AM30" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN30" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS30">
+        <f>AM30/AN30-1</f>
+        <v/>
+      </c>
+      <c r="AT30">
+        <f>AO30/AN30-1</f>
+        <v/>
+      </c>
+      <c r="AV30" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW30" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB30">
+        <f>AV30/AW30-1</f>
+        <v/>
+      </c>
+      <c r="BC30">
+        <f>AX30/AW30-1</f>
+        <v/>
+      </c>
+      <c r="BE30" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF30" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK30">
+        <f>BE30/BF30-1</f>
+        <v/>
+      </c>
+      <c r="BL30">
+        <f>BG30/BF30-1</f>
+        <v/>
+      </c>
+      <c r="BN30" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO30" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ30" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT30">
+        <f>BN30/BO30-1</f>
+        <v/>
+      </c>
+      <c r="BU30">
+        <f>BP30/BO30-1</f>
+        <v/>
+      </c>
+      <c r="BW30" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX30" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ30" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA30" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC30">
+        <f>BW30/BX30-1</f>
+        <v/>
+      </c>
+      <c r="CD30">
+        <f>BY30/BX30-1</f>
+        <v/>
+      </c>
+      <c r="CF30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI30" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ30" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL30">
+        <f>CF30/CG30-1</f>
+        <v/>
+      </c>
+      <c r="CM30">
+        <f>CH30/CG30-1</f>
+        <v/>
+      </c>
+      <c r="CO30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS30" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU30">
+        <f>CO30/CP30-1</f>
+        <v/>
+      </c>
+      <c r="CV30">
+        <f>CQ30/CP30-1</f>
+        <v/>
+      </c>
+      <c r="CX30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY30" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA30" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB30" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD30">
+        <f>CX30/CY30-1</f>
+        <v/>
+      </c>
+      <c r="DE30">
+        <f>CZ30/CY30-1</f>
+        <v/>
+      </c>
+      <c r="DG30" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH30" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ30" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK30" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM30">
+        <f>DG30/DH30-1</f>
+        <v/>
+      </c>
+      <c r="DN30">
+        <f>DI30/DH30-1</f>
+        <v/>
+      </c>
+      <c r="DP30" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ30" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS30" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT30" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV30">
+        <f>DP30/DQ30-1</f>
+        <v/>
+      </c>
+      <c r="DW30">
+        <f>DR30/DQ30-1</f>
+        <v/>
+      </c>
+      <c r="DY30" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ30" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EB30" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC30" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EE30">
+        <f>DY30/DZ30-1</f>
+        <v/>
+      </c>
+      <c r="EF30">
+        <f>EA30/DZ30-1</f>
+        <v/>
+      </c>
+      <c r="EH30" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI30" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK30" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL30" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN30">
+        <f>EH30/EI30-1</f>
+        <v/>
+      </c>
+      <c r="EO30">
+        <f>EJ30/EI30-1</f>
+        <v/>
+      </c>
+      <c r="EQ30" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER30" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET30" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU30" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW30">
+        <f>EQ30/ER30-1</f>
+        <v/>
+      </c>
+      <c r="EX30">
+        <f>ES30/ER30-1</f>
+        <v/>
+      </c>
+      <c r="EZ30" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA30" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC30" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD30" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF30">
+        <f>EZ30/FA30-1</f>
+        <v/>
+      </c>
+      <c r="FG30">
+        <f>FB30/FA30-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG30"/>
+  <dimension ref="A1:FG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -14024,6 +14024,447 @@
         <v/>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>29 Jul 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I31">
+        <f>C31/D31-1</f>
+        <v/>
+      </c>
+      <c r="J31">
+        <f>E31/D31-1</f>
+        <v/>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R31">
+        <f>L31/M31-1</f>
+        <v/>
+      </c>
+      <c r="S31">
+        <f>N31/M31-1</f>
+        <v/>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA31">
+        <f>U31/V31-1</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>W31/V31-1</f>
+        <v/>
+      </c>
+      <c r="AD31" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <f>AD31/AE31-1</f>
+        <v/>
+      </c>
+      <c r="AK31">
+        <f>AF31/AE31-1</f>
+        <v/>
+      </c>
+      <c r="AM31" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN31" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS31">
+        <f>AM31/AN31-1</f>
+        <v/>
+      </c>
+      <c r="AT31">
+        <f>AO31/AN31-1</f>
+        <v/>
+      </c>
+      <c r="AV31" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW31" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB31">
+        <f>AV31/AW31-1</f>
+        <v/>
+      </c>
+      <c r="BC31">
+        <f>AX31/AW31-1</f>
+        <v/>
+      </c>
+      <c r="BE31" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF31" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK31">
+        <f>BE31/BF31-1</f>
+        <v/>
+      </c>
+      <c r="BL31">
+        <f>BG31/BF31-1</f>
+        <v/>
+      </c>
+      <c r="BN31" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO31" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ31" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT31">
+        <f>BN31/BO31-1</f>
+        <v/>
+      </c>
+      <c r="BU31">
+        <f>BP31/BO31-1</f>
+        <v/>
+      </c>
+      <c r="BW31" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX31" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ31" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA31" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC31">
+        <f>BW31/BX31-1</f>
+        <v/>
+      </c>
+      <c r="CD31">
+        <f>BY31/BX31-1</f>
+        <v/>
+      </c>
+      <c r="CF31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI31" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ31" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL31">
+        <f>CF31/CG31-1</f>
+        <v/>
+      </c>
+      <c r="CM31">
+        <f>CH31/CG31-1</f>
+        <v/>
+      </c>
+      <c r="CO31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS31" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU31">
+        <f>CO31/CP31-1</f>
+        <v/>
+      </c>
+      <c r="CV31">
+        <f>CQ31/CP31-1</f>
+        <v/>
+      </c>
+      <c r="CX31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY31" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA31" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB31" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD31">
+        <f>CX31/CY31-1</f>
+        <v/>
+      </c>
+      <c r="DE31">
+        <f>CZ31/CY31-1</f>
+        <v/>
+      </c>
+      <c r="DG31" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH31" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ31" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK31" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM31">
+        <f>DG31/DH31-1</f>
+        <v/>
+      </c>
+      <c r="DN31">
+        <f>DI31/DH31-1</f>
+        <v/>
+      </c>
+      <c r="DP31" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ31" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS31" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT31" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV31">
+        <f>DP31/DQ31-1</f>
+        <v/>
+      </c>
+      <c r="DW31">
+        <f>DR31/DQ31-1</f>
+        <v/>
+      </c>
+      <c r="DY31" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ31" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB31" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC31" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE31">
+        <f>DY31/DZ31-1</f>
+        <v/>
+      </c>
+      <c r="EF31">
+        <f>EA31/DZ31-1</f>
+        <v/>
+      </c>
+      <c r="EH31" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI31" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK31" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL31" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN31">
+        <f>EH31/EI31-1</f>
+        <v/>
+      </c>
+      <c r="EO31">
+        <f>EJ31/EI31-1</f>
+        <v/>
+      </c>
+      <c r="EQ31" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER31" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET31" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU31" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW31">
+        <f>EQ31/ER31-1</f>
+        <v/>
+      </c>
+      <c r="EX31">
+        <f>ES31/ER31-1</f>
+        <v/>
+      </c>
+      <c r="EZ31" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA31" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC31" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD31" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF31">
+        <f>EZ31/FA31-1</f>
+        <v/>
+      </c>
+      <c r="FG31">
+        <f>FB31/FA31-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG31"/>
+  <dimension ref="A1:FG32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -14465,6 +14465,447 @@
         <v/>
       </c>
     </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>29 Jul 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I32">
+        <f>C32/D32-1</f>
+        <v/>
+      </c>
+      <c r="J32">
+        <f>E32/D32-1</f>
+        <v/>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R32">
+        <f>L32/M32-1</f>
+        <v/>
+      </c>
+      <c r="S32">
+        <f>N32/M32-1</f>
+        <v/>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA32">
+        <f>U32/V32-1</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>W32/V32-1</f>
+        <v/>
+      </c>
+      <c r="AD32" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE32" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <f>AD32/AE32-1</f>
+        <v/>
+      </c>
+      <c r="AK32">
+        <f>AF32/AE32-1</f>
+        <v/>
+      </c>
+      <c r="AM32" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN32" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS32">
+        <f>AM32/AN32-1</f>
+        <v/>
+      </c>
+      <c r="AT32">
+        <f>AO32/AN32-1</f>
+        <v/>
+      </c>
+      <c r="AV32" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW32" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB32">
+        <f>AV32/AW32-1</f>
+        <v/>
+      </c>
+      <c r="BC32">
+        <f>AX32/AW32-1</f>
+        <v/>
+      </c>
+      <c r="BE32" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF32" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK32">
+        <f>BE32/BF32-1</f>
+        <v/>
+      </c>
+      <c r="BL32">
+        <f>BG32/BF32-1</f>
+        <v/>
+      </c>
+      <c r="BN32" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO32" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ32" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT32">
+        <f>BN32/BO32-1</f>
+        <v/>
+      </c>
+      <c r="BU32">
+        <f>BP32/BO32-1</f>
+        <v/>
+      </c>
+      <c r="BW32" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX32" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ32" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA32" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC32">
+        <f>BW32/BX32-1</f>
+        <v/>
+      </c>
+      <c r="CD32">
+        <f>BY32/BX32-1</f>
+        <v/>
+      </c>
+      <c r="CF32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI32" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ32" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL32">
+        <f>CF32/CG32-1</f>
+        <v/>
+      </c>
+      <c r="CM32">
+        <f>CH32/CG32-1</f>
+        <v/>
+      </c>
+      <c r="CO32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS32" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU32">
+        <f>CO32/CP32-1</f>
+        <v/>
+      </c>
+      <c r="CV32">
+        <f>CQ32/CP32-1</f>
+        <v/>
+      </c>
+      <c r="CX32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY32" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA32" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB32" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD32">
+        <f>CX32/CY32-1</f>
+        <v/>
+      </c>
+      <c r="DE32">
+        <f>CZ32/CY32-1</f>
+        <v/>
+      </c>
+      <c r="DG32" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH32" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ32" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK32" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM32">
+        <f>DG32/DH32-1</f>
+        <v/>
+      </c>
+      <c r="DN32">
+        <f>DI32/DH32-1</f>
+        <v/>
+      </c>
+      <c r="DP32" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ32" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS32" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT32" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV32">
+        <f>DP32/DQ32-1</f>
+        <v/>
+      </c>
+      <c r="DW32">
+        <f>DR32/DQ32-1</f>
+        <v/>
+      </c>
+      <c r="DY32" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ32" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB32" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC32" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE32">
+        <f>DY32/DZ32-1</f>
+        <v/>
+      </c>
+      <c r="EF32">
+        <f>EA32/DZ32-1</f>
+        <v/>
+      </c>
+      <c r="EH32" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI32" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK32" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL32" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN32">
+        <f>EH32/EI32-1</f>
+        <v/>
+      </c>
+      <c r="EO32">
+        <f>EJ32/EI32-1</f>
+        <v/>
+      </c>
+      <c r="EQ32" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER32" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ET32" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU32" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EW32">
+        <f>EQ32/ER32-1</f>
+        <v/>
+      </c>
+      <c r="EX32">
+        <f>ES32/ER32-1</f>
+        <v/>
+      </c>
+      <c r="EZ32" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA32" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC32" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD32" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF32">
+        <f>EZ32/FA32-1</f>
+        <v/>
+      </c>
+      <c r="FG32">
+        <f>FB32/FA32-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG32"/>
+  <dimension ref="A1:FG33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -14906,6 +14906,445 @@
         <v/>
       </c>
     </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>30 Jul 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I33">
+        <f>C33/D33-1</f>
+        <v/>
+      </c>
+      <c r="J33">
+        <f>E33/D33-1</f>
+        <v/>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R33">
+        <f>L33/M33-1</f>
+        <v/>
+      </c>
+      <c r="S33">
+        <f>N33/M33-1</f>
+        <v/>
+      </c>
+      <c r="U33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA33">
+        <f>U33/V33-1</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>W33/V33-1</f>
+        <v/>
+      </c>
+      <c r="AD33" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE33" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <f>AD33/AE33-1</f>
+        <v/>
+      </c>
+      <c r="AK33">
+        <f>AF33/AE33-1</f>
+        <v/>
+      </c>
+      <c r="AM33" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN33" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS33">
+        <f>AM33/AN33-1</f>
+        <v/>
+      </c>
+      <c r="AT33">
+        <f>AO33/AN33-1</f>
+        <v/>
+      </c>
+      <c r="AV33" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW33" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB33">
+        <f>AV33/AW33-1</f>
+        <v/>
+      </c>
+      <c r="BC33">
+        <f>AX33/AW33-1</f>
+        <v/>
+      </c>
+      <c r="BE33" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF33" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK33">
+        <f>BE33/BF33-1</f>
+        <v/>
+      </c>
+      <c r="BL33">
+        <f>BG33/BF33-1</f>
+        <v/>
+      </c>
+      <c r="BN33" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO33" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ33" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT33">
+        <f>BN33/BO33-1</f>
+        <v/>
+      </c>
+      <c r="BU33">
+        <f>BP33/BO33-1</f>
+        <v/>
+      </c>
+      <c r="BW33" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX33" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ33" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA33" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC33">
+        <f>BW33/BX33-1</f>
+        <v/>
+      </c>
+      <c r="CD33">
+        <f>BY33/BX33-1</f>
+        <v/>
+      </c>
+      <c r="CF33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI33" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ33" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL33">
+        <f>CF33/CG33-1</f>
+        <v/>
+      </c>
+      <c r="CM33">
+        <f>CH33/CG33-1</f>
+        <v/>
+      </c>
+      <c r="CO33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS33" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU33">
+        <f>CO33/CP33-1</f>
+        <v/>
+      </c>
+      <c r="CV33">
+        <f>CQ33/CP33-1</f>
+        <v/>
+      </c>
+      <c r="CX33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY33" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA33" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB33" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD33">
+        <f>CX33/CY33-1</f>
+        <v/>
+      </c>
+      <c r="DE33">
+        <f>CZ33/CY33-1</f>
+        <v/>
+      </c>
+      <c r="DG33" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH33" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ33" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK33" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM33">
+        <f>DG33/DH33-1</f>
+        <v/>
+      </c>
+      <c r="DN33">
+        <f>DI33/DH33-1</f>
+        <v/>
+      </c>
+      <c r="DP33" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ33" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS33" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT33" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV33">
+        <f>DP33/DQ33-1</f>
+        <v/>
+      </c>
+      <c r="DW33">
+        <f>DR33/DQ33-1</f>
+        <v/>
+      </c>
+      <c r="DY33" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ33" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB33" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC33" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE33">
+        <f>DY33/DZ33-1</f>
+        <v/>
+      </c>
+      <c r="EF33">
+        <f>EA33/DZ33-1</f>
+        <v/>
+      </c>
+      <c r="EH33" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI33" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK33" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL33" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN33">
+        <f>EH33/EI33-1</f>
+        <v/>
+      </c>
+      <c r="EO33">
+        <f>EJ33/EI33-1</f>
+        <v/>
+      </c>
+      <c r="EQ33" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER33" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET33" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU33" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW33">
+        <f>EQ33/ER33-1</f>
+        <v/>
+      </c>
+      <c r="EX33">
+        <f>ES33/ER33-1</f>
+        <v/>
+      </c>
+      <c r="EZ33" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA33" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC33" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD33" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF33">
+        <f>EZ33/FA33-1</f>
+        <v/>
+      </c>
+      <c r="FG33">
+        <f>FB33/FA33-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG33"/>
+  <dimension ref="A1:FG34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -15345,6 +15345,447 @@
         <v/>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>30 Jul 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I34">
+        <f>C34/D34-1</f>
+        <v/>
+      </c>
+      <c r="J34">
+        <f>E34/D34-1</f>
+        <v/>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R34">
+        <f>L34/M34-1</f>
+        <v/>
+      </c>
+      <c r="S34">
+        <f>N34/M34-1</f>
+        <v/>
+      </c>
+      <c r="U34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA34">
+        <f>U34/V34-1</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>W34/V34-1</f>
+        <v/>
+      </c>
+      <c r="AD34" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE34" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <f>AD34/AE34-1</f>
+        <v/>
+      </c>
+      <c r="AK34">
+        <f>AF34/AE34-1</f>
+        <v/>
+      </c>
+      <c r="AM34" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN34" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS34">
+        <f>AM34/AN34-1</f>
+        <v/>
+      </c>
+      <c r="AT34">
+        <f>AO34/AN34-1</f>
+        <v/>
+      </c>
+      <c r="AV34" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW34" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB34">
+        <f>AV34/AW34-1</f>
+        <v/>
+      </c>
+      <c r="BC34">
+        <f>AX34/AW34-1</f>
+        <v/>
+      </c>
+      <c r="BE34" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF34" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK34">
+        <f>BE34/BF34-1</f>
+        <v/>
+      </c>
+      <c r="BL34">
+        <f>BG34/BF34-1</f>
+        <v/>
+      </c>
+      <c r="BN34" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO34" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ34" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR34" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT34">
+        <f>BN34/BO34-1</f>
+        <v/>
+      </c>
+      <c r="BU34">
+        <f>BP34/BO34-1</f>
+        <v/>
+      </c>
+      <c r="BW34" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX34" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ34" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA34" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC34">
+        <f>BW34/BX34-1</f>
+        <v/>
+      </c>
+      <c r="CD34">
+        <f>BY34/BX34-1</f>
+        <v/>
+      </c>
+      <c r="CF34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI34" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ34" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL34">
+        <f>CF34/CG34-1</f>
+        <v/>
+      </c>
+      <c r="CM34">
+        <f>CH34/CG34-1</f>
+        <v/>
+      </c>
+      <c r="CO34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS34" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU34">
+        <f>CO34/CP34-1</f>
+        <v/>
+      </c>
+      <c r="CV34">
+        <f>CQ34/CP34-1</f>
+        <v/>
+      </c>
+      <c r="CX34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY34" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA34" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB34" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD34">
+        <f>CX34/CY34-1</f>
+        <v/>
+      </c>
+      <c r="DE34">
+        <f>CZ34/CY34-1</f>
+        <v/>
+      </c>
+      <c r="DG34" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH34" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ34" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK34" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM34">
+        <f>DG34/DH34-1</f>
+        <v/>
+      </c>
+      <c r="DN34">
+        <f>DI34/DH34-1</f>
+        <v/>
+      </c>
+      <c r="DP34" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ34" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DS34" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT34" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DV34">
+        <f>DP34/DQ34-1</f>
+        <v/>
+      </c>
+      <c r="DW34">
+        <f>DR34/DQ34-1</f>
+        <v/>
+      </c>
+      <c r="DY34" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ34" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB34" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC34" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE34">
+        <f>DY34/DZ34-1</f>
+        <v/>
+      </c>
+      <c r="EF34">
+        <f>EA34/DZ34-1</f>
+        <v/>
+      </c>
+      <c r="EH34" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI34" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK34" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL34" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN34">
+        <f>EH34/EI34-1</f>
+        <v/>
+      </c>
+      <c r="EO34">
+        <f>EJ34/EI34-1</f>
+        <v/>
+      </c>
+      <c r="EQ34" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER34" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET34" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU34" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW34">
+        <f>EQ34/ER34-1</f>
+        <v/>
+      </c>
+      <c r="EX34">
+        <f>ES34/ER34-1</f>
+        <v/>
+      </c>
+      <c r="EZ34" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA34" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC34" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD34" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF34">
+        <f>EZ34/FA34-1</f>
+        <v/>
+      </c>
+      <c r="FG34">
+        <f>FB34/FA34-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG34"/>
+  <dimension ref="A1:FG35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -15786,6 +15786,447 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>30 Jul 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I35">
+        <f>C35/D35-1</f>
+        <v/>
+      </c>
+      <c r="J35">
+        <f>E35/D35-1</f>
+        <v/>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="R35">
+        <f>L35/M35-1</f>
+        <v/>
+      </c>
+      <c r="S35">
+        <f>N35/M35-1</f>
+        <v/>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V35" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA35">
+        <f>U35/V35-1</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>W35/V35-1</f>
+        <v/>
+      </c>
+      <c r="AD35" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE35" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <f>AD35/AE35-1</f>
+        <v/>
+      </c>
+      <c r="AK35">
+        <f>AF35/AE35-1</f>
+        <v/>
+      </c>
+      <c r="AM35" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN35" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS35">
+        <f>AM35/AN35-1</f>
+        <v/>
+      </c>
+      <c r="AT35">
+        <f>AO35/AN35-1</f>
+        <v/>
+      </c>
+      <c r="AV35" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW35" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB35">
+        <f>AV35/AW35-1</f>
+        <v/>
+      </c>
+      <c r="BC35">
+        <f>AX35/AW35-1</f>
+        <v/>
+      </c>
+      <c r="BE35" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF35" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI35" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK35">
+        <f>BE35/BF35-1</f>
+        <v/>
+      </c>
+      <c r="BL35">
+        <f>BG35/BF35-1</f>
+        <v/>
+      </c>
+      <c r="BN35" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO35" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ35" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR35" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT35">
+        <f>BN35/BO35-1</f>
+        <v/>
+      </c>
+      <c r="BU35">
+        <f>BP35/BO35-1</f>
+        <v/>
+      </c>
+      <c r="BW35" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX35" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ35" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA35" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC35">
+        <f>BW35/BX35-1</f>
+        <v/>
+      </c>
+      <c r="CD35">
+        <f>BY35/BX35-1</f>
+        <v/>
+      </c>
+      <c r="CF35" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG35" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI35" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ35" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL35">
+        <f>CF35/CG35-1</f>
+        <v/>
+      </c>
+      <c r="CM35">
+        <f>CH35/CG35-1</f>
+        <v/>
+      </c>
+      <c r="CO35" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP35" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS35" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU35">
+        <f>CO35/CP35-1</f>
+        <v/>
+      </c>
+      <c r="CV35">
+        <f>CQ35/CP35-1</f>
+        <v/>
+      </c>
+      <c r="CX35" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY35" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA35" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB35" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD35">
+        <f>CX35/CY35-1</f>
+        <v/>
+      </c>
+      <c r="DE35">
+        <f>CZ35/CY35-1</f>
+        <v/>
+      </c>
+      <c r="DG35" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH35" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ35" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK35" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM35">
+        <f>DG35/DH35-1</f>
+        <v/>
+      </c>
+      <c r="DN35">
+        <f>DI35/DH35-1</f>
+        <v/>
+      </c>
+      <c r="DP35" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ35" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS35" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT35" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV35">
+        <f>DP35/DQ35-1</f>
+        <v/>
+      </c>
+      <c r="DW35">
+        <f>DR35/DQ35-1</f>
+        <v/>
+      </c>
+      <c r="DY35" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ35" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB35" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC35" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE35">
+        <f>DY35/DZ35-1</f>
+        <v/>
+      </c>
+      <c r="EF35">
+        <f>EA35/DZ35-1</f>
+        <v/>
+      </c>
+      <c r="EH35" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI35" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK35" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL35" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN35">
+        <f>EH35/EI35-1</f>
+        <v/>
+      </c>
+      <c r="EO35">
+        <f>EJ35/EI35-1</f>
+        <v/>
+      </c>
+      <c r="EQ35" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER35" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET35" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU35" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW35">
+        <f>EQ35/ER35-1</f>
+        <v/>
+      </c>
+      <c r="EX35">
+        <f>ES35/ER35-1</f>
+        <v/>
+      </c>
+      <c r="EZ35" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA35" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC35" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD35" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF35">
+        <f>EZ35/FA35-1</f>
+        <v/>
+      </c>
+      <c r="FG35">
+        <f>FB35/FA35-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG35"/>
+  <dimension ref="A1:FG36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -16227,6 +16227,445 @@
         <v/>
       </c>
     </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>30 Jul 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I36">
+        <f>C36/D36-1</f>
+        <v/>
+      </c>
+      <c r="J36">
+        <f>E36/D36-1</f>
+        <v/>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R36">
+        <f>L36/M36-1</f>
+        <v/>
+      </c>
+      <c r="S36">
+        <f>N36/M36-1</f>
+        <v/>
+      </c>
+      <c r="U36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA36">
+        <f>U36/V36-1</f>
+        <v/>
+      </c>
+      <c r="AB36">
+        <f>W36/V36-1</f>
+        <v/>
+      </c>
+      <c r="AD36" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE36" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <f>AD36/AE36-1</f>
+        <v/>
+      </c>
+      <c r="AK36">
+        <f>AF36/AE36-1</f>
+        <v/>
+      </c>
+      <c r="AM36" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN36" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS36">
+        <f>AM36/AN36-1</f>
+        <v/>
+      </c>
+      <c r="AT36">
+        <f>AO36/AN36-1</f>
+        <v/>
+      </c>
+      <c r="AV36" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW36" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB36">
+        <f>AV36/AW36-1</f>
+        <v/>
+      </c>
+      <c r="BC36">
+        <f>AX36/AW36-1</f>
+        <v/>
+      </c>
+      <c r="BE36" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF36" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK36">
+        <f>BE36/BF36-1</f>
+        <v/>
+      </c>
+      <c r="BL36">
+        <f>BG36/BF36-1</f>
+        <v/>
+      </c>
+      <c r="BN36" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO36" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ36" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR36" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT36">
+        <f>BN36/BO36-1</f>
+        <v/>
+      </c>
+      <c r="BU36">
+        <f>BP36/BO36-1</f>
+        <v/>
+      </c>
+      <c r="BW36" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX36" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ36" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA36" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC36">
+        <f>BW36/BX36-1</f>
+        <v/>
+      </c>
+      <c r="CD36">
+        <f>BY36/BX36-1</f>
+        <v/>
+      </c>
+      <c r="CF36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI36" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ36" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL36">
+        <f>CF36/CG36-1</f>
+        <v/>
+      </c>
+      <c r="CM36">
+        <f>CH36/CG36-1</f>
+        <v/>
+      </c>
+      <c r="CO36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS36" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU36">
+        <f>CO36/CP36-1</f>
+        <v/>
+      </c>
+      <c r="CV36">
+        <f>CQ36/CP36-1</f>
+        <v/>
+      </c>
+      <c r="CX36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY36" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA36" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB36" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD36">
+        <f>CX36/CY36-1</f>
+        <v/>
+      </c>
+      <c r="DE36">
+        <f>CZ36/CY36-1</f>
+        <v/>
+      </c>
+      <c r="DG36" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH36" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ36" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK36" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM36">
+        <f>DG36/DH36-1</f>
+        <v/>
+      </c>
+      <c r="DN36">
+        <f>DI36/DH36-1</f>
+        <v/>
+      </c>
+      <c r="DP36" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ36" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS36" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT36" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV36">
+        <f>DP36/DQ36-1</f>
+        <v/>
+      </c>
+      <c r="DW36">
+        <f>DR36/DQ36-1</f>
+        <v/>
+      </c>
+      <c r="DY36" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ36" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB36" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC36" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE36">
+        <f>DY36/DZ36-1</f>
+        <v/>
+      </c>
+      <c r="EF36">
+        <f>EA36/DZ36-1</f>
+        <v/>
+      </c>
+      <c r="EH36" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI36" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK36" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL36" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN36">
+        <f>EH36/EI36-1</f>
+        <v/>
+      </c>
+      <c r="EO36">
+        <f>EJ36/EI36-1</f>
+        <v/>
+      </c>
+      <c r="EQ36" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER36" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET36" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU36" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW36">
+        <f>EQ36/ER36-1</f>
+        <v/>
+      </c>
+      <c r="EX36">
+        <f>ES36/ER36-1</f>
+        <v/>
+      </c>
+      <c r="EZ36" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA36" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC36" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD36" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF36">
+        <f>EZ36/FA36-1</f>
+        <v/>
+      </c>
+      <c r="FG36">
+        <f>FB36/FA36-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG36"/>
+  <dimension ref="A1:FG37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -16666,6 +16666,445 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>31 Jul 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I37">
+        <f>C37/D37-1</f>
+        <v/>
+      </c>
+      <c r="J37">
+        <f>E37/D37-1</f>
+        <v/>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R37">
+        <f>L37/M37-1</f>
+        <v/>
+      </c>
+      <c r="S37">
+        <f>N37/M37-1</f>
+        <v/>
+      </c>
+      <c r="U37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA37">
+        <f>U37/V37-1</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>W37/V37-1</f>
+        <v/>
+      </c>
+      <c r="AD37" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE37" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <f>AD37/AE37-1</f>
+        <v/>
+      </c>
+      <c r="AK37">
+        <f>AF37/AE37-1</f>
+        <v/>
+      </c>
+      <c r="AM37" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN37" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS37">
+        <f>AM37/AN37-1</f>
+        <v/>
+      </c>
+      <c r="AT37">
+        <f>AO37/AN37-1</f>
+        <v/>
+      </c>
+      <c r="AV37" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW37" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB37">
+        <f>AV37/AW37-1</f>
+        <v/>
+      </c>
+      <c r="BC37">
+        <f>AX37/AW37-1</f>
+        <v/>
+      </c>
+      <c r="BE37" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF37" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK37">
+        <f>BE37/BF37-1</f>
+        <v/>
+      </c>
+      <c r="BL37">
+        <f>BG37/BF37-1</f>
+        <v/>
+      </c>
+      <c r="BN37" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO37" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ37" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR37" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT37">
+        <f>BN37/BO37-1</f>
+        <v/>
+      </c>
+      <c r="BU37">
+        <f>BP37/BO37-1</f>
+        <v/>
+      </c>
+      <c r="BW37" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX37" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ37" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA37" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC37">
+        <f>BW37/BX37-1</f>
+        <v/>
+      </c>
+      <c r="CD37">
+        <f>BY37/BX37-1</f>
+        <v/>
+      </c>
+      <c r="CF37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI37" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ37" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL37">
+        <f>CF37/CG37-1</f>
+        <v/>
+      </c>
+      <c r="CM37">
+        <f>CH37/CG37-1</f>
+        <v/>
+      </c>
+      <c r="CO37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS37" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU37">
+        <f>CO37/CP37-1</f>
+        <v/>
+      </c>
+      <c r="CV37">
+        <f>CQ37/CP37-1</f>
+        <v/>
+      </c>
+      <c r="CX37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY37" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA37" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB37" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD37">
+        <f>CX37/CY37-1</f>
+        <v/>
+      </c>
+      <c r="DE37">
+        <f>CZ37/CY37-1</f>
+        <v/>
+      </c>
+      <c r="DG37" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH37" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ37" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK37" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM37">
+        <f>DG37/DH37-1</f>
+        <v/>
+      </c>
+      <c r="DN37">
+        <f>DI37/DH37-1</f>
+        <v/>
+      </c>
+      <c r="DP37" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ37" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS37" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT37" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV37">
+        <f>DP37/DQ37-1</f>
+        <v/>
+      </c>
+      <c r="DW37">
+        <f>DR37/DQ37-1</f>
+        <v/>
+      </c>
+      <c r="DY37" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ37" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB37" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC37" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE37">
+        <f>DY37/DZ37-1</f>
+        <v/>
+      </c>
+      <c r="EF37">
+        <f>EA37/DZ37-1</f>
+        <v/>
+      </c>
+      <c r="EH37" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI37" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK37" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL37" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN37">
+        <f>EH37/EI37-1</f>
+        <v/>
+      </c>
+      <c r="EO37">
+        <f>EJ37/EI37-1</f>
+        <v/>
+      </c>
+      <c r="EQ37" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER37" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET37" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU37" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW37">
+        <f>EQ37/ER37-1</f>
+        <v/>
+      </c>
+      <c r="EX37">
+        <f>ES37/ER37-1</f>
+        <v/>
+      </c>
+      <c r="EZ37" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA37" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC37" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD37" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF37">
+        <f>EZ37/FA37-1</f>
+        <v/>
+      </c>
+      <c r="FG37">
+        <f>FB37/FA37-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG37"/>
+  <dimension ref="A1:FG38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -17105,6 +17105,445 @@
         <v/>
       </c>
     </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>31 Jul 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I38">
+        <f>C38/D38-1</f>
+        <v/>
+      </c>
+      <c r="J38">
+        <f>E38/D38-1</f>
+        <v/>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R38">
+        <f>L38/M38-1</f>
+        <v/>
+      </c>
+      <c r="S38">
+        <f>N38/M38-1</f>
+        <v/>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA38">
+        <f>U38/V38-1</f>
+        <v/>
+      </c>
+      <c r="AB38">
+        <f>W38/V38-1</f>
+        <v/>
+      </c>
+      <c r="AD38" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE38" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <f>AD38/AE38-1</f>
+        <v/>
+      </c>
+      <c r="AK38">
+        <f>AF38/AE38-1</f>
+        <v/>
+      </c>
+      <c r="AM38" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN38" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS38">
+        <f>AM38/AN38-1</f>
+        <v/>
+      </c>
+      <c r="AT38">
+        <f>AO38/AN38-1</f>
+        <v/>
+      </c>
+      <c r="AV38" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW38" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB38">
+        <f>AV38/AW38-1</f>
+        <v/>
+      </c>
+      <c r="BC38">
+        <f>AX38/AW38-1</f>
+        <v/>
+      </c>
+      <c r="BE38" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF38" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK38">
+        <f>BE38/BF38-1</f>
+        <v/>
+      </c>
+      <c r="BL38">
+        <f>BG38/BF38-1</f>
+        <v/>
+      </c>
+      <c r="BN38" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO38" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ38" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR38" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT38">
+        <f>BN38/BO38-1</f>
+        <v/>
+      </c>
+      <c r="BU38">
+        <f>BP38/BO38-1</f>
+        <v/>
+      </c>
+      <c r="BW38" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX38" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ38" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA38" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC38">
+        <f>BW38/BX38-1</f>
+        <v/>
+      </c>
+      <c r="CD38">
+        <f>BY38/BX38-1</f>
+        <v/>
+      </c>
+      <c r="CF38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI38" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ38" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL38">
+        <f>CF38/CG38-1</f>
+        <v/>
+      </c>
+      <c r="CM38">
+        <f>CH38/CG38-1</f>
+        <v/>
+      </c>
+      <c r="CO38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS38" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU38">
+        <f>CO38/CP38-1</f>
+        <v/>
+      </c>
+      <c r="CV38">
+        <f>CQ38/CP38-1</f>
+        <v/>
+      </c>
+      <c r="CX38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY38" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA38" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB38" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD38">
+        <f>CX38/CY38-1</f>
+        <v/>
+      </c>
+      <c r="DE38">
+        <f>CZ38/CY38-1</f>
+        <v/>
+      </c>
+      <c r="DG38" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH38" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ38" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK38" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM38">
+        <f>DG38/DH38-1</f>
+        <v/>
+      </c>
+      <c r="DN38">
+        <f>DI38/DH38-1</f>
+        <v/>
+      </c>
+      <c r="DP38" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ38" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS38" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT38" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV38">
+        <f>DP38/DQ38-1</f>
+        <v/>
+      </c>
+      <c r="DW38">
+        <f>DR38/DQ38-1</f>
+        <v/>
+      </c>
+      <c r="DY38" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ38" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB38" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC38" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE38">
+        <f>DY38/DZ38-1</f>
+        <v/>
+      </c>
+      <c r="EF38">
+        <f>EA38/DZ38-1</f>
+        <v/>
+      </c>
+      <c r="EH38" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI38" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK38" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL38" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN38">
+        <f>EH38/EI38-1</f>
+        <v/>
+      </c>
+      <c r="EO38">
+        <f>EJ38/EI38-1</f>
+        <v/>
+      </c>
+      <c r="EQ38" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER38" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET38" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU38" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW38">
+        <f>EQ38/ER38-1</f>
+        <v/>
+      </c>
+      <c r="EX38">
+        <f>ES38/ER38-1</f>
+        <v/>
+      </c>
+      <c r="EZ38" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA38" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC38" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD38" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF38">
+        <f>EZ38/FA38-1</f>
+        <v/>
+      </c>
+      <c r="FG38">
+        <f>FB38/FA38-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG38"/>
+  <dimension ref="A1:FG39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -17544,6 +17544,447 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>31 Jul 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I39">
+        <f>C39/D39-1</f>
+        <v/>
+      </c>
+      <c r="J39">
+        <f>E39/D39-1</f>
+        <v/>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R39">
+        <f>L39/M39-1</f>
+        <v/>
+      </c>
+      <c r="S39">
+        <f>N39/M39-1</f>
+        <v/>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA39">
+        <f>U39/V39-1</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>W39/V39-1</f>
+        <v/>
+      </c>
+      <c r="AD39" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <f>AD39/AE39-1</f>
+        <v/>
+      </c>
+      <c r="AK39">
+        <f>AF39/AE39-1</f>
+        <v/>
+      </c>
+      <c r="AM39" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN39" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS39">
+        <f>AM39/AN39-1</f>
+        <v/>
+      </c>
+      <c r="AT39">
+        <f>AO39/AN39-1</f>
+        <v/>
+      </c>
+      <c r="AV39" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW39" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB39">
+        <f>AV39/AW39-1</f>
+        <v/>
+      </c>
+      <c r="BC39">
+        <f>AX39/AW39-1</f>
+        <v/>
+      </c>
+      <c r="BE39" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF39" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI39" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK39">
+        <f>BE39/BF39-1</f>
+        <v/>
+      </c>
+      <c r="BL39">
+        <f>BG39/BF39-1</f>
+        <v/>
+      </c>
+      <c r="BN39" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO39" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ39" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR39" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT39">
+        <f>BN39/BO39-1</f>
+        <v/>
+      </c>
+      <c r="BU39">
+        <f>BP39/BO39-1</f>
+        <v/>
+      </c>
+      <c r="BW39" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX39" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ39" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA39" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC39">
+        <f>BW39/BX39-1</f>
+        <v/>
+      </c>
+      <c r="CD39">
+        <f>BY39/BX39-1</f>
+        <v/>
+      </c>
+      <c r="CF39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI39" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ39" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL39">
+        <f>CF39/CG39-1</f>
+        <v/>
+      </c>
+      <c r="CM39">
+        <f>CH39/CG39-1</f>
+        <v/>
+      </c>
+      <c r="CO39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS39" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU39">
+        <f>CO39/CP39-1</f>
+        <v/>
+      </c>
+      <c r="CV39">
+        <f>CQ39/CP39-1</f>
+        <v/>
+      </c>
+      <c r="CX39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY39" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA39" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB39" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD39">
+        <f>CX39/CY39-1</f>
+        <v/>
+      </c>
+      <c r="DE39">
+        <f>CZ39/CY39-1</f>
+        <v/>
+      </c>
+      <c r="DG39" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH39" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ39" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK39" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM39">
+        <f>DG39/DH39-1</f>
+        <v/>
+      </c>
+      <c r="DN39">
+        <f>DI39/DH39-1</f>
+        <v/>
+      </c>
+      <c r="DP39" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ39" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS39" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT39" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV39">
+        <f>DP39/DQ39-1</f>
+        <v/>
+      </c>
+      <c r="DW39">
+        <f>DR39/DQ39-1</f>
+        <v/>
+      </c>
+      <c r="DY39" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ39" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB39" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC39" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE39">
+        <f>DY39/DZ39-1</f>
+        <v/>
+      </c>
+      <c r="EF39">
+        <f>EA39/DZ39-1</f>
+        <v/>
+      </c>
+      <c r="EH39" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI39" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK39" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL39" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN39">
+        <f>EH39/EI39-1</f>
+        <v/>
+      </c>
+      <c r="EO39">
+        <f>EJ39/EI39-1</f>
+        <v/>
+      </c>
+      <c r="EQ39" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER39" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET39" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU39" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW39">
+        <f>EQ39/ER39-1</f>
+        <v/>
+      </c>
+      <c r="EX39">
+        <f>ES39/ER39-1</f>
+        <v/>
+      </c>
+      <c r="EZ39" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA39" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC39" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD39" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF39">
+        <f>EZ39/FA39-1</f>
+        <v/>
+      </c>
+      <c r="FG39">
+        <f>FB39/FA39-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG39"/>
+  <dimension ref="A1:FG40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -17985,6 +17985,447 @@
         <v/>
       </c>
     </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>31 Jul 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I40">
+        <f>C40/D40-1</f>
+        <v/>
+      </c>
+      <c r="J40">
+        <f>E40/D40-1</f>
+        <v/>
+      </c>
+      <c r="L40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R40">
+        <f>L40/M40-1</f>
+        <v/>
+      </c>
+      <c r="S40">
+        <f>N40/M40-1</f>
+        <v/>
+      </c>
+      <c r="U40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA40">
+        <f>U40/V40-1</f>
+        <v/>
+      </c>
+      <c r="AB40">
+        <f>W40/V40-1</f>
+        <v/>
+      </c>
+      <c r="AD40" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE40" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <f>AD40/AE40-1</f>
+        <v/>
+      </c>
+      <c r="AK40">
+        <f>AF40/AE40-1</f>
+        <v/>
+      </c>
+      <c r="AM40" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN40" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS40">
+        <f>AM40/AN40-1</f>
+        <v/>
+      </c>
+      <c r="AT40">
+        <f>AO40/AN40-1</f>
+        <v/>
+      </c>
+      <c r="AV40" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BB40">
+        <f>AV40/AW40-1</f>
+        <v/>
+      </c>
+      <c r="BC40">
+        <f>AX40/AW40-1</f>
+        <v/>
+      </c>
+      <c r="BE40" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF40" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI40" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK40">
+        <f>BE40/BF40-1</f>
+        <v/>
+      </c>
+      <c r="BL40">
+        <f>BG40/BF40-1</f>
+        <v/>
+      </c>
+      <c r="BN40" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO40" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ40" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR40" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT40">
+        <f>BN40/BO40-1</f>
+        <v/>
+      </c>
+      <c r="BU40">
+        <f>BP40/BO40-1</f>
+        <v/>
+      </c>
+      <c r="BW40" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX40" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ40" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA40" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC40">
+        <f>BW40/BX40-1</f>
+        <v/>
+      </c>
+      <c r="CD40">
+        <f>BY40/BX40-1</f>
+        <v/>
+      </c>
+      <c r="CF40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI40" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ40" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL40">
+        <f>CF40/CG40-1</f>
+        <v/>
+      </c>
+      <c r="CM40">
+        <f>CH40/CG40-1</f>
+        <v/>
+      </c>
+      <c r="CO40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS40" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU40">
+        <f>CO40/CP40-1</f>
+        <v/>
+      </c>
+      <c r="CV40">
+        <f>CQ40/CP40-1</f>
+        <v/>
+      </c>
+      <c r="CX40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY40" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA40" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB40" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD40">
+        <f>CX40/CY40-1</f>
+        <v/>
+      </c>
+      <c r="DE40">
+        <f>CZ40/CY40-1</f>
+        <v/>
+      </c>
+      <c r="DG40" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH40" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ40" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK40" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM40">
+        <f>DG40/DH40-1</f>
+        <v/>
+      </c>
+      <c r="DN40">
+        <f>DI40/DH40-1</f>
+        <v/>
+      </c>
+      <c r="DP40" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ40" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS40" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT40" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV40">
+        <f>DP40/DQ40-1</f>
+        <v/>
+      </c>
+      <c r="DW40">
+        <f>DR40/DQ40-1</f>
+        <v/>
+      </c>
+      <c r="DY40" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ40" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB40" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC40" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE40">
+        <f>DY40/DZ40-1</f>
+        <v/>
+      </c>
+      <c r="EF40">
+        <f>EA40/DZ40-1</f>
+        <v/>
+      </c>
+      <c r="EH40" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI40" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK40" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL40" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN40">
+        <f>EH40/EI40-1</f>
+        <v/>
+      </c>
+      <c r="EO40">
+        <f>EJ40/EI40-1</f>
+        <v/>
+      </c>
+      <c r="EQ40" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER40" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET40" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU40" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW40">
+        <f>EQ40/ER40-1</f>
+        <v/>
+      </c>
+      <c r="EX40">
+        <f>ES40/ER40-1</f>
+        <v/>
+      </c>
+      <c r="EZ40" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA40" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC40" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD40" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF40">
+        <f>EZ40/FA40-1</f>
+        <v/>
+      </c>
+      <c r="FG40">
+        <f>FB40/FA40-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG40"/>
+  <dimension ref="A1:FG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -18426,6 +18426,445 @@
         <v/>
       </c>
     </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>01 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I41">
+        <f>C41/D41-1</f>
+        <v/>
+      </c>
+      <c r="J41">
+        <f>E41/D41-1</f>
+        <v/>
+      </c>
+      <c r="L41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R41">
+        <f>L41/M41-1</f>
+        <v/>
+      </c>
+      <c r="S41">
+        <f>N41/M41-1</f>
+        <v/>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA41">
+        <f>U41/V41-1</f>
+        <v/>
+      </c>
+      <c r="AB41">
+        <f>W41/V41-1</f>
+        <v/>
+      </c>
+      <c r="AD41" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE41" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <f>AD41/AE41-1</f>
+        <v/>
+      </c>
+      <c r="AK41">
+        <f>AF41/AE41-1</f>
+        <v/>
+      </c>
+      <c r="AM41" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN41" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS41">
+        <f>AM41/AN41-1</f>
+        <v/>
+      </c>
+      <c r="AT41">
+        <f>AO41/AN41-1</f>
+        <v/>
+      </c>
+      <c r="AV41" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW41" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB41">
+        <f>AV41/AW41-1</f>
+        <v/>
+      </c>
+      <c r="BC41">
+        <f>AX41/AW41-1</f>
+        <v/>
+      </c>
+      <c r="BE41" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF41" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI41" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK41">
+        <f>BE41/BF41-1</f>
+        <v/>
+      </c>
+      <c r="BL41">
+        <f>BG41/BF41-1</f>
+        <v/>
+      </c>
+      <c r="BN41" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO41" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ41" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR41" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT41">
+        <f>BN41/BO41-1</f>
+        <v/>
+      </c>
+      <c r="BU41">
+        <f>BP41/BO41-1</f>
+        <v/>
+      </c>
+      <c r="BW41" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX41" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ41" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA41" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC41">
+        <f>BW41/BX41-1</f>
+        <v/>
+      </c>
+      <c r="CD41">
+        <f>BY41/BX41-1</f>
+        <v/>
+      </c>
+      <c r="CF41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI41" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ41" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL41">
+        <f>CF41/CG41-1</f>
+        <v/>
+      </c>
+      <c r="CM41">
+        <f>CH41/CG41-1</f>
+        <v/>
+      </c>
+      <c r="CO41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS41" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU41">
+        <f>CO41/CP41-1</f>
+        <v/>
+      </c>
+      <c r="CV41">
+        <f>CQ41/CP41-1</f>
+        <v/>
+      </c>
+      <c r="CX41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY41" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA41" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB41" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD41">
+        <f>CX41/CY41-1</f>
+        <v/>
+      </c>
+      <c r="DE41">
+        <f>CZ41/CY41-1</f>
+        <v/>
+      </c>
+      <c r="DG41" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH41" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ41" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK41" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM41">
+        <f>DG41/DH41-1</f>
+        <v/>
+      </c>
+      <c r="DN41">
+        <f>DI41/DH41-1</f>
+        <v/>
+      </c>
+      <c r="DP41" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ41" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS41" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT41" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV41">
+        <f>DP41/DQ41-1</f>
+        <v/>
+      </c>
+      <c r="DW41">
+        <f>DR41/DQ41-1</f>
+        <v/>
+      </c>
+      <c r="DY41" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ41" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB41" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC41" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE41">
+        <f>DY41/DZ41-1</f>
+        <v/>
+      </c>
+      <c r="EF41">
+        <f>EA41/DZ41-1</f>
+        <v/>
+      </c>
+      <c r="EH41" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI41" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK41" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL41" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN41">
+        <f>EH41/EI41-1</f>
+        <v/>
+      </c>
+      <c r="EO41">
+        <f>EJ41/EI41-1</f>
+        <v/>
+      </c>
+      <c r="EQ41" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER41" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET41" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU41" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW41">
+        <f>EQ41/ER41-1</f>
+        <v/>
+      </c>
+      <c r="EX41">
+        <f>ES41/ER41-1</f>
+        <v/>
+      </c>
+      <c r="EZ41" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA41" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC41" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD41" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF41">
+        <f>EZ41/FA41-1</f>
+        <v/>
+      </c>
+      <c r="FG41">
+        <f>FB41/FA41-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG41"/>
+  <dimension ref="A1:FG42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -18865,6 +18865,445 @@
         <v/>
       </c>
     </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>01 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I42">
+        <f>C42/D42-1</f>
+        <v/>
+      </c>
+      <c r="J42">
+        <f>E42/D42-1</f>
+        <v/>
+      </c>
+      <c r="L42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R42">
+        <f>L42/M42-1</f>
+        <v/>
+      </c>
+      <c r="S42">
+        <f>N42/M42-1</f>
+        <v/>
+      </c>
+      <c r="U42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA42">
+        <f>U42/V42-1</f>
+        <v/>
+      </c>
+      <c r="AB42">
+        <f>W42/V42-1</f>
+        <v/>
+      </c>
+      <c r="AD42" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE42" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <f>AD42/AE42-1</f>
+        <v/>
+      </c>
+      <c r="AK42">
+        <f>AF42/AE42-1</f>
+        <v/>
+      </c>
+      <c r="AM42" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN42" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS42">
+        <f>AM42/AN42-1</f>
+        <v/>
+      </c>
+      <c r="AT42">
+        <f>AO42/AN42-1</f>
+        <v/>
+      </c>
+      <c r="AV42" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW42" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB42">
+        <f>AV42/AW42-1</f>
+        <v/>
+      </c>
+      <c r="BC42">
+        <f>AX42/AW42-1</f>
+        <v/>
+      </c>
+      <c r="BE42" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF42" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI42" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK42">
+        <f>BE42/BF42-1</f>
+        <v/>
+      </c>
+      <c r="BL42">
+        <f>BG42/BF42-1</f>
+        <v/>
+      </c>
+      <c r="BN42" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO42" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ42" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR42" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT42">
+        <f>BN42/BO42-1</f>
+        <v/>
+      </c>
+      <c r="BU42">
+        <f>BP42/BO42-1</f>
+        <v/>
+      </c>
+      <c r="BW42" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX42" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ42" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA42" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC42">
+        <f>BW42/BX42-1</f>
+        <v/>
+      </c>
+      <c r="CD42">
+        <f>BY42/BX42-1</f>
+        <v/>
+      </c>
+      <c r="CF42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI42" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ42" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL42">
+        <f>CF42/CG42-1</f>
+        <v/>
+      </c>
+      <c r="CM42">
+        <f>CH42/CG42-1</f>
+        <v/>
+      </c>
+      <c r="CO42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS42" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU42">
+        <f>CO42/CP42-1</f>
+        <v/>
+      </c>
+      <c r="CV42">
+        <f>CQ42/CP42-1</f>
+        <v/>
+      </c>
+      <c r="CX42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY42" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA42" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB42" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD42">
+        <f>CX42/CY42-1</f>
+        <v/>
+      </c>
+      <c r="DE42">
+        <f>CZ42/CY42-1</f>
+        <v/>
+      </c>
+      <c r="DG42" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH42" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ42" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK42" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM42">
+        <f>DG42/DH42-1</f>
+        <v/>
+      </c>
+      <c r="DN42">
+        <f>DI42/DH42-1</f>
+        <v/>
+      </c>
+      <c r="DP42" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ42" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS42" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT42" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV42">
+        <f>DP42/DQ42-1</f>
+        <v/>
+      </c>
+      <c r="DW42">
+        <f>DR42/DQ42-1</f>
+        <v/>
+      </c>
+      <c r="DY42" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ42" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB42" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC42" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE42">
+        <f>DY42/DZ42-1</f>
+        <v/>
+      </c>
+      <c r="EF42">
+        <f>EA42/DZ42-1</f>
+        <v/>
+      </c>
+      <c r="EH42" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI42" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK42" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL42" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN42">
+        <f>EH42/EI42-1</f>
+        <v/>
+      </c>
+      <c r="EO42">
+        <f>EJ42/EI42-1</f>
+        <v/>
+      </c>
+      <c r="EQ42" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER42" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET42" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU42" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW42">
+        <f>EQ42/ER42-1</f>
+        <v/>
+      </c>
+      <c r="EX42">
+        <f>ES42/ER42-1</f>
+        <v/>
+      </c>
+      <c r="EZ42" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA42" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC42" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD42" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF42">
+        <f>EZ42/FA42-1</f>
+        <v/>
+      </c>
+      <c r="FG42">
+        <f>FB42/FA42-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG42"/>
+  <dimension ref="A1:FG43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -19304,6 +19304,445 @@
         <v/>
       </c>
     </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>01 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I43">
+        <f>C43/D43-1</f>
+        <v/>
+      </c>
+      <c r="J43">
+        <f>E43/D43-1</f>
+        <v/>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R43">
+        <f>L43/M43-1</f>
+        <v/>
+      </c>
+      <c r="S43">
+        <f>N43/M43-1</f>
+        <v/>
+      </c>
+      <c r="U43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA43">
+        <f>U43/V43-1</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>W43/V43-1</f>
+        <v/>
+      </c>
+      <c r="AD43" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE43" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <f>AD43/AE43-1</f>
+        <v/>
+      </c>
+      <c r="AK43">
+        <f>AF43/AE43-1</f>
+        <v/>
+      </c>
+      <c r="AM43" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN43" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS43">
+        <f>AM43/AN43-1</f>
+        <v/>
+      </c>
+      <c r="AT43">
+        <f>AO43/AN43-1</f>
+        <v/>
+      </c>
+      <c r="AV43" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW43" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB43">
+        <f>AV43/AW43-1</f>
+        <v/>
+      </c>
+      <c r="BC43">
+        <f>AX43/AW43-1</f>
+        <v/>
+      </c>
+      <c r="BE43" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF43" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI43" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK43">
+        <f>BE43/BF43-1</f>
+        <v/>
+      </c>
+      <c r="BL43">
+        <f>BG43/BF43-1</f>
+        <v/>
+      </c>
+      <c r="BN43" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO43" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ43" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR43" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT43">
+        <f>BN43/BO43-1</f>
+        <v/>
+      </c>
+      <c r="BU43">
+        <f>BP43/BO43-1</f>
+        <v/>
+      </c>
+      <c r="BW43" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX43" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ43" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA43" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC43">
+        <f>BW43/BX43-1</f>
+        <v/>
+      </c>
+      <c r="CD43">
+        <f>BY43/BX43-1</f>
+        <v/>
+      </c>
+      <c r="CF43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI43" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ43" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL43">
+        <f>CF43/CG43-1</f>
+        <v/>
+      </c>
+      <c r="CM43">
+        <f>CH43/CG43-1</f>
+        <v/>
+      </c>
+      <c r="CO43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS43" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU43">
+        <f>CO43/CP43-1</f>
+        <v/>
+      </c>
+      <c r="CV43">
+        <f>CQ43/CP43-1</f>
+        <v/>
+      </c>
+      <c r="CX43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY43" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA43" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB43" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD43">
+        <f>CX43/CY43-1</f>
+        <v/>
+      </c>
+      <c r="DE43">
+        <f>CZ43/CY43-1</f>
+        <v/>
+      </c>
+      <c r="DG43" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH43" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ43" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK43" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM43">
+        <f>DG43/DH43-1</f>
+        <v/>
+      </c>
+      <c r="DN43">
+        <f>DI43/DH43-1</f>
+        <v/>
+      </c>
+      <c r="DP43" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ43" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS43" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT43" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV43">
+        <f>DP43/DQ43-1</f>
+        <v/>
+      </c>
+      <c r="DW43">
+        <f>DR43/DQ43-1</f>
+        <v/>
+      </c>
+      <c r="DY43" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ43" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB43" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC43" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE43">
+        <f>DY43/DZ43-1</f>
+        <v/>
+      </c>
+      <c r="EF43">
+        <f>EA43/DZ43-1</f>
+        <v/>
+      </c>
+      <c r="EH43" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI43" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK43" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL43" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN43">
+        <f>EH43/EI43-1</f>
+        <v/>
+      </c>
+      <c r="EO43">
+        <f>EJ43/EI43-1</f>
+        <v/>
+      </c>
+      <c r="EQ43" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER43" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET43" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU43" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW43">
+        <f>EQ43/ER43-1</f>
+        <v/>
+      </c>
+      <c r="EX43">
+        <f>ES43/ER43-1</f>
+        <v/>
+      </c>
+      <c r="EZ43" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA43" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC43" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD43" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF43">
+        <f>EZ43/FA43-1</f>
+        <v/>
+      </c>
+      <c r="FG43">
+        <f>FB43/FA43-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG43"/>
+  <dimension ref="A1:FG44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -19743,6 +19743,445 @@
         <v/>
       </c>
     </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>01 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I44">
+        <f>C44/D44-1</f>
+        <v/>
+      </c>
+      <c r="J44">
+        <f>E44/D44-1</f>
+        <v/>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R44">
+        <f>L44/M44-1</f>
+        <v/>
+      </c>
+      <c r="S44">
+        <f>N44/M44-1</f>
+        <v/>
+      </c>
+      <c r="U44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA44">
+        <f>U44/V44-1</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>W44/V44-1</f>
+        <v/>
+      </c>
+      <c r="AD44" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE44" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <f>AD44/AE44-1</f>
+        <v/>
+      </c>
+      <c r="AK44">
+        <f>AF44/AE44-1</f>
+        <v/>
+      </c>
+      <c r="AM44" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN44" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS44">
+        <f>AM44/AN44-1</f>
+        <v/>
+      </c>
+      <c r="AT44">
+        <f>AO44/AN44-1</f>
+        <v/>
+      </c>
+      <c r="AV44" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW44" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB44">
+        <f>AV44/AW44-1</f>
+        <v/>
+      </c>
+      <c r="BC44">
+        <f>AX44/AW44-1</f>
+        <v/>
+      </c>
+      <c r="BE44" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF44" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI44" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK44">
+        <f>BE44/BF44-1</f>
+        <v/>
+      </c>
+      <c r="BL44">
+        <f>BG44/BF44-1</f>
+        <v/>
+      </c>
+      <c r="BN44" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO44" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ44" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR44" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT44">
+        <f>BN44/BO44-1</f>
+        <v/>
+      </c>
+      <c r="BU44">
+        <f>BP44/BO44-1</f>
+        <v/>
+      </c>
+      <c r="BW44" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX44" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ44" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA44" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC44">
+        <f>BW44/BX44-1</f>
+        <v/>
+      </c>
+      <c r="CD44">
+        <f>BY44/BX44-1</f>
+        <v/>
+      </c>
+      <c r="CF44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI44" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ44" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL44">
+        <f>CF44/CG44-1</f>
+        <v/>
+      </c>
+      <c r="CM44">
+        <f>CH44/CG44-1</f>
+        <v/>
+      </c>
+      <c r="CO44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS44" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU44">
+        <f>CO44/CP44-1</f>
+        <v/>
+      </c>
+      <c r="CV44">
+        <f>CQ44/CP44-1</f>
+        <v/>
+      </c>
+      <c r="CX44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY44" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA44" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB44" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD44">
+        <f>CX44/CY44-1</f>
+        <v/>
+      </c>
+      <c r="DE44">
+        <f>CZ44/CY44-1</f>
+        <v/>
+      </c>
+      <c r="DG44" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH44" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ44" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK44" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM44">
+        <f>DG44/DH44-1</f>
+        <v/>
+      </c>
+      <c r="DN44">
+        <f>DI44/DH44-1</f>
+        <v/>
+      </c>
+      <c r="DP44" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ44" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS44" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT44" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV44">
+        <f>DP44/DQ44-1</f>
+        <v/>
+      </c>
+      <c r="DW44">
+        <f>DR44/DQ44-1</f>
+        <v/>
+      </c>
+      <c r="DY44" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ44" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB44" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC44" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE44">
+        <f>DY44/DZ44-1</f>
+        <v/>
+      </c>
+      <c r="EF44">
+        <f>EA44/DZ44-1</f>
+        <v/>
+      </c>
+      <c r="EH44" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI44" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK44" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL44" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN44">
+        <f>EH44/EI44-1</f>
+        <v/>
+      </c>
+      <c r="EO44">
+        <f>EJ44/EI44-1</f>
+        <v/>
+      </c>
+      <c r="EQ44" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER44" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET44" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU44" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW44">
+        <f>EQ44/ER44-1</f>
+        <v/>
+      </c>
+      <c r="EX44">
+        <f>ES44/ER44-1</f>
+        <v/>
+      </c>
+      <c r="EZ44" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA44" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC44" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD44" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF44">
+        <f>EZ44/FA44-1</f>
+        <v/>
+      </c>
+      <c r="FG44">
+        <f>FB44/FA44-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG44"/>
+  <dimension ref="A1:FG45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -20182,6 +20182,445 @@
         <v/>
       </c>
     </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>02 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I45">
+        <f>C45/D45-1</f>
+        <v/>
+      </c>
+      <c r="J45">
+        <f>E45/D45-1</f>
+        <v/>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R45">
+        <f>L45/M45-1</f>
+        <v/>
+      </c>
+      <c r="S45">
+        <f>N45/M45-1</f>
+        <v/>
+      </c>
+      <c r="U45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA45">
+        <f>U45/V45-1</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>W45/V45-1</f>
+        <v/>
+      </c>
+      <c r="AD45" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE45" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <f>AD45/AE45-1</f>
+        <v/>
+      </c>
+      <c r="AK45">
+        <f>AF45/AE45-1</f>
+        <v/>
+      </c>
+      <c r="AM45" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN45" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS45">
+        <f>AM45/AN45-1</f>
+        <v/>
+      </c>
+      <c r="AT45">
+        <f>AO45/AN45-1</f>
+        <v/>
+      </c>
+      <c r="AV45" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW45" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB45">
+        <f>AV45/AW45-1</f>
+        <v/>
+      </c>
+      <c r="BC45">
+        <f>AX45/AW45-1</f>
+        <v/>
+      </c>
+      <c r="BE45" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF45" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK45">
+        <f>BE45/BF45-1</f>
+        <v/>
+      </c>
+      <c r="BL45">
+        <f>BG45/BF45-1</f>
+        <v/>
+      </c>
+      <c r="BN45" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO45" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ45" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR45" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT45">
+        <f>BN45/BO45-1</f>
+        <v/>
+      </c>
+      <c r="BU45">
+        <f>BP45/BO45-1</f>
+        <v/>
+      </c>
+      <c r="BW45" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX45" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ45" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA45" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC45">
+        <f>BW45/BX45-1</f>
+        <v/>
+      </c>
+      <c r="CD45">
+        <f>BY45/BX45-1</f>
+        <v/>
+      </c>
+      <c r="CF45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI45" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ45" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL45">
+        <f>CF45/CG45-1</f>
+        <v/>
+      </c>
+      <c r="CM45">
+        <f>CH45/CG45-1</f>
+        <v/>
+      </c>
+      <c r="CO45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS45" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU45">
+        <f>CO45/CP45-1</f>
+        <v/>
+      </c>
+      <c r="CV45">
+        <f>CQ45/CP45-1</f>
+        <v/>
+      </c>
+      <c r="CX45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY45" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA45" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB45" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD45">
+        <f>CX45/CY45-1</f>
+        <v/>
+      </c>
+      <c r="DE45">
+        <f>CZ45/CY45-1</f>
+        <v/>
+      </c>
+      <c r="DG45" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH45" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ45" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK45" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM45">
+        <f>DG45/DH45-1</f>
+        <v/>
+      </c>
+      <c r="DN45">
+        <f>DI45/DH45-1</f>
+        <v/>
+      </c>
+      <c r="DP45" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ45" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS45" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT45" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV45">
+        <f>DP45/DQ45-1</f>
+        <v/>
+      </c>
+      <c r="DW45">
+        <f>DR45/DQ45-1</f>
+        <v/>
+      </c>
+      <c r="DY45" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ45" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB45" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC45" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE45">
+        <f>DY45/DZ45-1</f>
+        <v/>
+      </c>
+      <c r="EF45">
+        <f>EA45/DZ45-1</f>
+        <v/>
+      </c>
+      <c r="EH45" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI45" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK45" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL45" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN45">
+        <f>EH45/EI45-1</f>
+        <v/>
+      </c>
+      <c r="EO45">
+        <f>EJ45/EI45-1</f>
+        <v/>
+      </c>
+      <c r="EQ45" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER45" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET45" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU45" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW45">
+        <f>EQ45/ER45-1</f>
+        <v/>
+      </c>
+      <c r="EX45">
+        <f>ES45/ER45-1</f>
+        <v/>
+      </c>
+      <c r="EZ45" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA45" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC45" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD45" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF45">
+        <f>EZ45/FA45-1</f>
+        <v/>
+      </c>
+      <c r="FG45">
+        <f>FB45/FA45-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG45"/>
+  <dimension ref="A1:FG46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -20621,6 +20621,445 @@
         <v/>
       </c>
     </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>02 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I46">
+        <f>C46/D46-1</f>
+        <v/>
+      </c>
+      <c r="J46">
+        <f>E46/D46-1</f>
+        <v/>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R46">
+        <f>L46/M46-1</f>
+        <v/>
+      </c>
+      <c r="S46">
+        <f>N46/M46-1</f>
+        <v/>
+      </c>
+      <c r="U46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA46">
+        <f>U46/V46-1</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>W46/V46-1</f>
+        <v/>
+      </c>
+      <c r="AD46" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE46" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <f>AD46/AE46-1</f>
+        <v/>
+      </c>
+      <c r="AK46">
+        <f>AF46/AE46-1</f>
+        <v/>
+      </c>
+      <c r="AM46" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN46" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS46">
+        <f>AM46/AN46-1</f>
+        <v/>
+      </c>
+      <c r="AT46">
+        <f>AO46/AN46-1</f>
+        <v/>
+      </c>
+      <c r="AV46" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW46" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB46">
+        <f>AV46/AW46-1</f>
+        <v/>
+      </c>
+      <c r="BC46">
+        <f>AX46/AW46-1</f>
+        <v/>
+      </c>
+      <c r="BE46" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF46" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI46" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK46">
+        <f>BE46/BF46-1</f>
+        <v/>
+      </c>
+      <c r="BL46">
+        <f>BG46/BF46-1</f>
+        <v/>
+      </c>
+      <c r="BN46" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO46" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ46" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR46" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT46">
+        <f>BN46/BO46-1</f>
+        <v/>
+      </c>
+      <c r="BU46">
+        <f>BP46/BO46-1</f>
+        <v/>
+      </c>
+      <c r="BW46" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX46" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ46" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA46" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC46">
+        <f>BW46/BX46-1</f>
+        <v/>
+      </c>
+      <c r="CD46">
+        <f>BY46/BX46-1</f>
+        <v/>
+      </c>
+      <c r="CF46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI46" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ46" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL46">
+        <f>CF46/CG46-1</f>
+        <v/>
+      </c>
+      <c r="CM46">
+        <f>CH46/CG46-1</f>
+        <v/>
+      </c>
+      <c r="CO46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS46" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU46">
+        <f>CO46/CP46-1</f>
+        <v/>
+      </c>
+      <c r="CV46">
+        <f>CQ46/CP46-1</f>
+        <v/>
+      </c>
+      <c r="CX46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY46" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA46" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB46" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD46">
+        <f>CX46/CY46-1</f>
+        <v/>
+      </c>
+      <c r="DE46">
+        <f>CZ46/CY46-1</f>
+        <v/>
+      </c>
+      <c r="DG46" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH46" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ46" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK46" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM46">
+        <f>DG46/DH46-1</f>
+        <v/>
+      </c>
+      <c r="DN46">
+        <f>DI46/DH46-1</f>
+        <v/>
+      </c>
+      <c r="DP46" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ46" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS46" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT46" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV46">
+        <f>DP46/DQ46-1</f>
+        <v/>
+      </c>
+      <c r="DW46">
+        <f>DR46/DQ46-1</f>
+        <v/>
+      </c>
+      <c r="DY46" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ46" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB46" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE46">
+        <f>DY46/DZ46-1</f>
+        <v/>
+      </c>
+      <c r="EF46">
+        <f>EA46/DZ46-1</f>
+        <v/>
+      </c>
+      <c r="EH46" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI46" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK46" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL46" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN46">
+        <f>EH46/EI46-1</f>
+        <v/>
+      </c>
+      <c r="EO46">
+        <f>EJ46/EI46-1</f>
+        <v/>
+      </c>
+      <c r="EQ46" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER46" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET46" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU46" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW46">
+        <f>EQ46/ER46-1</f>
+        <v/>
+      </c>
+      <c r="EX46">
+        <f>ES46/ER46-1</f>
+        <v/>
+      </c>
+      <c r="EZ46" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA46" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC46" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD46" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF46">
+        <f>EZ46/FA46-1</f>
+        <v/>
+      </c>
+      <c r="FG46">
+        <f>FB46/FA46-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG46"/>
+  <dimension ref="A1:FG47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -21060,6 +21060,445 @@
         <v/>
       </c>
     </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>02 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I47">
+        <f>C47/D47-1</f>
+        <v/>
+      </c>
+      <c r="J47">
+        <f>E47/D47-1</f>
+        <v/>
+      </c>
+      <c r="L47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R47">
+        <f>L47/M47-1</f>
+        <v/>
+      </c>
+      <c r="S47">
+        <f>N47/M47-1</f>
+        <v/>
+      </c>
+      <c r="U47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA47">
+        <f>U47/V47-1</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>W47/V47-1</f>
+        <v/>
+      </c>
+      <c r="AD47" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE47" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <f>AD47/AE47-1</f>
+        <v/>
+      </c>
+      <c r="AK47">
+        <f>AF47/AE47-1</f>
+        <v/>
+      </c>
+      <c r="AM47" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN47" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS47">
+        <f>AM47/AN47-1</f>
+        <v/>
+      </c>
+      <c r="AT47">
+        <f>AO47/AN47-1</f>
+        <v/>
+      </c>
+      <c r="AV47" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW47" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB47">
+        <f>AV47/AW47-1</f>
+        <v/>
+      </c>
+      <c r="BC47">
+        <f>AX47/AW47-1</f>
+        <v/>
+      </c>
+      <c r="BE47" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF47" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK47">
+        <f>BE47/BF47-1</f>
+        <v/>
+      </c>
+      <c r="BL47">
+        <f>BG47/BF47-1</f>
+        <v/>
+      </c>
+      <c r="BN47" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO47" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ47" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR47" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT47">
+        <f>BN47/BO47-1</f>
+        <v/>
+      </c>
+      <c r="BU47">
+        <f>BP47/BO47-1</f>
+        <v/>
+      </c>
+      <c r="BW47" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX47" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ47" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA47" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC47">
+        <f>BW47/BX47-1</f>
+        <v/>
+      </c>
+      <c r="CD47">
+        <f>BY47/BX47-1</f>
+        <v/>
+      </c>
+      <c r="CF47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI47" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ47" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL47">
+        <f>CF47/CG47-1</f>
+        <v/>
+      </c>
+      <c r="CM47">
+        <f>CH47/CG47-1</f>
+        <v/>
+      </c>
+      <c r="CO47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR47" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS47" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU47">
+        <f>CO47/CP47-1</f>
+        <v/>
+      </c>
+      <c r="CV47">
+        <f>CQ47/CP47-1</f>
+        <v/>
+      </c>
+      <c r="CX47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY47" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA47" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB47" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD47">
+        <f>CX47/CY47-1</f>
+        <v/>
+      </c>
+      <c r="DE47">
+        <f>CZ47/CY47-1</f>
+        <v/>
+      </c>
+      <c r="DG47" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH47" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ47" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK47" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM47">
+        <f>DG47/DH47-1</f>
+        <v/>
+      </c>
+      <c r="DN47">
+        <f>DI47/DH47-1</f>
+        <v/>
+      </c>
+      <c r="DP47" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ47" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS47" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT47" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV47">
+        <f>DP47/DQ47-1</f>
+        <v/>
+      </c>
+      <c r="DW47">
+        <f>DR47/DQ47-1</f>
+        <v/>
+      </c>
+      <c r="DY47" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ47" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB47" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE47">
+        <f>DY47/DZ47-1</f>
+        <v/>
+      </c>
+      <c r="EF47">
+        <f>EA47/DZ47-1</f>
+        <v/>
+      </c>
+      <c r="EH47" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI47" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK47" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL47" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN47">
+        <f>EH47/EI47-1</f>
+        <v/>
+      </c>
+      <c r="EO47">
+        <f>EJ47/EI47-1</f>
+        <v/>
+      </c>
+      <c r="EQ47" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER47" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET47" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU47" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW47">
+        <f>EQ47/ER47-1</f>
+        <v/>
+      </c>
+      <c r="EX47">
+        <f>ES47/ER47-1</f>
+        <v/>
+      </c>
+      <c r="EZ47" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA47" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC47" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD47" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF47">
+        <f>EZ47/FA47-1</f>
+        <v/>
+      </c>
+      <c r="FG47">
+        <f>FB47/FA47-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG47"/>
+  <dimension ref="A1:FG48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -21499,6 +21499,445 @@
         <v/>
       </c>
     </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>02 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I48">
+        <f>C48/D48-1</f>
+        <v/>
+      </c>
+      <c r="J48">
+        <f>E48/D48-1</f>
+        <v/>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R48">
+        <f>L48/M48-1</f>
+        <v/>
+      </c>
+      <c r="S48">
+        <f>N48/M48-1</f>
+        <v/>
+      </c>
+      <c r="U48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA48">
+        <f>U48/V48-1</f>
+        <v/>
+      </c>
+      <c r="AB48">
+        <f>W48/V48-1</f>
+        <v/>
+      </c>
+      <c r="AD48" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE48" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <f>AD48/AE48-1</f>
+        <v/>
+      </c>
+      <c r="AK48">
+        <f>AF48/AE48-1</f>
+        <v/>
+      </c>
+      <c r="AM48" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN48" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS48">
+        <f>AM48/AN48-1</f>
+        <v/>
+      </c>
+      <c r="AT48">
+        <f>AO48/AN48-1</f>
+        <v/>
+      </c>
+      <c r="AV48" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW48" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB48">
+        <f>AV48/AW48-1</f>
+        <v/>
+      </c>
+      <c r="BC48">
+        <f>AX48/AW48-1</f>
+        <v/>
+      </c>
+      <c r="BE48" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF48" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI48" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK48">
+        <f>BE48/BF48-1</f>
+        <v/>
+      </c>
+      <c r="BL48">
+        <f>BG48/BF48-1</f>
+        <v/>
+      </c>
+      <c r="BN48" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO48" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ48" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR48" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT48">
+        <f>BN48/BO48-1</f>
+        <v/>
+      </c>
+      <c r="BU48">
+        <f>BP48/BO48-1</f>
+        <v/>
+      </c>
+      <c r="BW48" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX48" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ48" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA48" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC48">
+        <f>BW48/BX48-1</f>
+        <v/>
+      </c>
+      <c r="CD48">
+        <f>BY48/BX48-1</f>
+        <v/>
+      </c>
+      <c r="CF48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI48" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ48" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL48">
+        <f>CF48/CG48-1</f>
+        <v/>
+      </c>
+      <c r="CM48">
+        <f>CH48/CG48-1</f>
+        <v/>
+      </c>
+      <c r="CO48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR48" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS48" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU48">
+        <f>CO48/CP48-1</f>
+        <v/>
+      </c>
+      <c r="CV48">
+        <f>CQ48/CP48-1</f>
+        <v/>
+      </c>
+      <c r="CX48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY48" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA48" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB48" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD48">
+        <f>CX48/CY48-1</f>
+        <v/>
+      </c>
+      <c r="DE48">
+        <f>CZ48/CY48-1</f>
+        <v/>
+      </c>
+      <c r="DG48" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH48" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ48" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK48" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM48">
+        <f>DG48/DH48-1</f>
+        <v/>
+      </c>
+      <c r="DN48">
+        <f>DI48/DH48-1</f>
+        <v/>
+      </c>
+      <c r="DP48" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ48" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS48" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT48" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV48">
+        <f>DP48/DQ48-1</f>
+        <v/>
+      </c>
+      <c r="DW48">
+        <f>DR48/DQ48-1</f>
+        <v/>
+      </c>
+      <c r="DY48" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ48" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB48" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC48" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE48">
+        <f>DY48/DZ48-1</f>
+        <v/>
+      </c>
+      <c r="EF48">
+        <f>EA48/DZ48-1</f>
+        <v/>
+      </c>
+      <c r="EH48" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI48" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK48" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL48" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN48">
+        <f>EH48/EI48-1</f>
+        <v/>
+      </c>
+      <c r="EO48">
+        <f>EJ48/EI48-1</f>
+        <v/>
+      </c>
+      <c r="EQ48" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER48" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET48" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU48" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW48">
+        <f>EQ48/ER48-1</f>
+        <v/>
+      </c>
+      <c r="EX48">
+        <f>ES48/ER48-1</f>
+        <v/>
+      </c>
+      <c r="EZ48" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA48" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC48" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD48" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF48">
+        <f>EZ48/FA48-1</f>
+        <v/>
+      </c>
+      <c r="FG48">
+        <f>FB48/FA48-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG48"/>
+  <dimension ref="A1:FG49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -21938,6 +21938,445 @@
         <v/>
       </c>
     </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>03 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I49">
+        <f>C49/D49-1</f>
+        <v/>
+      </c>
+      <c r="J49">
+        <f>E49/D49-1</f>
+        <v/>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R49">
+        <f>L49/M49-1</f>
+        <v/>
+      </c>
+      <c r="S49">
+        <f>N49/M49-1</f>
+        <v/>
+      </c>
+      <c r="U49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA49">
+        <f>U49/V49-1</f>
+        <v/>
+      </c>
+      <c r="AB49">
+        <f>W49/V49-1</f>
+        <v/>
+      </c>
+      <c r="AD49" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE49" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <f>AD49/AE49-1</f>
+        <v/>
+      </c>
+      <c r="AK49">
+        <f>AF49/AE49-1</f>
+        <v/>
+      </c>
+      <c r="AM49" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN49" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS49">
+        <f>AM49/AN49-1</f>
+        <v/>
+      </c>
+      <c r="AT49">
+        <f>AO49/AN49-1</f>
+        <v/>
+      </c>
+      <c r="AV49" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW49" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB49">
+        <f>AV49/AW49-1</f>
+        <v/>
+      </c>
+      <c r="BC49">
+        <f>AX49/AW49-1</f>
+        <v/>
+      </c>
+      <c r="BE49" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF49" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI49" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK49">
+        <f>BE49/BF49-1</f>
+        <v/>
+      </c>
+      <c r="BL49">
+        <f>BG49/BF49-1</f>
+        <v/>
+      </c>
+      <c r="BN49" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO49" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ49" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR49" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT49">
+        <f>BN49/BO49-1</f>
+        <v/>
+      </c>
+      <c r="BU49">
+        <f>BP49/BO49-1</f>
+        <v/>
+      </c>
+      <c r="BW49" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX49" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ49" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA49" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC49">
+        <f>BW49/BX49-1</f>
+        <v/>
+      </c>
+      <c r="CD49">
+        <f>BY49/BX49-1</f>
+        <v/>
+      </c>
+      <c r="CF49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI49" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ49" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL49">
+        <f>CF49/CG49-1</f>
+        <v/>
+      </c>
+      <c r="CM49">
+        <f>CH49/CG49-1</f>
+        <v/>
+      </c>
+      <c r="CO49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR49" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS49" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU49">
+        <f>CO49/CP49-1</f>
+        <v/>
+      </c>
+      <c r="CV49">
+        <f>CQ49/CP49-1</f>
+        <v/>
+      </c>
+      <c r="CX49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY49" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA49" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB49" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD49">
+        <f>CX49/CY49-1</f>
+        <v/>
+      </c>
+      <c r="DE49">
+        <f>CZ49/CY49-1</f>
+        <v/>
+      </c>
+      <c r="DG49" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH49" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ49" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK49" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM49">
+        <f>DG49/DH49-1</f>
+        <v/>
+      </c>
+      <c r="DN49">
+        <f>DI49/DH49-1</f>
+        <v/>
+      </c>
+      <c r="DP49" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ49" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS49" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT49" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV49">
+        <f>DP49/DQ49-1</f>
+        <v/>
+      </c>
+      <c r="DW49">
+        <f>DR49/DQ49-1</f>
+        <v/>
+      </c>
+      <c r="DY49" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ49" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB49" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC49" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE49">
+        <f>DY49/DZ49-1</f>
+        <v/>
+      </c>
+      <c r="EF49">
+        <f>EA49/DZ49-1</f>
+        <v/>
+      </c>
+      <c r="EH49" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI49" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK49" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL49" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN49">
+        <f>EH49/EI49-1</f>
+        <v/>
+      </c>
+      <c r="EO49">
+        <f>EJ49/EI49-1</f>
+        <v/>
+      </c>
+      <c r="EQ49" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER49" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET49" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU49" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW49">
+        <f>EQ49/ER49-1</f>
+        <v/>
+      </c>
+      <c r="EX49">
+        <f>ES49/ER49-1</f>
+        <v/>
+      </c>
+      <c r="EZ49" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA49" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC49" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD49" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF49">
+        <f>EZ49/FA49-1</f>
+        <v/>
+      </c>
+      <c r="FG49">
+        <f>FB49/FA49-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG49"/>
+  <dimension ref="A1:FG50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -22377,6 +22377,445 @@
         <v/>
       </c>
     </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>03 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I50">
+        <f>C50/D50-1</f>
+        <v/>
+      </c>
+      <c r="J50">
+        <f>E50/D50-1</f>
+        <v/>
+      </c>
+      <c r="L50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R50">
+        <f>L50/M50-1</f>
+        <v/>
+      </c>
+      <c r="S50">
+        <f>N50/M50-1</f>
+        <v/>
+      </c>
+      <c r="U50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA50">
+        <f>U50/V50-1</f>
+        <v/>
+      </c>
+      <c r="AB50">
+        <f>W50/V50-1</f>
+        <v/>
+      </c>
+      <c r="AD50" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE50" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <f>AD50/AE50-1</f>
+        <v/>
+      </c>
+      <c r="AK50">
+        <f>AF50/AE50-1</f>
+        <v/>
+      </c>
+      <c r="AM50" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN50" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS50">
+        <f>AM50/AN50-1</f>
+        <v/>
+      </c>
+      <c r="AT50">
+        <f>AO50/AN50-1</f>
+        <v/>
+      </c>
+      <c r="AV50" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW50" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB50">
+        <f>AV50/AW50-1</f>
+        <v/>
+      </c>
+      <c r="BC50">
+        <f>AX50/AW50-1</f>
+        <v/>
+      </c>
+      <c r="BE50" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF50" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI50" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK50">
+        <f>BE50/BF50-1</f>
+        <v/>
+      </c>
+      <c r="BL50">
+        <f>BG50/BF50-1</f>
+        <v/>
+      </c>
+      <c r="BN50" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO50" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ50" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR50" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT50">
+        <f>BN50/BO50-1</f>
+        <v/>
+      </c>
+      <c r="BU50">
+        <f>BP50/BO50-1</f>
+        <v/>
+      </c>
+      <c r="BW50" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX50" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ50" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA50" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC50">
+        <f>BW50/BX50-1</f>
+        <v/>
+      </c>
+      <c r="CD50">
+        <f>BY50/BX50-1</f>
+        <v/>
+      </c>
+      <c r="CF50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI50" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ50" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL50">
+        <f>CF50/CG50-1</f>
+        <v/>
+      </c>
+      <c r="CM50">
+        <f>CH50/CG50-1</f>
+        <v/>
+      </c>
+      <c r="CO50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR50" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS50" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU50">
+        <f>CO50/CP50-1</f>
+        <v/>
+      </c>
+      <c r="CV50">
+        <f>CQ50/CP50-1</f>
+        <v/>
+      </c>
+      <c r="CX50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY50" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA50" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB50" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD50">
+        <f>CX50/CY50-1</f>
+        <v/>
+      </c>
+      <c r="DE50">
+        <f>CZ50/CY50-1</f>
+        <v/>
+      </c>
+      <c r="DG50" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH50" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ50" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK50" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM50">
+        <f>DG50/DH50-1</f>
+        <v/>
+      </c>
+      <c r="DN50">
+        <f>DI50/DH50-1</f>
+        <v/>
+      </c>
+      <c r="DP50" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ50" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS50" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT50" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV50">
+        <f>DP50/DQ50-1</f>
+        <v/>
+      </c>
+      <c r="DW50">
+        <f>DR50/DQ50-1</f>
+        <v/>
+      </c>
+      <c r="DY50" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ50" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB50" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC50" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE50">
+        <f>DY50/DZ50-1</f>
+        <v/>
+      </c>
+      <c r="EF50">
+        <f>EA50/DZ50-1</f>
+        <v/>
+      </c>
+      <c r="EH50" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI50" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK50" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL50" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN50">
+        <f>EH50/EI50-1</f>
+        <v/>
+      </c>
+      <c r="EO50">
+        <f>EJ50/EI50-1</f>
+        <v/>
+      </c>
+      <c r="EQ50" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER50" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET50" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU50" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW50">
+        <f>EQ50/ER50-1</f>
+        <v/>
+      </c>
+      <c r="EX50">
+        <f>ES50/ER50-1</f>
+        <v/>
+      </c>
+      <c r="EZ50" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA50" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC50" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD50" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF50">
+        <f>EZ50/FA50-1</f>
+        <v/>
+      </c>
+      <c r="FG50">
+        <f>FB50/FA50-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG50"/>
+  <dimension ref="A1:FG51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -22816,6 +22816,445 @@
         <v/>
       </c>
     </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>03 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I51">
+        <f>C51/D51-1</f>
+        <v/>
+      </c>
+      <c r="J51">
+        <f>E51/D51-1</f>
+        <v/>
+      </c>
+      <c r="L51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R51">
+        <f>L51/M51-1</f>
+        <v/>
+      </c>
+      <c r="S51">
+        <f>N51/M51-1</f>
+        <v/>
+      </c>
+      <c r="U51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA51">
+        <f>U51/V51-1</f>
+        <v/>
+      </c>
+      <c r="AB51">
+        <f>W51/V51-1</f>
+        <v/>
+      </c>
+      <c r="AD51" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE51" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <f>AD51/AE51-1</f>
+        <v/>
+      </c>
+      <c r="AK51">
+        <f>AF51/AE51-1</f>
+        <v/>
+      </c>
+      <c r="AM51" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN51" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS51">
+        <f>AM51/AN51-1</f>
+        <v/>
+      </c>
+      <c r="AT51">
+        <f>AO51/AN51-1</f>
+        <v/>
+      </c>
+      <c r="AV51" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW51" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB51">
+        <f>AV51/AW51-1</f>
+        <v/>
+      </c>
+      <c r="BC51">
+        <f>AX51/AW51-1</f>
+        <v/>
+      </c>
+      <c r="BE51" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF51" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH51" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI51" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK51">
+        <f>BE51/BF51-1</f>
+        <v/>
+      </c>
+      <c r="BL51">
+        <f>BG51/BF51-1</f>
+        <v/>
+      </c>
+      <c r="BN51" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO51" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ51" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR51" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT51">
+        <f>BN51/BO51-1</f>
+        <v/>
+      </c>
+      <c r="BU51">
+        <f>BP51/BO51-1</f>
+        <v/>
+      </c>
+      <c r="BW51" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX51" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ51" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA51" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC51">
+        <f>BW51/BX51-1</f>
+        <v/>
+      </c>
+      <c r="CD51">
+        <f>BY51/BX51-1</f>
+        <v/>
+      </c>
+      <c r="CF51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI51" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ51" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL51">
+        <f>CF51/CG51-1</f>
+        <v/>
+      </c>
+      <c r="CM51">
+        <f>CH51/CG51-1</f>
+        <v/>
+      </c>
+      <c r="CO51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR51" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS51" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU51">
+        <f>CO51/CP51-1</f>
+        <v/>
+      </c>
+      <c r="CV51">
+        <f>CQ51/CP51-1</f>
+        <v/>
+      </c>
+      <c r="CX51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY51" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA51" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB51" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD51">
+        <f>CX51/CY51-1</f>
+        <v/>
+      </c>
+      <c r="DE51">
+        <f>CZ51/CY51-1</f>
+        <v/>
+      </c>
+      <c r="DG51" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH51" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ51" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK51" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM51">
+        <f>DG51/DH51-1</f>
+        <v/>
+      </c>
+      <c r="DN51">
+        <f>DI51/DH51-1</f>
+        <v/>
+      </c>
+      <c r="DP51" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ51" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS51" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT51" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV51">
+        <f>DP51/DQ51-1</f>
+        <v/>
+      </c>
+      <c r="DW51">
+        <f>DR51/DQ51-1</f>
+        <v/>
+      </c>
+      <c r="DY51" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ51" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB51" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC51" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE51">
+        <f>DY51/DZ51-1</f>
+        <v/>
+      </c>
+      <c r="EF51">
+        <f>EA51/DZ51-1</f>
+        <v/>
+      </c>
+      <c r="EH51" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI51" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK51" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL51" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN51">
+        <f>EH51/EI51-1</f>
+        <v/>
+      </c>
+      <c r="EO51">
+        <f>EJ51/EI51-1</f>
+        <v/>
+      </c>
+      <c r="EQ51" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER51" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET51" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU51" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW51">
+        <f>EQ51/ER51-1</f>
+        <v/>
+      </c>
+      <c r="EX51">
+        <f>ES51/ER51-1</f>
+        <v/>
+      </c>
+      <c r="EZ51" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA51" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC51" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD51" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF51">
+        <f>EZ51/FA51-1</f>
+        <v/>
+      </c>
+      <c r="FG51">
+        <f>FB51/FA51-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG51"/>
+  <dimension ref="A1:FG52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -23255,6 +23255,445 @@
         <v/>
       </c>
     </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>03 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I52">
+        <f>C52/D52-1</f>
+        <v/>
+      </c>
+      <c r="J52">
+        <f>E52/D52-1</f>
+        <v/>
+      </c>
+      <c r="L52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R52">
+        <f>L52/M52-1</f>
+        <v/>
+      </c>
+      <c r="S52">
+        <f>N52/M52-1</f>
+        <v/>
+      </c>
+      <c r="U52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA52">
+        <f>U52/V52-1</f>
+        <v/>
+      </c>
+      <c r="AB52">
+        <f>W52/V52-1</f>
+        <v/>
+      </c>
+      <c r="AD52" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE52" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <f>AD52/AE52-1</f>
+        <v/>
+      </c>
+      <c r="AK52">
+        <f>AF52/AE52-1</f>
+        <v/>
+      </c>
+      <c r="AM52" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN52" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS52">
+        <f>AM52/AN52-1</f>
+        <v/>
+      </c>
+      <c r="AT52">
+        <f>AO52/AN52-1</f>
+        <v/>
+      </c>
+      <c r="AV52" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW52" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB52">
+        <f>AV52/AW52-1</f>
+        <v/>
+      </c>
+      <c r="BC52">
+        <f>AX52/AW52-1</f>
+        <v/>
+      </c>
+      <c r="BE52" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF52" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH52" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI52" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK52">
+        <f>BE52/BF52-1</f>
+        <v/>
+      </c>
+      <c r="BL52">
+        <f>BG52/BF52-1</f>
+        <v/>
+      </c>
+      <c r="BN52" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO52" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ52" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR52" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT52">
+        <f>BN52/BO52-1</f>
+        <v/>
+      </c>
+      <c r="BU52">
+        <f>BP52/BO52-1</f>
+        <v/>
+      </c>
+      <c r="BW52" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX52" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ52" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA52" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC52">
+        <f>BW52/BX52-1</f>
+        <v/>
+      </c>
+      <c r="CD52">
+        <f>BY52/BX52-1</f>
+        <v/>
+      </c>
+      <c r="CF52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI52" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ52" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL52">
+        <f>CF52/CG52-1</f>
+        <v/>
+      </c>
+      <c r="CM52">
+        <f>CH52/CG52-1</f>
+        <v/>
+      </c>
+      <c r="CO52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR52" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS52" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU52">
+        <f>CO52/CP52-1</f>
+        <v/>
+      </c>
+      <c r="CV52">
+        <f>CQ52/CP52-1</f>
+        <v/>
+      </c>
+      <c r="CX52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY52" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA52" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB52" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD52">
+        <f>CX52/CY52-1</f>
+        <v/>
+      </c>
+      <c r="DE52">
+        <f>CZ52/CY52-1</f>
+        <v/>
+      </c>
+      <c r="DG52" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH52" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ52" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK52" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM52">
+        <f>DG52/DH52-1</f>
+        <v/>
+      </c>
+      <c r="DN52">
+        <f>DI52/DH52-1</f>
+        <v/>
+      </c>
+      <c r="DP52" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ52" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS52" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT52" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV52">
+        <f>DP52/DQ52-1</f>
+        <v/>
+      </c>
+      <c r="DW52">
+        <f>DR52/DQ52-1</f>
+        <v/>
+      </c>
+      <c r="DY52" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ52" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB52" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC52" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE52">
+        <f>DY52/DZ52-1</f>
+        <v/>
+      </c>
+      <c r="EF52">
+        <f>EA52/DZ52-1</f>
+        <v/>
+      </c>
+      <c r="EH52" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI52" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK52" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL52" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN52">
+        <f>EH52/EI52-1</f>
+        <v/>
+      </c>
+      <c r="EO52">
+        <f>EJ52/EI52-1</f>
+        <v/>
+      </c>
+      <c r="EQ52" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER52" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET52" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU52" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW52">
+        <f>EQ52/ER52-1</f>
+        <v/>
+      </c>
+      <c r="EX52">
+        <f>ES52/ER52-1</f>
+        <v/>
+      </c>
+      <c r="EZ52" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA52" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC52" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD52" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF52">
+        <f>EZ52/FA52-1</f>
+        <v/>
+      </c>
+      <c r="FG52">
+        <f>FB52/FA52-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG52"/>
+  <dimension ref="A1:FG53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -23694,6 +23694,445 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>04 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I53">
+        <f>C53/D53-1</f>
+        <v/>
+      </c>
+      <c r="J53">
+        <f>E53/D53-1</f>
+        <v/>
+      </c>
+      <c r="L53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R53">
+        <f>L53/M53-1</f>
+        <v/>
+      </c>
+      <c r="S53">
+        <f>N53/M53-1</f>
+        <v/>
+      </c>
+      <c r="U53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA53">
+        <f>U53/V53-1</f>
+        <v/>
+      </c>
+      <c r="AB53">
+        <f>W53/V53-1</f>
+        <v/>
+      </c>
+      <c r="AD53" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE53" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <f>AD53/AE53-1</f>
+        <v/>
+      </c>
+      <c r="AK53">
+        <f>AF53/AE53-1</f>
+        <v/>
+      </c>
+      <c r="AM53" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN53" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS53">
+        <f>AM53/AN53-1</f>
+        <v/>
+      </c>
+      <c r="AT53">
+        <f>AO53/AN53-1</f>
+        <v/>
+      </c>
+      <c r="AV53" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW53" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB53">
+        <f>AV53/AW53-1</f>
+        <v/>
+      </c>
+      <c r="BC53">
+        <f>AX53/AW53-1</f>
+        <v/>
+      </c>
+      <c r="BE53" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF53" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI53" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK53">
+        <f>BE53/BF53-1</f>
+        <v/>
+      </c>
+      <c r="BL53">
+        <f>BG53/BF53-1</f>
+        <v/>
+      </c>
+      <c r="BN53" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO53" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ53" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR53" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT53">
+        <f>BN53/BO53-1</f>
+        <v/>
+      </c>
+      <c r="BU53">
+        <f>BP53/BO53-1</f>
+        <v/>
+      </c>
+      <c r="BW53" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX53" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ53" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA53" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC53">
+        <f>BW53/BX53-1</f>
+        <v/>
+      </c>
+      <c r="CD53">
+        <f>BY53/BX53-1</f>
+        <v/>
+      </c>
+      <c r="CF53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI53" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ53" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL53">
+        <f>CF53/CG53-1</f>
+        <v/>
+      </c>
+      <c r="CM53">
+        <f>CH53/CG53-1</f>
+        <v/>
+      </c>
+      <c r="CO53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR53" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS53" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU53">
+        <f>CO53/CP53-1</f>
+        <v/>
+      </c>
+      <c r="CV53">
+        <f>CQ53/CP53-1</f>
+        <v/>
+      </c>
+      <c r="CX53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY53" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA53" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB53" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD53">
+        <f>CX53/CY53-1</f>
+        <v/>
+      </c>
+      <c r="DE53">
+        <f>CZ53/CY53-1</f>
+        <v/>
+      </c>
+      <c r="DG53" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH53" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ53" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK53" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM53">
+        <f>DG53/DH53-1</f>
+        <v/>
+      </c>
+      <c r="DN53">
+        <f>DI53/DH53-1</f>
+        <v/>
+      </c>
+      <c r="DP53" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ53" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS53" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT53" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV53">
+        <f>DP53/DQ53-1</f>
+        <v/>
+      </c>
+      <c r="DW53">
+        <f>DR53/DQ53-1</f>
+        <v/>
+      </c>
+      <c r="DY53" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ53" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB53" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE53">
+        <f>DY53/DZ53-1</f>
+        <v/>
+      </c>
+      <c r="EF53">
+        <f>EA53/DZ53-1</f>
+        <v/>
+      </c>
+      <c r="EH53" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI53" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK53" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL53" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN53">
+        <f>EH53/EI53-1</f>
+        <v/>
+      </c>
+      <c r="EO53">
+        <f>EJ53/EI53-1</f>
+        <v/>
+      </c>
+      <c r="EQ53" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER53" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET53" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU53" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW53">
+        <f>EQ53/ER53-1</f>
+        <v/>
+      </c>
+      <c r="EX53">
+        <f>ES53/ER53-1</f>
+        <v/>
+      </c>
+      <c r="EZ53" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA53" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC53" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD53" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF53">
+        <f>EZ53/FA53-1</f>
+        <v/>
+      </c>
+      <c r="FG53">
+        <f>FB53/FA53-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG53"/>
+  <dimension ref="A1:FG54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -24133,6 +24133,449 @@
         <v/>
       </c>
     </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>04 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I54">
+        <f>C54/D54-1</f>
+        <v/>
+      </c>
+      <c r="J54">
+        <f>E54/D54-1</f>
+        <v/>
+      </c>
+      <c r="L54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R54">
+        <f>L54/M54-1</f>
+        <v/>
+      </c>
+      <c r="S54">
+        <f>N54/M54-1</f>
+        <v/>
+      </c>
+      <c r="U54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA54">
+        <f>U54/V54-1</f>
+        <v/>
+      </c>
+      <c r="AB54">
+        <f>W54/V54-1</f>
+        <v/>
+      </c>
+      <c r="AD54" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE54" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <f>AD54/AE54-1</f>
+        <v/>
+      </c>
+      <c r="AK54">
+        <f>AF54/AE54-1</f>
+        <v/>
+      </c>
+      <c r="AM54" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN54" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS54">
+        <f>AM54/AN54-1</f>
+        <v/>
+      </c>
+      <c r="AT54">
+        <f>AO54/AN54-1</f>
+        <v/>
+      </c>
+      <c r="AV54" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW54" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB54">
+        <f>AV54/AW54-1</f>
+        <v/>
+      </c>
+      <c r="BC54">
+        <f>AX54/AW54-1</f>
+        <v/>
+      </c>
+      <c r="BE54" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF54" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH54" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI54" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK54">
+        <f>BE54/BF54-1</f>
+        <v/>
+      </c>
+      <c r="BL54">
+        <f>BG54/BF54-1</f>
+        <v/>
+      </c>
+      <c r="BN54" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO54" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ54" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR54" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT54">
+        <f>BN54/BO54-1</f>
+        <v/>
+      </c>
+      <c r="BU54">
+        <f>BP54/BO54-1</f>
+        <v/>
+      </c>
+      <c r="BW54" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX54" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ54" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA54" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC54">
+        <f>BW54/BX54-1</f>
+        <v/>
+      </c>
+      <c r="CD54">
+        <f>BY54/BX54-1</f>
+        <v/>
+      </c>
+      <c r="CF54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI54" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ54" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL54">
+        <f>CF54/CG54-1</f>
+        <v/>
+      </c>
+      <c r="CM54">
+        <f>CH54/CG54-1</f>
+        <v/>
+      </c>
+      <c r="CO54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR54" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS54" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU54">
+        <f>CO54/CP54-1</f>
+        <v/>
+      </c>
+      <c r="CV54">
+        <f>CQ54/CP54-1</f>
+        <v/>
+      </c>
+      <c r="CX54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY54" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA54" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB54" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD54">
+        <f>CX54/CY54-1</f>
+        <v/>
+      </c>
+      <c r="DE54">
+        <f>CZ54/CY54-1</f>
+        <v/>
+      </c>
+      <c r="DG54" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH54" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ54" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK54" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM54">
+        <f>DG54/DH54-1</f>
+        <v/>
+      </c>
+      <c r="DN54">
+        <f>DI54/DH54-1</f>
+        <v/>
+      </c>
+      <c r="DP54" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ54" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS54" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT54" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV54">
+        <f>DP54/DQ54-1</f>
+        <v/>
+      </c>
+      <c r="DW54">
+        <f>DR54/DQ54-1</f>
+        <v/>
+      </c>
+      <c r="DY54" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ54" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB54" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE54">
+        <f>DY54/DZ54-1</f>
+        <v/>
+      </c>
+      <c r="EF54">
+        <f>EA54/DZ54-1</f>
+        <v/>
+      </c>
+      <c r="EH54" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI54" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EK54" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL54" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EN54">
+        <f>EH54/EI54-1</f>
+        <v/>
+      </c>
+      <c r="EO54">
+        <f>EJ54/EI54-1</f>
+        <v/>
+      </c>
+      <c r="EQ54" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER54" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ET54" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU54" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EW54">
+        <f>EQ54/ER54-1</f>
+        <v/>
+      </c>
+      <c r="EX54">
+        <f>ES54/ER54-1</f>
+        <v/>
+      </c>
+      <c r="EZ54" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA54" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC54" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD54" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF54">
+        <f>EZ54/FA54-1</f>
+        <v/>
+      </c>
+      <c r="FG54">
+        <f>FB54/FA54-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG54"/>
+  <dimension ref="A1:FG55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -24576,6 +24576,445 @@
         <v/>
       </c>
     </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>04 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I55">
+        <f>C55/D55-1</f>
+        <v/>
+      </c>
+      <c r="J55">
+        <f>E55/D55-1</f>
+        <v/>
+      </c>
+      <c r="L55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R55">
+        <f>L55/M55-1</f>
+        <v/>
+      </c>
+      <c r="S55">
+        <f>N55/M55-1</f>
+        <v/>
+      </c>
+      <c r="U55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA55">
+        <f>U55/V55-1</f>
+        <v/>
+      </c>
+      <c r="AB55">
+        <f>W55/V55-1</f>
+        <v/>
+      </c>
+      <c r="AD55" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE55" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <f>AD55/AE55-1</f>
+        <v/>
+      </c>
+      <c r="AK55">
+        <f>AF55/AE55-1</f>
+        <v/>
+      </c>
+      <c r="AM55" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN55" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS55">
+        <f>AM55/AN55-1</f>
+        <v/>
+      </c>
+      <c r="AT55">
+        <f>AO55/AN55-1</f>
+        <v/>
+      </c>
+      <c r="AV55" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW55" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB55">
+        <f>AV55/AW55-1</f>
+        <v/>
+      </c>
+      <c r="BC55">
+        <f>AX55/AW55-1</f>
+        <v/>
+      </c>
+      <c r="BE55" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF55" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI55" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK55">
+        <f>BE55/BF55-1</f>
+        <v/>
+      </c>
+      <c r="BL55">
+        <f>BG55/BF55-1</f>
+        <v/>
+      </c>
+      <c r="BN55" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO55" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ55" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR55" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT55">
+        <f>BN55/BO55-1</f>
+        <v/>
+      </c>
+      <c r="BU55">
+        <f>BP55/BO55-1</f>
+        <v/>
+      </c>
+      <c r="BW55" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX55" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ55" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA55" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC55">
+        <f>BW55/BX55-1</f>
+        <v/>
+      </c>
+      <c r="CD55">
+        <f>BY55/BX55-1</f>
+        <v/>
+      </c>
+      <c r="CF55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI55" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ55" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL55">
+        <f>CF55/CG55-1</f>
+        <v/>
+      </c>
+      <c r="CM55">
+        <f>CH55/CG55-1</f>
+        <v/>
+      </c>
+      <c r="CO55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR55" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS55" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU55">
+        <f>CO55/CP55-1</f>
+        <v/>
+      </c>
+      <c r="CV55">
+        <f>CQ55/CP55-1</f>
+        <v/>
+      </c>
+      <c r="CX55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY55" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA55" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB55" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD55">
+        <f>CX55/CY55-1</f>
+        <v/>
+      </c>
+      <c r="DE55">
+        <f>CZ55/CY55-1</f>
+        <v/>
+      </c>
+      <c r="DG55" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH55" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ55" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK55" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM55">
+        <f>DG55/DH55-1</f>
+        <v/>
+      </c>
+      <c r="DN55">
+        <f>DI55/DH55-1</f>
+        <v/>
+      </c>
+      <c r="DP55" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ55" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS55" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT55" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV55">
+        <f>DP55/DQ55-1</f>
+        <v/>
+      </c>
+      <c r="DW55">
+        <f>DR55/DQ55-1</f>
+        <v/>
+      </c>
+      <c r="DY55" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ55" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB55" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC55" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE55">
+        <f>DY55/DZ55-1</f>
+        <v/>
+      </c>
+      <c r="EF55">
+        <f>EA55/DZ55-1</f>
+        <v/>
+      </c>
+      <c r="EH55" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI55" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK55" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL55" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN55">
+        <f>EH55/EI55-1</f>
+        <v/>
+      </c>
+      <c r="EO55">
+        <f>EJ55/EI55-1</f>
+        <v/>
+      </c>
+      <c r="EQ55" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER55" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET55" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU55" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW55">
+        <f>EQ55/ER55-1</f>
+        <v/>
+      </c>
+      <c r="EX55">
+        <f>ES55/ER55-1</f>
+        <v/>
+      </c>
+      <c r="EZ55" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA55" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC55" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD55" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF55">
+        <f>EZ55/FA55-1</f>
+        <v/>
+      </c>
+      <c r="FG55">
+        <f>FB55/FA55-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG55"/>
+  <dimension ref="A1:FG56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -25015,6 +25015,447 @@
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>04 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I56">
+        <f>C56/D56-1</f>
+        <v/>
+      </c>
+      <c r="J56">
+        <f>E56/D56-1</f>
+        <v/>
+      </c>
+      <c r="L56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R56">
+        <f>L56/M56-1</f>
+        <v/>
+      </c>
+      <c r="S56">
+        <f>N56/M56-1</f>
+        <v/>
+      </c>
+      <c r="U56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA56">
+        <f>U56/V56-1</f>
+        <v/>
+      </c>
+      <c r="AB56">
+        <f>W56/V56-1</f>
+        <v/>
+      </c>
+      <c r="AD56" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE56" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <f>AD56/AE56-1</f>
+        <v/>
+      </c>
+      <c r="AK56">
+        <f>AF56/AE56-1</f>
+        <v/>
+      </c>
+      <c r="AM56" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN56" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS56">
+        <f>AM56/AN56-1</f>
+        <v/>
+      </c>
+      <c r="AT56">
+        <f>AO56/AN56-1</f>
+        <v/>
+      </c>
+      <c r="AV56" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BB56">
+        <f>AV56/AW56-1</f>
+        <v/>
+      </c>
+      <c r="BC56">
+        <f>AX56/AW56-1</f>
+        <v/>
+      </c>
+      <c r="BE56" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF56" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH56" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI56" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK56">
+        <f>BE56/BF56-1</f>
+        <v/>
+      </c>
+      <c r="BL56">
+        <f>BG56/BF56-1</f>
+        <v/>
+      </c>
+      <c r="BN56" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO56" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ56" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR56" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT56">
+        <f>BN56/BO56-1</f>
+        <v/>
+      </c>
+      <c r="BU56">
+        <f>BP56/BO56-1</f>
+        <v/>
+      </c>
+      <c r="BW56" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX56" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ56" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA56" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC56">
+        <f>BW56/BX56-1</f>
+        <v/>
+      </c>
+      <c r="CD56">
+        <f>BY56/BX56-1</f>
+        <v/>
+      </c>
+      <c r="CF56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI56" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ56" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL56">
+        <f>CF56/CG56-1</f>
+        <v/>
+      </c>
+      <c r="CM56">
+        <f>CH56/CG56-1</f>
+        <v/>
+      </c>
+      <c r="CO56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR56" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS56" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU56">
+        <f>CO56/CP56-1</f>
+        <v/>
+      </c>
+      <c r="CV56">
+        <f>CQ56/CP56-1</f>
+        <v/>
+      </c>
+      <c r="CX56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY56" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA56" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB56" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD56">
+        <f>CX56/CY56-1</f>
+        <v/>
+      </c>
+      <c r="DE56">
+        <f>CZ56/CY56-1</f>
+        <v/>
+      </c>
+      <c r="DG56" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH56" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ56" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK56" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM56">
+        <f>DG56/DH56-1</f>
+        <v/>
+      </c>
+      <c r="DN56">
+        <f>DI56/DH56-1</f>
+        <v/>
+      </c>
+      <c r="DP56" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ56" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS56" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT56" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV56">
+        <f>DP56/DQ56-1</f>
+        <v/>
+      </c>
+      <c r="DW56">
+        <f>DR56/DQ56-1</f>
+        <v/>
+      </c>
+      <c r="DY56" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ56" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB56" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC56" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE56">
+        <f>DY56/DZ56-1</f>
+        <v/>
+      </c>
+      <c r="EF56">
+        <f>EA56/DZ56-1</f>
+        <v/>
+      </c>
+      <c r="EH56" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI56" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK56" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL56" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN56">
+        <f>EH56/EI56-1</f>
+        <v/>
+      </c>
+      <c r="EO56">
+        <f>EJ56/EI56-1</f>
+        <v/>
+      </c>
+      <c r="EQ56" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER56" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET56" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU56" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW56">
+        <f>EQ56/ER56-1</f>
+        <v/>
+      </c>
+      <c r="EX56">
+        <f>ES56/ER56-1</f>
+        <v/>
+      </c>
+      <c r="EZ56" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA56" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC56" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD56" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF56">
+        <f>EZ56/FA56-1</f>
+        <v/>
+      </c>
+      <c r="FG56">
+        <f>FB56/FA56-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG56"/>
+  <dimension ref="A1:FG57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -25456,6 +25456,445 @@
         <v/>
       </c>
     </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>05 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I57">
+        <f>C57/D57-1</f>
+        <v/>
+      </c>
+      <c r="J57">
+        <f>E57/D57-1</f>
+        <v/>
+      </c>
+      <c r="L57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R57">
+        <f>L57/M57-1</f>
+        <v/>
+      </c>
+      <c r="S57">
+        <f>N57/M57-1</f>
+        <v/>
+      </c>
+      <c r="U57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA57">
+        <f>U57/V57-1</f>
+        <v/>
+      </c>
+      <c r="AB57">
+        <f>W57/V57-1</f>
+        <v/>
+      </c>
+      <c r="AD57" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE57" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <f>AD57/AE57-1</f>
+        <v/>
+      </c>
+      <c r="AK57">
+        <f>AF57/AE57-1</f>
+        <v/>
+      </c>
+      <c r="AM57" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN57" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS57">
+        <f>AM57/AN57-1</f>
+        <v/>
+      </c>
+      <c r="AT57">
+        <f>AO57/AN57-1</f>
+        <v/>
+      </c>
+      <c r="AV57" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW57" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB57">
+        <f>AV57/AW57-1</f>
+        <v/>
+      </c>
+      <c r="BC57">
+        <f>AX57/AW57-1</f>
+        <v/>
+      </c>
+      <c r="BE57" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF57" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH57" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI57" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK57">
+        <f>BE57/BF57-1</f>
+        <v/>
+      </c>
+      <c r="BL57">
+        <f>BG57/BF57-1</f>
+        <v/>
+      </c>
+      <c r="BN57" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO57" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ57" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR57" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT57">
+        <f>BN57/BO57-1</f>
+        <v/>
+      </c>
+      <c r="BU57">
+        <f>BP57/BO57-1</f>
+        <v/>
+      </c>
+      <c r="BW57" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX57" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ57" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA57" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC57">
+        <f>BW57/BX57-1</f>
+        <v/>
+      </c>
+      <c r="CD57">
+        <f>BY57/BX57-1</f>
+        <v/>
+      </c>
+      <c r="CF57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI57" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ57" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL57">
+        <f>CF57/CG57-1</f>
+        <v/>
+      </c>
+      <c r="CM57">
+        <f>CH57/CG57-1</f>
+        <v/>
+      </c>
+      <c r="CO57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS57" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU57">
+        <f>CO57/CP57-1</f>
+        <v/>
+      </c>
+      <c r="CV57">
+        <f>CQ57/CP57-1</f>
+        <v/>
+      </c>
+      <c r="CX57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY57" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA57" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB57" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD57">
+        <f>CX57/CY57-1</f>
+        <v/>
+      </c>
+      <c r="DE57">
+        <f>CZ57/CY57-1</f>
+        <v/>
+      </c>
+      <c r="DG57" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH57" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ57" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK57" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM57">
+        <f>DG57/DH57-1</f>
+        <v/>
+      </c>
+      <c r="DN57">
+        <f>DI57/DH57-1</f>
+        <v/>
+      </c>
+      <c r="DP57" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ57" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS57" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT57" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV57">
+        <f>DP57/DQ57-1</f>
+        <v/>
+      </c>
+      <c r="DW57">
+        <f>DR57/DQ57-1</f>
+        <v/>
+      </c>
+      <c r="DY57" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ57" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB57" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC57" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE57">
+        <f>DY57/DZ57-1</f>
+        <v/>
+      </c>
+      <c r="EF57">
+        <f>EA57/DZ57-1</f>
+        <v/>
+      </c>
+      <c r="EH57" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI57" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK57" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL57" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN57">
+        <f>EH57/EI57-1</f>
+        <v/>
+      </c>
+      <c r="EO57">
+        <f>EJ57/EI57-1</f>
+        <v/>
+      </c>
+      <c r="EQ57" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER57" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET57" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU57" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW57">
+        <f>EQ57/ER57-1</f>
+        <v/>
+      </c>
+      <c r="EX57">
+        <f>ES57/ER57-1</f>
+        <v/>
+      </c>
+      <c r="EZ57" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA57" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC57" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD57" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF57">
+        <f>EZ57/FA57-1</f>
+        <v/>
+      </c>
+      <c r="FG57">
+        <f>FB57/FA57-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG57"/>
+  <dimension ref="A1:FG58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -25895,6 +25895,445 @@
         <v/>
       </c>
     </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>05 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I58">
+        <f>C58/D58-1</f>
+        <v/>
+      </c>
+      <c r="J58">
+        <f>E58/D58-1</f>
+        <v/>
+      </c>
+      <c r="L58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R58">
+        <f>L58/M58-1</f>
+        <v/>
+      </c>
+      <c r="S58">
+        <f>N58/M58-1</f>
+        <v/>
+      </c>
+      <c r="U58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA58">
+        <f>U58/V58-1</f>
+        <v/>
+      </c>
+      <c r="AB58">
+        <f>W58/V58-1</f>
+        <v/>
+      </c>
+      <c r="AD58" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE58" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <f>AD58/AE58-1</f>
+        <v/>
+      </c>
+      <c r="AK58">
+        <f>AF58/AE58-1</f>
+        <v/>
+      </c>
+      <c r="AM58" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN58" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS58">
+        <f>AM58/AN58-1</f>
+        <v/>
+      </c>
+      <c r="AT58">
+        <f>AO58/AN58-1</f>
+        <v/>
+      </c>
+      <c r="AV58" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW58" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB58">
+        <f>AV58/AW58-1</f>
+        <v/>
+      </c>
+      <c r="BC58">
+        <f>AX58/AW58-1</f>
+        <v/>
+      </c>
+      <c r="BE58" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF58" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH58" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI58" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK58">
+        <f>BE58/BF58-1</f>
+        <v/>
+      </c>
+      <c r="BL58">
+        <f>BG58/BF58-1</f>
+        <v/>
+      </c>
+      <c r="BN58" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO58" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ58" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR58" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT58">
+        <f>BN58/BO58-1</f>
+        <v/>
+      </c>
+      <c r="BU58">
+        <f>BP58/BO58-1</f>
+        <v/>
+      </c>
+      <c r="BW58" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX58" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ58" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA58" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC58">
+        <f>BW58/BX58-1</f>
+        <v/>
+      </c>
+      <c r="CD58">
+        <f>BY58/BX58-1</f>
+        <v/>
+      </c>
+      <c r="CF58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI58" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ58" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL58">
+        <f>CF58/CG58-1</f>
+        <v/>
+      </c>
+      <c r="CM58">
+        <f>CH58/CG58-1</f>
+        <v/>
+      </c>
+      <c r="CO58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR58" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS58" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU58">
+        <f>CO58/CP58-1</f>
+        <v/>
+      </c>
+      <c r="CV58">
+        <f>CQ58/CP58-1</f>
+        <v/>
+      </c>
+      <c r="CX58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY58" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA58" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB58" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD58">
+        <f>CX58/CY58-1</f>
+        <v/>
+      </c>
+      <c r="DE58">
+        <f>CZ58/CY58-1</f>
+        <v/>
+      </c>
+      <c r="DG58" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH58" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ58" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK58" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM58">
+        <f>DG58/DH58-1</f>
+        <v/>
+      </c>
+      <c r="DN58">
+        <f>DI58/DH58-1</f>
+        <v/>
+      </c>
+      <c r="DP58" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ58" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS58" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT58" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV58">
+        <f>DP58/DQ58-1</f>
+        <v/>
+      </c>
+      <c r="DW58">
+        <f>DR58/DQ58-1</f>
+        <v/>
+      </c>
+      <c r="DY58" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ58" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB58" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC58" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE58">
+        <f>DY58/DZ58-1</f>
+        <v/>
+      </c>
+      <c r="EF58">
+        <f>EA58/DZ58-1</f>
+        <v/>
+      </c>
+      <c r="EH58" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI58" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK58" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL58" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN58">
+        <f>EH58/EI58-1</f>
+        <v/>
+      </c>
+      <c r="EO58">
+        <f>EJ58/EI58-1</f>
+        <v/>
+      </c>
+      <c r="EQ58" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER58" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET58" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU58" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW58">
+        <f>EQ58/ER58-1</f>
+        <v/>
+      </c>
+      <c r="EX58">
+        <f>ES58/ER58-1</f>
+        <v/>
+      </c>
+      <c r="EZ58" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA58" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC58" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD58" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF58">
+        <f>EZ58/FA58-1</f>
+        <v/>
+      </c>
+      <c r="FG58">
+        <f>FB58/FA58-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG58"/>
+  <dimension ref="A1:FG59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -26334,6 +26334,449 @@
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>05 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I59">
+        <f>C59/D59-1</f>
+        <v/>
+      </c>
+      <c r="J59">
+        <f>E59/D59-1</f>
+        <v/>
+      </c>
+      <c r="L59" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M59" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R59">
+        <f>L59/M59-1</f>
+        <v/>
+      </c>
+      <c r="S59">
+        <f>N59/M59-1</f>
+        <v/>
+      </c>
+      <c r="U59" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V59" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA59">
+        <f>U59/V59-1</f>
+        <v/>
+      </c>
+      <c r="AB59">
+        <f>W59/V59-1</f>
+        <v/>
+      </c>
+      <c r="AD59" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE59" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ59">
+        <f>AD59/AE59-1</f>
+        <v/>
+      </c>
+      <c r="AK59">
+        <f>AF59/AE59-1</f>
+        <v/>
+      </c>
+      <c r="AM59" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN59" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS59">
+        <f>AM59/AN59-1</f>
+        <v/>
+      </c>
+      <c r="AT59">
+        <f>AO59/AN59-1</f>
+        <v/>
+      </c>
+      <c r="AV59" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW59" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB59">
+        <f>AV59/AW59-1</f>
+        <v/>
+      </c>
+      <c r="BC59">
+        <f>AX59/AW59-1</f>
+        <v/>
+      </c>
+      <c r="BE59" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF59" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH59" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI59" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK59">
+        <f>BE59/BF59-1</f>
+        <v/>
+      </c>
+      <c r="BL59">
+        <f>BG59/BF59-1</f>
+        <v/>
+      </c>
+      <c r="BN59" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO59" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ59" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR59" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT59">
+        <f>BN59/BO59-1</f>
+        <v/>
+      </c>
+      <c r="BU59">
+        <f>BP59/BO59-1</f>
+        <v/>
+      </c>
+      <c r="BW59" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX59" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ59" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA59" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC59">
+        <f>BW59/BX59-1</f>
+        <v/>
+      </c>
+      <c r="CD59">
+        <f>BY59/BX59-1</f>
+        <v/>
+      </c>
+      <c r="CF59" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG59" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI59" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ59" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL59">
+        <f>CF59/CG59-1</f>
+        <v/>
+      </c>
+      <c r="CM59">
+        <f>CH59/CG59-1</f>
+        <v/>
+      </c>
+      <c r="CO59" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CP59" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR59" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CS59" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU59">
+        <f>CO59/CP59-1</f>
+        <v/>
+      </c>
+      <c r="CV59">
+        <f>CQ59/CP59-1</f>
+        <v/>
+      </c>
+      <c r="CX59" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY59" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA59" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB59" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD59">
+        <f>CX59/CY59-1</f>
+        <v/>
+      </c>
+      <c r="DE59">
+        <f>CZ59/CY59-1</f>
+        <v/>
+      </c>
+      <c r="DG59" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH59" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ59" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK59" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM59">
+        <f>DG59/DH59-1</f>
+        <v/>
+      </c>
+      <c r="DN59">
+        <f>DI59/DH59-1</f>
+        <v/>
+      </c>
+      <c r="DP59" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ59" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DS59" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT59" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DV59">
+        <f>DP59/DQ59-1</f>
+        <v/>
+      </c>
+      <c r="DW59">
+        <f>DR59/DQ59-1</f>
+        <v/>
+      </c>
+      <c r="DY59" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ59" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB59" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC59" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE59">
+        <f>DY59/DZ59-1</f>
+        <v/>
+      </c>
+      <c r="EF59">
+        <f>EA59/DZ59-1</f>
+        <v/>
+      </c>
+      <c r="EH59" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI59" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK59" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL59" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN59">
+        <f>EH59/EI59-1</f>
+        <v/>
+      </c>
+      <c r="EO59">
+        <f>EJ59/EI59-1</f>
+        <v/>
+      </c>
+      <c r="EQ59" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER59" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET59" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU59" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW59">
+        <f>EQ59/ER59-1</f>
+        <v/>
+      </c>
+      <c r="EX59">
+        <f>ES59/ER59-1</f>
+        <v/>
+      </c>
+      <c r="EZ59" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA59" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC59" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD59" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF59">
+        <f>EZ59/FA59-1</f>
+        <v/>
+      </c>
+      <c r="FG59">
+        <f>FB59/FA59-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG59"/>
+  <dimension ref="A1:FG60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -26777,6 +26777,447 @@
         <v/>
       </c>
     </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>05 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I60">
+        <f>C60/D60-1</f>
+        <v/>
+      </c>
+      <c r="J60">
+        <f>E60/D60-1</f>
+        <v/>
+      </c>
+      <c r="L60" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M60" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R60">
+        <f>L60/M60-1</f>
+        <v/>
+      </c>
+      <c r="S60">
+        <f>N60/M60-1</f>
+        <v/>
+      </c>
+      <c r="U60" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V60" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA60">
+        <f>U60/V60-1</f>
+        <v/>
+      </c>
+      <c r="AB60">
+        <f>W60/V60-1</f>
+        <v/>
+      </c>
+      <c r="AD60" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE60" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <f>AD60/AE60-1</f>
+        <v/>
+      </c>
+      <c r="AK60">
+        <f>AF60/AE60-1</f>
+        <v/>
+      </c>
+      <c r="AM60" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN60" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS60">
+        <f>AM60/AN60-1</f>
+        <v/>
+      </c>
+      <c r="AT60">
+        <f>AO60/AN60-1</f>
+        <v/>
+      </c>
+      <c r="AV60" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW60" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB60">
+        <f>AV60/AW60-1</f>
+        <v/>
+      </c>
+      <c r="BC60">
+        <f>AX60/AW60-1</f>
+        <v/>
+      </c>
+      <c r="BE60" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF60" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH60" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI60" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK60">
+        <f>BE60/BF60-1</f>
+        <v/>
+      </c>
+      <c r="BL60">
+        <f>BG60/BF60-1</f>
+        <v/>
+      </c>
+      <c r="BN60" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO60" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ60" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR60" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT60">
+        <f>BN60/BO60-1</f>
+        <v/>
+      </c>
+      <c r="BU60">
+        <f>BP60/BO60-1</f>
+        <v/>
+      </c>
+      <c r="BW60" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX60" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ60" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA60" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC60">
+        <f>BW60/BX60-1</f>
+        <v/>
+      </c>
+      <c r="CD60">
+        <f>BY60/BX60-1</f>
+        <v/>
+      </c>
+      <c r="CF60" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG60" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI60" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ60" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL60">
+        <f>CF60/CG60-1</f>
+        <v/>
+      </c>
+      <c r="CM60">
+        <f>CH60/CG60-1</f>
+        <v/>
+      </c>
+      <c r="CO60" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CP60" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR60" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CS60" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU60">
+        <f>CO60/CP60-1</f>
+        <v/>
+      </c>
+      <c r="CV60">
+        <f>CQ60/CP60-1</f>
+        <v/>
+      </c>
+      <c r="CX60" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY60" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA60" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB60" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD60">
+        <f>CX60/CY60-1</f>
+        <v/>
+      </c>
+      <c r="DE60">
+        <f>CZ60/CY60-1</f>
+        <v/>
+      </c>
+      <c r="DG60" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH60" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ60" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK60" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM60">
+        <f>DG60/DH60-1</f>
+        <v/>
+      </c>
+      <c r="DN60">
+        <f>DI60/DH60-1</f>
+        <v/>
+      </c>
+      <c r="DP60" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ60" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS60" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT60" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV60">
+        <f>DP60/DQ60-1</f>
+        <v/>
+      </c>
+      <c r="DW60">
+        <f>DR60/DQ60-1</f>
+        <v/>
+      </c>
+      <c r="DY60" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ60" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB60" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC60" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE60">
+        <f>DY60/DZ60-1</f>
+        <v/>
+      </c>
+      <c r="EF60">
+        <f>EA60/DZ60-1</f>
+        <v/>
+      </c>
+      <c r="EH60" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI60" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK60" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL60" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN60">
+        <f>EH60/EI60-1</f>
+        <v/>
+      </c>
+      <c r="EO60">
+        <f>EJ60/EI60-1</f>
+        <v/>
+      </c>
+      <c r="EQ60" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER60" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET60" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU60" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW60">
+        <f>EQ60/ER60-1</f>
+        <v/>
+      </c>
+      <c r="EX60">
+        <f>ES60/ER60-1</f>
+        <v/>
+      </c>
+      <c r="EZ60" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA60" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC60" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD60" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF60">
+        <f>EZ60/FA60-1</f>
+        <v/>
+      </c>
+      <c r="FG60">
+        <f>FB60/FA60-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG60"/>
+  <dimension ref="A1:FG61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -27218,6 +27218,445 @@
         <v/>
       </c>
     </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>06 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I61">
+        <f>C61/D61-1</f>
+        <v/>
+      </c>
+      <c r="J61">
+        <f>E61/D61-1</f>
+        <v/>
+      </c>
+      <c r="L61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R61">
+        <f>L61/M61-1</f>
+        <v/>
+      </c>
+      <c r="S61">
+        <f>N61/M61-1</f>
+        <v/>
+      </c>
+      <c r="U61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA61">
+        <f>U61/V61-1</f>
+        <v/>
+      </c>
+      <c r="AB61">
+        <f>W61/V61-1</f>
+        <v/>
+      </c>
+      <c r="AD61" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE61" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <f>AD61/AE61-1</f>
+        <v/>
+      </c>
+      <c r="AK61">
+        <f>AF61/AE61-1</f>
+        <v/>
+      </c>
+      <c r="AM61" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN61" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS61">
+        <f>AM61/AN61-1</f>
+        <v/>
+      </c>
+      <c r="AT61">
+        <f>AO61/AN61-1</f>
+        <v/>
+      </c>
+      <c r="AV61" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW61" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB61">
+        <f>AV61/AW61-1</f>
+        <v/>
+      </c>
+      <c r="BC61">
+        <f>AX61/AW61-1</f>
+        <v/>
+      </c>
+      <c r="BE61" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF61" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH61" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI61" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK61">
+        <f>BE61/BF61-1</f>
+        <v/>
+      </c>
+      <c r="BL61">
+        <f>BG61/BF61-1</f>
+        <v/>
+      </c>
+      <c r="BN61" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO61" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ61" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR61" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT61">
+        <f>BN61/BO61-1</f>
+        <v/>
+      </c>
+      <c r="BU61">
+        <f>BP61/BO61-1</f>
+        <v/>
+      </c>
+      <c r="BW61" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX61" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ61" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA61" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC61">
+        <f>BW61/BX61-1</f>
+        <v/>
+      </c>
+      <c r="CD61">
+        <f>BY61/BX61-1</f>
+        <v/>
+      </c>
+      <c r="CF61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI61" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ61" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL61">
+        <f>CF61/CG61-1</f>
+        <v/>
+      </c>
+      <c r="CM61">
+        <f>CH61/CG61-1</f>
+        <v/>
+      </c>
+      <c r="CO61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR61" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS61" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU61">
+        <f>CO61/CP61-1</f>
+        <v/>
+      </c>
+      <c r="CV61">
+        <f>CQ61/CP61-1</f>
+        <v/>
+      </c>
+      <c r="CX61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY61" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA61" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB61" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD61">
+        <f>CX61/CY61-1</f>
+        <v/>
+      </c>
+      <c r="DE61">
+        <f>CZ61/CY61-1</f>
+        <v/>
+      </c>
+      <c r="DG61" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH61" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ61" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK61" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM61">
+        <f>DG61/DH61-1</f>
+        <v/>
+      </c>
+      <c r="DN61">
+        <f>DI61/DH61-1</f>
+        <v/>
+      </c>
+      <c r="DP61" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ61" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS61" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT61" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV61">
+        <f>DP61/DQ61-1</f>
+        <v/>
+      </c>
+      <c r="DW61">
+        <f>DR61/DQ61-1</f>
+        <v/>
+      </c>
+      <c r="DY61" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ61" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB61" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC61" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE61">
+        <f>DY61/DZ61-1</f>
+        <v/>
+      </c>
+      <c r="EF61">
+        <f>EA61/DZ61-1</f>
+        <v/>
+      </c>
+      <c r="EH61" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI61" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK61" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL61" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN61">
+        <f>EH61/EI61-1</f>
+        <v/>
+      </c>
+      <c r="EO61">
+        <f>EJ61/EI61-1</f>
+        <v/>
+      </c>
+      <c r="EQ61" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER61" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET61" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU61" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW61">
+        <f>EQ61/ER61-1</f>
+        <v/>
+      </c>
+      <c r="EX61">
+        <f>ES61/ER61-1</f>
+        <v/>
+      </c>
+      <c r="EZ61" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA61" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC61" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD61" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF61">
+        <f>EZ61/FA61-1</f>
+        <v/>
+      </c>
+      <c r="FG61">
+        <f>FB61/FA61-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG61"/>
+  <dimension ref="A1:FG62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -27657,6 +27657,445 @@
         <v/>
       </c>
     </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>06 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I62">
+        <f>C62/D62-1</f>
+        <v/>
+      </c>
+      <c r="J62">
+        <f>E62/D62-1</f>
+        <v/>
+      </c>
+      <c r="L62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R62">
+        <f>L62/M62-1</f>
+        <v/>
+      </c>
+      <c r="S62">
+        <f>N62/M62-1</f>
+        <v/>
+      </c>
+      <c r="U62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA62">
+        <f>U62/V62-1</f>
+        <v/>
+      </c>
+      <c r="AB62">
+        <f>W62/V62-1</f>
+        <v/>
+      </c>
+      <c r="AD62" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE62" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <f>AD62/AE62-1</f>
+        <v/>
+      </c>
+      <c r="AK62">
+        <f>AF62/AE62-1</f>
+        <v/>
+      </c>
+      <c r="AM62" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN62" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS62">
+        <f>AM62/AN62-1</f>
+        <v/>
+      </c>
+      <c r="AT62">
+        <f>AO62/AN62-1</f>
+        <v/>
+      </c>
+      <c r="AV62" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW62" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB62">
+        <f>AV62/AW62-1</f>
+        <v/>
+      </c>
+      <c r="BC62">
+        <f>AX62/AW62-1</f>
+        <v/>
+      </c>
+      <c r="BE62" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF62" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH62" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI62" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK62">
+        <f>BE62/BF62-1</f>
+        <v/>
+      </c>
+      <c r="BL62">
+        <f>BG62/BF62-1</f>
+        <v/>
+      </c>
+      <c r="BN62" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO62" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ62" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR62" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT62">
+        <f>BN62/BO62-1</f>
+        <v/>
+      </c>
+      <c r="BU62">
+        <f>BP62/BO62-1</f>
+        <v/>
+      </c>
+      <c r="BW62" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX62" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ62" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA62" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC62">
+        <f>BW62/BX62-1</f>
+        <v/>
+      </c>
+      <c r="CD62">
+        <f>BY62/BX62-1</f>
+        <v/>
+      </c>
+      <c r="CF62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI62" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ62" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL62">
+        <f>CF62/CG62-1</f>
+        <v/>
+      </c>
+      <c r="CM62">
+        <f>CH62/CG62-1</f>
+        <v/>
+      </c>
+      <c r="CO62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR62" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS62" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU62">
+        <f>CO62/CP62-1</f>
+        <v/>
+      </c>
+      <c r="CV62">
+        <f>CQ62/CP62-1</f>
+        <v/>
+      </c>
+      <c r="CX62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY62" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA62" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB62" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD62">
+        <f>CX62/CY62-1</f>
+        <v/>
+      </c>
+      <c r="DE62">
+        <f>CZ62/CY62-1</f>
+        <v/>
+      </c>
+      <c r="DG62" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH62" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ62" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK62" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM62">
+        <f>DG62/DH62-1</f>
+        <v/>
+      </c>
+      <c r="DN62">
+        <f>DI62/DH62-1</f>
+        <v/>
+      </c>
+      <c r="DP62" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ62" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS62" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT62" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV62">
+        <f>DP62/DQ62-1</f>
+        <v/>
+      </c>
+      <c r="DW62">
+        <f>DR62/DQ62-1</f>
+        <v/>
+      </c>
+      <c r="DY62" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ62" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB62" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC62" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE62">
+        <f>DY62/DZ62-1</f>
+        <v/>
+      </c>
+      <c r="EF62">
+        <f>EA62/DZ62-1</f>
+        <v/>
+      </c>
+      <c r="EH62" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI62" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK62" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL62" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN62">
+        <f>EH62/EI62-1</f>
+        <v/>
+      </c>
+      <c r="EO62">
+        <f>EJ62/EI62-1</f>
+        <v/>
+      </c>
+      <c r="EQ62" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER62" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET62" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU62" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW62">
+        <f>EQ62/ER62-1</f>
+        <v/>
+      </c>
+      <c r="EX62">
+        <f>ES62/ER62-1</f>
+        <v/>
+      </c>
+      <c r="EZ62" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA62" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC62" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD62" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF62">
+        <f>EZ62/FA62-1</f>
+        <v/>
+      </c>
+      <c r="FG62">
+        <f>FB62/FA62-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG62"/>
+  <dimension ref="A1:FG63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -28096,6 +28096,447 @@
         <v/>
       </c>
     </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>07 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I63">
+        <f>C63/D63-1</f>
+        <v/>
+      </c>
+      <c r="J63">
+        <f>E63/D63-1</f>
+        <v/>
+      </c>
+      <c r="L63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R63">
+        <f>L63/M63-1</f>
+        <v/>
+      </c>
+      <c r="S63">
+        <f>N63/M63-1</f>
+        <v/>
+      </c>
+      <c r="U63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA63">
+        <f>U63/V63-1</f>
+        <v/>
+      </c>
+      <c r="AB63">
+        <f>W63/V63-1</f>
+        <v/>
+      </c>
+      <c r="AD63" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE63" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <f>AD63/AE63-1</f>
+        <v/>
+      </c>
+      <c r="AK63">
+        <f>AF63/AE63-1</f>
+        <v/>
+      </c>
+      <c r="AM63" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN63" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS63">
+        <f>AM63/AN63-1</f>
+        <v/>
+      </c>
+      <c r="AT63">
+        <f>AO63/AN63-1</f>
+        <v/>
+      </c>
+      <c r="AV63" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW63" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB63">
+        <f>AV63/AW63-1</f>
+        <v/>
+      </c>
+      <c r="BC63">
+        <f>AX63/AW63-1</f>
+        <v/>
+      </c>
+      <c r="BE63" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF63" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH63" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI63" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK63">
+        <f>BE63/BF63-1</f>
+        <v/>
+      </c>
+      <c r="BL63">
+        <f>BG63/BF63-1</f>
+        <v/>
+      </c>
+      <c r="BN63" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO63" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ63" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR63" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT63">
+        <f>BN63/BO63-1</f>
+        <v/>
+      </c>
+      <c r="BU63">
+        <f>BP63/BO63-1</f>
+        <v/>
+      </c>
+      <c r="BW63" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX63" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ63" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA63" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC63">
+        <f>BW63/BX63-1</f>
+        <v/>
+      </c>
+      <c r="CD63">
+        <f>BY63/BX63-1</f>
+        <v/>
+      </c>
+      <c r="CF63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI63" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ63" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL63">
+        <f>CF63/CG63-1</f>
+        <v/>
+      </c>
+      <c r="CM63">
+        <f>CH63/CG63-1</f>
+        <v/>
+      </c>
+      <c r="CO63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR63" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS63" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU63">
+        <f>CO63/CP63-1</f>
+        <v/>
+      </c>
+      <c r="CV63">
+        <f>CQ63/CP63-1</f>
+        <v/>
+      </c>
+      <c r="CX63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY63" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA63" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB63" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD63">
+        <f>CX63/CY63-1</f>
+        <v/>
+      </c>
+      <c r="DE63">
+        <f>CZ63/CY63-1</f>
+        <v/>
+      </c>
+      <c r="DG63" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH63" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ63" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK63" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM63">
+        <f>DG63/DH63-1</f>
+        <v/>
+      </c>
+      <c r="DN63">
+        <f>DI63/DH63-1</f>
+        <v/>
+      </c>
+      <c r="DP63" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ63" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS63" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT63" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV63">
+        <f>DP63/DQ63-1</f>
+        <v/>
+      </c>
+      <c r="DW63">
+        <f>DR63/DQ63-1</f>
+        <v/>
+      </c>
+      <c r="DY63" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ63" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB63" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC63" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE63">
+        <f>DY63/DZ63-1</f>
+        <v/>
+      </c>
+      <c r="EF63">
+        <f>EA63/DZ63-1</f>
+        <v/>
+      </c>
+      <c r="EH63" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI63" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK63" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL63" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN63">
+        <f>EH63/EI63-1</f>
+        <v/>
+      </c>
+      <c r="EO63">
+        <f>EJ63/EI63-1</f>
+        <v/>
+      </c>
+      <c r="EQ63" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER63" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET63" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU63" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW63">
+        <f>EQ63/ER63-1</f>
+        <v/>
+      </c>
+      <c r="EX63">
+        <f>ES63/ER63-1</f>
+        <v/>
+      </c>
+      <c r="EZ63" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA63" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FC63" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD63" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FF63">
+        <f>EZ63/FA63-1</f>
+        <v/>
+      </c>
+      <c r="FG63">
+        <f>FB63/FA63-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG63"/>
+  <dimension ref="A1:FG64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -28537,6 +28537,447 @@
         <v/>
       </c>
     </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>07 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I64">
+        <f>C64/D64-1</f>
+        <v/>
+      </c>
+      <c r="J64">
+        <f>E64/D64-1</f>
+        <v/>
+      </c>
+      <c r="L64" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M64" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R64">
+        <f>L64/M64-1</f>
+        <v/>
+      </c>
+      <c r="S64">
+        <f>N64/M64-1</f>
+        <v/>
+      </c>
+      <c r="U64" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V64" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA64">
+        <f>U64/V64-1</f>
+        <v/>
+      </c>
+      <c r="AB64">
+        <f>W64/V64-1</f>
+        <v/>
+      </c>
+      <c r="AD64" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE64" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ64">
+        <f>AD64/AE64-1</f>
+        <v/>
+      </c>
+      <c r="AK64">
+        <f>AF64/AE64-1</f>
+        <v/>
+      </c>
+      <c r="AM64" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN64" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS64">
+        <f>AM64/AN64-1</f>
+        <v/>
+      </c>
+      <c r="AT64">
+        <f>AO64/AN64-1</f>
+        <v/>
+      </c>
+      <c r="AV64" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW64" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB64">
+        <f>AV64/AW64-1</f>
+        <v/>
+      </c>
+      <c r="BC64">
+        <f>AX64/AW64-1</f>
+        <v/>
+      </c>
+      <c r="BE64" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF64" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH64" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI64" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK64">
+        <f>BE64/BF64-1</f>
+        <v/>
+      </c>
+      <c r="BL64">
+        <f>BG64/BF64-1</f>
+        <v/>
+      </c>
+      <c r="BN64" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO64" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ64" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR64" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT64">
+        <f>BN64/BO64-1</f>
+        <v/>
+      </c>
+      <c r="BU64">
+        <f>BP64/BO64-1</f>
+        <v/>
+      </c>
+      <c r="BW64" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX64" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ64" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA64" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC64">
+        <f>BW64/BX64-1</f>
+        <v/>
+      </c>
+      <c r="CD64">
+        <f>BY64/BX64-1</f>
+        <v/>
+      </c>
+      <c r="CF64" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG64" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI64" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ64" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL64">
+        <f>CF64/CG64-1</f>
+        <v/>
+      </c>
+      <c r="CM64">
+        <f>CH64/CG64-1</f>
+        <v/>
+      </c>
+      <c r="CO64" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP64" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CR64" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS64" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CU64">
+        <f>CO64/CP64-1</f>
+        <v/>
+      </c>
+      <c r="CV64">
+        <f>CQ64/CP64-1</f>
+        <v/>
+      </c>
+      <c r="CX64" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY64" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA64" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB64" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD64">
+        <f>CX64/CY64-1</f>
+        <v/>
+      </c>
+      <c r="DE64">
+        <f>CZ64/CY64-1</f>
+        <v/>
+      </c>
+      <c r="DG64" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH64" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ64" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK64" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM64">
+        <f>DG64/DH64-1</f>
+        <v/>
+      </c>
+      <c r="DN64">
+        <f>DI64/DH64-1</f>
+        <v/>
+      </c>
+      <c r="DP64" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ64" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS64" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT64" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV64">
+        <f>DP64/DQ64-1</f>
+        <v/>
+      </c>
+      <c r="DW64">
+        <f>DR64/DQ64-1</f>
+        <v/>
+      </c>
+      <c r="DY64" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ64" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB64" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC64" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE64">
+        <f>DY64/DZ64-1</f>
+        <v/>
+      </c>
+      <c r="EF64">
+        <f>EA64/DZ64-1</f>
+        <v/>
+      </c>
+      <c r="EH64" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI64" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK64" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL64" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN64">
+        <f>EH64/EI64-1</f>
+        <v/>
+      </c>
+      <c r="EO64">
+        <f>EJ64/EI64-1</f>
+        <v/>
+      </c>
+      <c r="EQ64" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER64" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET64" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU64" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW64">
+        <f>EQ64/ER64-1</f>
+        <v/>
+      </c>
+      <c r="EX64">
+        <f>ES64/ER64-1</f>
+        <v/>
+      </c>
+      <c r="EZ64" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA64" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC64" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD64" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF64">
+        <f>EZ64/FA64-1</f>
+        <v/>
+      </c>
+      <c r="FG64">
+        <f>FB64/FA64-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG64"/>
+  <dimension ref="A1:FG65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -28978,6 +28978,449 @@
         <v/>
       </c>
     </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>07 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I65">
+        <f>C65/D65-1</f>
+        <v/>
+      </c>
+      <c r="J65">
+        <f>E65/D65-1</f>
+        <v/>
+      </c>
+      <c r="L65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R65">
+        <f>L65/M65-1</f>
+        <v/>
+      </c>
+      <c r="S65">
+        <f>N65/M65-1</f>
+        <v/>
+      </c>
+      <c r="U65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA65">
+        <f>U65/V65-1</f>
+        <v/>
+      </c>
+      <c r="AB65">
+        <f>W65/V65-1</f>
+        <v/>
+      </c>
+      <c r="AD65" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE65" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <f>AD65/AE65-1</f>
+        <v/>
+      </c>
+      <c r="AK65">
+        <f>AF65/AE65-1</f>
+        <v/>
+      </c>
+      <c r="AM65" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN65" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS65">
+        <f>AM65/AN65-1</f>
+        <v/>
+      </c>
+      <c r="AT65">
+        <f>AO65/AN65-1</f>
+        <v/>
+      </c>
+      <c r="AV65" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW65" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB65">
+        <f>AV65/AW65-1</f>
+        <v/>
+      </c>
+      <c r="BC65">
+        <f>AX65/AW65-1</f>
+        <v/>
+      </c>
+      <c r="BE65" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF65" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH65" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI65" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK65">
+        <f>BE65/BF65-1</f>
+        <v/>
+      </c>
+      <c r="BL65">
+        <f>BG65/BF65-1</f>
+        <v/>
+      </c>
+      <c r="BN65" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO65" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ65" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR65" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT65">
+        <f>BN65/BO65-1</f>
+        <v/>
+      </c>
+      <c r="BU65">
+        <f>BP65/BO65-1</f>
+        <v/>
+      </c>
+      <c r="BW65" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX65" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BZ65" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA65" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC65">
+        <f>BW65/BX65-1</f>
+        <v/>
+      </c>
+      <c r="CD65">
+        <f>BY65/BX65-1</f>
+        <v/>
+      </c>
+      <c r="CF65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI65" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ65" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL65">
+        <f>CF65/CG65-1</f>
+        <v/>
+      </c>
+      <c r="CM65">
+        <f>CH65/CG65-1</f>
+        <v/>
+      </c>
+      <c r="CO65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR65" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS65" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU65">
+        <f>CO65/CP65-1</f>
+        <v/>
+      </c>
+      <c r="CV65">
+        <f>CQ65/CP65-1</f>
+        <v/>
+      </c>
+      <c r="CX65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY65" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA65" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB65" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD65">
+        <f>CX65/CY65-1</f>
+        <v/>
+      </c>
+      <c r="DE65">
+        <f>CZ65/CY65-1</f>
+        <v/>
+      </c>
+      <c r="DG65" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH65" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ65" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK65" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM65">
+        <f>DG65/DH65-1</f>
+        <v/>
+      </c>
+      <c r="DN65">
+        <f>DI65/DH65-1</f>
+        <v/>
+      </c>
+      <c r="DP65" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ65" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DS65" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT65" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DV65">
+        <f>DP65/DQ65-1</f>
+        <v/>
+      </c>
+      <c r="DW65">
+        <f>DR65/DQ65-1</f>
+        <v/>
+      </c>
+      <c r="DY65" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ65" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB65" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC65" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE65">
+        <f>DY65/DZ65-1</f>
+        <v/>
+      </c>
+      <c r="EF65">
+        <f>EA65/DZ65-1</f>
+        <v/>
+      </c>
+      <c r="EH65" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI65" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK65" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL65" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN65">
+        <f>EH65/EI65-1</f>
+        <v/>
+      </c>
+      <c r="EO65">
+        <f>EJ65/EI65-1</f>
+        <v/>
+      </c>
+      <c r="EQ65" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER65" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET65" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU65" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW65">
+        <f>EQ65/ER65-1</f>
+        <v/>
+      </c>
+      <c r="EX65">
+        <f>ES65/ER65-1</f>
+        <v/>
+      </c>
+      <c r="EZ65" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA65" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC65" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD65" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF65">
+        <f>EZ65/FA65-1</f>
+        <v/>
+      </c>
+      <c r="FG65">
+        <f>FB65/FA65-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG65"/>
+  <dimension ref="A1:FG66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -29421,6 +29421,451 @@
         <v/>
       </c>
     </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>07 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I66">
+        <f>C66/D66-1</f>
+        <v/>
+      </c>
+      <c r="J66">
+        <f>E66/D66-1</f>
+        <v/>
+      </c>
+      <c r="L66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R66">
+        <f>L66/M66-1</f>
+        <v/>
+      </c>
+      <c r="S66">
+        <f>N66/M66-1</f>
+        <v/>
+      </c>
+      <c r="U66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA66">
+        <f>U66/V66-1</f>
+        <v/>
+      </c>
+      <c r="AB66">
+        <f>W66/V66-1</f>
+        <v/>
+      </c>
+      <c r="AD66" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <f>AD66/AE66-1</f>
+        <v/>
+      </c>
+      <c r="AK66">
+        <f>AF66/AE66-1</f>
+        <v/>
+      </c>
+      <c r="AM66" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AS66">
+        <f>AM66/AN66-1</f>
+        <v/>
+      </c>
+      <c r="AT66">
+        <f>AO66/AN66-1</f>
+        <v/>
+      </c>
+      <c r="AV66" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BB66">
+        <f>AV66/AW66-1</f>
+        <v/>
+      </c>
+      <c r="BC66">
+        <f>AX66/AW66-1</f>
+        <v/>
+      </c>
+      <c r="BE66" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF66" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH66" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI66" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK66">
+        <f>BE66/BF66-1</f>
+        <v/>
+      </c>
+      <c r="BL66">
+        <f>BG66/BF66-1</f>
+        <v/>
+      </c>
+      <c r="BN66" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO66" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ66" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR66" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT66">
+        <f>BN66/BO66-1</f>
+        <v/>
+      </c>
+      <c r="BU66">
+        <f>BP66/BO66-1</f>
+        <v/>
+      </c>
+      <c r="BW66" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX66" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ66" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA66" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC66">
+        <f>BW66/BX66-1</f>
+        <v/>
+      </c>
+      <c r="CD66">
+        <f>BY66/BX66-1</f>
+        <v/>
+      </c>
+      <c r="CF66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI66" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ66" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL66">
+        <f>CF66/CG66-1</f>
+        <v/>
+      </c>
+      <c r="CM66">
+        <f>CH66/CG66-1</f>
+        <v/>
+      </c>
+      <c r="CO66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR66" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS66" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU66">
+        <f>CO66/CP66-1</f>
+        <v/>
+      </c>
+      <c r="CV66">
+        <f>CQ66/CP66-1</f>
+        <v/>
+      </c>
+      <c r="CX66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY66" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA66" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB66" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD66">
+        <f>CX66/CY66-1</f>
+        <v/>
+      </c>
+      <c r="DE66">
+        <f>CZ66/CY66-1</f>
+        <v/>
+      </c>
+      <c r="DG66" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH66" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ66" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK66" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM66">
+        <f>DG66/DH66-1</f>
+        <v/>
+      </c>
+      <c r="DN66">
+        <f>DI66/DH66-1</f>
+        <v/>
+      </c>
+      <c r="DP66" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ66" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS66" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT66" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV66">
+        <f>DP66/DQ66-1</f>
+        <v/>
+      </c>
+      <c r="DW66">
+        <f>DR66/DQ66-1</f>
+        <v/>
+      </c>
+      <c r="DY66" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ66" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB66" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC66" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE66">
+        <f>DY66/DZ66-1</f>
+        <v/>
+      </c>
+      <c r="EF66">
+        <f>EA66/DZ66-1</f>
+        <v/>
+      </c>
+      <c r="EH66" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI66" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK66" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL66" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN66">
+        <f>EH66/EI66-1</f>
+        <v/>
+      </c>
+      <c r="EO66">
+        <f>EJ66/EI66-1</f>
+        <v/>
+      </c>
+      <c r="EQ66" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER66" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET66" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU66" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW66">
+        <f>EQ66/ER66-1</f>
+        <v/>
+      </c>
+      <c r="EX66">
+        <f>ES66/ER66-1</f>
+        <v/>
+      </c>
+      <c r="EZ66" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA66" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC66" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD66" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF66">
+        <f>EZ66/FA66-1</f>
+        <v/>
+      </c>
+      <c r="FG66">
+        <f>FB66/FA66-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG66"/>
+  <dimension ref="A1:FG67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -29866,6 +29866,449 @@
         <v/>
       </c>
     </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>07 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I67">
+        <f>C67/D67-1</f>
+        <v/>
+      </c>
+      <c r="J67">
+        <f>E67/D67-1</f>
+        <v/>
+      </c>
+      <c r="L67" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M67" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R67">
+        <f>L67/M67-1</f>
+        <v/>
+      </c>
+      <c r="S67">
+        <f>N67/M67-1</f>
+        <v/>
+      </c>
+      <c r="U67" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V67" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA67">
+        <f>U67/V67-1</f>
+        <v/>
+      </c>
+      <c r="AB67">
+        <f>W67/V67-1</f>
+        <v/>
+      </c>
+      <c r="AD67" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE67" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <f>AD67/AE67-1</f>
+        <v/>
+      </c>
+      <c r="AK67">
+        <f>AF67/AE67-1</f>
+        <v/>
+      </c>
+      <c r="AM67" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN67" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS67">
+        <f>AM67/AN67-1</f>
+        <v/>
+      </c>
+      <c r="AT67">
+        <f>AO67/AN67-1</f>
+        <v/>
+      </c>
+      <c r="AV67" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW67" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB67">
+        <f>AV67/AW67-1</f>
+        <v/>
+      </c>
+      <c r="BC67">
+        <f>AX67/AW67-1</f>
+        <v/>
+      </c>
+      <c r="BE67" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF67" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH67" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI67" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK67">
+        <f>BE67/BF67-1</f>
+        <v/>
+      </c>
+      <c r="BL67">
+        <f>BG67/BF67-1</f>
+        <v/>
+      </c>
+      <c r="BN67" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO67" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ67" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR67" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT67">
+        <f>BN67/BO67-1</f>
+        <v/>
+      </c>
+      <c r="BU67">
+        <f>BP67/BO67-1</f>
+        <v/>
+      </c>
+      <c r="BW67" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX67" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ67" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA67" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC67">
+        <f>BW67/BX67-1</f>
+        <v/>
+      </c>
+      <c r="CD67">
+        <f>BY67/BX67-1</f>
+        <v/>
+      </c>
+      <c r="CF67" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG67" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI67" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ67" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL67">
+        <f>CF67/CG67-1</f>
+        <v/>
+      </c>
+      <c r="CM67">
+        <f>CH67/CG67-1</f>
+        <v/>
+      </c>
+      <c r="CO67" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP67" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CR67" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS67" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CU67">
+        <f>CO67/CP67-1</f>
+        <v/>
+      </c>
+      <c r="CV67">
+        <f>CQ67/CP67-1</f>
+        <v/>
+      </c>
+      <c r="CX67" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY67" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA67" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB67" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD67">
+        <f>CX67/CY67-1</f>
+        <v/>
+      </c>
+      <c r="DE67">
+        <f>CZ67/CY67-1</f>
+        <v/>
+      </c>
+      <c r="DG67" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH67" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ67" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK67" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM67">
+        <f>DG67/DH67-1</f>
+        <v/>
+      </c>
+      <c r="DN67">
+        <f>DI67/DH67-1</f>
+        <v/>
+      </c>
+      <c r="DP67" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ67" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DS67" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT67" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DV67">
+        <f>DP67/DQ67-1</f>
+        <v/>
+      </c>
+      <c r="DW67">
+        <f>DR67/DQ67-1</f>
+        <v/>
+      </c>
+      <c r="DY67" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ67" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB67" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC67" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE67">
+        <f>DY67/DZ67-1</f>
+        <v/>
+      </c>
+      <c r="EF67">
+        <f>EA67/DZ67-1</f>
+        <v/>
+      </c>
+      <c r="EH67" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI67" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK67" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL67" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN67">
+        <f>EH67/EI67-1</f>
+        <v/>
+      </c>
+      <c r="EO67">
+        <f>EJ67/EI67-1</f>
+        <v/>
+      </c>
+      <c r="EQ67" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER67" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET67" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU67" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW67">
+        <f>EQ67/ER67-1</f>
+        <v/>
+      </c>
+      <c r="EX67">
+        <f>ES67/ER67-1</f>
+        <v/>
+      </c>
+      <c r="EZ67" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA67" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC67" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD67" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF67">
+        <f>EZ67/FA67-1</f>
+        <v/>
+      </c>
+      <c r="FG67">
+        <f>FB67/FA67-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG67"/>
+  <dimension ref="A1:FG68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -30309,6 +30309,479 @@
         <v/>
       </c>
     </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>08 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I68">
+        <f>C68/D68-1</f>
+        <v/>
+      </c>
+      <c r="J68">
+        <f>E68/D68-1</f>
+        <v/>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M68" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R68">
+        <f>L68/M68-1</f>
+        <v/>
+      </c>
+      <c r="S68">
+        <f>N68/M68-1</f>
+        <v/>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V68" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA68">
+        <f>U68/V68-1</f>
+        <v/>
+      </c>
+      <c r="AB68">
+        <f>W68/V68-1</f>
+        <v/>
+      </c>
+      <c r="AD68" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE68" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <f>AD68/AE68-1</f>
+        <v/>
+      </c>
+      <c r="AK68">
+        <f>AF68/AE68-1</f>
+        <v/>
+      </c>
+      <c r="AM68" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN68" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS68">
+        <f>AM68/AN68-1</f>
+        <v/>
+      </c>
+      <c r="AT68">
+        <f>AO68/AN68-1</f>
+        <v/>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW68" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB68">
+        <f>AV68/AW68-1</f>
+        <v/>
+      </c>
+      <c r="BC68">
+        <f>AX68/AW68-1</f>
+        <v/>
+      </c>
+      <c r="BE68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF68" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI68" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK68">
+        <f>BE68/BF68-1</f>
+        <v/>
+      </c>
+      <c r="BL68">
+        <f>BG68/BF68-1</f>
+        <v/>
+      </c>
+      <c r="BN68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO68" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR68" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT68">
+        <f>BN68/BO68-1</f>
+        <v/>
+      </c>
+      <c r="BU68">
+        <f>BP68/BO68-1</f>
+        <v/>
+      </c>
+      <c r="BW68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BZ68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC68">
+        <f>BW68/BX68-1</f>
+        <v/>
+      </c>
+      <c r="CD68">
+        <f>BY68/BX68-1</f>
+        <v/>
+      </c>
+      <c r="CF68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG68" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ68" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL68">
+        <f>CF68/CG68-1</f>
+        <v/>
+      </c>
+      <c r="CM68">
+        <f>CH68/CG68-1</f>
+        <v/>
+      </c>
+      <c r="CO68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CP68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CR68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CS68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CU68">
+        <f>CO68/CP68-1</f>
+        <v/>
+      </c>
+      <c r="CV68">
+        <f>CQ68/CP68-1</f>
+        <v/>
+      </c>
+      <c r="CX68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY68" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB68" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD68">
+        <f>CX68/CY68-1</f>
+        <v/>
+      </c>
+      <c r="DE68">
+        <f>CZ68/CY68-1</f>
+        <v/>
+      </c>
+      <c r="DG68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH68" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK68" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM68">
+        <f>DG68/DH68-1</f>
+        <v/>
+      </c>
+      <c r="DN68">
+        <f>DI68/DH68-1</f>
+        <v/>
+      </c>
+      <c r="DP68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ68" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT68" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV68">
+        <f>DP68/DQ68-1</f>
+        <v/>
+      </c>
+      <c r="DW68">
+        <f>DR68/DQ68-1</f>
+        <v/>
+      </c>
+      <c r="DY68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ68" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC68" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE68">
+        <f>DY68/DZ68-1</f>
+        <v/>
+      </c>
+      <c r="EF68">
+        <f>EA68/DZ68-1</f>
+        <v/>
+      </c>
+      <c r="EH68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI68" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL68" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN68">
+        <f>EH68/EI68-1</f>
+        <v/>
+      </c>
+      <c r="EO68">
+        <f>EJ68/EI68-1</f>
+        <v/>
+      </c>
+      <c r="EQ68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER68" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU68" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW68">
+        <f>EQ68/ER68-1</f>
+        <v/>
+      </c>
+      <c r="EX68">
+        <f>ES68/ER68-1</f>
+        <v/>
+      </c>
+      <c r="EZ68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA68" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC68" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD68" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF68">
+        <f>EZ68/FA68-1</f>
+        <v/>
+      </c>
+      <c r="FG68">
+        <f>FB68/FA68-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG68"/>
+  <dimension ref="A1:FG69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -30782,6 +30782,447 @@
         <v/>
       </c>
     </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>08 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I69">
+        <f>C69/D69-1</f>
+        <v/>
+      </c>
+      <c r="J69">
+        <f>E69/D69-1</f>
+        <v/>
+      </c>
+      <c r="L69" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M69" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R69">
+        <f>L69/M69-1</f>
+        <v/>
+      </c>
+      <c r="S69">
+        <f>N69/M69-1</f>
+        <v/>
+      </c>
+      <c r="U69" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AA69">
+        <f>U69/V69-1</f>
+        <v/>
+      </c>
+      <c r="AB69">
+        <f>W69/V69-1</f>
+        <v/>
+      </c>
+      <c r="AD69" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE69" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <f>AD69/AE69-1</f>
+        <v/>
+      </c>
+      <c r="AK69">
+        <f>AF69/AE69-1</f>
+        <v/>
+      </c>
+      <c r="AM69" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN69" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS69">
+        <f>AM69/AN69-1</f>
+        <v/>
+      </c>
+      <c r="AT69">
+        <f>AO69/AN69-1</f>
+        <v/>
+      </c>
+      <c r="AV69" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW69" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB69">
+        <f>AV69/AW69-1</f>
+        <v/>
+      </c>
+      <c r="BC69">
+        <f>AX69/AW69-1</f>
+        <v/>
+      </c>
+      <c r="BE69" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF69" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH69" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI69" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK69">
+        <f>BE69/BF69-1</f>
+        <v/>
+      </c>
+      <c r="BL69">
+        <f>BG69/BF69-1</f>
+        <v/>
+      </c>
+      <c r="BN69" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO69" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ69" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR69" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT69">
+        <f>BN69/BO69-1</f>
+        <v/>
+      </c>
+      <c r="BU69">
+        <f>BP69/BO69-1</f>
+        <v/>
+      </c>
+      <c r="BW69" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX69" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ69" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA69" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC69">
+        <f>BW69/BX69-1</f>
+        <v/>
+      </c>
+      <c r="CD69">
+        <f>BY69/BX69-1</f>
+        <v/>
+      </c>
+      <c r="CF69" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG69" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI69" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ69" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL69">
+        <f>CF69/CG69-1</f>
+        <v/>
+      </c>
+      <c r="CM69">
+        <f>CH69/CG69-1</f>
+        <v/>
+      </c>
+      <c r="CO69" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP69" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR69" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS69" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU69">
+        <f>CO69/CP69-1</f>
+        <v/>
+      </c>
+      <c r="CV69">
+        <f>CQ69/CP69-1</f>
+        <v/>
+      </c>
+      <c r="CX69" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY69" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA69" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB69" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD69">
+        <f>CX69/CY69-1</f>
+        <v/>
+      </c>
+      <c r="DE69">
+        <f>CZ69/CY69-1</f>
+        <v/>
+      </c>
+      <c r="DG69" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH69" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ69" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK69" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM69">
+        <f>DG69/DH69-1</f>
+        <v/>
+      </c>
+      <c r="DN69">
+        <f>DI69/DH69-1</f>
+        <v/>
+      </c>
+      <c r="DP69" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ69" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS69" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT69" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV69">
+        <f>DP69/DQ69-1</f>
+        <v/>
+      </c>
+      <c r="DW69">
+        <f>DR69/DQ69-1</f>
+        <v/>
+      </c>
+      <c r="DY69" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ69" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB69" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC69" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE69">
+        <f>DY69/DZ69-1</f>
+        <v/>
+      </c>
+      <c r="EF69">
+        <f>EA69/DZ69-1</f>
+        <v/>
+      </c>
+      <c r="EH69" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI69" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK69" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL69" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN69">
+        <f>EH69/EI69-1</f>
+        <v/>
+      </c>
+      <c r="EO69">
+        <f>EJ69/EI69-1</f>
+        <v/>
+      </c>
+      <c r="EQ69" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER69" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET69" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU69" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW69">
+        <f>EQ69/ER69-1</f>
+        <v/>
+      </c>
+      <c r="EX69">
+        <f>ES69/ER69-1</f>
+        <v/>
+      </c>
+      <c r="EZ69" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA69" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC69" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD69" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF69">
+        <f>EZ69/FA69-1</f>
+        <v/>
+      </c>
+      <c r="FG69">
+        <f>FB69/FA69-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG69"/>
+  <dimension ref="A1:FG70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -31223,6 +31223,449 @@
         <v/>
       </c>
     </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>08 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I70">
+        <f>C70/D70-1</f>
+        <v/>
+      </c>
+      <c r="J70">
+        <f>E70/D70-1</f>
+        <v/>
+      </c>
+      <c r="L70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R70">
+        <f>L70/M70-1</f>
+        <v/>
+      </c>
+      <c r="S70">
+        <f>N70/M70-1</f>
+        <v/>
+      </c>
+      <c r="U70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA70">
+        <f>U70/V70-1</f>
+        <v/>
+      </c>
+      <c r="AB70">
+        <f>W70/V70-1</f>
+        <v/>
+      </c>
+      <c r="AD70" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE70" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <f>AD70/AE70-1</f>
+        <v/>
+      </c>
+      <c r="AK70">
+        <f>AF70/AE70-1</f>
+        <v/>
+      </c>
+      <c r="AM70" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AS70">
+        <f>AM70/AN70-1</f>
+        <v/>
+      </c>
+      <c r="AT70">
+        <f>AO70/AN70-1</f>
+        <v/>
+      </c>
+      <c r="AV70" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW70" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB70">
+        <f>AV70/AW70-1</f>
+        <v/>
+      </c>
+      <c r="BC70">
+        <f>AX70/AW70-1</f>
+        <v/>
+      </c>
+      <c r="BE70" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF70" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH70" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI70" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK70">
+        <f>BE70/BF70-1</f>
+        <v/>
+      </c>
+      <c r="BL70">
+        <f>BG70/BF70-1</f>
+        <v/>
+      </c>
+      <c r="BN70" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO70" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ70" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR70" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT70">
+        <f>BN70/BO70-1</f>
+        <v/>
+      </c>
+      <c r="BU70">
+        <f>BP70/BO70-1</f>
+        <v/>
+      </c>
+      <c r="BW70" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX70" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ70" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA70" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC70">
+        <f>BW70/BX70-1</f>
+        <v/>
+      </c>
+      <c r="CD70">
+        <f>BY70/BX70-1</f>
+        <v/>
+      </c>
+      <c r="CF70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI70" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ70" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL70">
+        <f>CF70/CG70-1</f>
+        <v/>
+      </c>
+      <c r="CM70">
+        <f>CH70/CG70-1</f>
+        <v/>
+      </c>
+      <c r="CO70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR70" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS70" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU70">
+        <f>CO70/CP70-1</f>
+        <v/>
+      </c>
+      <c r="CV70">
+        <f>CQ70/CP70-1</f>
+        <v/>
+      </c>
+      <c r="CX70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY70" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA70" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB70" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD70">
+        <f>CX70/CY70-1</f>
+        <v/>
+      </c>
+      <c r="DE70">
+        <f>CZ70/CY70-1</f>
+        <v/>
+      </c>
+      <c r="DG70" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH70" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ70" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK70" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM70">
+        <f>DG70/DH70-1</f>
+        <v/>
+      </c>
+      <c r="DN70">
+        <f>DI70/DH70-1</f>
+        <v/>
+      </c>
+      <c r="DP70" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ70" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DS70" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT70" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DV70">
+        <f>DP70/DQ70-1</f>
+        <v/>
+      </c>
+      <c r="DW70">
+        <f>DR70/DQ70-1</f>
+        <v/>
+      </c>
+      <c r="DY70" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ70" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB70" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC70" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE70">
+        <f>DY70/DZ70-1</f>
+        <v/>
+      </c>
+      <c r="EF70">
+        <f>EA70/DZ70-1</f>
+        <v/>
+      </c>
+      <c r="EH70" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI70" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK70" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL70" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN70">
+        <f>EH70/EI70-1</f>
+        <v/>
+      </c>
+      <c r="EO70">
+        <f>EJ70/EI70-1</f>
+        <v/>
+      </c>
+      <c r="EQ70" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER70" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET70" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU70" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW70">
+        <f>EQ70/ER70-1</f>
+        <v/>
+      </c>
+      <c r="EX70">
+        <f>ES70/ER70-1</f>
+        <v/>
+      </c>
+      <c r="EZ70" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA70" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC70" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD70" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF70">
+        <f>EZ70/FA70-1</f>
+        <v/>
+      </c>
+      <c r="FG70">
+        <f>FB70/FA70-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG70"/>
+  <dimension ref="A1:FG71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -31666,6 +31666,447 @@
         <v/>
       </c>
     </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>08 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I71">
+        <f>C71/D71-1</f>
+        <v/>
+      </c>
+      <c r="J71">
+        <f>E71/D71-1</f>
+        <v/>
+      </c>
+      <c r="L71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R71">
+        <f>L71/M71-1</f>
+        <v/>
+      </c>
+      <c r="S71">
+        <f>N71/M71-1</f>
+        <v/>
+      </c>
+      <c r="U71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA71">
+        <f>U71/V71-1</f>
+        <v/>
+      </c>
+      <c r="AB71">
+        <f>W71/V71-1</f>
+        <v/>
+      </c>
+      <c r="AD71" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE71" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <f>AD71/AE71-1</f>
+        <v/>
+      </c>
+      <c r="AK71">
+        <f>AF71/AE71-1</f>
+        <v/>
+      </c>
+      <c r="AM71" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN71" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS71">
+        <f>AM71/AN71-1</f>
+        <v/>
+      </c>
+      <c r="AT71">
+        <f>AO71/AN71-1</f>
+        <v/>
+      </c>
+      <c r="AV71" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW71" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB71">
+        <f>AV71/AW71-1</f>
+        <v/>
+      </c>
+      <c r="BC71">
+        <f>AX71/AW71-1</f>
+        <v/>
+      </c>
+      <c r="BE71" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF71" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH71" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI71" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK71">
+        <f>BE71/BF71-1</f>
+        <v/>
+      </c>
+      <c r="BL71">
+        <f>BG71/BF71-1</f>
+        <v/>
+      </c>
+      <c r="BN71" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO71" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ71" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR71" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT71">
+        <f>BN71/BO71-1</f>
+        <v/>
+      </c>
+      <c r="BU71">
+        <f>BP71/BO71-1</f>
+        <v/>
+      </c>
+      <c r="BW71" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX71" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ71" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA71" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC71">
+        <f>BW71/BX71-1</f>
+        <v/>
+      </c>
+      <c r="CD71">
+        <f>BY71/BX71-1</f>
+        <v/>
+      </c>
+      <c r="CF71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI71" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ71" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL71">
+        <f>CF71/CG71-1</f>
+        <v/>
+      </c>
+      <c r="CM71">
+        <f>CH71/CG71-1</f>
+        <v/>
+      </c>
+      <c r="CO71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR71" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS71" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU71">
+        <f>CO71/CP71-1</f>
+        <v/>
+      </c>
+      <c r="CV71">
+        <f>CQ71/CP71-1</f>
+        <v/>
+      </c>
+      <c r="CX71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY71" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA71" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB71" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD71">
+        <f>CX71/CY71-1</f>
+        <v/>
+      </c>
+      <c r="DE71">
+        <f>CZ71/CY71-1</f>
+        <v/>
+      </c>
+      <c r="DG71" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH71" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ71" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK71" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM71">
+        <f>DG71/DH71-1</f>
+        <v/>
+      </c>
+      <c r="DN71">
+        <f>DI71/DH71-1</f>
+        <v/>
+      </c>
+      <c r="DP71" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ71" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DS71" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT71" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DV71">
+        <f>DP71/DQ71-1</f>
+        <v/>
+      </c>
+      <c r="DW71">
+        <f>DR71/DQ71-1</f>
+        <v/>
+      </c>
+      <c r="DY71" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ71" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB71" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC71" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE71">
+        <f>DY71/DZ71-1</f>
+        <v/>
+      </c>
+      <c r="EF71">
+        <f>EA71/DZ71-1</f>
+        <v/>
+      </c>
+      <c r="EH71" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI71" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK71" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL71" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN71">
+        <f>EH71/EI71-1</f>
+        <v/>
+      </c>
+      <c r="EO71">
+        <f>EJ71/EI71-1</f>
+        <v/>
+      </c>
+      <c r="EQ71" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER71" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET71" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU71" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW71">
+        <f>EQ71/ER71-1</f>
+        <v/>
+      </c>
+      <c r="EX71">
+        <f>ES71/ER71-1</f>
+        <v/>
+      </c>
+      <c r="EZ71" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA71" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC71" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD71" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF71">
+        <f>EZ71/FA71-1</f>
+        <v/>
+      </c>
+      <c r="FG71">
+        <f>FB71/FA71-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG71"/>
+  <dimension ref="A1:FG72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -32107,6 +32107,445 @@
         <v/>
       </c>
     </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>09 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I72">
+        <f>C72/D72-1</f>
+        <v/>
+      </c>
+      <c r="J72">
+        <f>E72/D72-1</f>
+        <v/>
+      </c>
+      <c r="L72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R72">
+        <f>L72/M72-1</f>
+        <v/>
+      </c>
+      <c r="S72">
+        <f>N72/M72-1</f>
+        <v/>
+      </c>
+      <c r="U72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA72">
+        <f>U72/V72-1</f>
+        <v/>
+      </c>
+      <c r="AB72">
+        <f>W72/V72-1</f>
+        <v/>
+      </c>
+      <c r="AD72" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE72" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ72">
+        <f>AD72/AE72-1</f>
+        <v/>
+      </c>
+      <c r="AK72">
+        <f>AF72/AE72-1</f>
+        <v/>
+      </c>
+      <c r="AM72" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN72" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS72">
+        <f>AM72/AN72-1</f>
+        <v/>
+      </c>
+      <c r="AT72">
+        <f>AO72/AN72-1</f>
+        <v/>
+      </c>
+      <c r="AV72" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW72" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB72">
+        <f>AV72/AW72-1</f>
+        <v/>
+      </c>
+      <c r="BC72">
+        <f>AX72/AW72-1</f>
+        <v/>
+      </c>
+      <c r="BE72" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF72" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH72" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI72" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK72">
+        <f>BE72/BF72-1</f>
+        <v/>
+      </c>
+      <c r="BL72">
+        <f>BG72/BF72-1</f>
+        <v/>
+      </c>
+      <c r="BN72" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO72" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ72" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR72" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT72">
+        <f>BN72/BO72-1</f>
+        <v/>
+      </c>
+      <c r="BU72">
+        <f>BP72/BO72-1</f>
+        <v/>
+      </c>
+      <c r="BW72" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX72" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ72" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA72" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC72">
+        <f>BW72/BX72-1</f>
+        <v/>
+      </c>
+      <c r="CD72">
+        <f>BY72/BX72-1</f>
+        <v/>
+      </c>
+      <c r="CF72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI72" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ72" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL72">
+        <f>CF72/CG72-1</f>
+        <v/>
+      </c>
+      <c r="CM72">
+        <f>CH72/CG72-1</f>
+        <v/>
+      </c>
+      <c r="CO72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR72" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS72" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU72">
+        <f>CO72/CP72-1</f>
+        <v/>
+      </c>
+      <c r="CV72">
+        <f>CQ72/CP72-1</f>
+        <v/>
+      </c>
+      <c r="CX72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY72" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA72" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB72" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD72">
+        <f>CX72/CY72-1</f>
+        <v/>
+      </c>
+      <c r="DE72">
+        <f>CZ72/CY72-1</f>
+        <v/>
+      </c>
+      <c r="DG72" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH72" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ72" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK72" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM72">
+        <f>DG72/DH72-1</f>
+        <v/>
+      </c>
+      <c r="DN72">
+        <f>DI72/DH72-1</f>
+        <v/>
+      </c>
+      <c r="DP72" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ72" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS72" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT72" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV72">
+        <f>DP72/DQ72-1</f>
+        <v/>
+      </c>
+      <c r="DW72">
+        <f>DR72/DQ72-1</f>
+        <v/>
+      </c>
+      <c r="DY72" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ72" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB72" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC72" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE72">
+        <f>DY72/DZ72-1</f>
+        <v/>
+      </c>
+      <c r="EF72">
+        <f>EA72/DZ72-1</f>
+        <v/>
+      </c>
+      <c r="EH72" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI72" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK72" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL72" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN72">
+        <f>EH72/EI72-1</f>
+        <v/>
+      </c>
+      <c r="EO72">
+        <f>EJ72/EI72-1</f>
+        <v/>
+      </c>
+      <c r="EQ72" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER72" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET72" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU72" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW72">
+        <f>EQ72/ER72-1</f>
+        <v/>
+      </c>
+      <c r="EX72">
+        <f>ES72/ER72-1</f>
+        <v/>
+      </c>
+      <c r="EZ72" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA72" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC72" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD72" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF72">
+        <f>EZ72/FA72-1</f>
+        <v/>
+      </c>
+      <c r="FG72">
+        <f>FB72/FA72-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG72"/>
+  <dimension ref="A1:FG73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -32546,6 +32546,447 @@
         <v/>
       </c>
     </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>09 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I73">
+        <f>C73/D73-1</f>
+        <v/>
+      </c>
+      <c r="J73">
+        <f>E73/D73-1</f>
+        <v/>
+      </c>
+      <c r="L73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R73">
+        <f>L73/M73-1</f>
+        <v/>
+      </c>
+      <c r="S73">
+        <f>N73/M73-1</f>
+        <v/>
+      </c>
+      <c r="U73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA73">
+        <f>U73/V73-1</f>
+        <v/>
+      </c>
+      <c r="AB73">
+        <f>W73/V73-1</f>
+        <v/>
+      </c>
+      <c r="AD73" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE73" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <f>AD73/AE73-1</f>
+        <v/>
+      </c>
+      <c r="AK73">
+        <f>AF73/AE73-1</f>
+        <v/>
+      </c>
+      <c r="AM73" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN73" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS73">
+        <f>AM73/AN73-1</f>
+        <v/>
+      </c>
+      <c r="AT73">
+        <f>AO73/AN73-1</f>
+        <v/>
+      </c>
+      <c r="AV73" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW73" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB73">
+        <f>AV73/AW73-1</f>
+        <v/>
+      </c>
+      <c r="BC73">
+        <f>AX73/AW73-1</f>
+        <v/>
+      </c>
+      <c r="BE73" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF73" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH73" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI73" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK73">
+        <f>BE73/BF73-1</f>
+        <v/>
+      </c>
+      <c r="BL73">
+        <f>BG73/BF73-1</f>
+        <v/>
+      </c>
+      <c r="BN73" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO73" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ73" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR73" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT73">
+        <f>BN73/BO73-1</f>
+        <v/>
+      </c>
+      <c r="BU73">
+        <f>BP73/BO73-1</f>
+        <v/>
+      </c>
+      <c r="BW73" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX73" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ73" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA73" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC73">
+        <f>BW73/BX73-1</f>
+        <v/>
+      </c>
+      <c r="CD73">
+        <f>BY73/BX73-1</f>
+        <v/>
+      </c>
+      <c r="CF73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI73" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ73" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL73">
+        <f>CF73/CG73-1</f>
+        <v/>
+      </c>
+      <c r="CM73">
+        <f>CH73/CG73-1</f>
+        <v/>
+      </c>
+      <c r="CO73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR73" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS73" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU73">
+        <f>CO73/CP73-1</f>
+        <v/>
+      </c>
+      <c r="CV73">
+        <f>CQ73/CP73-1</f>
+        <v/>
+      </c>
+      <c r="CX73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY73" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA73" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB73" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD73">
+        <f>CX73/CY73-1</f>
+        <v/>
+      </c>
+      <c r="DE73">
+        <f>CZ73/CY73-1</f>
+        <v/>
+      </c>
+      <c r="DG73" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH73" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ73" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK73" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM73">
+        <f>DG73/DH73-1</f>
+        <v/>
+      </c>
+      <c r="DN73">
+        <f>DI73/DH73-1</f>
+        <v/>
+      </c>
+      <c r="DP73" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ73" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS73" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT73" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV73">
+        <f>DP73/DQ73-1</f>
+        <v/>
+      </c>
+      <c r="DW73">
+        <f>DR73/DQ73-1</f>
+        <v/>
+      </c>
+      <c r="DY73" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ73" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB73" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC73" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE73">
+        <f>DY73/DZ73-1</f>
+        <v/>
+      </c>
+      <c r="EF73">
+        <f>EA73/DZ73-1</f>
+        <v/>
+      </c>
+      <c r="EH73" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI73" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EK73" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL73" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EN73">
+        <f>EH73/EI73-1</f>
+        <v/>
+      </c>
+      <c r="EO73">
+        <f>EJ73/EI73-1</f>
+        <v/>
+      </c>
+      <c r="EQ73" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER73" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET73" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU73" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW73">
+        <f>EQ73/ER73-1</f>
+        <v/>
+      </c>
+      <c r="EX73">
+        <f>ES73/ER73-1</f>
+        <v/>
+      </c>
+      <c r="EZ73" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA73" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC73" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD73" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF73">
+        <f>EZ73/FA73-1</f>
+        <v/>
+      </c>
+      <c r="FG73">
+        <f>FB73/FA73-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG73"/>
+  <dimension ref="A1:FG74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -32987,6 +32987,445 @@
         <v/>
       </c>
     </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>09 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I74">
+        <f>C74/D74-1</f>
+        <v/>
+      </c>
+      <c r="J74">
+        <f>E74/D74-1</f>
+        <v/>
+      </c>
+      <c r="L74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R74">
+        <f>L74/M74-1</f>
+        <v/>
+      </c>
+      <c r="S74">
+        <f>N74/M74-1</f>
+        <v/>
+      </c>
+      <c r="U74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA74">
+        <f>U74/V74-1</f>
+        <v/>
+      </c>
+      <c r="AB74">
+        <f>W74/V74-1</f>
+        <v/>
+      </c>
+      <c r="AD74" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE74" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ74">
+        <f>AD74/AE74-1</f>
+        <v/>
+      </c>
+      <c r="AK74">
+        <f>AF74/AE74-1</f>
+        <v/>
+      </c>
+      <c r="AM74" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN74" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS74">
+        <f>AM74/AN74-1</f>
+        <v/>
+      </c>
+      <c r="AT74">
+        <f>AO74/AN74-1</f>
+        <v/>
+      </c>
+      <c r="AV74" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW74" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB74">
+        <f>AV74/AW74-1</f>
+        <v/>
+      </c>
+      <c r="BC74">
+        <f>AX74/AW74-1</f>
+        <v/>
+      </c>
+      <c r="BE74" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF74" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH74" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI74" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK74">
+        <f>BE74/BF74-1</f>
+        <v/>
+      </c>
+      <c r="BL74">
+        <f>BG74/BF74-1</f>
+        <v/>
+      </c>
+      <c r="BN74" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO74" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ74" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR74" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT74">
+        <f>BN74/BO74-1</f>
+        <v/>
+      </c>
+      <c r="BU74">
+        <f>BP74/BO74-1</f>
+        <v/>
+      </c>
+      <c r="BW74" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX74" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ74" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA74" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC74">
+        <f>BW74/BX74-1</f>
+        <v/>
+      </c>
+      <c r="CD74">
+        <f>BY74/BX74-1</f>
+        <v/>
+      </c>
+      <c r="CF74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI74" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ74" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL74">
+        <f>CF74/CG74-1</f>
+        <v/>
+      </c>
+      <c r="CM74">
+        <f>CH74/CG74-1</f>
+        <v/>
+      </c>
+      <c r="CO74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR74" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS74" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU74">
+        <f>CO74/CP74-1</f>
+        <v/>
+      </c>
+      <c r="CV74">
+        <f>CQ74/CP74-1</f>
+        <v/>
+      </c>
+      <c r="CX74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY74" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA74" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB74" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD74">
+        <f>CX74/CY74-1</f>
+        <v/>
+      </c>
+      <c r="DE74">
+        <f>CZ74/CY74-1</f>
+        <v/>
+      </c>
+      <c r="DG74" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH74" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ74" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK74" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM74">
+        <f>DG74/DH74-1</f>
+        <v/>
+      </c>
+      <c r="DN74">
+        <f>DI74/DH74-1</f>
+        <v/>
+      </c>
+      <c r="DP74" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ74" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS74" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT74" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV74">
+        <f>DP74/DQ74-1</f>
+        <v/>
+      </c>
+      <c r="DW74">
+        <f>DR74/DQ74-1</f>
+        <v/>
+      </c>
+      <c r="DY74" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ74" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB74" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC74" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE74">
+        <f>DY74/DZ74-1</f>
+        <v/>
+      </c>
+      <c r="EF74">
+        <f>EA74/DZ74-1</f>
+        <v/>
+      </c>
+      <c r="EH74" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI74" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK74" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL74" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN74">
+        <f>EH74/EI74-1</f>
+        <v/>
+      </c>
+      <c r="EO74">
+        <f>EJ74/EI74-1</f>
+        <v/>
+      </c>
+      <c r="EQ74" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER74" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET74" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU74" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW74">
+        <f>EQ74/ER74-1</f>
+        <v/>
+      </c>
+      <c r="EX74">
+        <f>ES74/ER74-1</f>
+        <v/>
+      </c>
+      <c r="EZ74" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA74" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC74" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD74" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF74">
+        <f>EZ74/FA74-1</f>
+        <v/>
+      </c>
+      <c r="FG74">
+        <f>FB74/FA74-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG74"/>
+  <dimension ref="A1:FG75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -33426,6 +33426,445 @@
         <v/>
       </c>
     </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>09 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I75">
+        <f>C75/D75-1</f>
+        <v/>
+      </c>
+      <c r="J75">
+        <f>E75/D75-1</f>
+        <v/>
+      </c>
+      <c r="L75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R75">
+        <f>L75/M75-1</f>
+        <v/>
+      </c>
+      <c r="S75">
+        <f>N75/M75-1</f>
+        <v/>
+      </c>
+      <c r="U75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA75">
+        <f>U75/V75-1</f>
+        <v/>
+      </c>
+      <c r="AB75">
+        <f>W75/V75-1</f>
+        <v/>
+      </c>
+      <c r="AD75" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE75" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ75">
+        <f>AD75/AE75-1</f>
+        <v/>
+      </c>
+      <c r="AK75">
+        <f>AF75/AE75-1</f>
+        <v/>
+      </c>
+      <c r="AM75" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN75" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS75">
+        <f>AM75/AN75-1</f>
+        <v/>
+      </c>
+      <c r="AT75">
+        <f>AO75/AN75-1</f>
+        <v/>
+      </c>
+      <c r="AV75" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW75" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB75">
+        <f>AV75/AW75-1</f>
+        <v/>
+      </c>
+      <c r="BC75">
+        <f>AX75/AW75-1</f>
+        <v/>
+      </c>
+      <c r="BE75" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF75" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH75" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI75" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK75">
+        <f>BE75/BF75-1</f>
+        <v/>
+      </c>
+      <c r="BL75">
+        <f>BG75/BF75-1</f>
+        <v/>
+      </c>
+      <c r="BN75" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO75" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ75" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR75" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT75">
+        <f>BN75/BO75-1</f>
+        <v/>
+      </c>
+      <c r="BU75">
+        <f>BP75/BO75-1</f>
+        <v/>
+      </c>
+      <c r="BW75" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX75" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ75" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA75" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC75">
+        <f>BW75/BX75-1</f>
+        <v/>
+      </c>
+      <c r="CD75">
+        <f>BY75/BX75-1</f>
+        <v/>
+      </c>
+      <c r="CF75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI75" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ75" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL75">
+        <f>CF75/CG75-1</f>
+        <v/>
+      </c>
+      <c r="CM75">
+        <f>CH75/CG75-1</f>
+        <v/>
+      </c>
+      <c r="CO75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR75" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS75" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU75">
+        <f>CO75/CP75-1</f>
+        <v/>
+      </c>
+      <c r="CV75">
+        <f>CQ75/CP75-1</f>
+        <v/>
+      </c>
+      <c r="CX75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY75" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA75" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB75" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD75">
+        <f>CX75/CY75-1</f>
+        <v/>
+      </c>
+      <c r="DE75">
+        <f>CZ75/CY75-1</f>
+        <v/>
+      </c>
+      <c r="DG75" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH75" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ75" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK75" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM75">
+        <f>DG75/DH75-1</f>
+        <v/>
+      </c>
+      <c r="DN75">
+        <f>DI75/DH75-1</f>
+        <v/>
+      </c>
+      <c r="DP75" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ75" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS75" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT75" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV75">
+        <f>DP75/DQ75-1</f>
+        <v/>
+      </c>
+      <c r="DW75">
+        <f>DR75/DQ75-1</f>
+        <v/>
+      </c>
+      <c r="DY75" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ75" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB75" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC75" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE75">
+        <f>DY75/DZ75-1</f>
+        <v/>
+      </c>
+      <c r="EF75">
+        <f>EA75/DZ75-1</f>
+        <v/>
+      </c>
+      <c r="EH75" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI75" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK75" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL75" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN75">
+        <f>EH75/EI75-1</f>
+        <v/>
+      </c>
+      <c r="EO75">
+        <f>EJ75/EI75-1</f>
+        <v/>
+      </c>
+      <c r="EQ75" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER75" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET75" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU75" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW75">
+        <f>EQ75/ER75-1</f>
+        <v/>
+      </c>
+      <c r="EX75">
+        <f>ES75/ER75-1</f>
+        <v/>
+      </c>
+      <c r="EZ75" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA75" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC75" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD75" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF75">
+        <f>EZ75/FA75-1</f>
+        <v/>
+      </c>
+      <c r="FG75">
+        <f>FB75/FA75-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG75"/>
+  <dimension ref="A1:FG76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -33865,6 +33865,445 @@
         <v/>
       </c>
     </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>10 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I76">
+        <f>C76/D76-1</f>
+        <v/>
+      </c>
+      <c r="J76">
+        <f>E76/D76-1</f>
+        <v/>
+      </c>
+      <c r="L76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R76">
+        <f>L76/M76-1</f>
+        <v/>
+      </c>
+      <c r="S76">
+        <f>N76/M76-1</f>
+        <v/>
+      </c>
+      <c r="U76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA76">
+        <f>U76/V76-1</f>
+        <v/>
+      </c>
+      <c r="AB76">
+        <f>W76/V76-1</f>
+        <v/>
+      </c>
+      <c r="AD76" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE76" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ76">
+        <f>AD76/AE76-1</f>
+        <v/>
+      </c>
+      <c r="AK76">
+        <f>AF76/AE76-1</f>
+        <v/>
+      </c>
+      <c r="AM76" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN76" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS76">
+        <f>AM76/AN76-1</f>
+        <v/>
+      </c>
+      <c r="AT76">
+        <f>AO76/AN76-1</f>
+        <v/>
+      </c>
+      <c r="AV76" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW76" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB76">
+        <f>AV76/AW76-1</f>
+        <v/>
+      </c>
+      <c r="BC76">
+        <f>AX76/AW76-1</f>
+        <v/>
+      </c>
+      <c r="BE76" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF76" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH76" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI76" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK76">
+        <f>BE76/BF76-1</f>
+        <v/>
+      </c>
+      <c r="BL76">
+        <f>BG76/BF76-1</f>
+        <v/>
+      </c>
+      <c r="BN76" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO76" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ76" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR76" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT76">
+        <f>BN76/BO76-1</f>
+        <v/>
+      </c>
+      <c r="BU76">
+        <f>BP76/BO76-1</f>
+        <v/>
+      </c>
+      <c r="BW76" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX76" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ76" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA76" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC76">
+        <f>BW76/BX76-1</f>
+        <v/>
+      </c>
+      <c r="CD76">
+        <f>BY76/BX76-1</f>
+        <v/>
+      </c>
+      <c r="CF76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI76" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ76" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL76">
+        <f>CF76/CG76-1</f>
+        <v/>
+      </c>
+      <c r="CM76">
+        <f>CH76/CG76-1</f>
+        <v/>
+      </c>
+      <c r="CO76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR76" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS76" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU76">
+        <f>CO76/CP76-1</f>
+        <v/>
+      </c>
+      <c r="CV76">
+        <f>CQ76/CP76-1</f>
+        <v/>
+      </c>
+      <c r="CX76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY76" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA76" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB76" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD76">
+        <f>CX76/CY76-1</f>
+        <v/>
+      </c>
+      <c r="DE76">
+        <f>CZ76/CY76-1</f>
+        <v/>
+      </c>
+      <c r="DG76" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH76" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ76" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK76" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM76">
+        <f>DG76/DH76-1</f>
+        <v/>
+      </c>
+      <c r="DN76">
+        <f>DI76/DH76-1</f>
+        <v/>
+      </c>
+      <c r="DP76" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ76" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS76" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT76" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV76">
+        <f>DP76/DQ76-1</f>
+        <v/>
+      </c>
+      <c r="DW76">
+        <f>DR76/DQ76-1</f>
+        <v/>
+      </c>
+      <c r="DY76" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ76" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB76" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC76" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE76">
+        <f>DY76/DZ76-1</f>
+        <v/>
+      </c>
+      <c r="EF76">
+        <f>EA76/DZ76-1</f>
+        <v/>
+      </c>
+      <c r="EH76" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI76" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK76" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL76" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN76">
+        <f>EH76/EI76-1</f>
+        <v/>
+      </c>
+      <c r="EO76">
+        <f>EJ76/EI76-1</f>
+        <v/>
+      </c>
+      <c r="EQ76" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER76" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET76" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU76" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW76">
+        <f>EQ76/ER76-1</f>
+        <v/>
+      </c>
+      <c r="EX76">
+        <f>ES76/ER76-1</f>
+        <v/>
+      </c>
+      <c r="EZ76" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA76" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC76" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD76" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF76">
+        <f>EZ76/FA76-1</f>
+        <v/>
+      </c>
+      <c r="FG76">
+        <f>FB76/FA76-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG76"/>
+  <dimension ref="A1:FG77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -34304,6 +34304,445 @@
         <v/>
       </c>
     </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>10 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I77">
+        <f>C77/D77-1</f>
+        <v/>
+      </c>
+      <c r="J77">
+        <f>E77/D77-1</f>
+        <v/>
+      </c>
+      <c r="L77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R77">
+        <f>L77/M77-1</f>
+        <v/>
+      </c>
+      <c r="S77">
+        <f>N77/M77-1</f>
+        <v/>
+      </c>
+      <c r="U77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA77">
+        <f>U77/V77-1</f>
+        <v/>
+      </c>
+      <c r="AB77">
+        <f>W77/V77-1</f>
+        <v/>
+      </c>
+      <c r="AD77" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE77" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ77">
+        <f>AD77/AE77-1</f>
+        <v/>
+      </c>
+      <c r="AK77">
+        <f>AF77/AE77-1</f>
+        <v/>
+      </c>
+      <c r="AM77" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN77" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS77">
+        <f>AM77/AN77-1</f>
+        <v/>
+      </c>
+      <c r="AT77">
+        <f>AO77/AN77-1</f>
+        <v/>
+      </c>
+      <c r="AV77" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW77" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB77">
+        <f>AV77/AW77-1</f>
+        <v/>
+      </c>
+      <c r="BC77">
+        <f>AX77/AW77-1</f>
+        <v/>
+      </c>
+      <c r="BE77" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF77" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH77" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI77" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK77">
+        <f>BE77/BF77-1</f>
+        <v/>
+      </c>
+      <c r="BL77">
+        <f>BG77/BF77-1</f>
+        <v/>
+      </c>
+      <c r="BN77" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO77" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ77" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR77" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT77">
+        <f>BN77/BO77-1</f>
+        <v/>
+      </c>
+      <c r="BU77">
+        <f>BP77/BO77-1</f>
+        <v/>
+      </c>
+      <c r="BW77" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX77" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ77" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA77" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC77">
+        <f>BW77/BX77-1</f>
+        <v/>
+      </c>
+      <c r="CD77">
+        <f>BY77/BX77-1</f>
+        <v/>
+      </c>
+      <c r="CF77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI77" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ77" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL77">
+        <f>CF77/CG77-1</f>
+        <v/>
+      </c>
+      <c r="CM77">
+        <f>CH77/CG77-1</f>
+        <v/>
+      </c>
+      <c r="CO77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR77" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS77" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU77">
+        <f>CO77/CP77-1</f>
+        <v/>
+      </c>
+      <c r="CV77">
+        <f>CQ77/CP77-1</f>
+        <v/>
+      </c>
+      <c r="CX77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY77" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA77" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB77" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD77">
+        <f>CX77/CY77-1</f>
+        <v/>
+      </c>
+      <c r="DE77">
+        <f>CZ77/CY77-1</f>
+        <v/>
+      </c>
+      <c r="DG77" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH77" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ77" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK77" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM77">
+        <f>DG77/DH77-1</f>
+        <v/>
+      </c>
+      <c r="DN77">
+        <f>DI77/DH77-1</f>
+        <v/>
+      </c>
+      <c r="DP77" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ77" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS77" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT77" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV77">
+        <f>DP77/DQ77-1</f>
+        <v/>
+      </c>
+      <c r="DW77">
+        <f>DR77/DQ77-1</f>
+        <v/>
+      </c>
+      <c r="DY77" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ77" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB77" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC77" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE77">
+        <f>DY77/DZ77-1</f>
+        <v/>
+      </c>
+      <c r="EF77">
+        <f>EA77/DZ77-1</f>
+        <v/>
+      </c>
+      <c r="EH77" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI77" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK77" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL77" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN77">
+        <f>EH77/EI77-1</f>
+        <v/>
+      </c>
+      <c r="EO77">
+        <f>EJ77/EI77-1</f>
+        <v/>
+      </c>
+      <c r="EQ77" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER77" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET77" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU77" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW77">
+        <f>EQ77/ER77-1</f>
+        <v/>
+      </c>
+      <c r="EX77">
+        <f>ES77/ER77-1</f>
+        <v/>
+      </c>
+      <c r="EZ77" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA77" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC77" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD77" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF77">
+        <f>EZ77/FA77-1</f>
+        <v/>
+      </c>
+      <c r="FG77">
+        <f>FB77/FA77-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG77"/>
+  <dimension ref="A1:FG78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -34743,6 +34743,445 @@
         <v/>
       </c>
     </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>10 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I78">
+        <f>C78/D78-1</f>
+        <v/>
+      </c>
+      <c r="J78">
+        <f>E78/D78-1</f>
+        <v/>
+      </c>
+      <c r="L78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R78">
+        <f>L78/M78-1</f>
+        <v/>
+      </c>
+      <c r="S78">
+        <f>N78/M78-1</f>
+        <v/>
+      </c>
+      <c r="U78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA78">
+        <f>U78/V78-1</f>
+        <v/>
+      </c>
+      <c r="AB78">
+        <f>W78/V78-1</f>
+        <v/>
+      </c>
+      <c r="AD78" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE78" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <f>AD78/AE78-1</f>
+        <v/>
+      </c>
+      <c r="AK78">
+        <f>AF78/AE78-1</f>
+        <v/>
+      </c>
+      <c r="AM78" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN78" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS78">
+        <f>AM78/AN78-1</f>
+        <v/>
+      </c>
+      <c r="AT78">
+        <f>AO78/AN78-1</f>
+        <v/>
+      </c>
+      <c r="AV78" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW78" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB78">
+        <f>AV78/AW78-1</f>
+        <v/>
+      </c>
+      <c r="BC78">
+        <f>AX78/AW78-1</f>
+        <v/>
+      </c>
+      <c r="BE78" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF78" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH78" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI78" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK78">
+        <f>BE78/BF78-1</f>
+        <v/>
+      </c>
+      <c r="BL78">
+        <f>BG78/BF78-1</f>
+        <v/>
+      </c>
+      <c r="BN78" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO78" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ78" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR78" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT78">
+        <f>BN78/BO78-1</f>
+        <v/>
+      </c>
+      <c r="BU78">
+        <f>BP78/BO78-1</f>
+        <v/>
+      </c>
+      <c r="BW78" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX78" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ78" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA78" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC78">
+        <f>BW78/BX78-1</f>
+        <v/>
+      </c>
+      <c r="CD78">
+        <f>BY78/BX78-1</f>
+        <v/>
+      </c>
+      <c r="CF78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI78" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ78" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL78">
+        <f>CF78/CG78-1</f>
+        <v/>
+      </c>
+      <c r="CM78">
+        <f>CH78/CG78-1</f>
+        <v/>
+      </c>
+      <c r="CO78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR78" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS78" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU78">
+        <f>CO78/CP78-1</f>
+        <v/>
+      </c>
+      <c r="CV78">
+        <f>CQ78/CP78-1</f>
+        <v/>
+      </c>
+      <c r="CX78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY78" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA78" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB78" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD78">
+        <f>CX78/CY78-1</f>
+        <v/>
+      </c>
+      <c r="DE78">
+        <f>CZ78/CY78-1</f>
+        <v/>
+      </c>
+      <c r="DG78" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH78" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ78" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK78" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM78">
+        <f>DG78/DH78-1</f>
+        <v/>
+      </c>
+      <c r="DN78">
+        <f>DI78/DH78-1</f>
+        <v/>
+      </c>
+      <c r="DP78" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ78" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS78" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT78" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV78">
+        <f>DP78/DQ78-1</f>
+        <v/>
+      </c>
+      <c r="DW78">
+        <f>DR78/DQ78-1</f>
+        <v/>
+      </c>
+      <c r="DY78" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ78" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB78" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC78" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE78">
+        <f>DY78/DZ78-1</f>
+        <v/>
+      </c>
+      <c r="EF78">
+        <f>EA78/DZ78-1</f>
+        <v/>
+      </c>
+      <c r="EH78" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI78" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK78" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL78" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN78">
+        <f>EH78/EI78-1</f>
+        <v/>
+      </c>
+      <c r="EO78">
+        <f>EJ78/EI78-1</f>
+        <v/>
+      </c>
+      <c r="EQ78" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER78" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET78" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU78" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW78">
+        <f>EQ78/ER78-1</f>
+        <v/>
+      </c>
+      <c r="EX78">
+        <f>ES78/ER78-1</f>
+        <v/>
+      </c>
+      <c r="EZ78" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA78" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC78" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD78" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF78">
+        <f>EZ78/FA78-1</f>
+        <v/>
+      </c>
+      <c r="FG78">
+        <f>FB78/FA78-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG78"/>
+  <dimension ref="A1:FG79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -35182,6 +35182,445 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>10 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I79">
+        <f>C79/D79-1</f>
+        <v/>
+      </c>
+      <c r="J79">
+        <f>E79/D79-1</f>
+        <v/>
+      </c>
+      <c r="L79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R79">
+        <f>L79/M79-1</f>
+        <v/>
+      </c>
+      <c r="S79">
+        <f>N79/M79-1</f>
+        <v/>
+      </c>
+      <c r="U79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA79">
+        <f>U79/V79-1</f>
+        <v/>
+      </c>
+      <c r="AB79">
+        <f>W79/V79-1</f>
+        <v/>
+      </c>
+      <c r="AD79" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE79" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ79">
+        <f>AD79/AE79-1</f>
+        <v/>
+      </c>
+      <c r="AK79">
+        <f>AF79/AE79-1</f>
+        <v/>
+      </c>
+      <c r="AM79" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN79" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS79">
+        <f>AM79/AN79-1</f>
+        <v/>
+      </c>
+      <c r="AT79">
+        <f>AO79/AN79-1</f>
+        <v/>
+      </c>
+      <c r="AV79" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW79" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB79">
+        <f>AV79/AW79-1</f>
+        <v/>
+      </c>
+      <c r="BC79">
+        <f>AX79/AW79-1</f>
+        <v/>
+      </c>
+      <c r="BE79" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF79" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH79" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI79" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK79">
+        <f>BE79/BF79-1</f>
+        <v/>
+      </c>
+      <c r="BL79">
+        <f>BG79/BF79-1</f>
+        <v/>
+      </c>
+      <c r="BN79" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO79" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ79" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR79" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT79">
+        <f>BN79/BO79-1</f>
+        <v/>
+      </c>
+      <c r="BU79">
+        <f>BP79/BO79-1</f>
+        <v/>
+      </c>
+      <c r="BW79" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX79" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ79" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA79" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC79">
+        <f>BW79/BX79-1</f>
+        <v/>
+      </c>
+      <c r="CD79">
+        <f>BY79/BX79-1</f>
+        <v/>
+      </c>
+      <c r="CF79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI79" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ79" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL79">
+        <f>CF79/CG79-1</f>
+        <v/>
+      </c>
+      <c r="CM79">
+        <f>CH79/CG79-1</f>
+        <v/>
+      </c>
+      <c r="CO79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR79" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS79" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU79">
+        <f>CO79/CP79-1</f>
+        <v/>
+      </c>
+      <c r="CV79">
+        <f>CQ79/CP79-1</f>
+        <v/>
+      </c>
+      <c r="CX79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY79" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA79" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB79" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD79">
+        <f>CX79/CY79-1</f>
+        <v/>
+      </c>
+      <c r="DE79">
+        <f>CZ79/CY79-1</f>
+        <v/>
+      </c>
+      <c r="DG79" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH79" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ79" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK79" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM79">
+        <f>DG79/DH79-1</f>
+        <v/>
+      </c>
+      <c r="DN79">
+        <f>DI79/DH79-1</f>
+        <v/>
+      </c>
+      <c r="DP79" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ79" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS79" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT79" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV79">
+        <f>DP79/DQ79-1</f>
+        <v/>
+      </c>
+      <c r="DW79">
+        <f>DR79/DQ79-1</f>
+        <v/>
+      </c>
+      <c r="DY79" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ79" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE79">
+        <f>DY79/DZ79-1</f>
+        <v/>
+      </c>
+      <c r="EF79">
+        <f>EA79/DZ79-1</f>
+        <v/>
+      </c>
+      <c r="EH79" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI79" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN79">
+        <f>EH79/EI79-1</f>
+        <v/>
+      </c>
+      <c r="EO79">
+        <f>EJ79/EI79-1</f>
+        <v/>
+      </c>
+      <c r="EQ79" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER79" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET79" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU79" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW79">
+        <f>EQ79/ER79-1</f>
+        <v/>
+      </c>
+      <c r="EX79">
+        <f>ES79/ER79-1</f>
+        <v/>
+      </c>
+      <c r="EZ79" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA79" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC79" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD79" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF79">
+        <f>EZ79/FA79-1</f>
+        <v/>
+      </c>
+      <c r="FG79">
+        <f>FB79/FA79-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG79"/>
+  <dimension ref="A1:FG80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -35621,6 +35621,447 @@
         <v/>
       </c>
     </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>11 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I80">
+        <f>C80/D80-1</f>
+        <v/>
+      </c>
+      <c r="J80">
+        <f>E80/D80-1</f>
+        <v/>
+      </c>
+      <c r="L80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R80">
+        <f>L80/M80-1</f>
+        <v/>
+      </c>
+      <c r="S80">
+        <f>N80/M80-1</f>
+        <v/>
+      </c>
+      <c r="U80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA80">
+        <f>U80/V80-1</f>
+        <v/>
+      </c>
+      <c r="AB80">
+        <f>W80/V80-1</f>
+        <v/>
+      </c>
+      <c r="AD80" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE80" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ80">
+        <f>AD80/AE80-1</f>
+        <v/>
+      </c>
+      <c r="AK80">
+        <f>AF80/AE80-1</f>
+        <v/>
+      </c>
+      <c r="AM80" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN80" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS80">
+        <f>AM80/AN80-1</f>
+        <v/>
+      </c>
+      <c r="AT80">
+        <f>AO80/AN80-1</f>
+        <v/>
+      </c>
+      <c r="AV80" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW80" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB80">
+        <f>AV80/AW80-1</f>
+        <v/>
+      </c>
+      <c r="BC80">
+        <f>AX80/AW80-1</f>
+        <v/>
+      </c>
+      <c r="BE80" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF80" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI80" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK80">
+        <f>BE80/BF80-1</f>
+        <v/>
+      </c>
+      <c r="BL80">
+        <f>BG80/BF80-1</f>
+        <v/>
+      </c>
+      <c r="BN80" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO80" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ80" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR80" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT80">
+        <f>BN80/BO80-1</f>
+        <v/>
+      </c>
+      <c r="BU80">
+        <f>BP80/BO80-1</f>
+        <v/>
+      </c>
+      <c r="BW80" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX80" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ80" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA80" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC80">
+        <f>BW80/BX80-1</f>
+        <v/>
+      </c>
+      <c r="CD80">
+        <f>BY80/BX80-1</f>
+        <v/>
+      </c>
+      <c r="CF80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI80" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ80" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL80">
+        <f>CF80/CG80-1</f>
+        <v/>
+      </c>
+      <c r="CM80">
+        <f>CH80/CG80-1</f>
+        <v/>
+      </c>
+      <c r="CO80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR80" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS80" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU80">
+        <f>CO80/CP80-1</f>
+        <v/>
+      </c>
+      <c r="CV80">
+        <f>CQ80/CP80-1</f>
+        <v/>
+      </c>
+      <c r="CX80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY80" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA80" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB80" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD80">
+        <f>CX80/CY80-1</f>
+        <v/>
+      </c>
+      <c r="DE80">
+        <f>CZ80/CY80-1</f>
+        <v/>
+      </c>
+      <c r="DG80" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH80" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ80" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK80" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM80">
+        <f>DG80/DH80-1</f>
+        <v/>
+      </c>
+      <c r="DN80">
+        <f>DI80/DH80-1</f>
+        <v/>
+      </c>
+      <c r="DP80" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ80" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS80" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT80" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV80">
+        <f>DP80/DQ80-1</f>
+        <v/>
+      </c>
+      <c r="DW80">
+        <f>DR80/DQ80-1</f>
+        <v/>
+      </c>
+      <c r="DY80" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ80" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB80" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE80">
+        <f>DY80/DZ80-1</f>
+        <v/>
+      </c>
+      <c r="EF80">
+        <f>EA80/DZ80-1</f>
+        <v/>
+      </c>
+      <c r="EH80" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI80" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK80" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL80" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN80">
+        <f>EH80/EI80-1</f>
+        <v/>
+      </c>
+      <c r="EO80">
+        <f>EJ80/EI80-1</f>
+        <v/>
+      </c>
+      <c r="EQ80" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER80" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ET80" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU80" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EW80">
+        <f>EQ80/ER80-1</f>
+        <v/>
+      </c>
+      <c r="EX80">
+        <f>ES80/ER80-1</f>
+        <v/>
+      </c>
+      <c r="EZ80" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA80" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC80" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD80" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF80">
+        <f>EZ80/FA80-1</f>
+        <v/>
+      </c>
+      <c r="FG80">
+        <f>FB80/FA80-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG80"/>
+  <dimension ref="A1:FG81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -36062,6 +36062,445 @@
         <v/>
       </c>
     </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>11 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I81">
+        <f>C81/D81-1</f>
+        <v/>
+      </c>
+      <c r="J81">
+        <f>E81/D81-1</f>
+        <v/>
+      </c>
+      <c r="L81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R81">
+        <f>L81/M81-1</f>
+        <v/>
+      </c>
+      <c r="S81">
+        <f>N81/M81-1</f>
+        <v/>
+      </c>
+      <c r="U81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA81">
+        <f>U81/V81-1</f>
+        <v/>
+      </c>
+      <c r="AB81">
+        <f>W81/V81-1</f>
+        <v/>
+      </c>
+      <c r="AD81" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE81" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ81">
+        <f>AD81/AE81-1</f>
+        <v/>
+      </c>
+      <c r="AK81">
+        <f>AF81/AE81-1</f>
+        <v/>
+      </c>
+      <c r="AM81" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN81" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS81">
+        <f>AM81/AN81-1</f>
+        <v/>
+      </c>
+      <c r="AT81">
+        <f>AO81/AN81-1</f>
+        <v/>
+      </c>
+      <c r="AV81" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW81" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB81">
+        <f>AV81/AW81-1</f>
+        <v/>
+      </c>
+      <c r="BC81">
+        <f>AX81/AW81-1</f>
+        <v/>
+      </c>
+      <c r="BE81" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF81" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH81" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI81" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK81">
+        <f>BE81/BF81-1</f>
+        <v/>
+      </c>
+      <c r="BL81">
+        <f>BG81/BF81-1</f>
+        <v/>
+      </c>
+      <c r="BN81" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO81" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ81" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR81" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT81">
+        <f>BN81/BO81-1</f>
+        <v/>
+      </c>
+      <c r="BU81">
+        <f>BP81/BO81-1</f>
+        <v/>
+      </c>
+      <c r="BW81" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX81" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ81" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA81" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC81">
+        <f>BW81/BX81-1</f>
+        <v/>
+      </c>
+      <c r="CD81">
+        <f>BY81/BX81-1</f>
+        <v/>
+      </c>
+      <c r="CF81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI81" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ81" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL81">
+        <f>CF81/CG81-1</f>
+        <v/>
+      </c>
+      <c r="CM81">
+        <f>CH81/CG81-1</f>
+        <v/>
+      </c>
+      <c r="CO81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR81" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS81" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU81">
+        <f>CO81/CP81-1</f>
+        <v/>
+      </c>
+      <c r="CV81">
+        <f>CQ81/CP81-1</f>
+        <v/>
+      </c>
+      <c r="CX81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY81" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA81" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB81" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD81">
+        <f>CX81/CY81-1</f>
+        <v/>
+      </c>
+      <c r="DE81">
+        <f>CZ81/CY81-1</f>
+        <v/>
+      </c>
+      <c r="DG81" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH81" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ81" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK81" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM81">
+        <f>DG81/DH81-1</f>
+        <v/>
+      </c>
+      <c r="DN81">
+        <f>DI81/DH81-1</f>
+        <v/>
+      </c>
+      <c r="DP81" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ81" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS81" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT81" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV81">
+        <f>DP81/DQ81-1</f>
+        <v/>
+      </c>
+      <c r="DW81">
+        <f>DR81/DQ81-1</f>
+        <v/>
+      </c>
+      <c r="DY81" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ81" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB81" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC81" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE81">
+        <f>DY81/DZ81-1</f>
+        <v/>
+      </c>
+      <c r="EF81">
+        <f>EA81/DZ81-1</f>
+        <v/>
+      </c>
+      <c r="EH81" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI81" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK81" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL81" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN81">
+        <f>EH81/EI81-1</f>
+        <v/>
+      </c>
+      <c r="EO81">
+        <f>EJ81/EI81-1</f>
+        <v/>
+      </c>
+      <c r="EQ81" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER81" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET81" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU81" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW81">
+        <f>EQ81/ER81-1</f>
+        <v/>
+      </c>
+      <c r="EX81">
+        <f>ES81/ER81-1</f>
+        <v/>
+      </c>
+      <c r="EZ81" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA81" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC81" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD81" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF81">
+        <f>EZ81/FA81-1</f>
+        <v/>
+      </c>
+      <c r="FG81">
+        <f>FB81/FA81-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG81"/>
+  <dimension ref="A1:FG82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -36501,6 +36501,445 @@
         <v/>
       </c>
     </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>11 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I82">
+        <f>C82/D82-1</f>
+        <v/>
+      </c>
+      <c r="J82">
+        <f>E82/D82-1</f>
+        <v/>
+      </c>
+      <c r="L82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R82">
+        <f>L82/M82-1</f>
+        <v/>
+      </c>
+      <c r="S82">
+        <f>N82/M82-1</f>
+        <v/>
+      </c>
+      <c r="U82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA82">
+        <f>U82/V82-1</f>
+        <v/>
+      </c>
+      <c r="AB82">
+        <f>W82/V82-1</f>
+        <v/>
+      </c>
+      <c r="AD82" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE82" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ82">
+        <f>AD82/AE82-1</f>
+        <v/>
+      </c>
+      <c r="AK82">
+        <f>AF82/AE82-1</f>
+        <v/>
+      </c>
+      <c r="AM82" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN82" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS82">
+        <f>AM82/AN82-1</f>
+        <v/>
+      </c>
+      <c r="AT82">
+        <f>AO82/AN82-1</f>
+        <v/>
+      </c>
+      <c r="AV82" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW82" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB82">
+        <f>AV82/AW82-1</f>
+        <v/>
+      </c>
+      <c r="BC82">
+        <f>AX82/AW82-1</f>
+        <v/>
+      </c>
+      <c r="BE82" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF82" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH82" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI82" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK82">
+        <f>BE82/BF82-1</f>
+        <v/>
+      </c>
+      <c r="BL82">
+        <f>BG82/BF82-1</f>
+        <v/>
+      </c>
+      <c r="BN82" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO82" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ82" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR82" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT82">
+        <f>BN82/BO82-1</f>
+        <v/>
+      </c>
+      <c r="BU82">
+        <f>BP82/BO82-1</f>
+        <v/>
+      </c>
+      <c r="BW82" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX82" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ82" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA82" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC82">
+        <f>BW82/BX82-1</f>
+        <v/>
+      </c>
+      <c r="CD82">
+        <f>BY82/BX82-1</f>
+        <v/>
+      </c>
+      <c r="CF82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI82" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ82" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL82">
+        <f>CF82/CG82-1</f>
+        <v/>
+      </c>
+      <c r="CM82">
+        <f>CH82/CG82-1</f>
+        <v/>
+      </c>
+      <c r="CO82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR82" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS82" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU82">
+        <f>CO82/CP82-1</f>
+        <v/>
+      </c>
+      <c r="CV82">
+        <f>CQ82/CP82-1</f>
+        <v/>
+      </c>
+      <c r="CX82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY82" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA82" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB82" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD82">
+        <f>CX82/CY82-1</f>
+        <v/>
+      </c>
+      <c r="DE82">
+        <f>CZ82/CY82-1</f>
+        <v/>
+      </c>
+      <c r="DG82" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH82" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ82" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK82" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM82">
+        <f>DG82/DH82-1</f>
+        <v/>
+      </c>
+      <c r="DN82">
+        <f>DI82/DH82-1</f>
+        <v/>
+      </c>
+      <c r="DP82" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ82" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS82" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT82" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV82">
+        <f>DP82/DQ82-1</f>
+        <v/>
+      </c>
+      <c r="DW82">
+        <f>DR82/DQ82-1</f>
+        <v/>
+      </c>
+      <c r="DY82" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ82" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB82" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC82" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE82">
+        <f>DY82/DZ82-1</f>
+        <v/>
+      </c>
+      <c r="EF82">
+        <f>EA82/DZ82-1</f>
+        <v/>
+      </c>
+      <c r="EH82" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI82" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK82" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL82" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN82">
+        <f>EH82/EI82-1</f>
+        <v/>
+      </c>
+      <c r="EO82">
+        <f>EJ82/EI82-1</f>
+        <v/>
+      </c>
+      <c r="EQ82" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER82" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET82" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU82" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW82">
+        <f>EQ82/ER82-1</f>
+        <v/>
+      </c>
+      <c r="EX82">
+        <f>ES82/ER82-1</f>
+        <v/>
+      </c>
+      <c r="EZ82" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA82" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC82" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD82" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF82">
+        <f>EZ82/FA82-1</f>
+        <v/>
+      </c>
+      <c r="FG82">
+        <f>FB82/FA82-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG82"/>
+  <dimension ref="A1:FG83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -36940,6 +36940,445 @@
         <v/>
       </c>
     </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>11 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I83">
+        <f>C83/D83-1</f>
+        <v/>
+      </c>
+      <c r="J83">
+        <f>E83/D83-1</f>
+        <v/>
+      </c>
+      <c r="L83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R83">
+        <f>L83/M83-1</f>
+        <v/>
+      </c>
+      <c r="S83">
+        <f>N83/M83-1</f>
+        <v/>
+      </c>
+      <c r="U83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA83">
+        <f>U83/V83-1</f>
+        <v/>
+      </c>
+      <c r="AB83">
+        <f>W83/V83-1</f>
+        <v/>
+      </c>
+      <c r="AD83" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE83" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <f>AD83/AE83-1</f>
+        <v/>
+      </c>
+      <c r="AK83">
+        <f>AF83/AE83-1</f>
+        <v/>
+      </c>
+      <c r="AM83" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN83" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS83">
+        <f>AM83/AN83-1</f>
+        <v/>
+      </c>
+      <c r="AT83">
+        <f>AO83/AN83-1</f>
+        <v/>
+      </c>
+      <c r="AV83" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW83" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB83">
+        <f>AV83/AW83-1</f>
+        <v/>
+      </c>
+      <c r="BC83">
+        <f>AX83/AW83-1</f>
+        <v/>
+      </c>
+      <c r="BE83" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF83" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH83" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI83" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK83">
+        <f>BE83/BF83-1</f>
+        <v/>
+      </c>
+      <c r="BL83">
+        <f>BG83/BF83-1</f>
+        <v/>
+      </c>
+      <c r="BN83" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO83" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ83" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR83" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT83">
+        <f>BN83/BO83-1</f>
+        <v/>
+      </c>
+      <c r="BU83">
+        <f>BP83/BO83-1</f>
+        <v/>
+      </c>
+      <c r="BW83" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX83" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ83" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA83" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC83">
+        <f>BW83/BX83-1</f>
+        <v/>
+      </c>
+      <c r="CD83">
+        <f>BY83/BX83-1</f>
+        <v/>
+      </c>
+      <c r="CF83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI83" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ83" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL83">
+        <f>CF83/CG83-1</f>
+        <v/>
+      </c>
+      <c r="CM83">
+        <f>CH83/CG83-1</f>
+        <v/>
+      </c>
+      <c r="CO83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR83" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS83" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU83">
+        <f>CO83/CP83-1</f>
+        <v/>
+      </c>
+      <c r="CV83">
+        <f>CQ83/CP83-1</f>
+        <v/>
+      </c>
+      <c r="CX83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY83" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA83" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB83" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD83">
+        <f>CX83/CY83-1</f>
+        <v/>
+      </c>
+      <c r="DE83">
+        <f>CZ83/CY83-1</f>
+        <v/>
+      </c>
+      <c r="DG83" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH83" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ83" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK83" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM83">
+        <f>DG83/DH83-1</f>
+        <v/>
+      </c>
+      <c r="DN83">
+        <f>DI83/DH83-1</f>
+        <v/>
+      </c>
+      <c r="DP83" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ83" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS83" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT83" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV83">
+        <f>DP83/DQ83-1</f>
+        <v/>
+      </c>
+      <c r="DW83">
+        <f>DR83/DQ83-1</f>
+        <v/>
+      </c>
+      <c r="DY83" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ83" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB83" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC83" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE83">
+        <f>DY83/DZ83-1</f>
+        <v/>
+      </c>
+      <c r="EF83">
+        <f>EA83/DZ83-1</f>
+        <v/>
+      </c>
+      <c r="EH83" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI83" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK83" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL83" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN83">
+        <f>EH83/EI83-1</f>
+        <v/>
+      </c>
+      <c r="EO83">
+        <f>EJ83/EI83-1</f>
+        <v/>
+      </c>
+      <c r="EQ83" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER83" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET83" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU83" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW83">
+        <f>EQ83/ER83-1</f>
+        <v/>
+      </c>
+      <c r="EX83">
+        <f>ES83/ER83-1</f>
+        <v/>
+      </c>
+      <c r="EZ83" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA83" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC83" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD83" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF83">
+        <f>EZ83/FA83-1</f>
+        <v/>
+      </c>
+      <c r="FG83">
+        <f>FB83/FA83-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG83"/>
+  <dimension ref="A1:FG84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -37379,6 +37379,449 @@
         <v/>
       </c>
     </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>12 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I84">
+        <f>C84/D84-1</f>
+        <v/>
+      </c>
+      <c r="J84">
+        <f>E84/D84-1</f>
+        <v/>
+      </c>
+      <c r="L84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R84">
+        <f>L84/M84-1</f>
+        <v/>
+      </c>
+      <c r="S84">
+        <f>N84/M84-1</f>
+        <v/>
+      </c>
+      <c r="U84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA84">
+        <f>U84/V84-1</f>
+        <v/>
+      </c>
+      <c r="AB84">
+        <f>W84/V84-1</f>
+        <v/>
+      </c>
+      <c r="AD84" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AJ84">
+        <f>AD84/AE84-1</f>
+        <v/>
+      </c>
+      <c r="AK84">
+        <f>AF84/AE84-1</f>
+        <v/>
+      </c>
+      <c r="AM84" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN84" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AS84">
+        <f>AM84/AN84-1</f>
+        <v/>
+      </c>
+      <c r="AT84">
+        <f>AO84/AN84-1</f>
+        <v/>
+      </c>
+      <c r="AV84" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW84" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB84">
+        <f>AV84/AW84-1</f>
+        <v/>
+      </c>
+      <c r="BC84">
+        <f>AX84/AW84-1</f>
+        <v/>
+      </c>
+      <c r="BE84" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF84" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH84" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI84" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK84">
+        <f>BE84/BF84-1</f>
+        <v/>
+      </c>
+      <c r="BL84">
+        <f>BG84/BF84-1</f>
+        <v/>
+      </c>
+      <c r="BN84" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO84" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ84" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR84" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT84">
+        <f>BN84/BO84-1</f>
+        <v/>
+      </c>
+      <c r="BU84">
+        <f>BP84/BO84-1</f>
+        <v/>
+      </c>
+      <c r="BW84" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX84" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ84" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA84" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC84">
+        <f>BW84/BX84-1</f>
+        <v/>
+      </c>
+      <c r="CD84">
+        <f>BY84/BX84-1</f>
+        <v/>
+      </c>
+      <c r="CF84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI84" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ84" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL84">
+        <f>CF84/CG84-1</f>
+        <v/>
+      </c>
+      <c r="CM84">
+        <f>CH84/CG84-1</f>
+        <v/>
+      </c>
+      <c r="CO84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR84" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS84" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU84">
+        <f>CO84/CP84-1</f>
+        <v/>
+      </c>
+      <c r="CV84">
+        <f>CQ84/CP84-1</f>
+        <v/>
+      </c>
+      <c r="CX84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY84" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA84" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB84" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD84">
+        <f>CX84/CY84-1</f>
+        <v/>
+      </c>
+      <c r="DE84">
+        <f>CZ84/CY84-1</f>
+        <v/>
+      </c>
+      <c r="DG84" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH84" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ84" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK84" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM84">
+        <f>DG84/DH84-1</f>
+        <v/>
+      </c>
+      <c r="DN84">
+        <f>DI84/DH84-1</f>
+        <v/>
+      </c>
+      <c r="DP84" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ84" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS84" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT84" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV84">
+        <f>DP84/DQ84-1</f>
+        <v/>
+      </c>
+      <c r="DW84">
+        <f>DR84/DQ84-1</f>
+        <v/>
+      </c>
+      <c r="DY84" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ84" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB84" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC84" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE84">
+        <f>DY84/DZ84-1</f>
+        <v/>
+      </c>
+      <c r="EF84">
+        <f>EA84/DZ84-1</f>
+        <v/>
+      </c>
+      <c r="EH84" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI84" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK84" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL84" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN84">
+        <f>EH84/EI84-1</f>
+        <v/>
+      </c>
+      <c r="EO84">
+        <f>EJ84/EI84-1</f>
+        <v/>
+      </c>
+      <c r="EQ84" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER84" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET84" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU84" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW84">
+        <f>EQ84/ER84-1</f>
+        <v/>
+      </c>
+      <c r="EX84">
+        <f>ES84/ER84-1</f>
+        <v/>
+      </c>
+      <c r="EZ84" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA84" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC84" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD84" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF84">
+        <f>EZ84/FA84-1</f>
+        <v/>
+      </c>
+      <c r="FG84">
+        <f>FB84/FA84-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG84"/>
+  <dimension ref="A1:FG85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -37822,6 +37822,459 @@
         <v/>
       </c>
     </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>12 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I85">
+        <f>C85/D85-1</f>
+        <v/>
+      </c>
+      <c r="J85">
+        <f>E85/D85-1</f>
+        <v/>
+      </c>
+      <c r="L85" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M85" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R85">
+        <f>L85/M85-1</f>
+        <v/>
+      </c>
+      <c r="S85">
+        <f>N85/M85-1</f>
+        <v/>
+      </c>
+      <c r="U85" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V85" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA85">
+        <f>U85/V85-1</f>
+        <v/>
+      </c>
+      <c r="AB85">
+        <f>W85/V85-1</f>
+        <v/>
+      </c>
+      <c r="AD85" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE85" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ85">
+        <f>AD85/AE85-1</f>
+        <v/>
+      </c>
+      <c r="AK85">
+        <f>AF85/AE85-1</f>
+        <v/>
+      </c>
+      <c r="AM85" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AS85">
+        <f>AM85/AN85-1</f>
+        <v/>
+      </c>
+      <c r="AT85">
+        <f>AO85/AN85-1</f>
+        <v/>
+      </c>
+      <c r="AV85" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW85" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB85">
+        <f>AV85/AW85-1</f>
+        <v/>
+      </c>
+      <c r="BC85">
+        <f>AX85/AW85-1</f>
+        <v/>
+      </c>
+      <c r="BE85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF85" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI85" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK85">
+        <f>BE85/BF85-1</f>
+        <v/>
+      </c>
+      <c r="BL85">
+        <f>BG85/BF85-1</f>
+        <v/>
+      </c>
+      <c r="BN85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO85" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR85" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT85">
+        <f>BN85/BO85-1</f>
+        <v/>
+      </c>
+      <c r="BU85">
+        <f>BP85/BO85-1</f>
+        <v/>
+      </c>
+      <c r="BW85" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX85" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ85" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA85" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC85">
+        <f>BW85/BX85-1</f>
+        <v/>
+      </c>
+      <c r="CD85">
+        <f>BY85/BX85-1</f>
+        <v/>
+      </c>
+      <c r="CF85" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG85" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI85" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ85" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL85">
+        <f>CF85/CG85-1</f>
+        <v/>
+      </c>
+      <c r="CM85">
+        <f>CH85/CG85-1</f>
+        <v/>
+      </c>
+      <c r="CO85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CP85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CR85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CS85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CU85">
+        <f>CO85/CP85-1</f>
+        <v/>
+      </c>
+      <c r="CV85">
+        <f>CQ85/CP85-1</f>
+        <v/>
+      </c>
+      <c r="CX85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY85" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB85" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD85">
+        <f>CX85/CY85-1</f>
+        <v/>
+      </c>
+      <c r="DE85">
+        <f>CZ85/CY85-1</f>
+        <v/>
+      </c>
+      <c r="DG85" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH85" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ85" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK85" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM85">
+        <f>DG85/DH85-1</f>
+        <v/>
+      </c>
+      <c r="DN85">
+        <f>DI85/DH85-1</f>
+        <v/>
+      </c>
+      <c r="DP85" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ85" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS85" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT85" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV85">
+        <f>DP85/DQ85-1</f>
+        <v/>
+      </c>
+      <c r="DW85">
+        <f>DR85/DQ85-1</f>
+        <v/>
+      </c>
+      <c r="DY85" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ85" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB85" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC85" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE85">
+        <f>DY85/DZ85-1</f>
+        <v/>
+      </c>
+      <c r="EF85">
+        <f>EA85/DZ85-1</f>
+        <v/>
+      </c>
+      <c r="EH85" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI85" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK85" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL85" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN85">
+        <f>EH85/EI85-1</f>
+        <v/>
+      </c>
+      <c r="EO85">
+        <f>EJ85/EI85-1</f>
+        <v/>
+      </c>
+      <c r="EQ85" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ET85" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU85" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EW85">
+        <f>EQ85/ER85-1</f>
+        <v/>
+      </c>
+      <c r="EX85">
+        <f>ES85/ER85-1</f>
+        <v/>
+      </c>
+      <c r="EZ85" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA85" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC85" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD85" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF85">
+        <f>EZ85/FA85-1</f>
+        <v/>
+      </c>
+      <c r="FG85">
+        <f>FB85/FA85-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG85"/>
+  <dimension ref="A1:FG86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -38275,6 +38275,473 @@
         <v/>
       </c>
     </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>12 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I86">
+        <f>C86/D86-1</f>
+        <v/>
+      </c>
+      <c r="J86">
+        <f>E86/D86-1</f>
+        <v/>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M86" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R86">
+        <f>L86/M86-1</f>
+        <v/>
+      </c>
+      <c r="S86">
+        <f>N86/M86-1</f>
+        <v/>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V86" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA86">
+        <f>U86/V86-1</f>
+        <v/>
+      </c>
+      <c r="AB86">
+        <f>W86/V86-1</f>
+        <v/>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE86" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ86">
+        <f>AD86/AE86-1</f>
+        <v/>
+      </c>
+      <c r="AK86">
+        <f>AF86/AE86-1</f>
+        <v/>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN86" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS86">
+        <f>AM86/AN86-1</f>
+        <v/>
+      </c>
+      <c r="AT86">
+        <f>AO86/AN86-1</f>
+        <v/>
+      </c>
+      <c r="AV86" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW86" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB86">
+        <f>AV86/AW86-1</f>
+        <v/>
+      </c>
+      <c r="BC86">
+        <f>AX86/AW86-1</f>
+        <v/>
+      </c>
+      <c r="BE86" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF86" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH86" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI86" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK86">
+        <f>BE86/BF86-1</f>
+        <v/>
+      </c>
+      <c r="BL86">
+        <f>BG86/BF86-1</f>
+        <v/>
+      </c>
+      <c r="BN86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO86" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR86" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT86">
+        <f>BN86/BO86-1</f>
+        <v/>
+      </c>
+      <c r="BU86">
+        <f>BP86/BO86-1</f>
+        <v/>
+      </c>
+      <c r="BW86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX86" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA86" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC86">
+        <f>BW86/BX86-1</f>
+        <v/>
+      </c>
+      <c r="CD86">
+        <f>BY86/BX86-1</f>
+        <v/>
+      </c>
+      <c r="CF86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG86" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ86" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL86">
+        <f>CF86/CG86-1</f>
+        <v/>
+      </c>
+      <c r="CM86">
+        <f>CH86/CG86-1</f>
+        <v/>
+      </c>
+      <c r="CO86" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP86" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR86" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS86" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU86">
+        <f>CO86/CP86-1</f>
+        <v/>
+      </c>
+      <c r="CV86">
+        <f>CQ86/CP86-1</f>
+        <v/>
+      </c>
+      <c r="CX86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY86" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB86" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD86">
+        <f>CX86/CY86-1</f>
+        <v/>
+      </c>
+      <c r="DE86">
+        <f>CZ86/CY86-1</f>
+        <v/>
+      </c>
+      <c r="DG86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH86" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK86" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM86">
+        <f>DG86/DH86-1</f>
+        <v/>
+      </c>
+      <c r="DN86">
+        <f>DI86/DH86-1</f>
+        <v/>
+      </c>
+      <c r="DP86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ86" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT86" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV86">
+        <f>DP86/DQ86-1</f>
+        <v/>
+      </c>
+      <c r="DW86">
+        <f>DR86/DQ86-1</f>
+        <v/>
+      </c>
+      <c r="DY86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ86" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC86" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE86">
+        <f>DY86/DZ86-1</f>
+        <v/>
+      </c>
+      <c r="EF86">
+        <f>EA86/DZ86-1</f>
+        <v/>
+      </c>
+      <c r="EH86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI86" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL86" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN86">
+        <f>EH86/EI86-1</f>
+        <v/>
+      </c>
+      <c r="EO86">
+        <f>EJ86/EI86-1</f>
+        <v/>
+      </c>
+      <c r="EQ86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER86" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU86" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW86">
+        <f>EQ86/ER86-1</f>
+        <v/>
+      </c>
+      <c r="EX86">
+        <f>ES86/ER86-1</f>
+        <v/>
+      </c>
+      <c r="EZ86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA86" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC86" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD86" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF86">
+        <f>EZ86/FA86-1</f>
+        <v/>
+      </c>
+      <c r="FG86">
+        <f>FB86/FA86-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG86"/>
+  <dimension ref="A1:FG87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -38742,6 +38742,451 @@
         <v/>
       </c>
     </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>12 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I87">
+        <f>C87/D87-1</f>
+        <v/>
+      </c>
+      <c r="J87">
+        <f>E87/D87-1</f>
+        <v/>
+      </c>
+      <c r="L87" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M87" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R87">
+        <f>L87/M87-1</f>
+        <v/>
+      </c>
+      <c r="S87">
+        <f>N87/M87-1</f>
+        <v/>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V87" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA87">
+        <f>U87/V87-1</f>
+        <v/>
+      </c>
+      <c r="AB87">
+        <f>W87/V87-1</f>
+        <v/>
+      </c>
+      <c r="AD87" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE87" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ87">
+        <f>AD87/AE87-1</f>
+        <v/>
+      </c>
+      <c r="AK87">
+        <f>AF87/AE87-1</f>
+        <v/>
+      </c>
+      <c r="AM87" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AS87">
+        <f>AM87/AN87-1</f>
+        <v/>
+      </c>
+      <c r="AT87">
+        <f>AO87/AN87-1</f>
+        <v/>
+      </c>
+      <c r="AV87" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW87" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB87">
+        <f>AV87/AW87-1</f>
+        <v/>
+      </c>
+      <c r="BC87">
+        <f>AX87/AW87-1</f>
+        <v/>
+      </c>
+      <c r="BE87" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF87" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH87" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI87" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK87">
+        <f>BE87/BF87-1</f>
+        <v/>
+      </c>
+      <c r="BL87">
+        <f>BG87/BF87-1</f>
+        <v/>
+      </c>
+      <c r="BN87" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO87" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ87" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR87" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT87">
+        <f>BN87/BO87-1</f>
+        <v/>
+      </c>
+      <c r="BU87">
+        <f>BP87/BO87-1</f>
+        <v/>
+      </c>
+      <c r="BW87" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX87" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ87" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA87" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC87">
+        <f>BW87/BX87-1</f>
+        <v/>
+      </c>
+      <c r="CD87">
+        <f>BY87/BX87-1</f>
+        <v/>
+      </c>
+      <c r="CF87" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG87" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI87" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ87" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL87">
+        <f>CF87/CG87-1</f>
+        <v/>
+      </c>
+      <c r="CM87">
+        <f>CH87/CG87-1</f>
+        <v/>
+      </c>
+      <c r="CO87" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP87" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR87" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS87" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU87">
+        <f>CO87/CP87-1</f>
+        <v/>
+      </c>
+      <c r="CV87">
+        <f>CQ87/CP87-1</f>
+        <v/>
+      </c>
+      <c r="CX87" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY87" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA87" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB87" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD87">
+        <f>CX87/CY87-1</f>
+        <v/>
+      </c>
+      <c r="DE87">
+        <f>CZ87/CY87-1</f>
+        <v/>
+      </c>
+      <c r="DG87" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH87" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ87" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK87" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM87">
+        <f>DG87/DH87-1</f>
+        <v/>
+      </c>
+      <c r="DN87">
+        <f>DI87/DH87-1</f>
+        <v/>
+      </c>
+      <c r="DP87" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ87" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DS87" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT87" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DV87">
+        <f>DP87/DQ87-1</f>
+        <v/>
+      </c>
+      <c r="DW87">
+        <f>DR87/DQ87-1</f>
+        <v/>
+      </c>
+      <c r="DY87" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ87" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB87" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE87">
+        <f>DY87/DZ87-1</f>
+        <v/>
+      </c>
+      <c r="EF87">
+        <f>EA87/DZ87-1</f>
+        <v/>
+      </c>
+      <c r="EH87" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI87" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK87" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL87" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN87">
+        <f>EH87/EI87-1</f>
+        <v/>
+      </c>
+      <c r="EO87">
+        <f>EJ87/EI87-1</f>
+        <v/>
+      </c>
+      <c r="EQ87" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER87" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET87" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU87" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW87">
+        <f>EQ87/ER87-1</f>
+        <v/>
+      </c>
+      <c r="EX87">
+        <f>ES87/ER87-1</f>
+        <v/>
+      </c>
+      <c r="EZ87" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA87" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC87" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD87" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF87">
+        <f>EZ87/FA87-1</f>
+        <v/>
+      </c>
+      <c r="FG87">
+        <f>FB87/FA87-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG87"/>
+  <dimension ref="A1:FG88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -39187,6 +39187,471 @@
         <v/>
       </c>
     </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>13 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I88">
+        <f>C88/D88-1</f>
+        <v/>
+      </c>
+      <c r="J88">
+        <f>E88/D88-1</f>
+        <v/>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M88" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R88">
+        <f>L88/M88-1</f>
+        <v/>
+      </c>
+      <c r="S88">
+        <f>N88/M88-1</f>
+        <v/>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V88" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA88">
+        <f>U88/V88-1</f>
+        <v/>
+      </c>
+      <c r="AB88">
+        <f>W88/V88-1</f>
+        <v/>
+      </c>
+      <c r="AD88" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE88" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ88">
+        <f>AD88/AE88-1</f>
+        <v/>
+      </c>
+      <c r="AK88">
+        <f>AF88/AE88-1</f>
+        <v/>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN88" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS88">
+        <f>AM88/AN88-1</f>
+        <v/>
+      </c>
+      <c r="AT88">
+        <f>AO88/AN88-1</f>
+        <v/>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW88" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB88">
+        <f>AV88/AW88-1</f>
+        <v/>
+      </c>
+      <c r="BC88">
+        <f>AX88/AW88-1</f>
+        <v/>
+      </c>
+      <c r="BE88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF88" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI88" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK88">
+        <f>BE88/BF88-1</f>
+        <v/>
+      </c>
+      <c r="BL88">
+        <f>BG88/BF88-1</f>
+        <v/>
+      </c>
+      <c r="BN88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO88" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR88" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT88">
+        <f>BN88/BO88-1</f>
+        <v/>
+      </c>
+      <c r="BU88">
+        <f>BP88/BO88-1</f>
+        <v/>
+      </c>
+      <c r="BW88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX88" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA88" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC88">
+        <f>BW88/BX88-1</f>
+        <v/>
+      </c>
+      <c r="CD88">
+        <f>BY88/BX88-1</f>
+        <v/>
+      </c>
+      <c r="CF88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG88" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ88" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL88">
+        <f>CF88/CG88-1</f>
+        <v/>
+      </c>
+      <c r="CM88">
+        <f>CH88/CG88-1</f>
+        <v/>
+      </c>
+      <c r="CO88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CP88" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CS88" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU88">
+        <f>CO88/CP88-1</f>
+        <v/>
+      </c>
+      <c r="CV88">
+        <f>CQ88/CP88-1</f>
+        <v/>
+      </c>
+      <c r="CX88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY88" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB88" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD88">
+        <f>CX88/CY88-1</f>
+        <v/>
+      </c>
+      <c r="DE88">
+        <f>CZ88/CY88-1</f>
+        <v/>
+      </c>
+      <c r="DG88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH88" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK88" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM88">
+        <f>DG88/DH88-1</f>
+        <v/>
+      </c>
+      <c r="DN88">
+        <f>DI88/DH88-1</f>
+        <v/>
+      </c>
+      <c r="DP88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ88" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT88" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV88">
+        <f>DP88/DQ88-1</f>
+        <v/>
+      </c>
+      <c r="DW88">
+        <f>DR88/DQ88-1</f>
+        <v/>
+      </c>
+      <c r="DY88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ88" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB88" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC88" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE88">
+        <f>DY88/DZ88-1</f>
+        <v/>
+      </c>
+      <c r="EF88">
+        <f>EA88/DZ88-1</f>
+        <v/>
+      </c>
+      <c r="EH88" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI88" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK88" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL88" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN88">
+        <f>EH88/EI88-1</f>
+        <v/>
+      </c>
+      <c r="EO88">
+        <f>EJ88/EI88-1</f>
+        <v/>
+      </c>
+      <c r="EQ88" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER88" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET88" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU88" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW88">
+        <f>EQ88/ER88-1</f>
+        <v/>
+      </c>
+      <c r="EX88">
+        <f>ES88/ER88-1</f>
+        <v/>
+      </c>
+      <c r="EZ88" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA88" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC88" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD88" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF88">
+        <f>EZ88/FA88-1</f>
+        <v/>
+      </c>
+      <c r="FG88">
+        <f>FB88/FA88-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG88"/>
+  <dimension ref="A1:FG89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -39652,6 +39652,453 @@
         <v/>
       </c>
     </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>13 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I89">
+        <f>C89/D89-1</f>
+        <v/>
+      </c>
+      <c r="J89">
+        <f>E89/D89-1</f>
+        <v/>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M89" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R89">
+        <f>L89/M89-1</f>
+        <v/>
+      </c>
+      <c r="S89">
+        <f>N89/M89-1</f>
+        <v/>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V89" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA89">
+        <f>U89/V89-1</f>
+        <v/>
+      </c>
+      <c r="AB89">
+        <f>W89/V89-1</f>
+        <v/>
+      </c>
+      <c r="AD89" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE89" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ89">
+        <f>AD89/AE89-1</f>
+        <v/>
+      </c>
+      <c r="AK89">
+        <f>AF89/AE89-1</f>
+        <v/>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN89" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS89">
+        <f>AM89/AN89-1</f>
+        <v/>
+      </c>
+      <c r="AT89">
+        <f>AO89/AN89-1</f>
+        <v/>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW89" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB89">
+        <f>AV89/AW89-1</f>
+        <v/>
+      </c>
+      <c r="BC89">
+        <f>AX89/AW89-1</f>
+        <v/>
+      </c>
+      <c r="BE89" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF89" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH89" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI89" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK89">
+        <f>BE89/BF89-1</f>
+        <v/>
+      </c>
+      <c r="BL89">
+        <f>BG89/BF89-1</f>
+        <v/>
+      </c>
+      <c r="BN89" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO89" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ89" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR89" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT89">
+        <f>BN89/BO89-1</f>
+        <v/>
+      </c>
+      <c r="BU89">
+        <f>BP89/BO89-1</f>
+        <v/>
+      </c>
+      <c r="BW89" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX89" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ89" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA89" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC89">
+        <f>BW89/BX89-1</f>
+        <v/>
+      </c>
+      <c r="CD89">
+        <f>BY89/BX89-1</f>
+        <v/>
+      </c>
+      <c r="CF89" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG89" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI89" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ89" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL89">
+        <f>CF89/CG89-1</f>
+        <v/>
+      </c>
+      <c r="CM89">
+        <f>CH89/CG89-1</f>
+        <v/>
+      </c>
+      <c r="CO89" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP89" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR89" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS89" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU89">
+        <f>CO89/CP89-1</f>
+        <v/>
+      </c>
+      <c r="CV89">
+        <f>CQ89/CP89-1</f>
+        <v/>
+      </c>
+      <c r="CX89" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY89" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA89" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB89" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD89">
+        <f>CX89/CY89-1</f>
+        <v/>
+      </c>
+      <c r="DE89">
+        <f>CZ89/CY89-1</f>
+        <v/>
+      </c>
+      <c r="DG89" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH89" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ89" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK89" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM89">
+        <f>DG89/DH89-1</f>
+        <v/>
+      </c>
+      <c r="DN89">
+        <f>DI89/DH89-1</f>
+        <v/>
+      </c>
+      <c r="DP89" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ89" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS89" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT89" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV89">
+        <f>DP89/DQ89-1</f>
+        <v/>
+      </c>
+      <c r="DW89">
+        <f>DR89/DQ89-1</f>
+        <v/>
+      </c>
+      <c r="DY89" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ89" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB89" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC89" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE89">
+        <f>DY89/DZ89-1</f>
+        <v/>
+      </c>
+      <c r="EF89">
+        <f>EA89/DZ89-1</f>
+        <v/>
+      </c>
+      <c r="EH89" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI89" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK89" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL89" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN89">
+        <f>EH89/EI89-1</f>
+        <v/>
+      </c>
+      <c r="EO89">
+        <f>EJ89/EI89-1</f>
+        <v/>
+      </c>
+      <c r="EQ89" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER89" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET89" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU89" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW89">
+        <f>EQ89/ER89-1</f>
+        <v/>
+      </c>
+      <c r="EX89">
+        <f>ES89/ER89-1</f>
+        <v/>
+      </c>
+      <c r="EZ89" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA89" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC89" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD89" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF89">
+        <f>EZ89/FA89-1</f>
+        <v/>
+      </c>
+      <c r="FG89">
+        <f>FB89/FA89-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG89"/>
+  <dimension ref="A1:FG90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -40099,6 +40099,445 @@
         <v/>
       </c>
     </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>13 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I90">
+        <f>C90/D90-1</f>
+        <v/>
+      </c>
+      <c r="J90">
+        <f>E90/D90-1</f>
+        <v/>
+      </c>
+      <c r="L90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R90">
+        <f>L90/M90-1</f>
+        <v/>
+      </c>
+      <c r="S90">
+        <f>N90/M90-1</f>
+        <v/>
+      </c>
+      <c r="U90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA90">
+        <f>U90/V90-1</f>
+        <v/>
+      </c>
+      <c r="AB90">
+        <f>W90/V90-1</f>
+        <v/>
+      </c>
+      <c r="AD90" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE90" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ90">
+        <f>AD90/AE90-1</f>
+        <v/>
+      </c>
+      <c r="AK90">
+        <f>AF90/AE90-1</f>
+        <v/>
+      </c>
+      <c r="AM90" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN90" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS90">
+        <f>AM90/AN90-1</f>
+        <v/>
+      </c>
+      <c r="AT90">
+        <f>AO90/AN90-1</f>
+        <v/>
+      </c>
+      <c r="AV90" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW90" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB90">
+        <f>AV90/AW90-1</f>
+        <v/>
+      </c>
+      <c r="BC90">
+        <f>AX90/AW90-1</f>
+        <v/>
+      </c>
+      <c r="BE90" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF90" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI90" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK90">
+        <f>BE90/BF90-1</f>
+        <v/>
+      </c>
+      <c r="BL90">
+        <f>BG90/BF90-1</f>
+        <v/>
+      </c>
+      <c r="BN90" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO90" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ90" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR90" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT90">
+        <f>BN90/BO90-1</f>
+        <v/>
+      </c>
+      <c r="BU90">
+        <f>BP90/BO90-1</f>
+        <v/>
+      </c>
+      <c r="BW90" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX90" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ90" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA90" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC90">
+        <f>BW90/BX90-1</f>
+        <v/>
+      </c>
+      <c r="CD90">
+        <f>BY90/BX90-1</f>
+        <v/>
+      </c>
+      <c r="CF90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI90" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ90" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL90">
+        <f>CF90/CG90-1</f>
+        <v/>
+      </c>
+      <c r="CM90">
+        <f>CH90/CG90-1</f>
+        <v/>
+      </c>
+      <c r="CO90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR90" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS90" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU90">
+        <f>CO90/CP90-1</f>
+        <v/>
+      </c>
+      <c r="CV90">
+        <f>CQ90/CP90-1</f>
+        <v/>
+      </c>
+      <c r="CX90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY90" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA90" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB90" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD90">
+        <f>CX90/CY90-1</f>
+        <v/>
+      </c>
+      <c r="DE90">
+        <f>CZ90/CY90-1</f>
+        <v/>
+      </c>
+      <c r="DG90" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH90" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ90" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK90" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM90">
+        <f>DG90/DH90-1</f>
+        <v/>
+      </c>
+      <c r="DN90">
+        <f>DI90/DH90-1</f>
+        <v/>
+      </c>
+      <c r="DP90" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ90" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS90" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT90" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV90">
+        <f>DP90/DQ90-1</f>
+        <v/>
+      </c>
+      <c r="DW90">
+        <f>DR90/DQ90-1</f>
+        <v/>
+      </c>
+      <c r="DY90" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ90" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB90" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC90" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE90">
+        <f>DY90/DZ90-1</f>
+        <v/>
+      </c>
+      <c r="EF90">
+        <f>EA90/DZ90-1</f>
+        <v/>
+      </c>
+      <c r="EH90" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI90" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK90" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL90" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN90">
+        <f>EH90/EI90-1</f>
+        <v/>
+      </c>
+      <c r="EO90">
+        <f>EJ90/EI90-1</f>
+        <v/>
+      </c>
+      <c r="EQ90" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER90" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET90" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU90" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW90">
+        <f>EQ90/ER90-1</f>
+        <v/>
+      </c>
+      <c r="EX90">
+        <f>ES90/ER90-1</f>
+        <v/>
+      </c>
+      <c r="EZ90" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA90" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC90" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD90" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF90">
+        <f>EZ90/FA90-1</f>
+        <v/>
+      </c>
+      <c r="FG90">
+        <f>FB90/FA90-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG90"/>
+  <dimension ref="A1:FG91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -40538,6 +40538,447 @@
         <v/>
       </c>
     </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>13 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I91">
+        <f>C91/D91-1</f>
+        <v/>
+      </c>
+      <c r="J91">
+        <f>E91/D91-1</f>
+        <v/>
+      </c>
+      <c r="L91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R91">
+        <f>L91/M91-1</f>
+        <v/>
+      </c>
+      <c r="S91">
+        <f>N91/M91-1</f>
+        <v/>
+      </c>
+      <c r="U91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA91">
+        <f>U91/V91-1</f>
+        <v/>
+      </c>
+      <c r="AB91">
+        <f>W91/V91-1</f>
+        <v/>
+      </c>
+      <c r="AD91" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE91" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ91">
+        <f>AD91/AE91-1</f>
+        <v/>
+      </c>
+      <c r="AK91">
+        <f>AF91/AE91-1</f>
+        <v/>
+      </c>
+      <c r="AM91" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AS91">
+        <f>AM91/AN91-1</f>
+        <v/>
+      </c>
+      <c r="AT91">
+        <f>AO91/AN91-1</f>
+        <v/>
+      </c>
+      <c r="AV91" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW91" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB91">
+        <f>AV91/AW91-1</f>
+        <v/>
+      </c>
+      <c r="BC91">
+        <f>AX91/AW91-1</f>
+        <v/>
+      </c>
+      <c r="BE91" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF91" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH91" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI91" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK91">
+        <f>BE91/BF91-1</f>
+        <v/>
+      </c>
+      <c r="BL91">
+        <f>BG91/BF91-1</f>
+        <v/>
+      </c>
+      <c r="BN91" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO91" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ91" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR91" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT91">
+        <f>BN91/BO91-1</f>
+        <v/>
+      </c>
+      <c r="BU91">
+        <f>BP91/BO91-1</f>
+        <v/>
+      </c>
+      <c r="BW91" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX91" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ91" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA91" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC91">
+        <f>BW91/BX91-1</f>
+        <v/>
+      </c>
+      <c r="CD91">
+        <f>BY91/BX91-1</f>
+        <v/>
+      </c>
+      <c r="CF91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI91" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ91" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL91">
+        <f>CF91/CG91-1</f>
+        <v/>
+      </c>
+      <c r="CM91">
+        <f>CH91/CG91-1</f>
+        <v/>
+      </c>
+      <c r="CO91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR91" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS91" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU91">
+        <f>CO91/CP91-1</f>
+        <v/>
+      </c>
+      <c r="CV91">
+        <f>CQ91/CP91-1</f>
+        <v/>
+      </c>
+      <c r="CX91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY91" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA91" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB91" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD91">
+        <f>CX91/CY91-1</f>
+        <v/>
+      </c>
+      <c r="DE91">
+        <f>CZ91/CY91-1</f>
+        <v/>
+      </c>
+      <c r="DG91" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH91" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ91" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK91" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM91">
+        <f>DG91/DH91-1</f>
+        <v/>
+      </c>
+      <c r="DN91">
+        <f>DI91/DH91-1</f>
+        <v/>
+      </c>
+      <c r="DP91" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ91" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS91" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT91" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV91">
+        <f>DP91/DQ91-1</f>
+        <v/>
+      </c>
+      <c r="DW91">
+        <f>DR91/DQ91-1</f>
+        <v/>
+      </c>
+      <c r="DY91" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ91" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB91" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC91" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE91">
+        <f>DY91/DZ91-1</f>
+        <v/>
+      </c>
+      <c r="EF91">
+        <f>EA91/DZ91-1</f>
+        <v/>
+      </c>
+      <c r="EH91" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI91" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK91" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL91" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN91">
+        <f>EH91/EI91-1</f>
+        <v/>
+      </c>
+      <c r="EO91">
+        <f>EJ91/EI91-1</f>
+        <v/>
+      </c>
+      <c r="EQ91" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER91" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET91" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU91" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW91">
+        <f>EQ91/ER91-1</f>
+        <v/>
+      </c>
+      <c r="EX91">
+        <f>ES91/ER91-1</f>
+        <v/>
+      </c>
+      <c r="EZ91" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA91" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC91" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD91" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF91">
+        <f>EZ91/FA91-1</f>
+        <v/>
+      </c>
+      <c r="FG91">
+        <f>FB91/FA91-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG91"/>
+  <dimension ref="A1:FG92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -40979,6 +40979,449 @@
         <v/>
       </c>
     </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>14 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I92">
+        <f>C92/D92-1</f>
+        <v/>
+      </c>
+      <c r="J92">
+        <f>E92/D92-1</f>
+        <v/>
+      </c>
+      <c r="L92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R92">
+        <f>L92/M92-1</f>
+        <v/>
+      </c>
+      <c r="S92">
+        <f>N92/M92-1</f>
+        <v/>
+      </c>
+      <c r="U92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA92">
+        <f>U92/V92-1</f>
+        <v/>
+      </c>
+      <c r="AB92">
+        <f>W92/V92-1</f>
+        <v/>
+      </c>
+      <c r="AD92" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE92" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ92">
+        <f>AD92/AE92-1</f>
+        <v/>
+      </c>
+      <c r="AK92">
+        <f>AF92/AE92-1</f>
+        <v/>
+      </c>
+      <c r="AM92" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN92" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS92">
+        <f>AM92/AN92-1</f>
+        <v/>
+      </c>
+      <c r="AT92">
+        <f>AO92/AN92-1</f>
+        <v/>
+      </c>
+      <c r="AV92" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BB92">
+        <f>AV92/AW92-1</f>
+        <v/>
+      </c>
+      <c r="BC92">
+        <f>AX92/AW92-1</f>
+        <v/>
+      </c>
+      <c r="BE92" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF92" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH92" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI92" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK92">
+        <f>BE92/BF92-1</f>
+        <v/>
+      </c>
+      <c r="BL92">
+        <f>BG92/BF92-1</f>
+        <v/>
+      </c>
+      <c r="BN92" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO92" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ92" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR92" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT92">
+        <f>BN92/BO92-1</f>
+        <v/>
+      </c>
+      <c r="BU92">
+        <f>BP92/BO92-1</f>
+        <v/>
+      </c>
+      <c r="BW92" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX92" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ92" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA92" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC92">
+        <f>BW92/BX92-1</f>
+        <v/>
+      </c>
+      <c r="CD92">
+        <f>BY92/BX92-1</f>
+        <v/>
+      </c>
+      <c r="CF92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI92" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ92" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL92">
+        <f>CF92/CG92-1</f>
+        <v/>
+      </c>
+      <c r="CM92">
+        <f>CH92/CG92-1</f>
+        <v/>
+      </c>
+      <c r="CO92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR92" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS92" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU92">
+        <f>CO92/CP92-1</f>
+        <v/>
+      </c>
+      <c r="CV92">
+        <f>CQ92/CP92-1</f>
+        <v/>
+      </c>
+      <c r="CX92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY92" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA92" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB92" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD92">
+        <f>CX92/CY92-1</f>
+        <v/>
+      </c>
+      <c r="DE92">
+        <f>CZ92/CY92-1</f>
+        <v/>
+      </c>
+      <c r="DG92" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH92" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ92" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK92" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM92">
+        <f>DG92/DH92-1</f>
+        <v/>
+      </c>
+      <c r="DN92">
+        <f>DI92/DH92-1</f>
+        <v/>
+      </c>
+      <c r="DP92" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ92" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS92" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT92" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV92">
+        <f>DP92/DQ92-1</f>
+        <v/>
+      </c>
+      <c r="DW92">
+        <f>DR92/DQ92-1</f>
+        <v/>
+      </c>
+      <c r="DY92" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ92" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB92" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC92" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE92">
+        <f>DY92/DZ92-1</f>
+        <v/>
+      </c>
+      <c r="EF92">
+        <f>EA92/DZ92-1</f>
+        <v/>
+      </c>
+      <c r="EH92" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI92" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK92" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL92" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN92">
+        <f>EH92/EI92-1</f>
+        <v/>
+      </c>
+      <c r="EO92">
+        <f>EJ92/EI92-1</f>
+        <v/>
+      </c>
+      <c r="EQ92" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER92" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ET92" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU92" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EW92">
+        <f>EQ92/ER92-1</f>
+        <v/>
+      </c>
+      <c r="EX92">
+        <f>ES92/ER92-1</f>
+        <v/>
+      </c>
+      <c r="EZ92" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA92" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC92" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD92" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF92">
+        <f>EZ92/FA92-1</f>
+        <v/>
+      </c>
+      <c r="FG92">
+        <f>FB92/FA92-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG92"/>
+  <dimension ref="A1:FG93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -41422,6 +41422,447 @@
         <v/>
       </c>
     </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>14 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I93">
+        <f>C93/D93-1</f>
+        <v/>
+      </c>
+      <c r="J93">
+        <f>E93/D93-1</f>
+        <v/>
+      </c>
+      <c r="L93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R93">
+        <f>L93/M93-1</f>
+        <v/>
+      </c>
+      <c r="S93">
+        <f>N93/M93-1</f>
+        <v/>
+      </c>
+      <c r="U93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA93">
+        <f>U93/V93-1</f>
+        <v/>
+      </c>
+      <c r="AB93">
+        <f>W93/V93-1</f>
+        <v/>
+      </c>
+      <c r="AD93" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE93" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ93">
+        <f>AD93/AE93-1</f>
+        <v/>
+      </c>
+      <c r="AK93">
+        <f>AF93/AE93-1</f>
+        <v/>
+      </c>
+      <c r="AM93" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN93" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS93">
+        <f>AM93/AN93-1</f>
+        <v/>
+      </c>
+      <c r="AT93">
+        <f>AO93/AN93-1</f>
+        <v/>
+      </c>
+      <c r="AV93" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BB93">
+        <f>AV93/AW93-1</f>
+        <v/>
+      </c>
+      <c r="BC93">
+        <f>AX93/AW93-1</f>
+        <v/>
+      </c>
+      <c r="BE93" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF93" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH93" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI93" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK93">
+        <f>BE93/BF93-1</f>
+        <v/>
+      </c>
+      <c r="BL93">
+        <f>BG93/BF93-1</f>
+        <v/>
+      </c>
+      <c r="BN93" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO93" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ93" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR93" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT93">
+        <f>BN93/BO93-1</f>
+        <v/>
+      </c>
+      <c r="BU93">
+        <f>BP93/BO93-1</f>
+        <v/>
+      </c>
+      <c r="BW93" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX93" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ93" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA93" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC93">
+        <f>BW93/BX93-1</f>
+        <v/>
+      </c>
+      <c r="CD93">
+        <f>BY93/BX93-1</f>
+        <v/>
+      </c>
+      <c r="CF93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI93" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ93" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL93">
+        <f>CF93/CG93-1</f>
+        <v/>
+      </c>
+      <c r="CM93">
+        <f>CH93/CG93-1</f>
+        <v/>
+      </c>
+      <c r="CO93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR93" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS93" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU93">
+        <f>CO93/CP93-1</f>
+        <v/>
+      </c>
+      <c r="CV93">
+        <f>CQ93/CP93-1</f>
+        <v/>
+      </c>
+      <c r="CX93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY93" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA93" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB93" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD93">
+        <f>CX93/CY93-1</f>
+        <v/>
+      </c>
+      <c r="DE93">
+        <f>CZ93/CY93-1</f>
+        <v/>
+      </c>
+      <c r="DG93" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH93" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ93" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK93" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM93">
+        <f>DG93/DH93-1</f>
+        <v/>
+      </c>
+      <c r="DN93">
+        <f>DI93/DH93-1</f>
+        <v/>
+      </c>
+      <c r="DP93" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ93" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS93" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT93" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV93">
+        <f>DP93/DQ93-1</f>
+        <v/>
+      </c>
+      <c r="DW93">
+        <f>DR93/DQ93-1</f>
+        <v/>
+      </c>
+      <c r="DY93" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ93" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB93" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC93" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE93">
+        <f>DY93/DZ93-1</f>
+        <v/>
+      </c>
+      <c r="EF93">
+        <f>EA93/DZ93-1</f>
+        <v/>
+      </c>
+      <c r="EH93" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI93" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK93" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL93" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN93">
+        <f>EH93/EI93-1</f>
+        <v/>
+      </c>
+      <c r="EO93">
+        <f>EJ93/EI93-1</f>
+        <v/>
+      </c>
+      <c r="EQ93" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER93" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET93" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU93" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW93">
+        <f>EQ93/ER93-1</f>
+        <v/>
+      </c>
+      <c r="EX93">
+        <f>ES93/ER93-1</f>
+        <v/>
+      </c>
+      <c r="EZ93" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA93" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC93" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD93" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF93">
+        <f>EZ93/FA93-1</f>
+        <v/>
+      </c>
+      <c r="FG93">
+        <f>FB93/FA93-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG93"/>
+  <dimension ref="A1:FG94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -41863,6 +41863,447 @@
         <v/>
       </c>
     </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>14 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I94">
+        <f>C94/D94-1</f>
+        <v/>
+      </c>
+      <c r="J94">
+        <f>E94/D94-1</f>
+        <v/>
+      </c>
+      <c r="L94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R94">
+        <f>L94/M94-1</f>
+        <v/>
+      </c>
+      <c r="S94">
+        <f>N94/M94-1</f>
+        <v/>
+      </c>
+      <c r="U94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA94">
+        <f>U94/V94-1</f>
+        <v/>
+      </c>
+      <c r="AB94">
+        <f>W94/V94-1</f>
+        <v/>
+      </c>
+      <c r="AD94" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE94" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ94">
+        <f>AD94/AE94-1</f>
+        <v/>
+      </c>
+      <c r="AK94">
+        <f>AF94/AE94-1</f>
+        <v/>
+      </c>
+      <c r="AM94" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN94" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS94">
+        <f>AM94/AN94-1</f>
+        <v/>
+      </c>
+      <c r="AT94">
+        <f>AO94/AN94-1</f>
+        <v/>
+      </c>
+      <c r="AV94" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW94" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB94">
+        <f>AV94/AW94-1</f>
+        <v/>
+      </c>
+      <c r="BC94">
+        <f>AX94/AW94-1</f>
+        <v/>
+      </c>
+      <c r="BE94" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF94" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH94" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI94" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK94">
+        <f>BE94/BF94-1</f>
+        <v/>
+      </c>
+      <c r="BL94">
+        <f>BG94/BF94-1</f>
+        <v/>
+      </c>
+      <c r="BN94" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO94" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ94" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR94" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT94">
+        <f>BN94/BO94-1</f>
+        <v/>
+      </c>
+      <c r="BU94">
+        <f>BP94/BO94-1</f>
+        <v/>
+      </c>
+      <c r="BW94" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX94" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ94" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA94" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC94">
+        <f>BW94/BX94-1</f>
+        <v/>
+      </c>
+      <c r="CD94">
+        <f>BY94/BX94-1</f>
+        <v/>
+      </c>
+      <c r="CF94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI94" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ94" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL94">
+        <f>CF94/CG94-1</f>
+        <v/>
+      </c>
+      <c r="CM94">
+        <f>CH94/CG94-1</f>
+        <v/>
+      </c>
+      <c r="CO94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR94" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS94" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU94">
+        <f>CO94/CP94-1</f>
+        <v/>
+      </c>
+      <c r="CV94">
+        <f>CQ94/CP94-1</f>
+        <v/>
+      </c>
+      <c r="CX94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY94" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA94" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB94" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD94">
+        <f>CX94/CY94-1</f>
+        <v/>
+      </c>
+      <c r="DE94">
+        <f>CZ94/CY94-1</f>
+        <v/>
+      </c>
+      <c r="DG94" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH94" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ94" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK94" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM94">
+        <f>DG94/DH94-1</f>
+        <v/>
+      </c>
+      <c r="DN94">
+        <f>DI94/DH94-1</f>
+        <v/>
+      </c>
+      <c r="DP94" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ94" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS94" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT94" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV94">
+        <f>DP94/DQ94-1</f>
+        <v/>
+      </c>
+      <c r="DW94">
+        <f>DR94/DQ94-1</f>
+        <v/>
+      </c>
+      <c r="DY94" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ94" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB94" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC94" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE94">
+        <f>DY94/DZ94-1</f>
+        <v/>
+      </c>
+      <c r="EF94">
+        <f>EA94/DZ94-1</f>
+        <v/>
+      </c>
+      <c r="EH94" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI94" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK94" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL94" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN94">
+        <f>EH94/EI94-1</f>
+        <v/>
+      </c>
+      <c r="EO94">
+        <f>EJ94/EI94-1</f>
+        <v/>
+      </c>
+      <c r="EQ94" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER94" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET94" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU94" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW94">
+        <f>EQ94/ER94-1</f>
+        <v/>
+      </c>
+      <c r="EX94">
+        <f>ES94/ER94-1</f>
+        <v/>
+      </c>
+      <c r="EZ94" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA94" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC94" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD94" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF94">
+        <f>EZ94/FA94-1</f>
+        <v/>
+      </c>
+      <c r="FG94">
+        <f>FB94/FA94-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG94"/>
+  <dimension ref="A1:FG95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -42304,6 +42304,447 @@
         <v/>
       </c>
     </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>14 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I95">
+        <f>C95/D95-1</f>
+        <v/>
+      </c>
+      <c r="J95">
+        <f>E95/D95-1</f>
+        <v/>
+      </c>
+      <c r="L95" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M95" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R95">
+        <f>L95/M95-1</f>
+        <v/>
+      </c>
+      <c r="S95">
+        <f>N95/M95-1</f>
+        <v/>
+      </c>
+      <c r="U95" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AA95">
+        <f>U95/V95-1</f>
+        <v/>
+      </c>
+      <c r="AB95">
+        <f>W95/V95-1</f>
+        <v/>
+      </c>
+      <c r="AD95" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE95" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ95">
+        <f>AD95/AE95-1</f>
+        <v/>
+      </c>
+      <c r="AK95">
+        <f>AF95/AE95-1</f>
+        <v/>
+      </c>
+      <c r="AM95" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN95" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS95">
+        <f>AM95/AN95-1</f>
+        <v/>
+      </c>
+      <c r="AT95">
+        <f>AO95/AN95-1</f>
+        <v/>
+      </c>
+      <c r="AV95" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW95" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB95">
+        <f>AV95/AW95-1</f>
+        <v/>
+      </c>
+      <c r="BC95">
+        <f>AX95/AW95-1</f>
+        <v/>
+      </c>
+      <c r="BE95" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF95" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH95" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI95" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK95">
+        <f>BE95/BF95-1</f>
+        <v/>
+      </c>
+      <c r="BL95">
+        <f>BG95/BF95-1</f>
+        <v/>
+      </c>
+      <c r="BN95" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO95" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ95" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR95" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT95">
+        <f>BN95/BO95-1</f>
+        <v/>
+      </c>
+      <c r="BU95">
+        <f>BP95/BO95-1</f>
+        <v/>
+      </c>
+      <c r="BW95" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX95" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ95" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA95" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC95">
+        <f>BW95/BX95-1</f>
+        <v/>
+      </c>
+      <c r="CD95">
+        <f>BY95/BX95-1</f>
+        <v/>
+      </c>
+      <c r="CF95" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG95" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI95" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ95" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL95">
+        <f>CF95/CG95-1</f>
+        <v/>
+      </c>
+      <c r="CM95">
+        <f>CH95/CG95-1</f>
+        <v/>
+      </c>
+      <c r="CO95" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP95" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR95" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS95" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU95">
+        <f>CO95/CP95-1</f>
+        <v/>
+      </c>
+      <c r="CV95">
+        <f>CQ95/CP95-1</f>
+        <v/>
+      </c>
+      <c r="CX95" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY95" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA95" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB95" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD95">
+        <f>CX95/CY95-1</f>
+        <v/>
+      </c>
+      <c r="DE95">
+        <f>CZ95/CY95-1</f>
+        <v/>
+      </c>
+      <c r="DG95" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH95" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ95" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK95" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM95">
+        <f>DG95/DH95-1</f>
+        <v/>
+      </c>
+      <c r="DN95">
+        <f>DI95/DH95-1</f>
+        <v/>
+      </c>
+      <c r="DP95" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ95" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS95" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT95" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV95">
+        <f>DP95/DQ95-1</f>
+        <v/>
+      </c>
+      <c r="DW95">
+        <f>DR95/DQ95-1</f>
+        <v/>
+      </c>
+      <c r="DY95" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ95" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB95" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC95" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE95">
+        <f>DY95/DZ95-1</f>
+        <v/>
+      </c>
+      <c r="EF95">
+        <f>EA95/DZ95-1</f>
+        <v/>
+      </c>
+      <c r="EH95" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI95" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK95" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL95" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN95">
+        <f>EH95/EI95-1</f>
+        <v/>
+      </c>
+      <c r="EO95">
+        <f>EJ95/EI95-1</f>
+        <v/>
+      </c>
+      <c r="EQ95" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER95" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET95" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU95" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW95">
+        <f>EQ95/ER95-1</f>
+        <v/>
+      </c>
+      <c r="EX95">
+        <f>ES95/ER95-1</f>
+        <v/>
+      </c>
+      <c r="EZ95" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA95" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC95" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD95" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF95">
+        <f>EZ95/FA95-1</f>
+        <v/>
+      </c>
+      <c r="FG95">
+        <f>FB95/FA95-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG95"/>
+  <dimension ref="A1:FG96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -42745,6 +42745,445 @@
         <v/>
       </c>
     </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>15 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I96">
+        <f>C96/D96-1</f>
+        <v/>
+      </c>
+      <c r="J96">
+        <f>E96/D96-1</f>
+        <v/>
+      </c>
+      <c r="L96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R96">
+        <f>L96/M96-1</f>
+        <v/>
+      </c>
+      <c r="S96">
+        <f>N96/M96-1</f>
+        <v/>
+      </c>
+      <c r="U96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA96">
+        <f>U96/V96-1</f>
+        <v/>
+      </c>
+      <c r="AB96">
+        <f>W96/V96-1</f>
+        <v/>
+      </c>
+      <c r="AD96" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE96" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ96">
+        <f>AD96/AE96-1</f>
+        <v/>
+      </c>
+      <c r="AK96">
+        <f>AF96/AE96-1</f>
+        <v/>
+      </c>
+      <c r="AM96" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN96" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS96">
+        <f>AM96/AN96-1</f>
+        <v/>
+      </c>
+      <c r="AT96">
+        <f>AO96/AN96-1</f>
+        <v/>
+      </c>
+      <c r="AV96" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW96" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB96">
+        <f>AV96/AW96-1</f>
+        <v/>
+      </c>
+      <c r="BC96">
+        <f>AX96/AW96-1</f>
+        <v/>
+      </c>
+      <c r="BE96" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF96" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH96" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI96" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK96">
+        <f>BE96/BF96-1</f>
+        <v/>
+      </c>
+      <c r="BL96">
+        <f>BG96/BF96-1</f>
+        <v/>
+      </c>
+      <c r="BN96" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO96" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ96" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR96" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT96">
+        <f>BN96/BO96-1</f>
+        <v/>
+      </c>
+      <c r="BU96">
+        <f>BP96/BO96-1</f>
+        <v/>
+      </c>
+      <c r="BW96" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX96" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ96" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA96" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC96">
+        <f>BW96/BX96-1</f>
+        <v/>
+      </c>
+      <c r="CD96">
+        <f>BY96/BX96-1</f>
+        <v/>
+      </c>
+      <c r="CF96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI96" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ96" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL96">
+        <f>CF96/CG96-1</f>
+        <v/>
+      </c>
+      <c r="CM96">
+        <f>CH96/CG96-1</f>
+        <v/>
+      </c>
+      <c r="CO96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR96" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS96" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU96">
+        <f>CO96/CP96-1</f>
+        <v/>
+      </c>
+      <c r="CV96">
+        <f>CQ96/CP96-1</f>
+        <v/>
+      </c>
+      <c r="CX96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY96" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA96" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB96" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD96">
+        <f>CX96/CY96-1</f>
+        <v/>
+      </c>
+      <c r="DE96">
+        <f>CZ96/CY96-1</f>
+        <v/>
+      </c>
+      <c r="DG96" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH96" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ96" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK96" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM96">
+        <f>DG96/DH96-1</f>
+        <v/>
+      </c>
+      <c r="DN96">
+        <f>DI96/DH96-1</f>
+        <v/>
+      </c>
+      <c r="DP96" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ96" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS96" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT96" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV96">
+        <f>DP96/DQ96-1</f>
+        <v/>
+      </c>
+      <c r="DW96">
+        <f>DR96/DQ96-1</f>
+        <v/>
+      </c>
+      <c r="DY96" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ96" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB96" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC96" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE96">
+        <f>DY96/DZ96-1</f>
+        <v/>
+      </c>
+      <c r="EF96">
+        <f>EA96/DZ96-1</f>
+        <v/>
+      </c>
+      <c r="EH96" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI96" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK96" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL96" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN96">
+        <f>EH96/EI96-1</f>
+        <v/>
+      </c>
+      <c r="EO96">
+        <f>EJ96/EI96-1</f>
+        <v/>
+      </c>
+      <c r="EQ96" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER96" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET96" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU96" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW96">
+        <f>EQ96/ER96-1</f>
+        <v/>
+      </c>
+      <c r="EX96">
+        <f>ES96/ER96-1</f>
+        <v/>
+      </c>
+      <c r="EZ96" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA96" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC96" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD96" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF96">
+        <f>EZ96/FA96-1</f>
+        <v/>
+      </c>
+      <c r="FG96">
+        <f>FB96/FA96-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG96"/>
+  <dimension ref="A1:FG97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -43184,6 +43184,447 @@
         <v/>
       </c>
     </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>15 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I97">
+        <f>C97/D97-1</f>
+        <v/>
+      </c>
+      <c r="J97">
+        <f>E97/D97-1</f>
+        <v/>
+      </c>
+      <c r="L97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R97">
+        <f>L97/M97-1</f>
+        <v/>
+      </c>
+      <c r="S97">
+        <f>N97/M97-1</f>
+        <v/>
+      </c>
+      <c r="U97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA97">
+        <f>U97/V97-1</f>
+        <v/>
+      </c>
+      <c r="AB97">
+        <f>W97/V97-1</f>
+        <v/>
+      </c>
+      <c r="AD97" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE97" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ97">
+        <f>AD97/AE97-1</f>
+        <v/>
+      </c>
+      <c r="AK97">
+        <f>AF97/AE97-1</f>
+        <v/>
+      </c>
+      <c r="AM97" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN97" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS97">
+        <f>AM97/AN97-1</f>
+        <v/>
+      </c>
+      <c r="AT97">
+        <f>AO97/AN97-1</f>
+        <v/>
+      </c>
+      <c r="AV97" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW97" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB97">
+        <f>AV97/AW97-1</f>
+        <v/>
+      </c>
+      <c r="BC97">
+        <f>AX97/AW97-1</f>
+        <v/>
+      </c>
+      <c r="BE97" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF97" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH97" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI97" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK97">
+        <f>BE97/BF97-1</f>
+        <v/>
+      </c>
+      <c r="BL97">
+        <f>BG97/BF97-1</f>
+        <v/>
+      </c>
+      <c r="BN97" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO97" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ97" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR97" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT97">
+        <f>BN97/BO97-1</f>
+        <v/>
+      </c>
+      <c r="BU97">
+        <f>BP97/BO97-1</f>
+        <v/>
+      </c>
+      <c r="BW97" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX97" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ97" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA97" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC97">
+        <f>BW97/BX97-1</f>
+        <v/>
+      </c>
+      <c r="CD97">
+        <f>BY97/BX97-1</f>
+        <v/>
+      </c>
+      <c r="CF97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI97" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ97" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL97">
+        <f>CF97/CG97-1</f>
+        <v/>
+      </c>
+      <c r="CM97">
+        <f>CH97/CG97-1</f>
+        <v/>
+      </c>
+      <c r="CO97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR97" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS97" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU97">
+        <f>CO97/CP97-1</f>
+        <v/>
+      </c>
+      <c r="CV97">
+        <f>CQ97/CP97-1</f>
+        <v/>
+      </c>
+      <c r="CX97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY97" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA97" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB97" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD97">
+        <f>CX97/CY97-1</f>
+        <v/>
+      </c>
+      <c r="DE97">
+        <f>CZ97/CY97-1</f>
+        <v/>
+      </c>
+      <c r="DG97" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH97" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ97" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK97" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM97">
+        <f>DG97/DH97-1</f>
+        <v/>
+      </c>
+      <c r="DN97">
+        <f>DI97/DH97-1</f>
+        <v/>
+      </c>
+      <c r="DP97" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ97" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS97" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT97" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV97">
+        <f>DP97/DQ97-1</f>
+        <v/>
+      </c>
+      <c r="DW97">
+        <f>DR97/DQ97-1</f>
+        <v/>
+      </c>
+      <c r="DY97" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ97" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB97" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC97" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE97">
+        <f>DY97/DZ97-1</f>
+        <v/>
+      </c>
+      <c r="EF97">
+        <f>EA97/DZ97-1</f>
+        <v/>
+      </c>
+      <c r="EH97" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI97" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK97" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL97" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN97">
+        <f>EH97/EI97-1</f>
+        <v/>
+      </c>
+      <c r="EO97">
+        <f>EJ97/EI97-1</f>
+        <v/>
+      </c>
+      <c r="EQ97" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER97" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ET97" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU97" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EW97">
+        <f>EQ97/ER97-1</f>
+        <v/>
+      </c>
+      <c r="EX97">
+        <f>ES97/ER97-1</f>
+        <v/>
+      </c>
+      <c r="EZ97" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA97" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC97" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD97" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF97">
+        <f>EZ97/FA97-1</f>
+        <v/>
+      </c>
+      <c r="FG97">
+        <f>FB97/FA97-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG97"/>
+  <dimension ref="A1:FG98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -43625,6 +43625,447 @@
         <v/>
       </c>
     </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>15 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I98">
+        <f>C98/D98-1</f>
+        <v/>
+      </c>
+      <c r="J98">
+        <f>E98/D98-1</f>
+        <v/>
+      </c>
+      <c r="L98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R98">
+        <f>L98/M98-1</f>
+        <v/>
+      </c>
+      <c r="S98">
+        <f>N98/M98-1</f>
+        <v/>
+      </c>
+      <c r="U98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA98">
+        <f>U98/V98-1</f>
+        <v/>
+      </c>
+      <c r="AB98">
+        <f>W98/V98-1</f>
+        <v/>
+      </c>
+      <c r="AD98" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE98" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ98">
+        <f>AD98/AE98-1</f>
+        <v/>
+      </c>
+      <c r="AK98">
+        <f>AF98/AE98-1</f>
+        <v/>
+      </c>
+      <c r="AM98" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AS98">
+        <f>AM98/AN98-1</f>
+        <v/>
+      </c>
+      <c r="AT98">
+        <f>AO98/AN98-1</f>
+        <v/>
+      </c>
+      <c r="AV98" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW98" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB98">
+        <f>AV98/AW98-1</f>
+        <v/>
+      </c>
+      <c r="BC98">
+        <f>AX98/AW98-1</f>
+        <v/>
+      </c>
+      <c r="BE98" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF98" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH98" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI98" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK98">
+        <f>BE98/BF98-1</f>
+        <v/>
+      </c>
+      <c r="BL98">
+        <f>BG98/BF98-1</f>
+        <v/>
+      </c>
+      <c r="BN98" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO98" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ98" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR98" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT98">
+        <f>BN98/BO98-1</f>
+        <v/>
+      </c>
+      <c r="BU98">
+        <f>BP98/BO98-1</f>
+        <v/>
+      </c>
+      <c r="BW98" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX98" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ98" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA98" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC98">
+        <f>BW98/BX98-1</f>
+        <v/>
+      </c>
+      <c r="CD98">
+        <f>BY98/BX98-1</f>
+        <v/>
+      </c>
+      <c r="CF98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI98" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ98" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL98">
+        <f>CF98/CG98-1</f>
+        <v/>
+      </c>
+      <c r="CM98">
+        <f>CH98/CG98-1</f>
+        <v/>
+      </c>
+      <c r="CO98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR98" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS98" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU98">
+        <f>CO98/CP98-1</f>
+        <v/>
+      </c>
+      <c r="CV98">
+        <f>CQ98/CP98-1</f>
+        <v/>
+      </c>
+      <c r="CX98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY98" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA98" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB98" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD98">
+        <f>CX98/CY98-1</f>
+        <v/>
+      </c>
+      <c r="DE98">
+        <f>CZ98/CY98-1</f>
+        <v/>
+      </c>
+      <c r="DG98" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH98" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ98" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK98" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM98">
+        <f>DG98/DH98-1</f>
+        <v/>
+      </c>
+      <c r="DN98">
+        <f>DI98/DH98-1</f>
+        <v/>
+      </c>
+      <c r="DP98" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ98" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS98" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT98" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV98">
+        <f>DP98/DQ98-1</f>
+        <v/>
+      </c>
+      <c r="DW98">
+        <f>DR98/DQ98-1</f>
+        <v/>
+      </c>
+      <c r="DY98" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ98" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB98" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC98" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE98">
+        <f>DY98/DZ98-1</f>
+        <v/>
+      </c>
+      <c r="EF98">
+        <f>EA98/DZ98-1</f>
+        <v/>
+      </c>
+      <c r="EH98" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI98" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK98" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL98" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN98">
+        <f>EH98/EI98-1</f>
+        <v/>
+      </c>
+      <c r="EO98">
+        <f>EJ98/EI98-1</f>
+        <v/>
+      </c>
+      <c r="EQ98" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER98" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET98" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU98" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW98">
+        <f>EQ98/ER98-1</f>
+        <v/>
+      </c>
+      <c r="EX98">
+        <f>ES98/ER98-1</f>
+        <v/>
+      </c>
+      <c r="EZ98" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA98" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC98" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD98" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF98">
+        <f>EZ98/FA98-1</f>
+        <v/>
+      </c>
+      <c r="FG98">
+        <f>FB98/FA98-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG98"/>
+  <dimension ref="A1:FG99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -44066,6 +44066,449 @@
         <v/>
       </c>
     </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>15 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I99">
+        <f>C99/D99-1</f>
+        <v/>
+      </c>
+      <c r="J99">
+        <f>E99/D99-1</f>
+        <v/>
+      </c>
+      <c r="L99" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M99" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R99">
+        <f>L99/M99-1</f>
+        <v/>
+      </c>
+      <c r="S99">
+        <f>N99/M99-1</f>
+        <v/>
+      </c>
+      <c r="U99" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AA99">
+        <f>U99/V99-1</f>
+        <v/>
+      </c>
+      <c r="AB99">
+        <f>W99/V99-1</f>
+        <v/>
+      </c>
+      <c r="AD99" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE99" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ99">
+        <f>AD99/AE99-1</f>
+        <v/>
+      </c>
+      <c r="AK99">
+        <f>AF99/AE99-1</f>
+        <v/>
+      </c>
+      <c r="AM99" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AS99">
+        <f>AM99/AN99-1</f>
+        <v/>
+      </c>
+      <c r="AT99">
+        <f>AO99/AN99-1</f>
+        <v/>
+      </c>
+      <c r="AV99" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW99" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB99">
+        <f>AV99/AW99-1</f>
+        <v/>
+      </c>
+      <c r="BC99">
+        <f>AX99/AW99-1</f>
+        <v/>
+      </c>
+      <c r="BE99" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF99" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH99" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI99" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK99">
+        <f>BE99/BF99-1</f>
+        <v/>
+      </c>
+      <c r="BL99">
+        <f>BG99/BF99-1</f>
+        <v/>
+      </c>
+      <c r="BN99" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO99" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ99" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR99" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT99">
+        <f>BN99/BO99-1</f>
+        <v/>
+      </c>
+      <c r="BU99">
+        <f>BP99/BO99-1</f>
+        <v/>
+      </c>
+      <c r="BW99" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX99" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ99" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA99" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC99">
+        <f>BW99/BX99-1</f>
+        <v/>
+      </c>
+      <c r="CD99">
+        <f>BY99/BX99-1</f>
+        <v/>
+      </c>
+      <c r="CF99" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG99" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI99" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ99" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL99">
+        <f>CF99/CG99-1</f>
+        <v/>
+      </c>
+      <c r="CM99">
+        <f>CH99/CG99-1</f>
+        <v/>
+      </c>
+      <c r="CO99" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP99" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR99" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS99" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU99">
+        <f>CO99/CP99-1</f>
+        <v/>
+      </c>
+      <c r="CV99">
+        <f>CQ99/CP99-1</f>
+        <v/>
+      </c>
+      <c r="CX99" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY99" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA99" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB99" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD99">
+        <f>CX99/CY99-1</f>
+        <v/>
+      </c>
+      <c r="DE99">
+        <f>CZ99/CY99-1</f>
+        <v/>
+      </c>
+      <c r="DG99" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH99" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ99" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK99" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM99">
+        <f>DG99/DH99-1</f>
+        <v/>
+      </c>
+      <c r="DN99">
+        <f>DI99/DH99-1</f>
+        <v/>
+      </c>
+      <c r="DP99" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ99" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS99" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT99" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV99">
+        <f>DP99/DQ99-1</f>
+        <v/>
+      </c>
+      <c r="DW99">
+        <f>DR99/DQ99-1</f>
+        <v/>
+      </c>
+      <c r="DY99" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ99" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC99" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE99">
+        <f>DY99/DZ99-1</f>
+        <v/>
+      </c>
+      <c r="EF99">
+        <f>EA99/DZ99-1</f>
+        <v/>
+      </c>
+      <c r="EH99" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI99" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK99" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL99" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN99">
+        <f>EH99/EI99-1</f>
+        <v/>
+      </c>
+      <c r="EO99">
+        <f>EJ99/EI99-1</f>
+        <v/>
+      </c>
+      <c r="EQ99" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER99" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET99" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU99" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW99">
+        <f>EQ99/ER99-1</f>
+        <v/>
+      </c>
+      <c r="EX99">
+        <f>ES99/ER99-1</f>
+        <v/>
+      </c>
+      <c r="EZ99" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA99" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC99" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD99" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF99">
+        <f>EZ99/FA99-1</f>
+        <v/>
+      </c>
+      <c r="FG99">
+        <f>FB99/FA99-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG99"/>
+  <dimension ref="A1:FG100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -44509,6 +44509,445 @@
         <v/>
       </c>
     </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>16 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I100">
+        <f>C100/D100-1</f>
+        <v/>
+      </c>
+      <c r="J100">
+        <f>E100/D100-1</f>
+        <v/>
+      </c>
+      <c r="L100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R100">
+        <f>L100/M100-1</f>
+        <v/>
+      </c>
+      <c r="S100">
+        <f>N100/M100-1</f>
+        <v/>
+      </c>
+      <c r="U100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA100">
+        <f>U100/V100-1</f>
+        <v/>
+      </c>
+      <c r="AB100">
+        <f>W100/V100-1</f>
+        <v/>
+      </c>
+      <c r="AD100" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE100" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ100">
+        <f>AD100/AE100-1</f>
+        <v/>
+      </c>
+      <c r="AK100">
+        <f>AF100/AE100-1</f>
+        <v/>
+      </c>
+      <c r="AM100" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN100" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS100">
+        <f>AM100/AN100-1</f>
+        <v/>
+      </c>
+      <c r="AT100">
+        <f>AO100/AN100-1</f>
+        <v/>
+      </c>
+      <c r="AV100" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW100" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB100">
+        <f>AV100/AW100-1</f>
+        <v/>
+      </c>
+      <c r="BC100">
+        <f>AX100/AW100-1</f>
+        <v/>
+      </c>
+      <c r="BE100" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF100" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH100" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI100" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK100">
+        <f>BE100/BF100-1</f>
+        <v/>
+      </c>
+      <c r="BL100">
+        <f>BG100/BF100-1</f>
+        <v/>
+      </c>
+      <c r="BN100" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO100" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ100" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR100" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT100">
+        <f>BN100/BO100-1</f>
+        <v/>
+      </c>
+      <c r="BU100">
+        <f>BP100/BO100-1</f>
+        <v/>
+      </c>
+      <c r="BW100" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX100" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ100" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA100" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC100">
+        <f>BW100/BX100-1</f>
+        <v/>
+      </c>
+      <c r="CD100">
+        <f>BY100/BX100-1</f>
+        <v/>
+      </c>
+      <c r="CF100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI100" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ100" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL100">
+        <f>CF100/CG100-1</f>
+        <v/>
+      </c>
+      <c r="CM100">
+        <f>CH100/CG100-1</f>
+        <v/>
+      </c>
+      <c r="CO100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR100" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS100" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU100">
+        <f>CO100/CP100-1</f>
+        <v/>
+      </c>
+      <c r="CV100">
+        <f>CQ100/CP100-1</f>
+        <v/>
+      </c>
+      <c r="CX100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY100" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA100" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB100" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD100">
+        <f>CX100/CY100-1</f>
+        <v/>
+      </c>
+      <c r="DE100">
+        <f>CZ100/CY100-1</f>
+        <v/>
+      </c>
+      <c r="DG100" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH100" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ100" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK100" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM100">
+        <f>DG100/DH100-1</f>
+        <v/>
+      </c>
+      <c r="DN100">
+        <f>DI100/DH100-1</f>
+        <v/>
+      </c>
+      <c r="DP100" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ100" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS100" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT100" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV100">
+        <f>DP100/DQ100-1</f>
+        <v/>
+      </c>
+      <c r="DW100">
+        <f>DR100/DQ100-1</f>
+        <v/>
+      </c>
+      <c r="DY100" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ100" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB100" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC100" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE100">
+        <f>DY100/DZ100-1</f>
+        <v/>
+      </c>
+      <c r="EF100">
+        <f>EA100/DZ100-1</f>
+        <v/>
+      </c>
+      <c r="EH100" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI100" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK100" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL100" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN100">
+        <f>EH100/EI100-1</f>
+        <v/>
+      </c>
+      <c r="EO100">
+        <f>EJ100/EI100-1</f>
+        <v/>
+      </c>
+      <c r="EQ100" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER100" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET100" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU100" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW100">
+        <f>EQ100/ER100-1</f>
+        <v/>
+      </c>
+      <c r="EX100">
+        <f>ES100/ER100-1</f>
+        <v/>
+      </c>
+      <c r="EZ100" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA100" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC100" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD100" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF100">
+        <f>EZ100/FA100-1</f>
+        <v/>
+      </c>
+      <c r="FG100">
+        <f>FB100/FA100-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG100"/>
+  <dimension ref="A1:FG101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -44948,6 +44948,449 @@
         <v/>
       </c>
     </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>16 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I101">
+        <f>C101/D101-1</f>
+        <v/>
+      </c>
+      <c r="J101">
+        <f>E101/D101-1</f>
+        <v/>
+      </c>
+      <c r="L101" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M101" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R101">
+        <f>L101/M101-1</f>
+        <v/>
+      </c>
+      <c r="S101">
+        <f>N101/M101-1</f>
+        <v/>
+      </c>
+      <c r="U101" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V101" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA101">
+        <f>U101/V101-1</f>
+        <v/>
+      </c>
+      <c r="AB101">
+        <f>W101/V101-1</f>
+        <v/>
+      </c>
+      <c r="AD101" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE101" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ101">
+        <f>AD101/AE101-1</f>
+        <v/>
+      </c>
+      <c r="AK101">
+        <f>AF101/AE101-1</f>
+        <v/>
+      </c>
+      <c r="AM101" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN101" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS101">
+        <f>AM101/AN101-1</f>
+        <v/>
+      </c>
+      <c r="AT101">
+        <f>AO101/AN101-1</f>
+        <v/>
+      </c>
+      <c r="AV101" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW101" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB101">
+        <f>AV101/AW101-1</f>
+        <v/>
+      </c>
+      <c r="BC101">
+        <f>AX101/AW101-1</f>
+        <v/>
+      </c>
+      <c r="BE101" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF101" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH101" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI101" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK101">
+        <f>BE101/BF101-1</f>
+        <v/>
+      </c>
+      <c r="BL101">
+        <f>BG101/BF101-1</f>
+        <v/>
+      </c>
+      <c r="BN101" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO101" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ101" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR101" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT101">
+        <f>BN101/BO101-1</f>
+        <v/>
+      </c>
+      <c r="BU101">
+        <f>BP101/BO101-1</f>
+        <v/>
+      </c>
+      <c r="BW101" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX101" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ101" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA101" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC101">
+        <f>BW101/BX101-1</f>
+        <v/>
+      </c>
+      <c r="CD101">
+        <f>BY101/BX101-1</f>
+        <v/>
+      </c>
+      <c r="CF101" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG101" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI101" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ101" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL101">
+        <f>CF101/CG101-1</f>
+        <v/>
+      </c>
+      <c r="CM101">
+        <f>CH101/CG101-1</f>
+        <v/>
+      </c>
+      <c r="CO101" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP101" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CR101" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS101" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CU101">
+        <f>CO101/CP101-1</f>
+        <v/>
+      </c>
+      <c r="CV101">
+        <f>CQ101/CP101-1</f>
+        <v/>
+      </c>
+      <c r="CX101" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY101" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA101" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB101" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD101">
+        <f>CX101/CY101-1</f>
+        <v/>
+      </c>
+      <c r="DE101">
+        <f>CZ101/CY101-1</f>
+        <v/>
+      </c>
+      <c r="DG101" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH101" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ101" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK101" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM101">
+        <f>DG101/DH101-1</f>
+        <v/>
+      </c>
+      <c r="DN101">
+        <f>DI101/DH101-1</f>
+        <v/>
+      </c>
+      <c r="DP101" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ101" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS101" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT101" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV101">
+        <f>DP101/DQ101-1</f>
+        <v/>
+      </c>
+      <c r="DW101">
+        <f>DR101/DQ101-1</f>
+        <v/>
+      </c>
+      <c r="DY101" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ101" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB101" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC101" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE101">
+        <f>DY101/DZ101-1</f>
+        <v/>
+      </c>
+      <c r="EF101">
+        <f>EA101/DZ101-1</f>
+        <v/>
+      </c>
+      <c r="EH101" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI101" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK101" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL101" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN101">
+        <f>EH101/EI101-1</f>
+        <v/>
+      </c>
+      <c r="EO101">
+        <f>EJ101/EI101-1</f>
+        <v/>
+      </c>
+      <c r="EQ101" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER101" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET101" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU101" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW101">
+        <f>EQ101/ER101-1</f>
+        <v/>
+      </c>
+      <c r="EX101">
+        <f>ES101/ER101-1</f>
+        <v/>
+      </c>
+      <c r="EZ101" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA101" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC101" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD101" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF101">
+        <f>EZ101/FA101-1</f>
+        <v/>
+      </c>
+      <c r="FG101">
+        <f>FB101/FA101-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG101"/>
+  <dimension ref="A1:FG102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -45391,6 +45391,449 @@
         <v/>
       </c>
     </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>16 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I102">
+        <f>C102/D102-1</f>
+        <v/>
+      </c>
+      <c r="J102">
+        <f>E102/D102-1</f>
+        <v/>
+      </c>
+      <c r="L102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R102">
+        <f>L102/M102-1</f>
+        <v/>
+      </c>
+      <c r="S102">
+        <f>N102/M102-1</f>
+        <v/>
+      </c>
+      <c r="U102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA102">
+        <f>U102/V102-1</f>
+        <v/>
+      </c>
+      <c r="AB102">
+        <f>W102/V102-1</f>
+        <v/>
+      </c>
+      <c r="AD102" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <f>AD102/AE102-1</f>
+        <v/>
+      </c>
+      <c r="AK102">
+        <f>AF102/AE102-1</f>
+        <v/>
+      </c>
+      <c r="AM102" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN102" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS102">
+        <f>AM102/AN102-1</f>
+        <v/>
+      </c>
+      <c r="AT102">
+        <f>AO102/AN102-1</f>
+        <v/>
+      </c>
+      <c r="AV102" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW102" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB102">
+        <f>AV102/AW102-1</f>
+        <v/>
+      </c>
+      <c r="BC102">
+        <f>AX102/AW102-1</f>
+        <v/>
+      </c>
+      <c r="BE102" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF102" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH102" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI102" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK102">
+        <f>BE102/BF102-1</f>
+        <v/>
+      </c>
+      <c r="BL102">
+        <f>BG102/BF102-1</f>
+        <v/>
+      </c>
+      <c r="BN102" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO102" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ102" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR102" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT102">
+        <f>BN102/BO102-1</f>
+        <v/>
+      </c>
+      <c r="BU102">
+        <f>BP102/BO102-1</f>
+        <v/>
+      </c>
+      <c r="BW102" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX102" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ102" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA102" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC102">
+        <f>BW102/BX102-1</f>
+        <v/>
+      </c>
+      <c r="CD102">
+        <f>BY102/BX102-1</f>
+        <v/>
+      </c>
+      <c r="CF102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI102" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ102" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL102">
+        <f>CF102/CG102-1</f>
+        <v/>
+      </c>
+      <c r="CM102">
+        <f>CH102/CG102-1</f>
+        <v/>
+      </c>
+      <c r="CO102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR102" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS102" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU102">
+        <f>CO102/CP102-1</f>
+        <v/>
+      </c>
+      <c r="CV102">
+        <f>CQ102/CP102-1</f>
+        <v/>
+      </c>
+      <c r="CX102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY102" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA102" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB102" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD102">
+        <f>CX102/CY102-1</f>
+        <v/>
+      </c>
+      <c r="DE102">
+        <f>CZ102/CY102-1</f>
+        <v/>
+      </c>
+      <c r="DG102" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH102" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ102" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK102" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM102">
+        <f>DG102/DH102-1</f>
+        <v/>
+      </c>
+      <c r="DN102">
+        <f>DI102/DH102-1</f>
+        <v/>
+      </c>
+      <c r="DP102" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ102" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS102" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT102" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV102">
+        <f>DP102/DQ102-1</f>
+        <v/>
+      </c>
+      <c r="DW102">
+        <f>DR102/DQ102-1</f>
+        <v/>
+      </c>
+      <c r="DY102" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ102" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB102" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC102" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE102">
+        <f>DY102/DZ102-1</f>
+        <v/>
+      </c>
+      <c r="EF102">
+        <f>EA102/DZ102-1</f>
+        <v/>
+      </c>
+      <c r="EH102" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI102" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK102" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL102" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN102">
+        <f>EH102/EI102-1</f>
+        <v/>
+      </c>
+      <c r="EO102">
+        <f>EJ102/EI102-1</f>
+        <v/>
+      </c>
+      <c r="EQ102" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ER102" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET102" t="inlineStr">
+        <is>
+          <t>SM-F776UZWEXAA</t>
+        </is>
+      </c>
+      <c r="EU102" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW102">
+        <f>EQ102/ER102-1</f>
+        <v/>
+      </c>
+      <c r="EX102">
+        <f>ES102/ER102-1</f>
+        <v/>
+      </c>
+      <c r="EZ102" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA102" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC102" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD102" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF102">
+        <f>EZ102/FA102-1</f>
+        <v/>
+      </c>
+      <c r="FG102">
+        <f>FB102/FA102-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG102"/>
+  <dimension ref="A1:FG103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -45834,6 +45834,453 @@
         <v/>
       </c>
     </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>16 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I103">
+        <f>C103/D103-1</f>
+        <v/>
+      </c>
+      <c r="J103">
+        <f>E103/D103-1</f>
+        <v/>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M103" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R103">
+        <f>L103/M103-1</f>
+        <v/>
+      </c>
+      <c r="S103">
+        <f>N103/M103-1</f>
+        <v/>
+      </c>
+      <c r="U103" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AA103">
+        <f>U103/V103-1</f>
+        <v/>
+      </c>
+      <c r="AB103">
+        <f>W103/V103-1</f>
+        <v/>
+      </c>
+      <c r="AD103" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE103" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ103">
+        <f>AD103/AE103-1</f>
+        <v/>
+      </c>
+      <c r="AK103">
+        <f>AF103/AE103-1</f>
+        <v/>
+      </c>
+      <c r="AM103" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN103" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS103">
+        <f>AM103/AN103-1</f>
+        <v/>
+      </c>
+      <c r="AT103">
+        <f>AO103/AN103-1</f>
+        <v/>
+      </c>
+      <c r="AV103" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW103" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB103">
+        <f>AV103/AW103-1</f>
+        <v/>
+      </c>
+      <c r="BC103">
+        <f>AX103/AW103-1</f>
+        <v/>
+      </c>
+      <c r="BE103" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF103" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH103" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI103" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK103">
+        <f>BE103/BF103-1</f>
+        <v/>
+      </c>
+      <c r="BL103">
+        <f>BG103/BF103-1</f>
+        <v/>
+      </c>
+      <c r="BN103" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO103" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ103" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR103" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT103">
+        <f>BN103/BO103-1</f>
+        <v/>
+      </c>
+      <c r="BU103">
+        <f>BP103/BO103-1</f>
+        <v/>
+      </c>
+      <c r="BW103" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX103" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ103" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA103" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC103">
+        <f>BW103/BX103-1</f>
+        <v/>
+      </c>
+      <c r="CD103">
+        <f>BY103/BX103-1</f>
+        <v/>
+      </c>
+      <c r="CF103" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG103" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI103" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ103" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL103">
+        <f>CF103/CG103-1</f>
+        <v/>
+      </c>
+      <c r="CM103">
+        <f>CH103/CG103-1</f>
+        <v/>
+      </c>
+      <c r="CO103" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP103" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR103" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS103" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU103">
+        <f>CO103/CP103-1</f>
+        <v/>
+      </c>
+      <c r="CV103">
+        <f>CQ103/CP103-1</f>
+        <v/>
+      </c>
+      <c r="CX103" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY103" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA103" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB103" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD103">
+        <f>CX103/CY103-1</f>
+        <v/>
+      </c>
+      <c r="DE103">
+        <f>CZ103/CY103-1</f>
+        <v/>
+      </c>
+      <c r="DG103" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH103" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ103" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK103" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM103">
+        <f>DG103/DH103-1</f>
+        <v/>
+      </c>
+      <c r="DN103">
+        <f>DI103/DH103-1</f>
+        <v/>
+      </c>
+      <c r="DP103" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ103" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS103" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT103" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV103">
+        <f>DP103/DQ103-1</f>
+        <v/>
+      </c>
+      <c r="DW103">
+        <f>DR103/DQ103-1</f>
+        <v/>
+      </c>
+      <c r="DY103" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ103" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB103" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC103" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE103">
+        <f>DY103/DZ103-1</f>
+        <v/>
+      </c>
+      <c r="EF103">
+        <f>EA103/DZ103-1</f>
+        <v/>
+      </c>
+      <c r="EH103" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI103" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK103" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL103" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN103">
+        <f>EH103/EI103-1</f>
+        <v/>
+      </c>
+      <c r="EO103">
+        <f>EJ103/EI103-1</f>
+        <v/>
+      </c>
+      <c r="EQ103" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER103" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET103" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU103" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW103">
+        <f>EQ103/ER103-1</f>
+        <v/>
+      </c>
+      <c r="EX103">
+        <f>ES103/ER103-1</f>
+        <v/>
+      </c>
+      <c r="EZ103" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA103" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC103" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD103" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF103">
+        <f>EZ103/FA103-1</f>
+        <v/>
+      </c>
+      <c r="FG103">
+        <f>FB103/FA103-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG103"/>
+  <dimension ref="A1:FG104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -46281,6 +46281,451 @@
         <v/>
       </c>
     </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>17 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I104">
+        <f>C104/D104-1</f>
+        <v/>
+      </c>
+      <c r="J104">
+        <f>E104/D104-1</f>
+        <v/>
+      </c>
+      <c r="L104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R104">
+        <f>L104/M104-1</f>
+        <v/>
+      </c>
+      <c r="S104">
+        <f>N104/M104-1</f>
+        <v/>
+      </c>
+      <c r="U104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA104">
+        <f>U104/V104-1</f>
+        <v/>
+      </c>
+      <c r="AB104">
+        <f>W104/V104-1</f>
+        <v/>
+      </c>
+      <c r="AD104" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE104" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ104">
+        <f>AD104/AE104-1</f>
+        <v/>
+      </c>
+      <c r="AK104">
+        <f>AF104/AE104-1</f>
+        <v/>
+      </c>
+      <c r="AM104" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN104" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS104">
+        <f>AM104/AN104-1</f>
+        <v/>
+      </c>
+      <c r="AT104">
+        <f>AO104/AN104-1</f>
+        <v/>
+      </c>
+      <c r="AV104" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW104" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB104">
+        <f>AV104/AW104-1</f>
+        <v/>
+      </c>
+      <c r="BC104">
+        <f>AX104/AW104-1</f>
+        <v/>
+      </c>
+      <c r="BE104" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF104" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH104" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI104" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK104">
+        <f>BE104/BF104-1</f>
+        <v/>
+      </c>
+      <c r="BL104">
+        <f>BG104/BF104-1</f>
+        <v/>
+      </c>
+      <c r="BN104" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO104" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ104" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR104" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT104">
+        <f>BN104/BO104-1</f>
+        <v/>
+      </c>
+      <c r="BU104">
+        <f>BP104/BO104-1</f>
+        <v/>
+      </c>
+      <c r="BW104" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX104" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BZ104" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA104" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC104">
+        <f>BW104/BX104-1</f>
+        <v/>
+      </c>
+      <c r="CD104">
+        <f>BY104/BX104-1</f>
+        <v/>
+      </c>
+      <c r="CF104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI104" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ104" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL104">
+        <f>CF104/CG104-1</f>
+        <v/>
+      </c>
+      <c r="CM104">
+        <f>CH104/CG104-1</f>
+        <v/>
+      </c>
+      <c r="CO104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR104" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS104" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU104">
+        <f>CO104/CP104-1</f>
+        <v/>
+      </c>
+      <c r="CV104">
+        <f>CQ104/CP104-1</f>
+        <v/>
+      </c>
+      <c r="CX104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY104" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA104" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB104" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD104">
+        <f>CX104/CY104-1</f>
+        <v/>
+      </c>
+      <c r="DE104">
+        <f>CZ104/CY104-1</f>
+        <v/>
+      </c>
+      <c r="DG104" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH104" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ104" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK104" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM104">
+        <f>DG104/DH104-1</f>
+        <v/>
+      </c>
+      <c r="DN104">
+        <f>DI104/DH104-1</f>
+        <v/>
+      </c>
+      <c r="DP104" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ104" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS104" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT104" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV104">
+        <f>DP104/DQ104-1</f>
+        <v/>
+      </c>
+      <c r="DW104">
+        <f>DR104/DQ104-1</f>
+        <v/>
+      </c>
+      <c r="DY104" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ104" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB104" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC104" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE104">
+        <f>DY104/DZ104-1</f>
+        <v/>
+      </c>
+      <c r="EF104">
+        <f>EA104/DZ104-1</f>
+        <v/>
+      </c>
+      <c r="EH104" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI104" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK104" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL104" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN104">
+        <f>EH104/EI104-1</f>
+        <v/>
+      </c>
+      <c r="EO104">
+        <f>EJ104/EI104-1</f>
+        <v/>
+      </c>
+      <c r="EQ104" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER104" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET104" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU104" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW104">
+        <f>EQ104/ER104-1</f>
+        <v/>
+      </c>
+      <c r="EX104">
+        <f>ES104/ER104-1</f>
+        <v/>
+      </c>
+      <c r="EZ104" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA104" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC104" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD104" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF104">
+        <f>EZ104/FA104-1</f>
+        <v/>
+      </c>
+      <c r="FG104">
+        <f>FB104/FA104-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG104"/>
+  <dimension ref="A1:FG105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -46726,6 +46726,449 @@
         <v/>
       </c>
     </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>17 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I105">
+        <f>C105/D105-1</f>
+        <v/>
+      </c>
+      <c r="J105">
+        <f>E105/D105-1</f>
+        <v/>
+      </c>
+      <c r="L105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R105">
+        <f>L105/M105-1</f>
+        <v/>
+      </c>
+      <c r="S105">
+        <f>N105/M105-1</f>
+        <v/>
+      </c>
+      <c r="U105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA105">
+        <f>U105/V105-1</f>
+        <v/>
+      </c>
+      <c r="AB105">
+        <f>W105/V105-1</f>
+        <v/>
+      </c>
+      <c r="AD105" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE105" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ105">
+        <f>AD105/AE105-1</f>
+        <v/>
+      </c>
+      <c r="AK105">
+        <f>AF105/AE105-1</f>
+        <v/>
+      </c>
+      <c r="AM105" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN105" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS105">
+        <f>AM105/AN105-1</f>
+        <v/>
+      </c>
+      <c r="AT105">
+        <f>AO105/AN105-1</f>
+        <v/>
+      </c>
+      <c r="AV105" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW105" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB105">
+        <f>AV105/AW105-1</f>
+        <v/>
+      </c>
+      <c r="BC105">
+        <f>AX105/AW105-1</f>
+        <v/>
+      </c>
+      <c r="BE105" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF105" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH105" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI105" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK105">
+        <f>BE105/BF105-1</f>
+        <v/>
+      </c>
+      <c r="BL105">
+        <f>BG105/BF105-1</f>
+        <v/>
+      </c>
+      <c r="BN105" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO105" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ105" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR105" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT105">
+        <f>BN105/BO105-1</f>
+        <v/>
+      </c>
+      <c r="BU105">
+        <f>BP105/BO105-1</f>
+        <v/>
+      </c>
+      <c r="BW105" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX105" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ105" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA105" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC105">
+        <f>BW105/BX105-1</f>
+        <v/>
+      </c>
+      <c r="CD105">
+        <f>BY105/BX105-1</f>
+        <v/>
+      </c>
+      <c r="CF105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI105" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ105" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL105">
+        <f>CF105/CG105-1</f>
+        <v/>
+      </c>
+      <c r="CM105">
+        <f>CH105/CG105-1</f>
+        <v/>
+      </c>
+      <c r="CO105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR105" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS105" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU105">
+        <f>CO105/CP105-1</f>
+        <v/>
+      </c>
+      <c r="CV105">
+        <f>CQ105/CP105-1</f>
+        <v/>
+      </c>
+      <c r="CX105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY105" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA105" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB105" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD105">
+        <f>CX105/CY105-1</f>
+        <v/>
+      </c>
+      <c r="DE105">
+        <f>CZ105/CY105-1</f>
+        <v/>
+      </c>
+      <c r="DG105" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH105" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ105" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK105" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM105">
+        <f>DG105/DH105-1</f>
+        <v/>
+      </c>
+      <c r="DN105">
+        <f>DI105/DH105-1</f>
+        <v/>
+      </c>
+      <c r="DP105" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ105" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS105" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT105" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV105">
+        <f>DP105/DQ105-1</f>
+        <v/>
+      </c>
+      <c r="DW105">
+        <f>DR105/DQ105-1</f>
+        <v/>
+      </c>
+      <c r="DY105" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ105" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB105" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC105" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE105">
+        <f>DY105/DZ105-1</f>
+        <v/>
+      </c>
+      <c r="EF105">
+        <f>EA105/DZ105-1</f>
+        <v/>
+      </c>
+      <c r="EH105" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI105" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK105" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL105" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN105">
+        <f>EH105/EI105-1</f>
+        <v/>
+      </c>
+      <c r="EO105">
+        <f>EJ105/EI105-1</f>
+        <v/>
+      </c>
+      <c r="EQ105" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER105" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET105" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU105" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW105">
+        <f>EQ105/ER105-1</f>
+        <v/>
+      </c>
+      <c r="EX105">
+        <f>ES105/ER105-1</f>
+        <v/>
+      </c>
+      <c r="EZ105" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA105" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC105" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD105" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF105">
+        <f>EZ105/FA105-1</f>
+        <v/>
+      </c>
+      <c r="FG105">
+        <f>FB105/FA105-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG105"/>
+  <dimension ref="A1:FG106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -47169,6 +47169,455 @@
         <v/>
       </c>
     </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>17 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I106">
+        <f>C106/D106-1</f>
+        <v/>
+      </c>
+      <c r="J106">
+        <f>E106/D106-1</f>
+        <v/>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="R106">
+        <f>L106/M106-1</f>
+        <v/>
+      </c>
+      <c r="S106">
+        <f>N106/M106-1</f>
+        <v/>
+      </c>
+      <c r="U106" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V106" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA106">
+        <f>U106/V106-1</f>
+        <v/>
+      </c>
+      <c r="AB106">
+        <f>W106/V106-1</f>
+        <v/>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE106" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ106">
+        <f>AD106/AE106-1</f>
+        <v/>
+      </c>
+      <c r="AK106">
+        <f>AF106/AE106-1</f>
+        <v/>
+      </c>
+      <c r="AM106" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN106" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS106">
+        <f>AM106/AN106-1</f>
+        <v/>
+      </c>
+      <c r="AT106">
+        <f>AO106/AN106-1</f>
+        <v/>
+      </c>
+      <c r="AV106" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW106" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB106">
+        <f>AV106/AW106-1</f>
+        <v/>
+      </c>
+      <c r="BC106">
+        <f>AX106/AW106-1</f>
+        <v/>
+      </c>
+      <c r="BE106" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF106" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH106" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI106" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK106">
+        <f>BE106/BF106-1</f>
+        <v/>
+      </c>
+      <c r="BL106">
+        <f>BG106/BF106-1</f>
+        <v/>
+      </c>
+      <c r="BN106" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO106" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ106" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR106" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT106">
+        <f>BN106/BO106-1</f>
+        <v/>
+      </c>
+      <c r="BU106">
+        <f>BP106/BO106-1</f>
+        <v/>
+      </c>
+      <c r="BW106" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX106" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ106" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA106" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC106">
+        <f>BW106/BX106-1</f>
+        <v/>
+      </c>
+      <c r="CD106">
+        <f>BY106/BX106-1</f>
+        <v/>
+      </c>
+      <c r="CF106" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG106" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI106" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ106" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL106">
+        <f>CF106/CG106-1</f>
+        <v/>
+      </c>
+      <c r="CM106">
+        <f>CH106/CG106-1</f>
+        <v/>
+      </c>
+      <c r="CO106" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP106" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR106" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS106" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU106">
+        <f>CO106/CP106-1</f>
+        <v/>
+      </c>
+      <c r="CV106">
+        <f>CQ106/CP106-1</f>
+        <v/>
+      </c>
+      <c r="CX106" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY106" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA106" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB106" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD106">
+        <f>CX106/CY106-1</f>
+        <v/>
+      </c>
+      <c r="DE106">
+        <f>CZ106/CY106-1</f>
+        <v/>
+      </c>
+      <c r="DG106" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH106" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ106" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK106" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM106">
+        <f>DG106/DH106-1</f>
+        <v/>
+      </c>
+      <c r="DN106">
+        <f>DI106/DH106-1</f>
+        <v/>
+      </c>
+      <c r="DP106" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ106" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS106" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT106" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV106">
+        <f>DP106/DQ106-1</f>
+        <v/>
+      </c>
+      <c r="DW106">
+        <f>DR106/DQ106-1</f>
+        <v/>
+      </c>
+      <c r="DY106" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ106" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB106" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC106" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE106">
+        <f>DY106/DZ106-1</f>
+        <v/>
+      </c>
+      <c r="EF106">
+        <f>EA106/DZ106-1</f>
+        <v/>
+      </c>
+      <c r="EH106" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI106" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK106" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL106" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN106">
+        <f>EH106/EI106-1</f>
+        <v/>
+      </c>
+      <c r="EO106">
+        <f>EJ106/EI106-1</f>
+        <v/>
+      </c>
+      <c r="EQ106" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER106" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET106" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU106" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW106">
+        <f>EQ106/ER106-1</f>
+        <v/>
+      </c>
+      <c r="EX106">
+        <f>ES106/ER106-1</f>
+        <v/>
+      </c>
+      <c r="EZ106" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA106" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC106" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD106" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF106">
+        <f>EZ106/FA106-1</f>
+        <v/>
+      </c>
+      <c r="FG106">
+        <f>FB106/FA106-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG106"/>
+  <dimension ref="A1:FG107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -47618,6 +47618,449 @@
         <v/>
       </c>
     </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>17 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I107">
+        <f>C107/D107-1</f>
+        <v/>
+      </c>
+      <c r="J107">
+        <f>E107/D107-1</f>
+        <v/>
+      </c>
+      <c r="L107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R107">
+        <f>L107/M107-1</f>
+        <v/>
+      </c>
+      <c r="S107">
+        <f>N107/M107-1</f>
+        <v/>
+      </c>
+      <c r="U107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA107">
+        <f>U107/V107-1</f>
+        <v/>
+      </c>
+      <c r="AB107">
+        <f>W107/V107-1</f>
+        <v/>
+      </c>
+      <c r="AD107" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE107" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ107">
+        <f>AD107/AE107-1</f>
+        <v/>
+      </c>
+      <c r="AK107">
+        <f>AF107/AE107-1</f>
+        <v/>
+      </c>
+      <c r="AM107" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN107" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS107">
+        <f>AM107/AN107-1</f>
+        <v/>
+      </c>
+      <c r="AT107">
+        <f>AO107/AN107-1</f>
+        <v/>
+      </c>
+      <c r="AV107" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW107" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB107">
+        <f>AV107/AW107-1</f>
+        <v/>
+      </c>
+      <c r="BC107">
+        <f>AX107/AW107-1</f>
+        <v/>
+      </c>
+      <c r="BE107" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF107" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH107" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI107" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK107">
+        <f>BE107/BF107-1</f>
+        <v/>
+      </c>
+      <c r="BL107">
+        <f>BG107/BF107-1</f>
+        <v/>
+      </c>
+      <c r="BN107" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO107" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ107" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR107" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT107">
+        <f>BN107/BO107-1</f>
+        <v/>
+      </c>
+      <c r="BU107">
+        <f>BP107/BO107-1</f>
+        <v/>
+      </c>
+      <c r="BW107" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX107" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ107" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA107" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC107">
+        <f>BW107/BX107-1</f>
+        <v/>
+      </c>
+      <c r="CD107">
+        <f>BY107/BX107-1</f>
+        <v/>
+      </c>
+      <c r="CF107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI107" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ107" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL107">
+        <f>CF107/CG107-1</f>
+        <v/>
+      </c>
+      <c r="CM107">
+        <f>CH107/CG107-1</f>
+        <v/>
+      </c>
+      <c r="CO107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR107" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS107" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU107">
+        <f>CO107/CP107-1</f>
+        <v/>
+      </c>
+      <c r="CV107">
+        <f>CQ107/CP107-1</f>
+        <v/>
+      </c>
+      <c r="CX107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY107" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA107" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB107" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD107">
+        <f>CX107/CY107-1</f>
+        <v/>
+      </c>
+      <c r="DE107">
+        <f>CZ107/CY107-1</f>
+        <v/>
+      </c>
+      <c r="DG107" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH107" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ107" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK107" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM107">
+        <f>DG107/DH107-1</f>
+        <v/>
+      </c>
+      <c r="DN107">
+        <f>DI107/DH107-1</f>
+        <v/>
+      </c>
+      <c r="DP107" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ107" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS107" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT107" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV107">
+        <f>DP107/DQ107-1</f>
+        <v/>
+      </c>
+      <c r="DW107">
+        <f>DR107/DQ107-1</f>
+        <v/>
+      </c>
+      <c r="DY107" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ107" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB107" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC107" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE107">
+        <f>DY107/DZ107-1</f>
+        <v/>
+      </c>
+      <c r="EF107">
+        <f>EA107/DZ107-1</f>
+        <v/>
+      </c>
+      <c r="EH107" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI107" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK107" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL107" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN107">
+        <f>EH107/EI107-1</f>
+        <v/>
+      </c>
+      <c r="EO107">
+        <f>EJ107/EI107-1</f>
+        <v/>
+      </c>
+      <c r="EQ107" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER107" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET107" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU107" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW107">
+        <f>EQ107/ER107-1</f>
+        <v/>
+      </c>
+      <c r="EX107">
+        <f>ES107/ER107-1</f>
+        <v/>
+      </c>
+      <c r="EZ107" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA107" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC107" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD107" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF107">
+        <f>EZ107/FA107-1</f>
+        <v/>
+      </c>
+      <c r="FG107">
+        <f>FB107/FA107-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG107"/>
+  <dimension ref="A1:FG108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -48061,6 +48061,447 @@
         <v/>
       </c>
     </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>18 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I108">
+        <f>C108/D108-1</f>
+        <v/>
+      </c>
+      <c r="J108">
+        <f>E108/D108-1</f>
+        <v/>
+      </c>
+      <c r="L108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R108">
+        <f>L108/M108-1</f>
+        <v/>
+      </c>
+      <c r="S108">
+        <f>N108/M108-1</f>
+        <v/>
+      </c>
+      <c r="U108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA108">
+        <f>U108/V108-1</f>
+        <v/>
+      </c>
+      <c r="AB108">
+        <f>W108/V108-1</f>
+        <v/>
+      </c>
+      <c r="AD108" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE108" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ108">
+        <f>AD108/AE108-1</f>
+        <v/>
+      </c>
+      <c r="AK108">
+        <f>AF108/AE108-1</f>
+        <v/>
+      </c>
+      <c r="AM108" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN108" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS108">
+        <f>AM108/AN108-1</f>
+        <v/>
+      </c>
+      <c r="AT108">
+        <f>AO108/AN108-1</f>
+        <v/>
+      </c>
+      <c r="AV108" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW108" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB108">
+        <f>AV108/AW108-1</f>
+        <v/>
+      </c>
+      <c r="BC108">
+        <f>AX108/AW108-1</f>
+        <v/>
+      </c>
+      <c r="BE108" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF108" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH108" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI108" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK108">
+        <f>BE108/BF108-1</f>
+        <v/>
+      </c>
+      <c r="BL108">
+        <f>BG108/BF108-1</f>
+        <v/>
+      </c>
+      <c r="BN108" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO108" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ108" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR108" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT108">
+        <f>BN108/BO108-1</f>
+        <v/>
+      </c>
+      <c r="BU108">
+        <f>BP108/BO108-1</f>
+        <v/>
+      </c>
+      <c r="BW108" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX108" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ108" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA108" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC108">
+        <f>BW108/BX108-1</f>
+        <v/>
+      </c>
+      <c r="CD108">
+        <f>BY108/BX108-1</f>
+        <v/>
+      </c>
+      <c r="CF108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI108" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ108" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL108">
+        <f>CF108/CG108-1</f>
+        <v/>
+      </c>
+      <c r="CM108">
+        <f>CH108/CG108-1</f>
+        <v/>
+      </c>
+      <c r="CO108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR108" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS108" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU108">
+        <f>CO108/CP108-1</f>
+        <v/>
+      </c>
+      <c r="CV108">
+        <f>CQ108/CP108-1</f>
+        <v/>
+      </c>
+      <c r="CX108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY108" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA108" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB108" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD108">
+        <f>CX108/CY108-1</f>
+        <v/>
+      </c>
+      <c r="DE108">
+        <f>CZ108/CY108-1</f>
+        <v/>
+      </c>
+      <c r="DG108" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH108" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ108" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK108" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM108">
+        <f>DG108/DH108-1</f>
+        <v/>
+      </c>
+      <c r="DN108">
+        <f>DI108/DH108-1</f>
+        <v/>
+      </c>
+      <c r="DP108" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ108" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS108" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT108" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV108">
+        <f>DP108/DQ108-1</f>
+        <v/>
+      </c>
+      <c r="DW108">
+        <f>DR108/DQ108-1</f>
+        <v/>
+      </c>
+      <c r="DY108" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ108" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB108" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC108" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE108">
+        <f>DY108/DZ108-1</f>
+        <v/>
+      </c>
+      <c r="EF108">
+        <f>EA108/DZ108-1</f>
+        <v/>
+      </c>
+      <c r="EH108" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI108" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK108" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL108" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN108">
+        <f>EH108/EI108-1</f>
+        <v/>
+      </c>
+      <c r="EO108">
+        <f>EJ108/EI108-1</f>
+        <v/>
+      </c>
+      <c r="EQ108" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER108" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET108" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU108" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW108">
+        <f>EQ108/ER108-1</f>
+        <v/>
+      </c>
+      <c r="EX108">
+        <f>ES108/ER108-1</f>
+        <v/>
+      </c>
+      <c r="EZ108" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA108" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC108" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD108" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF108">
+        <f>EZ108/FA108-1</f>
+        <v/>
+      </c>
+      <c r="FG108">
+        <f>FB108/FA108-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG108"/>
+  <dimension ref="A1:IS109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -48502,6 +48502,689 @@
         <v/>
       </c>
     </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>18 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I109">
+        <f>C109/D109-1</f>
+        <v/>
+      </c>
+      <c r="J109">
+        <f>E109/D109-1</f>
+        <v/>
+      </c>
+      <c r="L109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R109">
+        <f>L109/M109-1</f>
+        <v/>
+      </c>
+      <c r="S109">
+        <f>N109/M109-1</f>
+        <v/>
+      </c>
+      <c r="U109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA109">
+        <f>U109/V109-1</f>
+        <v/>
+      </c>
+      <c r="AB109">
+        <f>W109/V109-1</f>
+        <v/>
+      </c>
+      <c r="AD109" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE109" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ109">
+        <f>AD109/AE109-1</f>
+        <v/>
+      </c>
+      <c r="AK109">
+        <f>AF109/AE109-1</f>
+        <v/>
+      </c>
+      <c r="AM109" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN109" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS109">
+        <f>AM109/AN109-1</f>
+        <v/>
+      </c>
+      <c r="AT109">
+        <f>AO109/AN109-1</f>
+        <v/>
+      </c>
+      <c r="AV109" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW109" s="9" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB109">
+        <f>AV109/AW109-1</f>
+        <v/>
+      </c>
+      <c r="BC109">
+        <f>AX109/AW109-1</f>
+        <v/>
+      </c>
+      <c r="BE109" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF109" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH109" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI109" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK109">
+        <f>BE109/BF109-1</f>
+        <v/>
+      </c>
+      <c r="BL109">
+        <f>BG109/BF109-1</f>
+        <v/>
+      </c>
+      <c r="BN109" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO109" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ109" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR109" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT109">
+        <f>BN109/BO109-1</f>
+        <v/>
+      </c>
+      <c r="BU109">
+        <f>BP109/BO109-1</f>
+        <v/>
+      </c>
+      <c r="BW109" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX109" s="9" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ109" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA109" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC109">
+        <f>BW109/BX109-1</f>
+        <v/>
+      </c>
+      <c r="CD109">
+        <f>BY109/BX109-1</f>
+        <v/>
+      </c>
+      <c r="CF109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI109" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ109" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL109">
+        <f>CF109/CG109-1</f>
+        <v/>
+      </c>
+      <c r="CM109">
+        <f>CH109/CG109-1</f>
+        <v/>
+      </c>
+      <c r="CO109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR109" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS109" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU109">
+        <f>CO109/CP109-1</f>
+        <v/>
+      </c>
+      <c r="CV109">
+        <f>CQ109/CP109-1</f>
+        <v/>
+      </c>
+      <c r="CX109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY109" s="9" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA109" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB109" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD109">
+        <f>CX109/CY109-1</f>
+        <v/>
+      </c>
+      <c r="DE109">
+        <f>CZ109/CY109-1</f>
+        <v/>
+      </c>
+      <c r="DG109" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH109" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ109" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK109" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM109">
+        <f>DG109/DH109-1</f>
+        <v/>
+      </c>
+      <c r="DN109">
+        <f>DI109/DH109-1</f>
+        <v/>
+      </c>
+      <c r="DP109" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ109" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS109" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT109" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV109">
+        <f>DP109/DQ109-1</f>
+        <v/>
+      </c>
+      <c r="DW109">
+        <f>DR109/DQ109-1</f>
+        <v/>
+      </c>
+      <c r="DY109" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ109" s="9" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB109" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC109" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE109">
+        <f>DY109/DZ109-1</f>
+        <v/>
+      </c>
+      <c r="EF109">
+        <f>EA109/DZ109-1</f>
+        <v/>
+      </c>
+      <c r="EH109" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI109" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK109" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL109" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN109">
+        <f>EH109/EI109-1</f>
+        <v/>
+      </c>
+      <c r="EO109">
+        <f>EJ109/EI109-1</f>
+        <v/>
+      </c>
+      <c r="EQ109" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER109" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET109" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU109" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW109">
+        <f>EQ109/ER109-1</f>
+        <v/>
+      </c>
+      <c r="EX109">
+        <f>ES109/ER109-1</f>
+        <v/>
+      </c>
+      <c r="EZ109" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA109" s="9" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC109" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD109" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF109">
+        <f>EZ109/FA109-1</f>
+        <v/>
+      </c>
+      <c r="FG109">
+        <f>FB109/FA109-1</f>
+        <v/>
+      </c>
+      <c r="FI109" s="9" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ109" s="9" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL109" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM109" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO109">
+        <f>FI109/FJ109-1</f>
+        <v/>
+      </c>
+      <c r="FP109">
+        <f>FK109/FJ109-1</f>
+        <v/>
+      </c>
+      <c r="FR109" s="9" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS109" s="9" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU109" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV109" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX109">
+        <f>FR109/FS109-1</f>
+        <v/>
+      </c>
+      <c r="FY109">
+        <f>FT109/FS109-1</f>
+        <v/>
+      </c>
+      <c r="GA109" s="9" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB109" s="9" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD109" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE109" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG109">
+        <f>GA109/GB109-1</f>
+        <v/>
+      </c>
+      <c r="GH109">
+        <f>GC109/GB109-1</f>
+        <v/>
+      </c>
+      <c r="GJ109" s="9" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK109" s="9" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM109" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN109" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP109">
+        <f>GJ109/GK109-1</f>
+        <v/>
+      </c>
+      <c r="GQ109">
+        <f>GL109/GK109-1</f>
+        <v/>
+      </c>
+      <c r="GS109" s="9" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT109" s="9" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV109" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW109" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY109">
+        <f>GS109/GT109-1</f>
+        <v/>
+      </c>
+      <c r="GZ109">
+        <f>GU109/GT109-1</f>
+        <v/>
+      </c>
+      <c r="HB109" s="9" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC109" s="9" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE109" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF109" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH109">
+        <f>HB109/HC109-1</f>
+        <v/>
+      </c>
+      <c r="HI109">
+        <f>HD109/HC109-1</f>
+        <v/>
+      </c>
+      <c r="HK109" s="9" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL109" s="9" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN109" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO109" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ109">
+        <f>HK109/HL109-1</f>
+        <v/>
+      </c>
+      <c r="HR109">
+        <f>HM109/HL109-1</f>
+        <v/>
+      </c>
+      <c r="HT109" s="9" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU109" s="9" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW109" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX109" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ109">
+        <f>HT109/HU109-1</f>
+        <v/>
+      </c>
+      <c r="IA109">
+        <f>HV109/HU109-1</f>
+        <v/>
+      </c>
+      <c r="IC109" s="9" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID109" s="9" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF109" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG109" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II109">
+        <f>IC109/ID109-1</f>
+        <v/>
+      </c>
+      <c r="IJ109">
+        <f>IE109/ID109-1</f>
+        <v/>
+      </c>
+      <c r="IL109" s="9" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM109" s="9" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO109" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP109" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR109">
+        <f>IL109/IM109-1</f>
+        <v/>
+      </c>
+      <c r="IS109">
+        <f>IN109/IM109-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS110"/>
+  <dimension ref="A1:IS111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -65754,6 +65754,689 @@
         <v/>
       </c>
     </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>18 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I111">
+        <f>C111/D111-1</f>
+        <v/>
+      </c>
+      <c r="J111">
+        <f>E111/D111-1</f>
+        <v/>
+      </c>
+      <c r="L111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R111">
+        <f>L111/M111-1</f>
+        <v/>
+      </c>
+      <c r="S111">
+        <f>N111/M111-1</f>
+        <v/>
+      </c>
+      <c r="U111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA111">
+        <f>U111/V111-1</f>
+        <v/>
+      </c>
+      <c r="AB111">
+        <f>W111/V111-1</f>
+        <v/>
+      </c>
+      <c r="AD111" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE111" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <f>AD111/AE111-1</f>
+        <v/>
+      </c>
+      <c r="AK111">
+        <f>AF111/AE111-1</f>
+        <v/>
+      </c>
+      <c r="AM111" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN111" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS111">
+        <f>AM111/AN111-1</f>
+        <v/>
+      </c>
+      <c r="AT111">
+        <f>AO111/AN111-1</f>
+        <v/>
+      </c>
+      <c r="AV111" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW111" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB111">
+        <f>AV111/AW111-1</f>
+        <v/>
+      </c>
+      <c r="BC111">
+        <f>AX111/AW111-1</f>
+        <v/>
+      </c>
+      <c r="BE111" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF111" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH111" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI111" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK111">
+        <f>BE111/BF111-1</f>
+        <v/>
+      </c>
+      <c r="BL111">
+        <f>BG111/BF111-1</f>
+        <v/>
+      </c>
+      <c r="BN111" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO111" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ111" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR111" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT111">
+        <f>BN111/BO111-1</f>
+        <v/>
+      </c>
+      <c r="BU111">
+        <f>BP111/BO111-1</f>
+        <v/>
+      </c>
+      <c r="BW111" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX111" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ111" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA111" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC111">
+        <f>BW111/BX111-1</f>
+        <v/>
+      </c>
+      <c r="CD111">
+        <f>BY111/BX111-1</f>
+        <v/>
+      </c>
+      <c r="CF111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI111" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ111" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL111">
+        <f>CF111/CG111-1</f>
+        <v/>
+      </c>
+      <c r="CM111">
+        <f>CH111/CG111-1</f>
+        <v/>
+      </c>
+      <c r="CO111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR111" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS111" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU111">
+        <f>CO111/CP111-1</f>
+        <v/>
+      </c>
+      <c r="CV111">
+        <f>CQ111/CP111-1</f>
+        <v/>
+      </c>
+      <c r="CX111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY111" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA111" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB111" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD111">
+        <f>CX111/CY111-1</f>
+        <v/>
+      </c>
+      <c r="DE111">
+        <f>CZ111/CY111-1</f>
+        <v/>
+      </c>
+      <c r="DG111" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH111" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ111" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK111" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM111">
+        <f>DG111/DH111-1</f>
+        <v/>
+      </c>
+      <c r="DN111">
+        <f>DI111/DH111-1</f>
+        <v/>
+      </c>
+      <c r="DP111" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ111" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS111" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT111" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV111">
+        <f>DP111/DQ111-1</f>
+        <v/>
+      </c>
+      <c r="DW111">
+        <f>DR111/DQ111-1</f>
+        <v/>
+      </c>
+      <c r="DY111" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ111" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB111" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC111" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE111">
+        <f>DY111/DZ111-1</f>
+        <v/>
+      </c>
+      <c r="EF111">
+        <f>EA111/DZ111-1</f>
+        <v/>
+      </c>
+      <c r="EH111" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI111" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK111" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL111" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN111">
+        <f>EH111/EI111-1</f>
+        <v/>
+      </c>
+      <c r="EO111">
+        <f>EJ111/EI111-1</f>
+        <v/>
+      </c>
+      <c r="EQ111" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER111" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET111" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU111" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW111">
+        <f>EQ111/ER111-1</f>
+        <v/>
+      </c>
+      <c r="EX111">
+        <f>ES111/ER111-1</f>
+        <v/>
+      </c>
+      <c r="EZ111" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA111" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC111" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD111" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF111">
+        <f>EZ111/FA111-1</f>
+        <v/>
+      </c>
+      <c r="FG111">
+        <f>FB111/FA111-1</f>
+        <v/>
+      </c>
+      <c r="FI111" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ111" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL111" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM111" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO111">
+        <f>FI111/FJ111-1</f>
+        <v/>
+      </c>
+      <c r="FP111">
+        <f>FK111/FJ111-1</f>
+        <v/>
+      </c>
+      <c r="FR111" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS111" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU111" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV111" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX111">
+        <f>FR111/FS111-1</f>
+        <v/>
+      </c>
+      <c r="FY111">
+        <f>FT111/FS111-1</f>
+        <v/>
+      </c>
+      <c r="GA111" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB111" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD111" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE111" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG111">
+        <f>GA111/GB111-1</f>
+        <v/>
+      </c>
+      <c r="GH111">
+        <f>GC111/GB111-1</f>
+        <v/>
+      </c>
+      <c r="GJ111" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK111" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM111" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN111" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP111">
+        <f>GJ111/GK111-1</f>
+        <v/>
+      </c>
+      <c r="GQ111">
+        <f>GL111/GK111-1</f>
+        <v/>
+      </c>
+      <c r="GS111" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT111" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV111" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW111" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY111">
+        <f>GS111/GT111-1</f>
+        <v/>
+      </c>
+      <c r="GZ111">
+        <f>GU111/GT111-1</f>
+        <v/>
+      </c>
+      <c r="HB111" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC111" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE111" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF111" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH111">
+        <f>HB111/HC111-1</f>
+        <v/>
+      </c>
+      <c r="HI111">
+        <f>HD111/HC111-1</f>
+        <v/>
+      </c>
+      <c r="HK111" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL111" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN111" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO111" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ111">
+        <f>HK111/HL111-1</f>
+        <v/>
+      </c>
+      <c r="HR111">
+        <f>HM111/HL111-1</f>
+        <v/>
+      </c>
+      <c r="HT111" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU111" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HW111" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX111" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HZ111">
+        <f>HT111/HU111-1</f>
+        <v/>
+      </c>
+      <c r="IA111">
+        <f>HV111/HU111-1</f>
+        <v/>
+      </c>
+      <c r="IC111" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID111" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF111" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG111" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II111">
+        <f>IC111/ID111-1</f>
+        <v/>
+      </c>
+      <c r="IJ111">
+        <f>IE111/ID111-1</f>
+        <v/>
+      </c>
+      <c r="IL111" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM111" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO111" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP111" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR111">
+        <f>IL111/IM111-1</f>
+        <v/>
+      </c>
+      <c r="IS111">
+        <f>IN111/IM111-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS111"/>
+  <dimension ref="A1:IS112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -66437,6 +66437,689 @@
         <v/>
       </c>
     </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>19 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I112">
+        <f>C112/D112-1</f>
+        <v/>
+      </c>
+      <c r="J112">
+        <f>E112/D112-1</f>
+        <v/>
+      </c>
+      <c r="L112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R112">
+        <f>L112/M112-1</f>
+        <v/>
+      </c>
+      <c r="S112">
+        <f>N112/M112-1</f>
+        <v/>
+      </c>
+      <c r="U112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA112">
+        <f>U112/V112-1</f>
+        <v/>
+      </c>
+      <c r="AB112">
+        <f>W112/V112-1</f>
+        <v/>
+      </c>
+      <c r="AD112" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE112" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ112">
+        <f>AD112/AE112-1</f>
+        <v/>
+      </c>
+      <c r="AK112">
+        <f>AF112/AE112-1</f>
+        <v/>
+      </c>
+      <c r="AM112" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN112" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS112">
+        <f>AM112/AN112-1</f>
+        <v/>
+      </c>
+      <c r="AT112">
+        <f>AO112/AN112-1</f>
+        <v/>
+      </c>
+      <c r="AV112" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW112" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB112">
+        <f>AV112/AW112-1</f>
+        <v/>
+      </c>
+      <c r="BC112">
+        <f>AX112/AW112-1</f>
+        <v/>
+      </c>
+      <c r="BE112" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF112" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH112" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI112" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK112">
+        <f>BE112/BF112-1</f>
+        <v/>
+      </c>
+      <c r="BL112">
+        <f>BG112/BF112-1</f>
+        <v/>
+      </c>
+      <c r="BN112" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO112" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ112" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR112" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT112">
+        <f>BN112/BO112-1</f>
+        <v/>
+      </c>
+      <c r="BU112">
+        <f>BP112/BO112-1</f>
+        <v/>
+      </c>
+      <c r="BW112" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX112" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ112" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA112" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC112">
+        <f>BW112/BX112-1</f>
+        <v/>
+      </c>
+      <c r="CD112">
+        <f>BY112/BX112-1</f>
+        <v/>
+      </c>
+      <c r="CF112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI112" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ112" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL112">
+        <f>CF112/CG112-1</f>
+        <v/>
+      </c>
+      <c r="CM112">
+        <f>CH112/CG112-1</f>
+        <v/>
+      </c>
+      <c r="CO112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR112" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS112" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU112">
+        <f>CO112/CP112-1</f>
+        <v/>
+      </c>
+      <c r="CV112">
+        <f>CQ112/CP112-1</f>
+        <v/>
+      </c>
+      <c r="CX112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY112" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA112" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB112" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD112">
+        <f>CX112/CY112-1</f>
+        <v/>
+      </c>
+      <c r="DE112">
+        <f>CZ112/CY112-1</f>
+        <v/>
+      </c>
+      <c r="DG112" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH112" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ112" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK112" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM112">
+        <f>DG112/DH112-1</f>
+        <v/>
+      </c>
+      <c r="DN112">
+        <f>DI112/DH112-1</f>
+        <v/>
+      </c>
+      <c r="DP112" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ112" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS112" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT112" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV112">
+        <f>DP112/DQ112-1</f>
+        <v/>
+      </c>
+      <c r="DW112">
+        <f>DR112/DQ112-1</f>
+        <v/>
+      </c>
+      <c r="DY112" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ112" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB112" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC112" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE112">
+        <f>DY112/DZ112-1</f>
+        <v/>
+      </c>
+      <c r="EF112">
+        <f>EA112/DZ112-1</f>
+        <v/>
+      </c>
+      <c r="EH112" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI112" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK112" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL112" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN112">
+        <f>EH112/EI112-1</f>
+        <v/>
+      </c>
+      <c r="EO112">
+        <f>EJ112/EI112-1</f>
+        <v/>
+      </c>
+      <c r="EQ112" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER112" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ET112" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU112" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EW112">
+        <f>EQ112/ER112-1</f>
+        <v/>
+      </c>
+      <c r="EX112">
+        <f>ES112/ER112-1</f>
+        <v/>
+      </c>
+      <c r="EZ112" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA112" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC112" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD112" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF112">
+        <f>EZ112/FA112-1</f>
+        <v/>
+      </c>
+      <c r="FG112">
+        <f>FB112/FA112-1</f>
+        <v/>
+      </c>
+      <c r="FI112" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ112" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL112" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM112" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO112">
+        <f>FI112/FJ112-1</f>
+        <v/>
+      </c>
+      <c r="FP112">
+        <f>FK112/FJ112-1</f>
+        <v/>
+      </c>
+      <c r="FR112" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS112" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU112" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV112" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX112">
+        <f>FR112/FS112-1</f>
+        <v/>
+      </c>
+      <c r="FY112">
+        <f>FT112/FS112-1</f>
+        <v/>
+      </c>
+      <c r="GA112" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB112" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD112" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE112" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG112">
+        <f>GA112/GB112-1</f>
+        <v/>
+      </c>
+      <c r="GH112">
+        <f>GC112/GB112-1</f>
+        <v/>
+      </c>
+      <c r="GJ112" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK112" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM112" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN112" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP112">
+        <f>GJ112/GK112-1</f>
+        <v/>
+      </c>
+      <c r="GQ112">
+        <f>GL112/GK112-1</f>
+        <v/>
+      </c>
+      <c r="GS112" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT112" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV112" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW112" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY112">
+        <f>GS112/GT112-1</f>
+        <v/>
+      </c>
+      <c r="GZ112">
+        <f>GU112/GT112-1</f>
+        <v/>
+      </c>
+      <c r="HB112" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC112" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE112" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF112" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH112">
+        <f>HB112/HC112-1</f>
+        <v/>
+      </c>
+      <c r="HI112">
+        <f>HD112/HC112-1</f>
+        <v/>
+      </c>
+      <c r="HK112" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL112" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN112" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO112" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ112">
+        <f>HK112/HL112-1</f>
+        <v/>
+      </c>
+      <c r="HR112">
+        <f>HM112/HL112-1</f>
+        <v/>
+      </c>
+      <c r="HT112" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU112" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW112" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX112" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ112">
+        <f>HT112/HU112-1</f>
+        <v/>
+      </c>
+      <c r="IA112">
+        <f>HV112/HU112-1</f>
+        <v/>
+      </c>
+      <c r="IC112" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID112" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF112" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG112" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II112">
+        <f>IC112/ID112-1</f>
+        <v/>
+      </c>
+      <c r="IJ112">
+        <f>IE112/ID112-1</f>
+        <v/>
+      </c>
+      <c r="IL112" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM112" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO112" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP112" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR112">
+        <f>IL112/IM112-1</f>
+        <v/>
+      </c>
+      <c r="IS112">
+        <f>IN112/IM112-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS112"/>
+  <dimension ref="A1:IS113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -67120,6 +67120,687 @@
         <v/>
       </c>
     </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>19 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I113">
+        <f>C113/D113-1</f>
+        <v/>
+      </c>
+      <c r="J113">
+        <f>E113/D113-1</f>
+        <v/>
+      </c>
+      <c r="L113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R113">
+        <f>L113/M113-1</f>
+        <v/>
+      </c>
+      <c r="S113">
+        <f>N113/M113-1</f>
+        <v/>
+      </c>
+      <c r="U113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA113">
+        <f>U113/V113-1</f>
+        <v/>
+      </c>
+      <c r="AB113">
+        <f>W113/V113-1</f>
+        <v/>
+      </c>
+      <c r="AD113" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE113" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ113">
+        <f>AD113/AE113-1</f>
+        <v/>
+      </c>
+      <c r="AK113">
+        <f>AF113/AE113-1</f>
+        <v/>
+      </c>
+      <c r="AM113" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN113" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS113">
+        <f>AM113/AN113-1</f>
+        <v/>
+      </c>
+      <c r="AT113">
+        <f>AO113/AN113-1</f>
+        <v/>
+      </c>
+      <c r="AV113" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW113" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB113">
+        <f>AV113/AW113-1</f>
+        <v/>
+      </c>
+      <c r="BC113">
+        <f>AX113/AW113-1</f>
+        <v/>
+      </c>
+      <c r="BE113" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF113" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH113" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI113" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK113">
+        <f>BE113/BF113-1</f>
+        <v/>
+      </c>
+      <c r="BL113">
+        <f>BG113/BF113-1</f>
+        <v/>
+      </c>
+      <c r="BN113" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO113" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ113" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR113" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT113">
+        <f>BN113/BO113-1</f>
+        <v/>
+      </c>
+      <c r="BU113">
+        <f>BP113/BO113-1</f>
+        <v/>
+      </c>
+      <c r="BW113" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX113" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ113" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA113" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC113">
+        <f>BW113/BX113-1</f>
+        <v/>
+      </c>
+      <c r="CD113">
+        <f>BY113/BX113-1</f>
+        <v/>
+      </c>
+      <c r="CF113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI113" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ113" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL113">
+        <f>CF113/CG113-1</f>
+        <v/>
+      </c>
+      <c r="CM113">
+        <f>CH113/CG113-1</f>
+        <v/>
+      </c>
+      <c r="CO113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR113" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS113" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU113">
+        <f>CO113/CP113-1</f>
+        <v/>
+      </c>
+      <c r="CV113">
+        <f>CQ113/CP113-1</f>
+        <v/>
+      </c>
+      <c r="CX113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY113" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA113" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB113" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD113">
+        <f>CX113/CY113-1</f>
+        <v/>
+      </c>
+      <c r="DE113">
+        <f>CZ113/CY113-1</f>
+        <v/>
+      </c>
+      <c r="DG113" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH113" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ113" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK113" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM113">
+        <f>DG113/DH113-1</f>
+        <v/>
+      </c>
+      <c r="DN113">
+        <f>DI113/DH113-1</f>
+        <v/>
+      </c>
+      <c r="DP113" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ113" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS113" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT113" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV113">
+        <f>DP113/DQ113-1</f>
+        <v/>
+      </c>
+      <c r="DW113">
+        <f>DR113/DQ113-1</f>
+        <v/>
+      </c>
+      <c r="DY113" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ113" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB113" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC113" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE113">
+        <f>DY113/DZ113-1</f>
+        <v/>
+      </c>
+      <c r="EF113">
+        <f>EA113/DZ113-1</f>
+        <v/>
+      </c>
+      <c r="EH113" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI113" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK113" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL113" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN113">
+        <f>EH113/EI113-1</f>
+        <v/>
+      </c>
+      <c r="EO113">
+        <f>EJ113/EI113-1</f>
+        <v/>
+      </c>
+      <c r="EQ113" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER113" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET113" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU113" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW113">
+        <f>EQ113/ER113-1</f>
+        <v/>
+      </c>
+      <c r="EX113">
+        <f>ES113/ER113-1</f>
+        <v/>
+      </c>
+      <c r="EZ113" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA113" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC113" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD113" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF113">
+        <f>EZ113/FA113-1</f>
+        <v/>
+      </c>
+      <c r="FG113">
+        <f>FB113/FA113-1</f>
+        <v/>
+      </c>
+      <c r="FI113" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ113" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL113" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM113" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO113">
+        <f>FI113/FJ113-1</f>
+        <v/>
+      </c>
+      <c r="FP113">
+        <f>FK113/FJ113-1</f>
+        <v/>
+      </c>
+      <c r="FR113" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS113" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU113" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV113" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX113">
+        <f>FR113/FS113-1</f>
+        <v/>
+      </c>
+      <c r="FY113">
+        <f>FT113/FS113-1</f>
+        <v/>
+      </c>
+      <c r="GA113" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB113" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD113" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE113" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG113">
+        <f>GA113/GB113-1</f>
+        <v/>
+      </c>
+      <c r="GH113">
+        <f>GC113/GB113-1</f>
+        <v/>
+      </c>
+      <c r="GJ113" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK113" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM113" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN113" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP113">
+        <f>GJ113/GK113-1</f>
+        <v/>
+      </c>
+      <c r="GQ113">
+        <f>GL113/GK113-1</f>
+        <v/>
+      </c>
+      <c r="GS113" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT113" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV113" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW113" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY113">
+        <f>GS113/GT113-1</f>
+        <v/>
+      </c>
+      <c r="GZ113">
+        <f>GU113/GT113-1</f>
+        <v/>
+      </c>
+      <c r="HB113" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC113" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE113" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF113" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH113">
+        <f>HB113/HC113-1</f>
+        <v/>
+      </c>
+      <c r="HI113">
+        <f>HD113/HC113-1</f>
+        <v/>
+      </c>
+      <c r="HK113" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL113" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN113" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO113" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ113">
+        <f>HK113/HL113-1</f>
+        <v/>
+      </c>
+      <c r="HR113">
+        <f>HM113/HL113-1</f>
+        <v/>
+      </c>
+      <c r="HT113" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU113" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW113" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX113" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ113">
+        <f>HT113/HU113-1</f>
+        <v/>
+      </c>
+      <c r="IA113">
+        <f>HV113/HU113-1</f>
+        <v/>
+      </c>
+      <c r="IC113" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID113" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF113" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG113" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II113">
+        <f>IC113/ID113-1</f>
+        <v/>
+      </c>
+      <c r="IJ113">
+        <f>IE113/ID113-1</f>
+        <v/>
+      </c>
+      <c r="IL113" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM113" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO113" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP113" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR113">
+        <f>IL113/IM113-1</f>
+        <v/>
+      </c>
+      <c r="IS113">
+        <f>IN113/IM113-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS113"/>
+  <dimension ref="A1:IS114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -67801,6 +67801,689 @@
         <v/>
       </c>
     </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>19 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I114">
+        <f>C114/D114-1</f>
+        <v/>
+      </c>
+      <c r="J114">
+        <f>E114/D114-1</f>
+        <v/>
+      </c>
+      <c r="L114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R114">
+        <f>L114/M114-1</f>
+        <v/>
+      </c>
+      <c r="S114">
+        <f>N114/M114-1</f>
+        <v/>
+      </c>
+      <c r="U114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA114">
+        <f>U114/V114-1</f>
+        <v/>
+      </c>
+      <c r="AB114">
+        <f>W114/V114-1</f>
+        <v/>
+      </c>
+      <c r="AD114" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE114" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ114">
+        <f>AD114/AE114-1</f>
+        <v/>
+      </c>
+      <c r="AK114">
+        <f>AF114/AE114-1</f>
+        <v/>
+      </c>
+      <c r="AM114" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN114" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AS114">
+        <f>AM114/AN114-1</f>
+        <v/>
+      </c>
+      <c r="AT114">
+        <f>AO114/AN114-1</f>
+        <v/>
+      </c>
+      <c r="AV114" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW114" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB114">
+        <f>AV114/AW114-1</f>
+        <v/>
+      </c>
+      <c r="BC114">
+        <f>AX114/AW114-1</f>
+        <v/>
+      </c>
+      <c r="BE114" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF114" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH114" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI114" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK114">
+        <f>BE114/BF114-1</f>
+        <v/>
+      </c>
+      <c r="BL114">
+        <f>BG114/BF114-1</f>
+        <v/>
+      </c>
+      <c r="BN114" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO114" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ114" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR114" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT114">
+        <f>BN114/BO114-1</f>
+        <v/>
+      </c>
+      <c r="BU114">
+        <f>BP114/BO114-1</f>
+        <v/>
+      </c>
+      <c r="BW114" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX114" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ114" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA114" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC114">
+        <f>BW114/BX114-1</f>
+        <v/>
+      </c>
+      <c r="CD114">
+        <f>BY114/BX114-1</f>
+        <v/>
+      </c>
+      <c r="CF114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI114" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ114" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL114">
+        <f>CF114/CG114-1</f>
+        <v/>
+      </c>
+      <c r="CM114">
+        <f>CH114/CG114-1</f>
+        <v/>
+      </c>
+      <c r="CO114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR114" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS114" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU114">
+        <f>CO114/CP114-1</f>
+        <v/>
+      </c>
+      <c r="CV114">
+        <f>CQ114/CP114-1</f>
+        <v/>
+      </c>
+      <c r="CX114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY114" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA114" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB114" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD114">
+        <f>CX114/CY114-1</f>
+        <v/>
+      </c>
+      <c r="DE114">
+        <f>CZ114/CY114-1</f>
+        <v/>
+      </c>
+      <c r="DG114" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH114" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ114" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK114" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM114">
+        <f>DG114/DH114-1</f>
+        <v/>
+      </c>
+      <c r="DN114">
+        <f>DI114/DH114-1</f>
+        <v/>
+      </c>
+      <c r="DP114" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ114" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS114" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT114" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV114">
+        <f>DP114/DQ114-1</f>
+        <v/>
+      </c>
+      <c r="DW114">
+        <f>DR114/DQ114-1</f>
+        <v/>
+      </c>
+      <c r="DY114" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ114" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB114" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC114" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE114">
+        <f>DY114/DZ114-1</f>
+        <v/>
+      </c>
+      <c r="EF114">
+        <f>EA114/DZ114-1</f>
+        <v/>
+      </c>
+      <c r="EH114" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI114" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK114" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL114" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN114">
+        <f>EH114/EI114-1</f>
+        <v/>
+      </c>
+      <c r="EO114">
+        <f>EJ114/EI114-1</f>
+        <v/>
+      </c>
+      <c r="EQ114" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER114" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET114" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU114" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW114">
+        <f>EQ114/ER114-1</f>
+        <v/>
+      </c>
+      <c r="EX114">
+        <f>ES114/ER114-1</f>
+        <v/>
+      </c>
+      <c r="EZ114" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA114" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC114" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD114" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF114">
+        <f>EZ114/FA114-1</f>
+        <v/>
+      </c>
+      <c r="FG114">
+        <f>FB114/FA114-1</f>
+        <v/>
+      </c>
+      <c r="FI114" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ114" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL114" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM114" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO114">
+        <f>FI114/FJ114-1</f>
+        <v/>
+      </c>
+      <c r="FP114">
+        <f>FK114/FJ114-1</f>
+        <v/>
+      </c>
+      <c r="FR114" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS114" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU114" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV114" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX114">
+        <f>FR114/FS114-1</f>
+        <v/>
+      </c>
+      <c r="FY114">
+        <f>FT114/FS114-1</f>
+        <v/>
+      </c>
+      <c r="GA114" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB114" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD114" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE114" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG114">
+        <f>GA114/GB114-1</f>
+        <v/>
+      </c>
+      <c r="GH114">
+        <f>GC114/GB114-1</f>
+        <v/>
+      </c>
+      <c r="GJ114" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK114" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM114" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN114" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP114">
+        <f>GJ114/GK114-1</f>
+        <v/>
+      </c>
+      <c r="GQ114">
+        <f>GL114/GK114-1</f>
+        <v/>
+      </c>
+      <c r="GS114" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT114" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV114" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW114" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY114">
+        <f>GS114/GT114-1</f>
+        <v/>
+      </c>
+      <c r="GZ114">
+        <f>GU114/GT114-1</f>
+        <v/>
+      </c>
+      <c r="HB114" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC114" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE114" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF114" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH114">
+        <f>HB114/HC114-1</f>
+        <v/>
+      </c>
+      <c r="HI114">
+        <f>HD114/HC114-1</f>
+        <v/>
+      </c>
+      <c r="HK114" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL114" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN114" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO114" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ114">
+        <f>HK114/HL114-1</f>
+        <v/>
+      </c>
+      <c r="HR114">
+        <f>HM114/HL114-1</f>
+        <v/>
+      </c>
+      <c r="HT114" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU114" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW114" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX114" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ114">
+        <f>HT114/HU114-1</f>
+        <v/>
+      </c>
+      <c r="IA114">
+        <f>HV114/HU114-1</f>
+        <v/>
+      </c>
+      <c r="IC114" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID114" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF114" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG114" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II114">
+        <f>IC114/ID114-1</f>
+        <v/>
+      </c>
+      <c r="IJ114">
+        <f>IE114/ID114-1</f>
+        <v/>
+      </c>
+      <c r="IL114" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM114" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO114" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP114" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR114">
+        <f>IL114/IM114-1</f>
+        <v/>
+      </c>
+      <c r="IS114">
+        <f>IN114/IM114-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS114"/>
+  <dimension ref="A1:IS115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -68484,6 +68484,691 @@
         <v/>
       </c>
     </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>20 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I115">
+        <f>C115/D115-1</f>
+        <v/>
+      </c>
+      <c r="J115">
+        <f>E115/D115-1</f>
+        <v/>
+      </c>
+      <c r="L115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R115">
+        <f>L115/M115-1</f>
+        <v/>
+      </c>
+      <c r="S115">
+        <f>N115/M115-1</f>
+        <v/>
+      </c>
+      <c r="U115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA115">
+        <f>U115/V115-1</f>
+        <v/>
+      </c>
+      <c r="AB115">
+        <f>W115/V115-1</f>
+        <v/>
+      </c>
+      <c r="AD115" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE115" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ115">
+        <f>AD115/AE115-1</f>
+        <v/>
+      </c>
+      <c r="AK115">
+        <f>AF115/AE115-1</f>
+        <v/>
+      </c>
+      <c r="AM115" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AS115">
+        <f>AM115/AN115-1</f>
+        <v/>
+      </c>
+      <c r="AT115">
+        <f>AO115/AN115-1</f>
+        <v/>
+      </c>
+      <c r="AV115" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW115" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB115">
+        <f>AV115/AW115-1</f>
+        <v/>
+      </c>
+      <c r="BC115">
+        <f>AX115/AW115-1</f>
+        <v/>
+      </c>
+      <c r="BE115" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF115" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH115" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI115" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK115">
+        <f>BE115/BF115-1</f>
+        <v/>
+      </c>
+      <c r="BL115">
+        <f>BG115/BF115-1</f>
+        <v/>
+      </c>
+      <c r="BN115" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO115" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ115" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR115" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT115">
+        <f>BN115/BO115-1</f>
+        <v/>
+      </c>
+      <c r="BU115">
+        <f>BP115/BO115-1</f>
+        <v/>
+      </c>
+      <c r="BW115" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX115" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ115" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA115" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC115">
+        <f>BW115/BX115-1</f>
+        <v/>
+      </c>
+      <c r="CD115">
+        <f>BY115/BX115-1</f>
+        <v/>
+      </c>
+      <c r="CF115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI115" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ115" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL115">
+        <f>CF115/CG115-1</f>
+        <v/>
+      </c>
+      <c r="CM115">
+        <f>CH115/CG115-1</f>
+        <v/>
+      </c>
+      <c r="CO115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR115" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS115" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU115">
+        <f>CO115/CP115-1</f>
+        <v/>
+      </c>
+      <c r="CV115">
+        <f>CQ115/CP115-1</f>
+        <v/>
+      </c>
+      <c r="CX115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY115" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA115" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB115" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD115">
+        <f>CX115/CY115-1</f>
+        <v/>
+      </c>
+      <c r="DE115">
+        <f>CZ115/CY115-1</f>
+        <v/>
+      </c>
+      <c r="DG115" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH115" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ115" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK115" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM115">
+        <f>DG115/DH115-1</f>
+        <v/>
+      </c>
+      <c r="DN115">
+        <f>DI115/DH115-1</f>
+        <v/>
+      </c>
+      <c r="DP115" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ115" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS115" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT115" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV115">
+        <f>DP115/DQ115-1</f>
+        <v/>
+      </c>
+      <c r="DW115">
+        <f>DR115/DQ115-1</f>
+        <v/>
+      </c>
+      <c r="DY115" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ115" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB115" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC115" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE115">
+        <f>DY115/DZ115-1</f>
+        <v/>
+      </c>
+      <c r="EF115">
+        <f>EA115/DZ115-1</f>
+        <v/>
+      </c>
+      <c r="EH115" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI115" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN115">
+        <f>EH115/EI115-1</f>
+        <v/>
+      </c>
+      <c r="EO115">
+        <f>EJ115/EI115-1</f>
+        <v/>
+      </c>
+      <c r="EQ115" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER115" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ET115" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU115" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EW115">
+        <f>EQ115/ER115-1</f>
+        <v/>
+      </c>
+      <c r="EX115">
+        <f>ES115/ER115-1</f>
+        <v/>
+      </c>
+      <c r="EZ115" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA115" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC115" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD115" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF115">
+        <f>EZ115/FA115-1</f>
+        <v/>
+      </c>
+      <c r="FG115">
+        <f>FB115/FA115-1</f>
+        <v/>
+      </c>
+      <c r="FI115" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ115" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL115" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM115" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO115">
+        <f>FI115/FJ115-1</f>
+        <v/>
+      </c>
+      <c r="FP115">
+        <f>FK115/FJ115-1</f>
+        <v/>
+      </c>
+      <c r="FR115" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS115" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU115" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV115" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX115">
+        <f>FR115/FS115-1</f>
+        <v/>
+      </c>
+      <c r="FY115">
+        <f>FT115/FS115-1</f>
+        <v/>
+      </c>
+      <c r="GA115" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB115" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD115" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE115" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG115">
+        <f>GA115/GB115-1</f>
+        <v/>
+      </c>
+      <c r="GH115">
+        <f>GC115/GB115-1</f>
+        <v/>
+      </c>
+      <c r="GJ115" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK115" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM115" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN115" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP115">
+        <f>GJ115/GK115-1</f>
+        <v/>
+      </c>
+      <c r="GQ115">
+        <f>GL115/GK115-1</f>
+        <v/>
+      </c>
+      <c r="GS115" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT115" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV115" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW115" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY115">
+        <f>GS115/GT115-1</f>
+        <v/>
+      </c>
+      <c r="GZ115">
+        <f>GU115/GT115-1</f>
+        <v/>
+      </c>
+      <c r="HB115" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC115" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE115" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF115" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH115">
+        <f>HB115/HC115-1</f>
+        <v/>
+      </c>
+      <c r="HI115">
+        <f>HD115/HC115-1</f>
+        <v/>
+      </c>
+      <c r="HK115" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL115" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN115" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO115" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ115">
+        <f>HK115/HL115-1</f>
+        <v/>
+      </c>
+      <c r="HR115">
+        <f>HM115/HL115-1</f>
+        <v/>
+      </c>
+      <c r="HT115" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU115" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW115" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX115" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ115">
+        <f>HT115/HU115-1</f>
+        <v/>
+      </c>
+      <c r="IA115">
+        <f>HV115/HU115-1</f>
+        <v/>
+      </c>
+      <c r="IC115" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID115" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF115" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG115" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II115">
+        <f>IC115/ID115-1</f>
+        <v/>
+      </c>
+      <c r="IJ115">
+        <f>IE115/ID115-1</f>
+        <v/>
+      </c>
+      <c r="IL115" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM115" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO115" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP115" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR115">
+        <f>IL115/IM115-1</f>
+        <v/>
+      </c>
+      <c r="IS115">
+        <f>IN115/IM115-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS115"/>
+  <dimension ref="A1:IS116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -69169,6 +69169,693 @@
         <v/>
       </c>
     </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>20 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D116" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I116">
+        <f>C116/D116-1</f>
+        <v/>
+      </c>
+      <c r="J116">
+        <f>E116/D116-1</f>
+        <v/>
+      </c>
+      <c r="L116" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M116" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R116">
+        <f>L116/M116-1</f>
+        <v/>
+      </c>
+      <c r="S116">
+        <f>N116/M116-1</f>
+        <v/>
+      </c>
+      <c r="U116" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V116" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA116">
+        <f>U116/V116-1</f>
+        <v/>
+      </c>
+      <c r="AB116">
+        <f>W116/V116-1</f>
+        <v/>
+      </c>
+      <c r="AD116" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AJ116">
+        <f>AD116/AE116-1</f>
+        <v/>
+      </c>
+      <c r="AK116">
+        <f>AF116/AE116-1</f>
+        <v/>
+      </c>
+      <c r="AM116" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN116" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS116">
+        <f>AM116/AN116-1</f>
+        <v/>
+      </c>
+      <c r="AT116">
+        <f>AO116/AN116-1</f>
+        <v/>
+      </c>
+      <c r="AV116" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW116" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB116">
+        <f>AV116/AW116-1</f>
+        <v/>
+      </c>
+      <c r="BC116">
+        <f>AX116/AW116-1</f>
+        <v/>
+      </c>
+      <c r="BE116" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF116" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH116" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI116" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK116">
+        <f>BE116/BF116-1</f>
+        <v/>
+      </c>
+      <c r="BL116">
+        <f>BG116/BF116-1</f>
+        <v/>
+      </c>
+      <c r="BN116" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO116" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ116" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR116" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT116">
+        <f>BN116/BO116-1</f>
+        <v/>
+      </c>
+      <c r="BU116">
+        <f>BP116/BO116-1</f>
+        <v/>
+      </c>
+      <c r="BW116" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX116" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ116" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA116" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC116">
+        <f>BW116/BX116-1</f>
+        <v/>
+      </c>
+      <c r="CD116">
+        <f>BY116/BX116-1</f>
+        <v/>
+      </c>
+      <c r="CF116" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG116" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI116" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ116" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL116">
+        <f>CF116/CG116-1</f>
+        <v/>
+      </c>
+      <c r="CM116">
+        <f>CH116/CG116-1</f>
+        <v/>
+      </c>
+      <c r="CO116" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP116" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR116" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS116" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU116">
+        <f>CO116/CP116-1</f>
+        <v/>
+      </c>
+      <c r="CV116">
+        <f>CQ116/CP116-1</f>
+        <v/>
+      </c>
+      <c r="CX116" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY116" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DA116" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB116" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DD116">
+        <f>CX116/CY116-1</f>
+        <v/>
+      </c>
+      <c r="DE116">
+        <f>CZ116/CY116-1</f>
+        <v/>
+      </c>
+      <c r="DG116" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH116" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ116" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK116" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM116">
+        <f>DG116/DH116-1</f>
+        <v/>
+      </c>
+      <c r="DN116">
+        <f>DI116/DH116-1</f>
+        <v/>
+      </c>
+      <c r="DP116" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ116" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS116" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT116" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV116">
+        <f>DP116/DQ116-1</f>
+        <v/>
+      </c>
+      <c r="DW116">
+        <f>DR116/DQ116-1</f>
+        <v/>
+      </c>
+      <c r="DY116" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ116" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB116" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC116" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE116">
+        <f>DY116/DZ116-1</f>
+        <v/>
+      </c>
+      <c r="EF116">
+        <f>EA116/DZ116-1</f>
+        <v/>
+      </c>
+      <c r="EH116" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI116" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK116" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL116" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN116">
+        <f>EH116/EI116-1</f>
+        <v/>
+      </c>
+      <c r="EO116">
+        <f>EJ116/EI116-1</f>
+        <v/>
+      </c>
+      <c r="EQ116" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER116" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET116" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU116" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW116">
+        <f>EQ116/ER116-1</f>
+        <v/>
+      </c>
+      <c r="EX116">
+        <f>ES116/ER116-1</f>
+        <v/>
+      </c>
+      <c r="EZ116" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA116" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC116" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD116" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF116">
+        <f>EZ116/FA116-1</f>
+        <v/>
+      </c>
+      <c r="FG116">
+        <f>FB116/FA116-1</f>
+        <v/>
+      </c>
+      <c r="FI116" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ116" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL116" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM116" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO116">
+        <f>FI116/FJ116-1</f>
+        <v/>
+      </c>
+      <c r="FP116">
+        <f>FK116/FJ116-1</f>
+        <v/>
+      </c>
+      <c r="FR116" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS116" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU116" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV116" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX116">
+        <f>FR116/FS116-1</f>
+        <v/>
+      </c>
+      <c r="FY116">
+        <f>FT116/FS116-1</f>
+        <v/>
+      </c>
+      <c r="GA116" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB116" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD116" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE116" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG116">
+        <f>GA116/GB116-1</f>
+        <v/>
+      </c>
+      <c r="GH116">
+        <f>GC116/GB116-1</f>
+        <v/>
+      </c>
+      <c r="GJ116" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK116" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GM116" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN116" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GP116">
+        <f>GJ116/GK116-1</f>
+        <v/>
+      </c>
+      <c r="GQ116">
+        <f>GL116/GK116-1</f>
+        <v/>
+      </c>
+      <c r="GS116" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT116" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV116" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW116" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY116">
+        <f>GS116/GT116-1</f>
+        <v/>
+      </c>
+      <c r="GZ116">
+        <f>GU116/GT116-1</f>
+        <v/>
+      </c>
+      <c r="HB116" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC116" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE116" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF116" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH116">
+        <f>HB116/HC116-1</f>
+        <v/>
+      </c>
+      <c r="HI116">
+        <f>HD116/HC116-1</f>
+        <v/>
+      </c>
+      <c r="HK116" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL116" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN116" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO116" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ116">
+        <f>HK116/HL116-1</f>
+        <v/>
+      </c>
+      <c r="HR116">
+        <f>HM116/HL116-1</f>
+        <v/>
+      </c>
+      <c r="HT116" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU116" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW116" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX116" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ116">
+        <f>HT116/HU116-1</f>
+        <v/>
+      </c>
+      <c r="IA116">
+        <f>HV116/HU116-1</f>
+        <v/>
+      </c>
+      <c r="IC116" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID116" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF116" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG116" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II116">
+        <f>IC116/ID116-1</f>
+        <v/>
+      </c>
+      <c r="IJ116">
+        <f>IE116/ID116-1</f>
+        <v/>
+      </c>
+      <c r="IL116" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM116" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO116" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP116" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR116">
+        <f>IL116/IM116-1</f>
+        <v/>
+      </c>
+      <c r="IS116">
+        <f>IN116/IM116-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS116"/>
+  <dimension ref="A1:IS117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -69856,6 +69856,721 @@
         <v/>
       </c>
     </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>20 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D117" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I117">
+        <f>C117/D117-1</f>
+        <v/>
+      </c>
+      <c r="J117">
+        <f>E117/D117-1</f>
+        <v/>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R117">
+        <f>L117/M117-1</f>
+        <v/>
+      </c>
+      <c r="S117">
+        <f>N117/M117-1</f>
+        <v/>
+      </c>
+      <c r="U117" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V117" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA117">
+        <f>U117/V117-1</f>
+        <v/>
+      </c>
+      <c r="AB117">
+        <f>W117/V117-1</f>
+        <v/>
+      </c>
+      <c r="AD117" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AJ117">
+        <f>AD117/AE117-1</f>
+        <v/>
+      </c>
+      <c r="AK117">
+        <f>AF117/AE117-1</f>
+        <v/>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN117" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS117">
+        <f>AM117/AN117-1</f>
+        <v/>
+      </c>
+      <c r="AT117">
+        <f>AO117/AN117-1</f>
+        <v/>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW117" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB117">
+        <f>AV117/AW117-1</f>
+        <v/>
+      </c>
+      <c r="BC117">
+        <f>AX117/AW117-1</f>
+        <v/>
+      </c>
+      <c r="BE117" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF117" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH117" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI117" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK117">
+        <f>BE117/BF117-1</f>
+        <v/>
+      </c>
+      <c r="BL117">
+        <f>BG117/BF117-1</f>
+        <v/>
+      </c>
+      <c r="BN117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO117" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR117" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT117">
+        <f>BN117/BO117-1</f>
+        <v/>
+      </c>
+      <c r="BU117">
+        <f>BP117/BO117-1</f>
+        <v/>
+      </c>
+      <c r="BW117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX117" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA117" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC117">
+        <f>BW117/BX117-1</f>
+        <v/>
+      </c>
+      <c r="CD117">
+        <f>BY117/BX117-1</f>
+        <v/>
+      </c>
+      <c r="CF117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG117" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ117" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL117">
+        <f>CF117/CG117-1</f>
+        <v/>
+      </c>
+      <c r="CM117">
+        <f>CH117/CG117-1</f>
+        <v/>
+      </c>
+      <c r="CO117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CP117" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CS117" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU117">
+        <f>CO117/CP117-1</f>
+        <v/>
+      </c>
+      <c r="CV117">
+        <f>CQ117/CP117-1</f>
+        <v/>
+      </c>
+      <c r="CX117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY117" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB117" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD117">
+        <f>CX117/CY117-1</f>
+        <v/>
+      </c>
+      <c r="DE117">
+        <f>CZ117/CY117-1</f>
+        <v/>
+      </c>
+      <c r="DG117" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH117" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ117" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK117" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM117">
+        <f>DG117/DH117-1</f>
+        <v/>
+      </c>
+      <c r="DN117">
+        <f>DI117/DH117-1</f>
+        <v/>
+      </c>
+      <c r="DP117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ117" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT117" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV117">
+        <f>DP117/DQ117-1</f>
+        <v/>
+      </c>
+      <c r="DW117">
+        <f>DR117/DQ117-1</f>
+        <v/>
+      </c>
+      <c r="DY117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ117" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC117" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE117">
+        <f>DY117/DZ117-1</f>
+        <v/>
+      </c>
+      <c r="EF117">
+        <f>EA117/DZ117-1</f>
+        <v/>
+      </c>
+      <c r="EH117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI117" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL117" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN117">
+        <f>EH117/EI117-1</f>
+        <v/>
+      </c>
+      <c r="EO117">
+        <f>EJ117/EI117-1</f>
+        <v/>
+      </c>
+      <c r="EQ117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER117" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU117" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW117">
+        <f>EQ117/ER117-1</f>
+        <v/>
+      </c>
+      <c r="EX117">
+        <f>ES117/ER117-1</f>
+        <v/>
+      </c>
+      <c r="EZ117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA117" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD117" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF117">
+        <f>EZ117/FA117-1</f>
+        <v/>
+      </c>
+      <c r="FG117">
+        <f>FB117/FA117-1</f>
+        <v/>
+      </c>
+      <c r="FI117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FJ117" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FM117" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO117">
+        <f>FI117/FJ117-1</f>
+        <v/>
+      </c>
+      <c r="FP117">
+        <f>FK117/FJ117-1</f>
+        <v/>
+      </c>
+      <c r="FR117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FS117" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FV117" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX117">
+        <f>FR117/FS117-1</f>
+        <v/>
+      </c>
+      <c r="FY117">
+        <f>FT117/FS117-1</f>
+        <v/>
+      </c>
+      <c r="GA117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GB117" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GE117" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG117">
+        <f>GA117/GB117-1</f>
+        <v/>
+      </c>
+      <c r="GH117">
+        <f>GC117/GB117-1</f>
+        <v/>
+      </c>
+      <c r="GJ117" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK117" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM117" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN117" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP117">
+        <f>GJ117/GK117-1</f>
+        <v/>
+      </c>
+      <c r="GQ117">
+        <f>GL117/GK117-1</f>
+        <v/>
+      </c>
+      <c r="GS117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GT117" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV117" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GW117" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY117">
+        <f>GS117/GT117-1</f>
+        <v/>
+      </c>
+      <c r="GZ117">
+        <f>GU117/GT117-1</f>
+        <v/>
+      </c>
+      <c r="HB117" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC117" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE117" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF117" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH117">
+        <f>HB117/HC117-1</f>
+        <v/>
+      </c>
+      <c r="HI117">
+        <f>HD117/HC117-1</f>
+        <v/>
+      </c>
+      <c r="HK117" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL117" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN117" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO117" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ117">
+        <f>HK117/HL117-1</f>
+        <v/>
+      </c>
+      <c r="HR117">
+        <f>HM117/HL117-1</f>
+        <v/>
+      </c>
+      <c r="HT117" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU117" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW117" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX117" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ117">
+        <f>HT117/HU117-1</f>
+        <v/>
+      </c>
+      <c r="IA117">
+        <f>HV117/HU117-1</f>
+        <v/>
+      </c>
+      <c r="IC117" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID117" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF117" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG117" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II117">
+        <f>IC117/ID117-1</f>
+        <v/>
+      </c>
+      <c r="IJ117">
+        <f>IE117/ID117-1</f>
+        <v/>
+      </c>
+      <c r="IL117" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM117" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO117" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP117" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR117">
+        <f>IL117/IM117-1</f>
+        <v/>
+      </c>
+      <c r="IS117">
+        <f>IN117/IM117-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS117"/>
+  <dimension ref="A1:IS118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -70571,6 +70571,703 @@
         <v/>
       </c>
     </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>20 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D118" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I118">
+        <f>C118/D118-1</f>
+        <v/>
+      </c>
+      <c r="J118">
+        <f>E118/D118-1</f>
+        <v/>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M118" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R118">
+        <f>L118/M118-1</f>
+        <v/>
+      </c>
+      <c r="S118">
+        <f>N118/M118-1</f>
+        <v/>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V118" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA118">
+        <f>U118/V118-1</f>
+        <v/>
+      </c>
+      <c r="AB118">
+        <f>W118/V118-1</f>
+        <v/>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE118" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ118">
+        <f>AD118/AE118-1</f>
+        <v/>
+      </c>
+      <c r="AK118">
+        <f>AF118/AE118-1</f>
+        <v/>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN118" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS118">
+        <f>AM118/AN118-1</f>
+        <v/>
+      </c>
+      <c r="AT118">
+        <f>AO118/AN118-1</f>
+        <v/>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW118" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB118">
+        <f>AV118/AW118-1</f>
+        <v/>
+      </c>
+      <c r="BC118">
+        <f>AX118/AW118-1</f>
+        <v/>
+      </c>
+      <c r="BE118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF118" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI118" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK118">
+        <f>BE118/BF118-1</f>
+        <v/>
+      </c>
+      <c r="BL118">
+        <f>BG118/BF118-1</f>
+        <v/>
+      </c>
+      <c r="BN118" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO118" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ118" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR118" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT118">
+        <f>BN118/BO118-1</f>
+        <v/>
+      </c>
+      <c r="BU118">
+        <f>BP118/BO118-1</f>
+        <v/>
+      </c>
+      <c r="BW118" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX118" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ118" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA118" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC118">
+        <f>BW118/BX118-1</f>
+        <v/>
+      </c>
+      <c r="CD118">
+        <f>BY118/BX118-1</f>
+        <v/>
+      </c>
+      <c r="CF118" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG118" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI118" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ118" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL118">
+        <f>CF118/CG118-1</f>
+        <v/>
+      </c>
+      <c r="CM118">
+        <f>CH118/CG118-1</f>
+        <v/>
+      </c>
+      <c r="CO118" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP118" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR118" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS118" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU118">
+        <f>CO118/CP118-1</f>
+        <v/>
+      </c>
+      <c r="CV118">
+        <f>CQ118/CP118-1</f>
+        <v/>
+      </c>
+      <c r="CX118" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY118" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA118" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB118" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD118">
+        <f>CX118/CY118-1</f>
+        <v/>
+      </c>
+      <c r="DE118">
+        <f>CZ118/CY118-1</f>
+        <v/>
+      </c>
+      <c r="DG118" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH118" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ118" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK118" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM118">
+        <f>DG118/DH118-1</f>
+        <v/>
+      </c>
+      <c r="DN118">
+        <f>DI118/DH118-1</f>
+        <v/>
+      </c>
+      <c r="DP118" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ118" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS118" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT118" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV118">
+        <f>DP118/DQ118-1</f>
+        <v/>
+      </c>
+      <c r="DW118">
+        <f>DR118/DQ118-1</f>
+        <v/>
+      </c>
+      <c r="DY118" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ118" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB118" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC118" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE118">
+        <f>DY118/DZ118-1</f>
+        <v/>
+      </c>
+      <c r="EF118">
+        <f>EA118/DZ118-1</f>
+        <v/>
+      </c>
+      <c r="EH118" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI118" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK118" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL118" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN118">
+        <f>EH118/EI118-1</f>
+        <v/>
+      </c>
+      <c r="EO118">
+        <f>EJ118/EI118-1</f>
+        <v/>
+      </c>
+      <c r="EQ118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER118" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU118" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW118">
+        <f>EQ118/ER118-1</f>
+        <v/>
+      </c>
+      <c r="EX118">
+        <f>ES118/ER118-1</f>
+        <v/>
+      </c>
+      <c r="EZ118" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA118" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC118" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD118" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF118">
+        <f>EZ118/FA118-1</f>
+        <v/>
+      </c>
+      <c r="FG118">
+        <f>FB118/FA118-1</f>
+        <v/>
+      </c>
+      <c r="FI118" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ118" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL118" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM118" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO118">
+        <f>FI118/FJ118-1</f>
+        <v/>
+      </c>
+      <c r="FP118">
+        <f>FK118/FJ118-1</f>
+        <v/>
+      </c>
+      <c r="FR118" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS118" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU118" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV118" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX118">
+        <f>FR118/FS118-1</f>
+        <v/>
+      </c>
+      <c r="FY118">
+        <f>FT118/FS118-1</f>
+        <v/>
+      </c>
+      <c r="GA118" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB118" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD118" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE118" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG118">
+        <f>GA118/GB118-1</f>
+        <v/>
+      </c>
+      <c r="GH118">
+        <f>GC118/GB118-1</f>
+        <v/>
+      </c>
+      <c r="GJ118" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GM118" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GP118">
+        <f>GJ118/GK118-1</f>
+        <v/>
+      </c>
+      <c r="GQ118">
+        <f>GL118/GK118-1</f>
+        <v/>
+      </c>
+      <c r="GS118" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT118" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV118" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW118" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY118">
+        <f>GS118/GT118-1</f>
+        <v/>
+      </c>
+      <c r="GZ118">
+        <f>GU118/GT118-1</f>
+        <v/>
+      </c>
+      <c r="HB118" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC118" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE118" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF118" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH118">
+        <f>HB118/HC118-1</f>
+        <v/>
+      </c>
+      <c r="HI118">
+        <f>HD118/HC118-1</f>
+        <v/>
+      </c>
+      <c r="HK118" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL118" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN118" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO118" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ118">
+        <f>HK118/HL118-1</f>
+        <v/>
+      </c>
+      <c r="HR118">
+        <f>HM118/HL118-1</f>
+        <v/>
+      </c>
+      <c r="HT118" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HW118" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX118" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HZ118">
+        <f>HT118/HU118-1</f>
+        <v/>
+      </c>
+      <c r="IA118">
+        <f>HV118/HU118-1</f>
+        <v/>
+      </c>
+      <c r="IC118" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID118" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF118" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG118" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II118">
+        <f>IC118/ID118-1</f>
+        <v/>
+      </c>
+      <c r="IJ118">
+        <f>IE118/ID118-1</f>
+        <v/>
+      </c>
+      <c r="IL118" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM118" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO118" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP118" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR118">
+        <f>IL118/IM118-1</f>
+        <v/>
+      </c>
+      <c r="IS118">
+        <f>IN118/IM118-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS118"/>
+  <dimension ref="A1:IS119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -71268,6 +71268,691 @@
         <v/>
       </c>
     </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>21 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I119">
+        <f>C119/D119-1</f>
+        <v/>
+      </c>
+      <c r="J119">
+        <f>E119/D119-1</f>
+        <v/>
+      </c>
+      <c r="L119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R119">
+        <f>L119/M119-1</f>
+        <v/>
+      </c>
+      <c r="S119">
+        <f>N119/M119-1</f>
+        <v/>
+      </c>
+      <c r="U119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA119">
+        <f>U119/V119-1</f>
+        <v/>
+      </c>
+      <c r="AB119">
+        <f>W119/V119-1</f>
+        <v/>
+      </c>
+      <c r="AD119" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE119" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ119">
+        <f>AD119/AE119-1</f>
+        <v/>
+      </c>
+      <c r="AK119">
+        <f>AF119/AE119-1</f>
+        <v/>
+      </c>
+      <c r="AM119" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN119" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS119">
+        <f>AM119/AN119-1</f>
+        <v/>
+      </c>
+      <c r="AT119">
+        <f>AO119/AN119-1</f>
+        <v/>
+      </c>
+      <c r="AV119" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW119" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB119">
+        <f>AV119/AW119-1</f>
+        <v/>
+      </c>
+      <c r="BC119">
+        <f>AX119/AW119-1</f>
+        <v/>
+      </c>
+      <c r="BE119" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF119" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BH119" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI119" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BK119">
+        <f>BE119/BF119-1</f>
+        <v/>
+      </c>
+      <c r="BL119">
+        <f>BG119/BF119-1</f>
+        <v/>
+      </c>
+      <c r="BN119" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO119" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BQ119" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR119" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BT119">
+        <f>BN119/BO119-1</f>
+        <v/>
+      </c>
+      <c r="BU119">
+        <f>BP119/BO119-1</f>
+        <v/>
+      </c>
+      <c r="BW119" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX119" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ119" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA119" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC119">
+        <f>BW119/BX119-1</f>
+        <v/>
+      </c>
+      <c r="CD119">
+        <f>BY119/BX119-1</f>
+        <v/>
+      </c>
+      <c r="CF119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI119" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ119" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL119">
+        <f>CF119/CG119-1</f>
+        <v/>
+      </c>
+      <c r="CM119">
+        <f>CH119/CG119-1</f>
+        <v/>
+      </c>
+      <c r="CO119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR119" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS119" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU119">
+        <f>CO119/CP119-1</f>
+        <v/>
+      </c>
+      <c r="CV119">
+        <f>CQ119/CP119-1</f>
+        <v/>
+      </c>
+      <c r="CX119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY119" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA119" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB119" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD119">
+        <f>CX119/CY119-1</f>
+        <v/>
+      </c>
+      <c r="DE119">
+        <f>CZ119/CY119-1</f>
+        <v/>
+      </c>
+      <c r="DG119" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH119" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ119" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK119" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM119">
+        <f>DG119/DH119-1</f>
+        <v/>
+      </c>
+      <c r="DN119">
+        <f>DI119/DH119-1</f>
+        <v/>
+      </c>
+      <c r="DP119" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ119" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS119" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT119" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV119">
+        <f>DP119/DQ119-1</f>
+        <v/>
+      </c>
+      <c r="DW119">
+        <f>DR119/DQ119-1</f>
+        <v/>
+      </c>
+      <c r="DY119" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ119" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB119" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE119">
+        <f>DY119/DZ119-1</f>
+        <v/>
+      </c>
+      <c r="EF119">
+        <f>EA119/DZ119-1</f>
+        <v/>
+      </c>
+      <c r="EH119" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI119" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK119" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL119" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN119">
+        <f>EH119/EI119-1</f>
+        <v/>
+      </c>
+      <c r="EO119">
+        <f>EJ119/EI119-1</f>
+        <v/>
+      </c>
+      <c r="EQ119" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER119" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET119" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU119" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW119">
+        <f>EQ119/ER119-1</f>
+        <v/>
+      </c>
+      <c r="EX119">
+        <f>ES119/ER119-1</f>
+        <v/>
+      </c>
+      <c r="EZ119" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA119" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC119" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD119" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF119">
+        <f>EZ119/FA119-1</f>
+        <v/>
+      </c>
+      <c r="FG119">
+        <f>FB119/FA119-1</f>
+        <v/>
+      </c>
+      <c r="FI119" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ119" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL119" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM119" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO119">
+        <f>FI119/FJ119-1</f>
+        <v/>
+      </c>
+      <c r="FP119">
+        <f>FK119/FJ119-1</f>
+        <v/>
+      </c>
+      <c r="FR119" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS119" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU119" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV119" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX119">
+        <f>FR119/FS119-1</f>
+        <v/>
+      </c>
+      <c r="FY119">
+        <f>FT119/FS119-1</f>
+        <v/>
+      </c>
+      <c r="GA119" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB119" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD119" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE119" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG119">
+        <f>GA119/GB119-1</f>
+        <v/>
+      </c>
+      <c r="GH119">
+        <f>GC119/GB119-1</f>
+        <v/>
+      </c>
+      <c r="GJ119" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK119" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM119" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN119" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP119">
+        <f>GJ119/GK119-1</f>
+        <v/>
+      </c>
+      <c r="GQ119">
+        <f>GL119/GK119-1</f>
+        <v/>
+      </c>
+      <c r="GS119" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT119" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV119" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW119" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY119">
+        <f>GS119/GT119-1</f>
+        <v/>
+      </c>
+      <c r="GZ119">
+        <f>GU119/GT119-1</f>
+        <v/>
+      </c>
+      <c r="HB119" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC119" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE119" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF119" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH119">
+        <f>HB119/HC119-1</f>
+        <v/>
+      </c>
+      <c r="HI119">
+        <f>HD119/HC119-1</f>
+        <v/>
+      </c>
+      <c r="HK119" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL119" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN119" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO119" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ119">
+        <f>HK119/HL119-1</f>
+        <v/>
+      </c>
+      <c r="HR119">
+        <f>HM119/HL119-1</f>
+        <v/>
+      </c>
+      <c r="HT119" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU119" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW119" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX119" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ119">
+        <f>HT119/HU119-1</f>
+        <v/>
+      </c>
+      <c r="IA119">
+        <f>HV119/HU119-1</f>
+        <v/>
+      </c>
+      <c r="IC119" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID119" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF119" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG119" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II119">
+        <f>IC119/ID119-1</f>
+        <v/>
+      </c>
+      <c r="IJ119">
+        <f>IE119/ID119-1</f>
+        <v/>
+      </c>
+      <c r="IL119" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM119" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO119" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP119" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR119">
+        <f>IL119/IM119-1</f>
+        <v/>
+      </c>
+      <c r="IS119">
+        <f>IN119/IM119-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS119"/>
+  <dimension ref="A1:IS120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -71953,6 +71953,691 @@
         <v/>
       </c>
     </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>21 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I120">
+        <f>C120/D120-1</f>
+        <v/>
+      </c>
+      <c r="J120">
+        <f>E120/D120-1</f>
+        <v/>
+      </c>
+      <c r="L120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R120">
+        <f>L120/M120-1</f>
+        <v/>
+      </c>
+      <c r="S120">
+        <f>N120/M120-1</f>
+        <v/>
+      </c>
+      <c r="U120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA120">
+        <f>U120/V120-1</f>
+        <v/>
+      </c>
+      <c r="AB120">
+        <f>W120/V120-1</f>
+        <v/>
+      </c>
+      <c r="AD120" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE120" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ120">
+        <f>AD120/AE120-1</f>
+        <v/>
+      </c>
+      <c r="AK120">
+        <f>AF120/AE120-1</f>
+        <v/>
+      </c>
+      <c r="AM120" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN120" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS120">
+        <f>AM120/AN120-1</f>
+        <v/>
+      </c>
+      <c r="AT120">
+        <f>AO120/AN120-1</f>
+        <v/>
+      </c>
+      <c r="AV120" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW120" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB120">
+        <f>AV120/AW120-1</f>
+        <v/>
+      </c>
+      <c r="BC120">
+        <f>AX120/AW120-1</f>
+        <v/>
+      </c>
+      <c r="BE120" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF120" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH120" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI120" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK120">
+        <f>BE120/BF120-1</f>
+        <v/>
+      </c>
+      <c r="BL120">
+        <f>BG120/BF120-1</f>
+        <v/>
+      </c>
+      <c r="BN120" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO120" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ120" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR120" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT120">
+        <f>BN120/BO120-1</f>
+        <v/>
+      </c>
+      <c r="BU120">
+        <f>BP120/BO120-1</f>
+        <v/>
+      </c>
+      <c r="BW120" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX120" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ120" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA120" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC120">
+        <f>BW120/BX120-1</f>
+        <v/>
+      </c>
+      <c r="CD120">
+        <f>BY120/BX120-1</f>
+        <v/>
+      </c>
+      <c r="CF120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI120" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ120" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL120">
+        <f>CF120/CG120-1</f>
+        <v/>
+      </c>
+      <c r="CM120">
+        <f>CH120/CG120-1</f>
+        <v/>
+      </c>
+      <c r="CO120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR120" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS120" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU120">
+        <f>CO120/CP120-1</f>
+        <v/>
+      </c>
+      <c r="CV120">
+        <f>CQ120/CP120-1</f>
+        <v/>
+      </c>
+      <c r="CX120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY120" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA120" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB120" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD120">
+        <f>CX120/CY120-1</f>
+        <v/>
+      </c>
+      <c r="DE120">
+        <f>CZ120/CY120-1</f>
+        <v/>
+      </c>
+      <c r="DG120" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH120" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ120" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK120" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM120">
+        <f>DG120/DH120-1</f>
+        <v/>
+      </c>
+      <c r="DN120">
+        <f>DI120/DH120-1</f>
+        <v/>
+      </c>
+      <c r="DP120" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ120" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS120" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT120" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV120">
+        <f>DP120/DQ120-1</f>
+        <v/>
+      </c>
+      <c r="DW120">
+        <f>DR120/DQ120-1</f>
+        <v/>
+      </c>
+      <c r="DY120" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ120" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB120" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE120">
+        <f>DY120/DZ120-1</f>
+        <v/>
+      </c>
+      <c r="EF120">
+        <f>EA120/DZ120-1</f>
+        <v/>
+      </c>
+      <c r="EH120" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI120" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK120" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL120" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN120">
+        <f>EH120/EI120-1</f>
+        <v/>
+      </c>
+      <c r="EO120">
+        <f>EJ120/EI120-1</f>
+        <v/>
+      </c>
+      <c r="EQ120" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER120" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET120" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU120" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW120">
+        <f>EQ120/ER120-1</f>
+        <v/>
+      </c>
+      <c r="EX120">
+        <f>ES120/ER120-1</f>
+        <v/>
+      </c>
+      <c r="EZ120" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA120" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC120" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD120" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF120">
+        <f>EZ120/FA120-1</f>
+        <v/>
+      </c>
+      <c r="FG120">
+        <f>FB120/FA120-1</f>
+        <v/>
+      </c>
+      <c r="FI120" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ120" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL120" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM120" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO120">
+        <f>FI120/FJ120-1</f>
+        <v/>
+      </c>
+      <c r="FP120">
+        <f>FK120/FJ120-1</f>
+        <v/>
+      </c>
+      <c r="FR120" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS120" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU120" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV120" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX120">
+        <f>FR120/FS120-1</f>
+        <v/>
+      </c>
+      <c r="FY120">
+        <f>FT120/FS120-1</f>
+        <v/>
+      </c>
+      <c r="GA120" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB120" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GD120" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE120" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GG120">
+        <f>GA120/GB120-1</f>
+        <v/>
+      </c>
+      <c r="GH120">
+        <f>GC120/GB120-1</f>
+        <v/>
+      </c>
+      <c r="GJ120" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK120" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GM120" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN120" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GP120">
+        <f>GJ120/GK120-1</f>
+        <v/>
+      </c>
+      <c r="GQ120">
+        <f>GL120/GK120-1</f>
+        <v/>
+      </c>
+      <c r="GS120" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT120" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV120" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW120" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY120">
+        <f>GS120/GT120-1</f>
+        <v/>
+      </c>
+      <c r="GZ120">
+        <f>GU120/GT120-1</f>
+        <v/>
+      </c>
+      <c r="HB120" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC120" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE120" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF120" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH120">
+        <f>HB120/HC120-1</f>
+        <v/>
+      </c>
+      <c r="HI120">
+        <f>HD120/HC120-1</f>
+        <v/>
+      </c>
+      <c r="HK120" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL120" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN120" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO120" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ120">
+        <f>HK120/HL120-1</f>
+        <v/>
+      </c>
+      <c r="HR120">
+        <f>HM120/HL120-1</f>
+        <v/>
+      </c>
+      <c r="HT120" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU120" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW120" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX120" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ120">
+        <f>HT120/HU120-1</f>
+        <v/>
+      </c>
+      <c r="IA120">
+        <f>HV120/HU120-1</f>
+        <v/>
+      </c>
+      <c r="IC120" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID120" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF120" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG120" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II120">
+        <f>IC120/ID120-1</f>
+        <v/>
+      </c>
+      <c r="IJ120">
+        <f>IE120/ID120-1</f>
+        <v/>
+      </c>
+      <c r="IL120" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM120" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO120" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP120" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR120">
+        <f>IL120/IM120-1</f>
+        <v/>
+      </c>
+      <c r="IS120">
+        <f>IN120/IM120-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS120"/>
+  <dimension ref="A1:IS121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -72638,6 +72638,687 @@
         <v/>
       </c>
     </row>
+    <row r="121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>21 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I121">
+        <f>C121/D121-1</f>
+        <v/>
+      </c>
+      <c r="J121">
+        <f>E121/D121-1</f>
+        <v/>
+      </c>
+      <c r="L121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R121">
+        <f>L121/M121-1</f>
+        <v/>
+      </c>
+      <c r="S121">
+        <f>N121/M121-1</f>
+        <v/>
+      </c>
+      <c r="U121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA121">
+        <f>U121/V121-1</f>
+        <v/>
+      </c>
+      <c r="AB121">
+        <f>W121/V121-1</f>
+        <v/>
+      </c>
+      <c r="AD121" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE121" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ121">
+        <f>AD121/AE121-1</f>
+        <v/>
+      </c>
+      <c r="AK121">
+        <f>AF121/AE121-1</f>
+        <v/>
+      </c>
+      <c r="AM121" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN121" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS121">
+        <f>AM121/AN121-1</f>
+        <v/>
+      </c>
+      <c r="AT121">
+        <f>AO121/AN121-1</f>
+        <v/>
+      </c>
+      <c r="AV121" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW121" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB121">
+        <f>AV121/AW121-1</f>
+        <v/>
+      </c>
+      <c r="BC121">
+        <f>AX121/AW121-1</f>
+        <v/>
+      </c>
+      <c r="BE121" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF121" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH121" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI121" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK121">
+        <f>BE121/BF121-1</f>
+        <v/>
+      </c>
+      <c r="BL121">
+        <f>BG121/BF121-1</f>
+        <v/>
+      </c>
+      <c r="BN121" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO121" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ121" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR121" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT121">
+        <f>BN121/BO121-1</f>
+        <v/>
+      </c>
+      <c r="BU121">
+        <f>BP121/BO121-1</f>
+        <v/>
+      </c>
+      <c r="BW121" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX121" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ121" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA121" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC121">
+        <f>BW121/BX121-1</f>
+        <v/>
+      </c>
+      <c r="CD121">
+        <f>BY121/BX121-1</f>
+        <v/>
+      </c>
+      <c r="CF121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI121" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ121" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL121">
+        <f>CF121/CG121-1</f>
+        <v/>
+      </c>
+      <c r="CM121">
+        <f>CH121/CG121-1</f>
+        <v/>
+      </c>
+      <c r="CO121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR121" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS121" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU121">
+        <f>CO121/CP121-1</f>
+        <v/>
+      </c>
+      <c r="CV121">
+        <f>CQ121/CP121-1</f>
+        <v/>
+      </c>
+      <c r="CX121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY121" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA121" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB121" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD121">
+        <f>CX121/CY121-1</f>
+        <v/>
+      </c>
+      <c r="DE121">
+        <f>CZ121/CY121-1</f>
+        <v/>
+      </c>
+      <c r="DG121" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH121" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ121" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK121" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM121">
+        <f>DG121/DH121-1</f>
+        <v/>
+      </c>
+      <c r="DN121">
+        <f>DI121/DH121-1</f>
+        <v/>
+      </c>
+      <c r="DP121" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ121" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS121" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT121" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV121">
+        <f>DP121/DQ121-1</f>
+        <v/>
+      </c>
+      <c r="DW121">
+        <f>DR121/DQ121-1</f>
+        <v/>
+      </c>
+      <c r="DY121" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ121" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB121" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC121" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE121">
+        <f>DY121/DZ121-1</f>
+        <v/>
+      </c>
+      <c r="EF121">
+        <f>EA121/DZ121-1</f>
+        <v/>
+      </c>
+      <c r="EH121" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI121" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK121" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL121" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN121">
+        <f>EH121/EI121-1</f>
+        <v/>
+      </c>
+      <c r="EO121">
+        <f>EJ121/EI121-1</f>
+        <v/>
+      </c>
+      <c r="EQ121" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER121" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET121" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU121" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW121">
+        <f>EQ121/ER121-1</f>
+        <v/>
+      </c>
+      <c r="EX121">
+        <f>ES121/ER121-1</f>
+        <v/>
+      </c>
+      <c r="EZ121" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA121" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC121" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD121" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF121">
+        <f>EZ121/FA121-1</f>
+        <v/>
+      </c>
+      <c r="FG121">
+        <f>FB121/FA121-1</f>
+        <v/>
+      </c>
+      <c r="FI121" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ121" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL121" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM121" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO121">
+        <f>FI121/FJ121-1</f>
+        <v/>
+      </c>
+      <c r="FP121">
+        <f>FK121/FJ121-1</f>
+        <v/>
+      </c>
+      <c r="FR121" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS121" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU121" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV121" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX121">
+        <f>FR121/FS121-1</f>
+        <v/>
+      </c>
+      <c r="FY121">
+        <f>FT121/FS121-1</f>
+        <v/>
+      </c>
+      <c r="GA121" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB121" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD121" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE121" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG121">
+        <f>GA121/GB121-1</f>
+        <v/>
+      </c>
+      <c r="GH121">
+        <f>GC121/GB121-1</f>
+        <v/>
+      </c>
+      <c r="GJ121" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK121" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM121" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN121" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP121">
+        <f>GJ121/GK121-1</f>
+        <v/>
+      </c>
+      <c r="GQ121">
+        <f>GL121/GK121-1</f>
+        <v/>
+      </c>
+      <c r="GS121" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT121" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV121" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW121" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY121">
+        <f>GS121/GT121-1</f>
+        <v/>
+      </c>
+      <c r="GZ121">
+        <f>GU121/GT121-1</f>
+        <v/>
+      </c>
+      <c r="HB121" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC121" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE121" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF121" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH121">
+        <f>HB121/HC121-1</f>
+        <v/>
+      </c>
+      <c r="HI121">
+        <f>HD121/HC121-1</f>
+        <v/>
+      </c>
+      <c r="HK121" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL121" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN121" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO121" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ121">
+        <f>HK121/HL121-1</f>
+        <v/>
+      </c>
+      <c r="HR121">
+        <f>HM121/HL121-1</f>
+        <v/>
+      </c>
+      <c r="HT121" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU121" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW121" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX121" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ121">
+        <f>HT121/HU121-1</f>
+        <v/>
+      </c>
+      <c r="IA121">
+        <f>HV121/HU121-1</f>
+        <v/>
+      </c>
+      <c r="IC121" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID121" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF121" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG121" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II121">
+        <f>IC121/ID121-1</f>
+        <v/>
+      </c>
+      <c r="IJ121">
+        <f>IE121/ID121-1</f>
+        <v/>
+      </c>
+      <c r="IL121" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM121" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO121" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP121" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR121">
+        <f>IL121/IM121-1</f>
+        <v/>
+      </c>
+      <c r="IS121">
+        <f>IN121/IM121-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS121"/>
+  <dimension ref="A1:IS122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -73319,6 +73319,723 @@
         <v/>
       </c>
     </row>
+    <row r="122">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>21 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D122" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I122">
+        <f>C122/D122-1</f>
+        <v/>
+      </c>
+      <c r="J122">
+        <f>E122/D122-1</f>
+        <v/>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M122" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R122">
+        <f>L122/M122-1</f>
+        <v/>
+      </c>
+      <c r="S122">
+        <f>N122/M122-1</f>
+        <v/>
+      </c>
+      <c r="U122" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V122" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA122">
+        <f>U122/V122-1</f>
+        <v/>
+      </c>
+      <c r="AB122">
+        <f>W122/V122-1</f>
+        <v/>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE122" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ122">
+        <f>AD122/AE122-1</f>
+        <v/>
+      </c>
+      <c r="AK122">
+        <f>AF122/AE122-1</f>
+        <v/>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN122" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS122">
+        <f>AM122/AN122-1</f>
+        <v/>
+      </c>
+      <c r="AT122">
+        <f>AO122/AN122-1</f>
+        <v/>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW122" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB122">
+        <f>AV122/AW122-1</f>
+        <v/>
+      </c>
+      <c r="BC122">
+        <f>AX122/AW122-1</f>
+        <v/>
+      </c>
+      <c r="BE122" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF122" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH122" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI122" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK122">
+        <f>BE122/BF122-1</f>
+        <v/>
+      </c>
+      <c r="BL122">
+        <f>BG122/BF122-1</f>
+        <v/>
+      </c>
+      <c r="BN122" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO122" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ122" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR122" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT122">
+        <f>BN122/BO122-1</f>
+        <v/>
+      </c>
+      <c r="BU122">
+        <f>BP122/BO122-1</f>
+        <v/>
+      </c>
+      <c r="BW122" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX122" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ122" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA122" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC122">
+        <f>BW122/BX122-1</f>
+        <v/>
+      </c>
+      <c r="CD122">
+        <f>BY122/BX122-1</f>
+        <v/>
+      </c>
+      <c r="CF122" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG122" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI122" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ122" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL122">
+        <f>CF122/CG122-1</f>
+        <v/>
+      </c>
+      <c r="CM122">
+        <f>CH122/CG122-1</f>
+        <v/>
+      </c>
+      <c r="CO122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CP122" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CS122" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU122">
+        <f>CO122/CP122-1</f>
+        <v/>
+      </c>
+      <c r="CV122">
+        <f>CQ122/CP122-1</f>
+        <v/>
+      </c>
+      <c r="CX122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY122" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB122" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD122">
+        <f>CX122/CY122-1</f>
+        <v/>
+      </c>
+      <c r="DE122">
+        <f>CZ122/CY122-1</f>
+        <v/>
+      </c>
+      <c r="DG122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH122" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK122" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM122">
+        <f>DG122/DH122-1</f>
+        <v/>
+      </c>
+      <c r="DN122">
+        <f>DI122/DH122-1</f>
+        <v/>
+      </c>
+      <c r="DP122" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ122" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS122" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT122" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV122">
+        <f>DP122/DQ122-1</f>
+        <v/>
+      </c>
+      <c r="DW122">
+        <f>DR122/DQ122-1</f>
+        <v/>
+      </c>
+      <c r="DY122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ122" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC122" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE122">
+        <f>DY122/DZ122-1</f>
+        <v/>
+      </c>
+      <c r="EF122">
+        <f>EA122/DZ122-1</f>
+        <v/>
+      </c>
+      <c r="EH122" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI122" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK122" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL122" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN122">
+        <f>EH122/EI122-1</f>
+        <v/>
+      </c>
+      <c r="EO122">
+        <f>EJ122/EI122-1</f>
+        <v/>
+      </c>
+      <c r="EQ122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER122" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU122" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW122">
+        <f>EQ122/ER122-1</f>
+        <v/>
+      </c>
+      <c r="EX122">
+        <f>ES122/ER122-1</f>
+        <v/>
+      </c>
+      <c r="EZ122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA122" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD122" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF122">
+        <f>EZ122/FA122-1</f>
+        <v/>
+      </c>
+      <c r="FG122">
+        <f>FB122/FA122-1</f>
+        <v/>
+      </c>
+      <c r="FI122" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ122" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL122" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM122" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO122">
+        <f>FI122/FJ122-1</f>
+        <v/>
+      </c>
+      <c r="FP122">
+        <f>FK122/FJ122-1</f>
+        <v/>
+      </c>
+      <c r="FR122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FS122" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FV122" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX122">
+        <f>FR122/FS122-1</f>
+        <v/>
+      </c>
+      <c r="FY122">
+        <f>FT122/FS122-1</f>
+        <v/>
+      </c>
+      <c r="GA122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GB122" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GE122" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG122">
+        <f>GA122/GB122-1</f>
+        <v/>
+      </c>
+      <c r="GH122">
+        <f>GC122/GB122-1</f>
+        <v/>
+      </c>
+      <c r="GJ122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GK122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GM122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GN122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GP122">
+        <f>GJ122/GK122-1</f>
+        <v/>
+      </c>
+      <c r="GQ122">
+        <f>GL122/GK122-1</f>
+        <v/>
+      </c>
+      <c r="GS122" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT122" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV122" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW122" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY122">
+        <f>GS122/GT122-1</f>
+        <v/>
+      </c>
+      <c r="GZ122">
+        <f>GU122/GT122-1</f>
+        <v/>
+      </c>
+      <c r="HB122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HC122" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HF122" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH122">
+        <f>HB122/HC122-1</f>
+        <v/>
+      </c>
+      <c r="HI122">
+        <f>HD122/HC122-1</f>
+        <v/>
+      </c>
+      <c r="HK122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HL122" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HO122" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ122">
+        <f>HK122/HL122-1</f>
+        <v/>
+      </c>
+      <c r="HR122">
+        <f>HM122/HL122-1</f>
+        <v/>
+      </c>
+      <c r="HT122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HU122" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HX122" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ122">
+        <f>HT122/HU122-1</f>
+        <v/>
+      </c>
+      <c r="IA122">
+        <f>HV122/HU122-1</f>
+        <v/>
+      </c>
+      <c r="IC122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ID122" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IG122" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II122">
+        <f>IC122/ID122-1</f>
+        <v/>
+      </c>
+      <c r="IJ122">
+        <f>IE122/ID122-1</f>
+        <v/>
+      </c>
+      <c r="IL122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IM122" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO122" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IP122" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR122">
+        <f>IL122/IM122-1</f>
+        <v/>
+      </c>
+      <c r="IS122">
+        <f>IN122/IM122-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS122"/>
+  <dimension ref="A1:IS123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -74036,6 +74036,693 @@
         <v/>
       </c>
     </row>
+    <row r="123">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>22 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D123" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I123">
+        <f>C123/D123-1</f>
+        <v/>
+      </c>
+      <c r="J123">
+        <f>E123/D123-1</f>
+        <v/>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M123" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R123">
+        <f>L123/M123-1</f>
+        <v/>
+      </c>
+      <c r="S123">
+        <f>N123/M123-1</f>
+        <v/>
+      </c>
+      <c r="U123" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V123" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA123">
+        <f>U123/V123-1</f>
+        <v/>
+      </c>
+      <c r="AB123">
+        <f>W123/V123-1</f>
+        <v/>
+      </c>
+      <c r="AD123" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE123" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ123">
+        <f>AD123/AE123-1</f>
+        <v/>
+      </c>
+      <c r="AK123">
+        <f>AF123/AE123-1</f>
+        <v/>
+      </c>
+      <c r="AM123" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN123" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS123">
+        <f>AM123/AN123-1</f>
+        <v/>
+      </c>
+      <c r="AT123">
+        <f>AO123/AN123-1</f>
+        <v/>
+      </c>
+      <c r="AV123" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW123" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB123">
+        <f>AV123/AW123-1</f>
+        <v/>
+      </c>
+      <c r="BC123">
+        <f>AX123/AW123-1</f>
+        <v/>
+      </c>
+      <c r="BE123" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF123" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH123" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI123" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK123">
+        <f>BE123/BF123-1</f>
+        <v/>
+      </c>
+      <c r="BL123">
+        <f>BG123/BF123-1</f>
+        <v/>
+      </c>
+      <c r="BN123" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO123" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BQ123" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR123" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BT123">
+        <f>BN123/BO123-1</f>
+        <v/>
+      </c>
+      <c r="BU123">
+        <f>BP123/BO123-1</f>
+        <v/>
+      </c>
+      <c r="BW123" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX123" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ123" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA123" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC123">
+        <f>BW123/BX123-1</f>
+        <v/>
+      </c>
+      <c r="CD123">
+        <f>BY123/BX123-1</f>
+        <v/>
+      </c>
+      <c r="CF123" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG123" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI123" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ123" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL123">
+        <f>CF123/CG123-1</f>
+        <v/>
+      </c>
+      <c r="CM123">
+        <f>CH123/CG123-1</f>
+        <v/>
+      </c>
+      <c r="CO123" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP123" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR123" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS123" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU123">
+        <f>CO123/CP123-1</f>
+        <v/>
+      </c>
+      <c r="CV123">
+        <f>CQ123/CP123-1</f>
+        <v/>
+      </c>
+      <c r="CX123" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY123" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA123" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB123" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD123">
+        <f>CX123/CY123-1</f>
+        <v/>
+      </c>
+      <c r="DE123">
+        <f>CZ123/CY123-1</f>
+        <v/>
+      </c>
+      <c r="DG123" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH123" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ123" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK123" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM123">
+        <f>DG123/DH123-1</f>
+        <v/>
+      </c>
+      <c r="DN123">
+        <f>DI123/DH123-1</f>
+        <v/>
+      </c>
+      <c r="DP123" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ123" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS123" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT123" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV123">
+        <f>DP123/DQ123-1</f>
+        <v/>
+      </c>
+      <c r="DW123">
+        <f>DR123/DQ123-1</f>
+        <v/>
+      </c>
+      <c r="DY123" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ123" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB123" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC123" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE123">
+        <f>DY123/DZ123-1</f>
+        <v/>
+      </c>
+      <c r="EF123">
+        <f>EA123/DZ123-1</f>
+        <v/>
+      </c>
+      <c r="EH123" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI123" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK123" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL123" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN123">
+        <f>EH123/EI123-1</f>
+        <v/>
+      </c>
+      <c r="EO123">
+        <f>EJ123/EI123-1</f>
+        <v/>
+      </c>
+      <c r="EQ123" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER123" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET123" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU123" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW123">
+        <f>EQ123/ER123-1</f>
+        <v/>
+      </c>
+      <c r="EX123">
+        <f>ES123/ER123-1</f>
+        <v/>
+      </c>
+      <c r="EZ123" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA123" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC123" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD123" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF123">
+        <f>EZ123/FA123-1</f>
+        <v/>
+      </c>
+      <c r="FG123">
+        <f>FB123/FA123-1</f>
+        <v/>
+      </c>
+      <c r="FI123" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ123" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL123" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM123" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO123">
+        <f>FI123/FJ123-1</f>
+        <v/>
+      </c>
+      <c r="FP123">
+        <f>FK123/FJ123-1</f>
+        <v/>
+      </c>
+      <c r="FR123" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS123" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU123" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV123" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX123">
+        <f>FR123/FS123-1</f>
+        <v/>
+      </c>
+      <c r="FY123">
+        <f>FT123/FS123-1</f>
+        <v/>
+      </c>
+      <c r="GA123" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB123" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD123" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE123" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG123">
+        <f>GA123/GB123-1</f>
+        <v/>
+      </c>
+      <c r="GH123">
+        <f>GC123/GB123-1</f>
+        <v/>
+      </c>
+      <c r="GJ123" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK123" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM123" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN123" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP123">
+        <f>GJ123/GK123-1</f>
+        <v/>
+      </c>
+      <c r="GQ123">
+        <f>GL123/GK123-1</f>
+        <v/>
+      </c>
+      <c r="GS123" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT123" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GV123" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW123" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GY123">
+        <f>GS123/GT123-1</f>
+        <v/>
+      </c>
+      <c r="GZ123">
+        <f>GU123/GT123-1</f>
+        <v/>
+      </c>
+      <c r="HB123" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC123" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE123" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF123" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH123">
+        <f>HB123/HC123-1</f>
+        <v/>
+      </c>
+      <c r="HI123">
+        <f>HD123/HC123-1</f>
+        <v/>
+      </c>
+      <c r="HK123" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL123" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN123" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO123" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ123">
+        <f>HK123/HL123-1</f>
+        <v/>
+      </c>
+      <c r="HR123">
+        <f>HM123/HL123-1</f>
+        <v/>
+      </c>
+      <c r="HT123" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU123" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW123" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX123" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ123">
+        <f>HT123/HU123-1</f>
+        <v/>
+      </c>
+      <c r="IA123">
+        <f>HV123/HU123-1</f>
+        <v/>
+      </c>
+      <c r="IC123" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID123" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF123" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG123" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II123">
+        <f>IC123/ID123-1</f>
+        <v/>
+      </c>
+      <c r="IJ123">
+        <f>IE123/ID123-1</f>
+        <v/>
+      </c>
+      <c r="IL123" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM123" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO123" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP123" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR123">
+        <f>IL123/IM123-1</f>
+        <v/>
+      </c>
+      <c r="IS123">
+        <f>IN123/IM123-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS123"/>
+  <dimension ref="A1:IS124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -74723,6 +74723,689 @@
         <v/>
       </c>
     </row>
+    <row r="124">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>22 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I124">
+        <f>C124/D124-1</f>
+        <v/>
+      </c>
+      <c r="J124">
+        <f>E124/D124-1</f>
+        <v/>
+      </c>
+      <c r="L124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R124">
+        <f>L124/M124-1</f>
+        <v/>
+      </c>
+      <c r="S124">
+        <f>N124/M124-1</f>
+        <v/>
+      </c>
+      <c r="U124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA124">
+        <f>U124/V124-1</f>
+        <v/>
+      </c>
+      <c r="AB124">
+        <f>W124/V124-1</f>
+        <v/>
+      </c>
+      <c r="AD124" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE124" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ124">
+        <f>AD124/AE124-1</f>
+        <v/>
+      </c>
+      <c r="AK124">
+        <f>AF124/AE124-1</f>
+        <v/>
+      </c>
+      <c r="AM124" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN124" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS124">
+        <f>AM124/AN124-1</f>
+        <v/>
+      </c>
+      <c r="AT124">
+        <f>AO124/AN124-1</f>
+        <v/>
+      </c>
+      <c r="AV124" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW124" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB124">
+        <f>AV124/AW124-1</f>
+        <v/>
+      </c>
+      <c r="BC124">
+        <f>AX124/AW124-1</f>
+        <v/>
+      </c>
+      <c r="BE124" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF124" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH124" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI124" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK124">
+        <f>BE124/BF124-1</f>
+        <v/>
+      </c>
+      <c r="BL124">
+        <f>BG124/BF124-1</f>
+        <v/>
+      </c>
+      <c r="BN124" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO124" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ124" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR124" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT124">
+        <f>BN124/BO124-1</f>
+        <v/>
+      </c>
+      <c r="BU124">
+        <f>BP124/BO124-1</f>
+        <v/>
+      </c>
+      <c r="BW124" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX124" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ124" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA124" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC124">
+        <f>BW124/BX124-1</f>
+        <v/>
+      </c>
+      <c r="CD124">
+        <f>BY124/BX124-1</f>
+        <v/>
+      </c>
+      <c r="CF124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI124" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ124" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL124">
+        <f>CF124/CG124-1</f>
+        <v/>
+      </c>
+      <c r="CM124">
+        <f>CH124/CG124-1</f>
+        <v/>
+      </c>
+      <c r="CO124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR124" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS124" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU124">
+        <f>CO124/CP124-1</f>
+        <v/>
+      </c>
+      <c r="CV124">
+        <f>CQ124/CP124-1</f>
+        <v/>
+      </c>
+      <c r="CX124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY124" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA124" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB124" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD124">
+        <f>CX124/CY124-1</f>
+        <v/>
+      </c>
+      <c r="DE124">
+        <f>CZ124/CY124-1</f>
+        <v/>
+      </c>
+      <c r="DG124" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH124" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ124" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK124" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM124">
+        <f>DG124/DH124-1</f>
+        <v/>
+      </c>
+      <c r="DN124">
+        <f>DI124/DH124-1</f>
+        <v/>
+      </c>
+      <c r="DP124" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ124" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS124" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT124" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV124">
+        <f>DP124/DQ124-1</f>
+        <v/>
+      </c>
+      <c r="DW124">
+        <f>DR124/DQ124-1</f>
+        <v/>
+      </c>
+      <c r="DY124" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ124" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB124" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC124" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE124">
+        <f>DY124/DZ124-1</f>
+        <v/>
+      </c>
+      <c r="EF124">
+        <f>EA124/DZ124-1</f>
+        <v/>
+      </c>
+      <c r="EH124" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI124" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK124" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL124" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN124">
+        <f>EH124/EI124-1</f>
+        <v/>
+      </c>
+      <c r="EO124">
+        <f>EJ124/EI124-1</f>
+        <v/>
+      </c>
+      <c r="EQ124" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER124" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET124" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU124" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW124">
+        <f>EQ124/ER124-1</f>
+        <v/>
+      </c>
+      <c r="EX124">
+        <f>ES124/ER124-1</f>
+        <v/>
+      </c>
+      <c r="EZ124" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA124" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC124" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD124" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF124">
+        <f>EZ124/FA124-1</f>
+        <v/>
+      </c>
+      <c r="FG124">
+        <f>FB124/FA124-1</f>
+        <v/>
+      </c>
+      <c r="FI124" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FJ124" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL124" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM124" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO124">
+        <f>FI124/FJ124-1</f>
+        <v/>
+      </c>
+      <c r="FP124">
+        <f>FK124/FJ124-1</f>
+        <v/>
+      </c>
+      <c r="FR124" s="11" t="n">
+        <v>479.99</v>
+      </c>
+      <c r="FS124" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU124" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV124" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX124">
+        <f>FR124/FS124-1</f>
+        <v/>
+      </c>
+      <c r="FY124">
+        <f>FT124/FS124-1</f>
+        <v/>
+      </c>
+      <c r="GA124" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GB124" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD124" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE124" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG124">
+        <f>GA124/GB124-1</f>
+        <v/>
+      </c>
+      <c r="GH124">
+        <f>GC124/GB124-1</f>
+        <v/>
+      </c>
+      <c r="GJ124" s="11" t="n">
+        <v>479.99</v>
+      </c>
+      <c r="GK124" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM124" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN124" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP124">
+        <f>GJ124/GK124-1</f>
+        <v/>
+      </c>
+      <c r="GQ124">
+        <f>GL124/GK124-1</f>
+        <v/>
+      </c>
+      <c r="GS124" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="GT124" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV124" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW124" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY124">
+        <f>GS124/GT124-1</f>
+        <v/>
+      </c>
+      <c r="GZ124">
+        <f>GU124/GT124-1</f>
+        <v/>
+      </c>
+      <c r="HB124" s="11" t="n">
+        <v>509.99</v>
+      </c>
+      <c r="HC124" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE124" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF124" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH124">
+        <f>HB124/HC124-1</f>
+        <v/>
+      </c>
+      <c r="HI124">
+        <f>HD124/HC124-1</f>
+        <v/>
+      </c>
+      <c r="HK124" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HL124" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN124" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO124" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ124">
+        <f>HK124/HL124-1</f>
+        <v/>
+      </c>
+      <c r="HR124">
+        <f>HM124/HL124-1</f>
+        <v/>
+      </c>
+      <c r="HT124" s="11" t="n">
+        <v>509.99</v>
+      </c>
+      <c r="HU124" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW124" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX124" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ124">
+        <f>HT124/HU124-1</f>
+        <v/>
+      </c>
+      <c r="IA124">
+        <f>HV124/HU124-1</f>
+        <v/>
+      </c>
+      <c r="IC124" s="11" t="n">
+        <v>799.99</v>
+      </c>
+      <c r="ID124" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF124" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG124" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II124">
+        <f>IC124/ID124-1</f>
+        <v/>
+      </c>
+      <c r="IJ124">
+        <f>IE124/ID124-1</f>
+        <v/>
+      </c>
+      <c r="IL124" s="11" t="n">
+        <v>799.99</v>
+      </c>
+      <c r="IM124" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO124" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP124" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR124">
+        <f>IL124/IM124-1</f>
+        <v/>
+      </c>
+      <c r="IS124">
+        <f>IN124/IM124-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS124"/>
+  <dimension ref="A1:IS125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -75406,6 +75406,733 @@
         <v/>
       </c>
     </row>
+    <row r="125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>22 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D125" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I125">
+        <f>C125/D125-1</f>
+        <v/>
+      </c>
+      <c r="J125">
+        <f>E125/D125-1</f>
+        <v/>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R125">
+        <f>L125/M125-1</f>
+        <v/>
+      </c>
+      <c r="S125">
+        <f>N125/M125-1</f>
+        <v/>
+      </c>
+      <c r="U125" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V125" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA125">
+        <f>U125/V125-1</f>
+        <v/>
+      </c>
+      <c r="AB125">
+        <f>W125/V125-1</f>
+        <v/>
+      </c>
+      <c r="AD125" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE125" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ125">
+        <f>AD125/AE125-1</f>
+        <v/>
+      </c>
+      <c r="AK125">
+        <f>AF125/AE125-1</f>
+        <v/>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN125" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS125">
+        <f>AM125/AN125-1</f>
+        <v/>
+      </c>
+      <c r="AT125">
+        <f>AO125/AN125-1</f>
+        <v/>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW125" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB125">
+        <f>AV125/AW125-1</f>
+        <v/>
+      </c>
+      <c r="BC125">
+        <f>AX125/AW125-1</f>
+        <v/>
+      </c>
+      <c r="BE125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF125" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI125" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK125">
+        <f>BE125/BF125-1</f>
+        <v/>
+      </c>
+      <c r="BL125">
+        <f>BG125/BF125-1</f>
+        <v/>
+      </c>
+      <c r="BN125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO125" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR125" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT125">
+        <f>BN125/BO125-1</f>
+        <v/>
+      </c>
+      <c r="BU125">
+        <f>BP125/BO125-1</f>
+        <v/>
+      </c>
+      <c r="BW125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX125" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA125" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC125">
+        <f>BW125/BX125-1</f>
+        <v/>
+      </c>
+      <c r="CD125">
+        <f>BY125/BX125-1</f>
+        <v/>
+      </c>
+      <c r="CF125" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG125" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI125" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ125" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL125">
+        <f>CF125/CG125-1</f>
+        <v/>
+      </c>
+      <c r="CM125">
+        <f>CH125/CG125-1</f>
+        <v/>
+      </c>
+      <c r="CO125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CP125" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CS125" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU125">
+        <f>CO125/CP125-1</f>
+        <v/>
+      </c>
+      <c r="CV125">
+        <f>CQ125/CP125-1</f>
+        <v/>
+      </c>
+      <c r="CX125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY125" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB125" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD125">
+        <f>CX125/CY125-1</f>
+        <v/>
+      </c>
+      <c r="DE125">
+        <f>CZ125/CY125-1</f>
+        <v/>
+      </c>
+      <c r="DG125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH125" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK125" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM125">
+        <f>DG125/DH125-1</f>
+        <v/>
+      </c>
+      <c r="DN125">
+        <f>DI125/DH125-1</f>
+        <v/>
+      </c>
+      <c r="DP125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ125" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT125" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV125">
+        <f>DP125/DQ125-1</f>
+        <v/>
+      </c>
+      <c r="DW125">
+        <f>DR125/DQ125-1</f>
+        <v/>
+      </c>
+      <c r="DY125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ125" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC125" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE125">
+        <f>DY125/DZ125-1</f>
+        <v/>
+      </c>
+      <c r="EF125">
+        <f>EA125/DZ125-1</f>
+        <v/>
+      </c>
+      <c r="EH125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI125" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL125" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN125">
+        <f>EH125/EI125-1</f>
+        <v/>
+      </c>
+      <c r="EO125">
+        <f>EJ125/EI125-1</f>
+        <v/>
+      </c>
+      <c r="EQ125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER125" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU125" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW125">
+        <f>EQ125/ER125-1</f>
+        <v/>
+      </c>
+      <c r="EX125">
+        <f>ES125/ER125-1</f>
+        <v/>
+      </c>
+      <c r="EZ125" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA125" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC125" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD125" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF125">
+        <f>EZ125/FA125-1</f>
+        <v/>
+      </c>
+      <c r="FG125">
+        <f>FB125/FA125-1</f>
+        <v/>
+      </c>
+      <c r="FI125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FJ125" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FM125" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO125">
+        <f>FI125/FJ125-1</f>
+        <v/>
+      </c>
+      <c r="FP125">
+        <f>FK125/FJ125-1</f>
+        <v/>
+      </c>
+      <c r="FR125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FS125" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FV125" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX125">
+        <f>FR125/FS125-1</f>
+        <v/>
+      </c>
+      <c r="FY125">
+        <f>FT125/FS125-1</f>
+        <v/>
+      </c>
+      <c r="GA125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GB125" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GE125" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG125">
+        <f>GA125/GB125-1</f>
+        <v/>
+      </c>
+      <c r="GH125">
+        <f>GC125/GB125-1</f>
+        <v/>
+      </c>
+      <c r="GJ125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GK125" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GN125" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP125">
+        <f>GJ125/GK125-1</f>
+        <v/>
+      </c>
+      <c r="GQ125">
+        <f>GL125/GK125-1</f>
+        <v/>
+      </c>
+      <c r="GS125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GT125" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GW125" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY125">
+        <f>GS125/GT125-1</f>
+        <v/>
+      </c>
+      <c r="GZ125">
+        <f>GU125/GT125-1</f>
+        <v/>
+      </c>
+      <c r="HB125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HC125" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HF125" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH125">
+        <f>HB125/HC125-1</f>
+        <v/>
+      </c>
+      <c r="HI125">
+        <f>HD125/HC125-1</f>
+        <v/>
+      </c>
+      <c r="HK125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HL125" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HO125" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ125">
+        <f>HK125/HL125-1</f>
+        <v/>
+      </c>
+      <c r="HR125">
+        <f>HM125/HL125-1</f>
+        <v/>
+      </c>
+      <c r="HT125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HU125" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HX125" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ125">
+        <f>HT125/HU125-1</f>
+        <v/>
+      </c>
+      <c r="IA125">
+        <f>HV125/HU125-1</f>
+        <v/>
+      </c>
+      <c r="IC125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ID125" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IG125" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II125">
+        <f>IC125/ID125-1</f>
+        <v/>
+      </c>
+      <c r="IJ125">
+        <f>IE125/ID125-1</f>
+        <v/>
+      </c>
+      <c r="IL125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IM125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IP125" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR125">
+        <f>IL125/IM125-1</f>
+        <v/>
+      </c>
+      <c r="IS125">
+        <f>IN125/IM125-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS125"/>
+  <dimension ref="A1:IS126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -76133,6 +76133,715 @@
         <v/>
       </c>
     </row>
+    <row r="126">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>22 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D126" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I126">
+        <f>C126/D126-1</f>
+        <v/>
+      </c>
+      <c r="J126">
+        <f>E126/D126-1</f>
+        <v/>
+      </c>
+      <c r="L126" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M126" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R126">
+        <f>L126/M126-1</f>
+        <v/>
+      </c>
+      <c r="S126">
+        <f>N126/M126-1</f>
+        <v/>
+      </c>
+      <c r="U126" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AA126">
+        <f>U126/V126-1</f>
+        <v/>
+      </c>
+      <c r="AB126">
+        <f>W126/V126-1</f>
+        <v/>
+      </c>
+      <c r="AD126" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AJ126">
+        <f>AD126/AE126-1</f>
+        <v/>
+      </c>
+      <c r="AK126">
+        <f>AF126/AE126-1</f>
+        <v/>
+      </c>
+      <c r="AM126" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN126" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS126">
+        <f>AM126/AN126-1</f>
+        <v/>
+      </c>
+      <c r="AT126">
+        <f>AO126/AN126-1</f>
+        <v/>
+      </c>
+      <c r="AV126" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW126" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB126">
+        <f>AV126/AW126-1</f>
+        <v/>
+      </c>
+      <c r="BC126">
+        <f>AX126/AW126-1</f>
+        <v/>
+      </c>
+      <c r="BE126" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF126" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH126" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI126" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK126">
+        <f>BE126/BF126-1</f>
+        <v/>
+      </c>
+      <c r="BL126">
+        <f>BG126/BF126-1</f>
+        <v/>
+      </c>
+      <c r="BN126" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO126" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ126" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR126" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT126">
+        <f>BN126/BO126-1</f>
+        <v/>
+      </c>
+      <c r="BU126">
+        <f>BP126/BO126-1</f>
+        <v/>
+      </c>
+      <c r="BW126" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX126" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ126" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA126" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC126">
+        <f>BW126/BX126-1</f>
+        <v/>
+      </c>
+      <c r="CD126">
+        <f>BY126/BX126-1</f>
+        <v/>
+      </c>
+      <c r="CF126" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG126" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI126" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ126" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL126">
+        <f>CF126/CG126-1</f>
+        <v/>
+      </c>
+      <c r="CM126">
+        <f>CH126/CG126-1</f>
+        <v/>
+      </c>
+      <c r="CO126" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP126" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR126" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS126" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU126">
+        <f>CO126/CP126-1</f>
+        <v/>
+      </c>
+      <c r="CV126">
+        <f>CQ126/CP126-1</f>
+        <v/>
+      </c>
+      <c r="CX126" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY126" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA126" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB126" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD126">
+        <f>CX126/CY126-1</f>
+        <v/>
+      </c>
+      <c r="DE126">
+        <f>CZ126/CY126-1</f>
+        <v/>
+      </c>
+      <c r="DG126" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH126" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ126" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK126" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM126">
+        <f>DG126/DH126-1</f>
+        <v/>
+      </c>
+      <c r="DN126">
+        <f>DI126/DH126-1</f>
+        <v/>
+      </c>
+      <c r="DP126" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ126" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS126" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT126" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV126">
+        <f>DP126/DQ126-1</f>
+        <v/>
+      </c>
+      <c r="DW126">
+        <f>DR126/DQ126-1</f>
+        <v/>
+      </c>
+      <c r="DY126" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ126" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB126" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC126" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE126">
+        <f>DY126/DZ126-1</f>
+        <v/>
+      </c>
+      <c r="EF126">
+        <f>EA126/DZ126-1</f>
+        <v/>
+      </c>
+      <c r="EH126" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EK126" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EN126">
+        <f>EH126/EI126-1</f>
+        <v/>
+      </c>
+      <c r="EO126">
+        <f>EJ126/EI126-1</f>
+        <v/>
+      </c>
+      <c r="EQ126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER126" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU126" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW126">
+        <f>EQ126/ER126-1</f>
+        <v/>
+      </c>
+      <c r="EX126">
+        <f>ES126/ER126-1</f>
+        <v/>
+      </c>
+      <c r="EZ126" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA126" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC126" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD126" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF126">
+        <f>EZ126/FA126-1</f>
+        <v/>
+      </c>
+      <c r="FG126">
+        <f>FB126/FA126-1</f>
+        <v/>
+      </c>
+      <c r="FI126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FJ126" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FM126" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO126">
+        <f>FI126/FJ126-1</f>
+        <v/>
+      </c>
+      <c r="FP126">
+        <f>FK126/FJ126-1</f>
+        <v/>
+      </c>
+      <c r="FR126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FS126" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FV126" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX126">
+        <f>FR126/FS126-1</f>
+        <v/>
+      </c>
+      <c r="FY126">
+        <f>FT126/FS126-1</f>
+        <v/>
+      </c>
+      <c r="GA126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GB126" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GE126" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG126">
+        <f>GA126/GB126-1</f>
+        <v/>
+      </c>
+      <c r="GH126">
+        <f>GC126/GB126-1</f>
+        <v/>
+      </c>
+      <c r="GJ126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GK126" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GN126" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP126">
+        <f>GJ126/GK126-1</f>
+        <v/>
+      </c>
+      <c r="GQ126">
+        <f>GL126/GK126-1</f>
+        <v/>
+      </c>
+      <c r="GS126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GT126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GV126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GW126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GY126">
+        <f>GS126/GT126-1</f>
+        <v/>
+      </c>
+      <c r="GZ126">
+        <f>GU126/GT126-1</f>
+        <v/>
+      </c>
+      <c r="HB126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HC126" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HF126" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH126">
+        <f>HB126/HC126-1</f>
+        <v/>
+      </c>
+      <c r="HI126">
+        <f>HD126/HC126-1</f>
+        <v/>
+      </c>
+      <c r="HK126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HL126" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HO126" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ126">
+        <f>HK126/HL126-1</f>
+        <v/>
+      </c>
+      <c r="HR126">
+        <f>HM126/HL126-1</f>
+        <v/>
+      </c>
+      <c r="HT126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HU126" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HX126" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ126">
+        <f>HT126/HU126-1</f>
+        <v/>
+      </c>
+      <c r="IA126">
+        <f>HV126/HU126-1</f>
+        <v/>
+      </c>
+      <c r="IC126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ID126" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IG126" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II126">
+        <f>IC126/ID126-1</f>
+        <v/>
+      </c>
+      <c r="IJ126">
+        <f>IE126/ID126-1</f>
+        <v/>
+      </c>
+      <c r="IL126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IM126" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO126" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IP126" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR126">
+        <f>IL126/IM126-1</f>
+        <v/>
+      </c>
+      <c r="IS126">
+        <f>IN126/IM126-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS126"/>
+  <dimension ref="A1:IS127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -76842,6 +76842,737 @@
         <v/>
       </c>
     </row>
+    <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>23 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D127" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I127">
+        <f>C127/D127-1</f>
+        <v/>
+      </c>
+      <c r="J127">
+        <f>E127/D127-1</f>
+        <v/>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R127">
+        <f>L127/M127-1</f>
+        <v/>
+      </c>
+      <c r="S127">
+        <f>N127/M127-1</f>
+        <v/>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V127" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA127">
+        <f>U127/V127-1</f>
+        <v/>
+      </c>
+      <c r="AB127">
+        <f>W127/V127-1</f>
+        <v/>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE127" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ127">
+        <f>AD127/AE127-1</f>
+        <v/>
+      </c>
+      <c r="AK127">
+        <f>AF127/AE127-1</f>
+        <v/>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN127" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS127">
+        <f>AM127/AN127-1</f>
+        <v/>
+      </c>
+      <c r="AT127">
+        <f>AO127/AN127-1</f>
+        <v/>
+      </c>
+      <c r="AV127" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW127" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB127">
+        <f>AV127/AW127-1</f>
+        <v/>
+      </c>
+      <c r="BC127">
+        <f>AX127/AW127-1</f>
+        <v/>
+      </c>
+      <c r="BE127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF127" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI127" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK127">
+        <f>BE127/BF127-1</f>
+        <v/>
+      </c>
+      <c r="BL127">
+        <f>BG127/BF127-1</f>
+        <v/>
+      </c>
+      <c r="BN127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO127" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR127" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT127">
+        <f>BN127/BO127-1</f>
+        <v/>
+      </c>
+      <c r="BU127">
+        <f>BP127/BO127-1</f>
+        <v/>
+      </c>
+      <c r="BW127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX127" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA127" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC127">
+        <f>BW127/BX127-1</f>
+        <v/>
+      </c>
+      <c r="CD127">
+        <f>BY127/BX127-1</f>
+        <v/>
+      </c>
+      <c r="CF127" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG127" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI127" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ127" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL127">
+        <f>CF127/CG127-1</f>
+        <v/>
+      </c>
+      <c r="CM127">
+        <f>CH127/CG127-1</f>
+        <v/>
+      </c>
+      <c r="CO127" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP127" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR127" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS127" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU127">
+        <f>CO127/CP127-1</f>
+        <v/>
+      </c>
+      <c r="CV127">
+        <f>CQ127/CP127-1</f>
+        <v/>
+      </c>
+      <c r="CX127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY127" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB127" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD127">
+        <f>CX127/CY127-1</f>
+        <v/>
+      </c>
+      <c r="DE127">
+        <f>CZ127/CY127-1</f>
+        <v/>
+      </c>
+      <c r="DG127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH127" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK127" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM127">
+        <f>DG127/DH127-1</f>
+        <v/>
+      </c>
+      <c r="DN127">
+        <f>DI127/DH127-1</f>
+        <v/>
+      </c>
+      <c r="DP127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ127" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT127" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV127">
+        <f>DP127/DQ127-1</f>
+        <v/>
+      </c>
+      <c r="DW127">
+        <f>DR127/DQ127-1</f>
+        <v/>
+      </c>
+      <c r="DY127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ127" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC127" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE127">
+        <f>DY127/DZ127-1</f>
+        <v/>
+      </c>
+      <c r="EF127">
+        <f>EA127/DZ127-1</f>
+        <v/>
+      </c>
+      <c r="EH127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI127" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL127" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN127">
+        <f>EH127/EI127-1</f>
+        <v/>
+      </c>
+      <c r="EO127">
+        <f>EJ127/EI127-1</f>
+        <v/>
+      </c>
+      <c r="EQ127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER127" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU127" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW127">
+        <f>EQ127/ER127-1</f>
+        <v/>
+      </c>
+      <c r="EX127">
+        <f>ES127/ER127-1</f>
+        <v/>
+      </c>
+      <c r="EZ127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FC127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FF127">
+        <f>EZ127/FA127-1</f>
+        <v/>
+      </c>
+      <c r="FG127">
+        <f>FB127/FA127-1</f>
+        <v/>
+      </c>
+      <c r="FI127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FJ127" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FM127" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO127">
+        <f>FI127/FJ127-1</f>
+        <v/>
+      </c>
+      <c r="FP127">
+        <f>FK127/FJ127-1</f>
+        <v/>
+      </c>
+      <c r="FR127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FS127" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FV127" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX127">
+        <f>FR127/FS127-1</f>
+        <v/>
+      </c>
+      <c r="FY127">
+        <f>FT127/FS127-1</f>
+        <v/>
+      </c>
+      <c r="GA127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GB127" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GE127" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG127">
+        <f>GA127/GB127-1</f>
+        <v/>
+      </c>
+      <c r="GH127">
+        <f>GC127/GB127-1</f>
+        <v/>
+      </c>
+      <c r="GJ127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GK127" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GN127" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP127">
+        <f>GJ127/GK127-1</f>
+        <v/>
+      </c>
+      <c r="GQ127">
+        <f>GL127/GK127-1</f>
+        <v/>
+      </c>
+      <c r="GS127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GT127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GV127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GW127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GY127">
+        <f>GS127/GT127-1</f>
+        <v/>
+      </c>
+      <c r="GZ127">
+        <f>GU127/GT127-1</f>
+        <v/>
+      </c>
+      <c r="HB127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HC127" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HF127" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH127">
+        <f>HB127/HC127-1</f>
+        <v/>
+      </c>
+      <c r="HI127">
+        <f>HD127/HC127-1</f>
+        <v/>
+      </c>
+      <c r="HK127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HL127" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HO127" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ127">
+        <f>HK127/HL127-1</f>
+        <v/>
+      </c>
+      <c r="HR127">
+        <f>HM127/HL127-1</f>
+        <v/>
+      </c>
+      <c r="HT127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HU127" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HX127" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ127">
+        <f>HT127/HU127-1</f>
+        <v/>
+      </c>
+      <c r="IA127">
+        <f>HV127/HU127-1</f>
+        <v/>
+      </c>
+      <c r="IC127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ID127" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IG127" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II127">
+        <f>IC127/ID127-1</f>
+        <v/>
+      </c>
+      <c r="IJ127">
+        <f>IE127/ID127-1</f>
+        <v/>
+      </c>
+      <c r="IL127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IM127" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IO127" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IP127" t="inlineStr">
+        <is>
+          <t>sm-l715uzsaxaa</t>
+        </is>
+      </c>
+      <c r="IR127">
+        <f>IL127/IM127-1</f>
+        <v/>
+      </c>
+      <c r="IS127">
+        <f>IN127/IM127-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS127"/>
+  <dimension ref="A1:IS128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -77573,6 +77573,741 @@
         <v/>
       </c>
     </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>23 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I128">
+        <f>C128/D128-1</f>
+        <v/>
+      </c>
+      <c r="J128">
+        <f>E128/D128-1</f>
+        <v/>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M128" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R128">
+        <f>L128/M128-1</f>
+        <v/>
+      </c>
+      <c r="S128">
+        <f>N128/M128-1</f>
+        <v/>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V128" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA128">
+        <f>U128/V128-1</f>
+        <v/>
+      </c>
+      <c r="AB128">
+        <f>W128/V128-1</f>
+        <v/>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE128" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ128">
+        <f>AD128/AE128-1</f>
+        <v/>
+      </c>
+      <c r="AK128">
+        <f>AF128/AE128-1</f>
+        <v/>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN128" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS128">
+        <f>AM128/AN128-1</f>
+        <v/>
+      </c>
+      <c r="AT128">
+        <f>AO128/AN128-1</f>
+        <v/>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW128" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB128">
+        <f>AV128/AW128-1</f>
+        <v/>
+      </c>
+      <c r="BC128">
+        <f>AX128/AW128-1</f>
+        <v/>
+      </c>
+      <c r="BE128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF128" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI128" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK128">
+        <f>BE128/BF128-1</f>
+        <v/>
+      </c>
+      <c r="BL128">
+        <f>BG128/BF128-1</f>
+        <v/>
+      </c>
+      <c r="BN128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO128" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR128" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT128">
+        <f>BN128/BO128-1</f>
+        <v/>
+      </c>
+      <c r="BU128">
+        <f>BP128/BO128-1</f>
+        <v/>
+      </c>
+      <c r="BW128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX128" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA128" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC128">
+        <f>BW128/BX128-1</f>
+        <v/>
+      </c>
+      <c r="CD128">
+        <f>BY128/BX128-1</f>
+        <v/>
+      </c>
+      <c r="CF128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG128" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ128" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL128">
+        <f>CF128/CG128-1</f>
+        <v/>
+      </c>
+      <c r="CM128">
+        <f>CH128/CG128-1</f>
+        <v/>
+      </c>
+      <c r="CO128" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP128" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR128" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS128" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU128">
+        <f>CO128/CP128-1</f>
+        <v/>
+      </c>
+      <c r="CV128">
+        <f>CQ128/CP128-1</f>
+        <v/>
+      </c>
+      <c r="CX128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY128" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB128" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD128">
+        <f>CX128/CY128-1</f>
+        <v/>
+      </c>
+      <c r="DE128">
+        <f>CZ128/CY128-1</f>
+        <v/>
+      </c>
+      <c r="DG128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH128" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK128" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM128">
+        <f>DG128/DH128-1</f>
+        <v/>
+      </c>
+      <c r="DN128">
+        <f>DI128/DH128-1</f>
+        <v/>
+      </c>
+      <c r="DP128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ128" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT128" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV128">
+        <f>DP128/DQ128-1</f>
+        <v/>
+      </c>
+      <c r="DW128">
+        <f>DR128/DQ128-1</f>
+        <v/>
+      </c>
+      <c r="DY128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ128" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC128" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE128">
+        <f>DY128/DZ128-1</f>
+        <v/>
+      </c>
+      <c r="EF128">
+        <f>EA128/DZ128-1</f>
+        <v/>
+      </c>
+      <c r="EH128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI128" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL128" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN128">
+        <f>EH128/EI128-1</f>
+        <v/>
+      </c>
+      <c r="EO128">
+        <f>EJ128/EI128-1</f>
+        <v/>
+      </c>
+      <c r="EQ128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER128" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU128" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW128">
+        <f>EQ128/ER128-1</f>
+        <v/>
+      </c>
+      <c r="EX128">
+        <f>ES128/ER128-1</f>
+        <v/>
+      </c>
+      <c r="EZ128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA128" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD128" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF128">
+        <f>EZ128/FA128-1</f>
+        <v/>
+      </c>
+      <c r="FG128">
+        <f>FB128/FA128-1</f>
+        <v/>
+      </c>
+      <c r="FI128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FJ128" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FM128" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO128">
+        <f>FI128/FJ128-1</f>
+        <v/>
+      </c>
+      <c r="FP128">
+        <f>FK128/FJ128-1</f>
+        <v/>
+      </c>
+      <c r="FR128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FS128" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FV128" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX128">
+        <f>FR128/FS128-1</f>
+        <v/>
+      </c>
+      <c r="FY128">
+        <f>FT128/FS128-1</f>
+        <v/>
+      </c>
+      <c r="GA128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GB128" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GE128" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG128">
+        <f>GA128/GB128-1</f>
+        <v/>
+      </c>
+      <c r="GH128">
+        <f>GC128/GB128-1</f>
+        <v/>
+      </c>
+      <c r="GJ128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GK128" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GN128" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP128">
+        <f>GJ128/GK128-1</f>
+        <v/>
+      </c>
+      <c r="GQ128">
+        <f>GL128/GK128-1</f>
+        <v/>
+      </c>
+      <c r="GS128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GT128" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GW128" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY128">
+        <f>GS128/GT128-1</f>
+        <v/>
+      </c>
+      <c r="GZ128">
+        <f>GU128/GT128-1</f>
+        <v/>
+      </c>
+      <c r="HB128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HC128" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HF128" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH128">
+        <f>HB128/HC128-1</f>
+        <v/>
+      </c>
+      <c r="HI128">
+        <f>HD128/HC128-1</f>
+        <v/>
+      </c>
+      <c r="HK128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HL128" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HO128" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ128">
+        <f>HK128/HL128-1</f>
+        <v/>
+      </c>
+      <c r="HR128">
+        <f>HM128/HL128-1</f>
+        <v/>
+      </c>
+      <c r="HT128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HU128" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HX128" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ128">
+        <f>HT128/HU128-1</f>
+        <v/>
+      </c>
+      <c r="IA128">
+        <f>HV128/HU128-1</f>
+        <v/>
+      </c>
+      <c r="IC128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ID128" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IG128" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II128">
+        <f>IC128/ID128-1</f>
+        <v/>
+      </c>
+      <c r="IJ128">
+        <f>IE128/ID128-1</f>
+        <v/>
+      </c>
+      <c r="IL128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IM128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IP128" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR128">
+        <f>IL128/IM128-1</f>
+        <v/>
+      </c>
+      <c r="IS128">
+        <f>IN128/IM128-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS128"/>
+  <dimension ref="A1:IS129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -78308,6 +78308,737 @@
         <v/>
       </c>
     </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>23 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I129">
+        <f>C129/D129-1</f>
+        <v/>
+      </c>
+      <c r="J129">
+        <f>E129/D129-1</f>
+        <v/>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R129">
+        <f>L129/M129-1</f>
+        <v/>
+      </c>
+      <c r="S129">
+        <f>N129/M129-1</f>
+        <v/>
+      </c>
+      <c r="U129" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V129" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA129">
+        <f>U129/V129-1</f>
+        <v/>
+      </c>
+      <c r="AB129">
+        <f>W129/V129-1</f>
+        <v/>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE129" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ129">
+        <f>AD129/AE129-1</f>
+        <v/>
+      </c>
+      <c r="AK129">
+        <f>AF129/AE129-1</f>
+        <v/>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN129" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS129">
+        <f>AM129/AN129-1</f>
+        <v/>
+      </c>
+      <c r="AT129">
+        <f>AO129/AN129-1</f>
+        <v/>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW129" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB129">
+        <f>AV129/AW129-1</f>
+        <v/>
+      </c>
+      <c r="BC129">
+        <f>AX129/AW129-1</f>
+        <v/>
+      </c>
+      <c r="BE129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF129" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI129" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK129">
+        <f>BE129/BF129-1</f>
+        <v/>
+      </c>
+      <c r="BL129">
+        <f>BG129/BF129-1</f>
+        <v/>
+      </c>
+      <c r="BN129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO129" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR129" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT129">
+        <f>BN129/BO129-1</f>
+        <v/>
+      </c>
+      <c r="BU129">
+        <f>BP129/BO129-1</f>
+        <v/>
+      </c>
+      <c r="BW129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX129" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA129" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC129">
+        <f>BW129/BX129-1</f>
+        <v/>
+      </c>
+      <c r="CD129">
+        <f>BY129/BX129-1</f>
+        <v/>
+      </c>
+      <c r="CF129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG129" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ129" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL129">
+        <f>CF129/CG129-1</f>
+        <v/>
+      </c>
+      <c r="CM129">
+        <f>CH129/CG129-1</f>
+        <v/>
+      </c>
+      <c r="CO129" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP129" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR129" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS129" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU129">
+        <f>CO129/CP129-1</f>
+        <v/>
+      </c>
+      <c r="CV129">
+        <f>CQ129/CP129-1</f>
+        <v/>
+      </c>
+      <c r="CX129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY129" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB129" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD129">
+        <f>CX129/CY129-1</f>
+        <v/>
+      </c>
+      <c r="DE129">
+        <f>CZ129/CY129-1</f>
+        <v/>
+      </c>
+      <c r="DG129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH129" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK129" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM129">
+        <f>DG129/DH129-1</f>
+        <v/>
+      </c>
+      <c r="DN129">
+        <f>DI129/DH129-1</f>
+        <v/>
+      </c>
+      <c r="DP129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ129" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT129" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV129">
+        <f>DP129/DQ129-1</f>
+        <v/>
+      </c>
+      <c r="DW129">
+        <f>DR129/DQ129-1</f>
+        <v/>
+      </c>
+      <c r="DY129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ129" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC129" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE129">
+        <f>DY129/DZ129-1</f>
+        <v/>
+      </c>
+      <c r="EF129">
+        <f>EA129/DZ129-1</f>
+        <v/>
+      </c>
+      <c r="EH129" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI129" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK129" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL129" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN129">
+        <f>EH129/EI129-1</f>
+        <v/>
+      </c>
+      <c r="EO129">
+        <f>EJ129/EI129-1</f>
+        <v/>
+      </c>
+      <c r="EQ129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER129" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU129" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW129">
+        <f>EQ129/ER129-1</f>
+        <v/>
+      </c>
+      <c r="EX129">
+        <f>ES129/ER129-1</f>
+        <v/>
+      </c>
+      <c r="EZ129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA129" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD129" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF129">
+        <f>EZ129/FA129-1</f>
+        <v/>
+      </c>
+      <c r="FG129">
+        <f>FB129/FA129-1</f>
+        <v/>
+      </c>
+      <c r="FI129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FJ129" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FM129" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO129">
+        <f>FI129/FJ129-1</f>
+        <v/>
+      </c>
+      <c r="FP129">
+        <f>FK129/FJ129-1</f>
+        <v/>
+      </c>
+      <c r="FR129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FS129" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FV129" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX129">
+        <f>FR129/FS129-1</f>
+        <v/>
+      </c>
+      <c r="FY129">
+        <f>FT129/FS129-1</f>
+        <v/>
+      </c>
+      <c r="GA129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GB129" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GE129" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG129">
+        <f>GA129/GB129-1</f>
+        <v/>
+      </c>
+      <c r="GH129">
+        <f>GC129/GB129-1</f>
+        <v/>
+      </c>
+      <c r="GJ129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GK129" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GN129" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP129">
+        <f>GJ129/GK129-1</f>
+        <v/>
+      </c>
+      <c r="GQ129">
+        <f>GL129/GK129-1</f>
+        <v/>
+      </c>
+      <c r="GS129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GT129" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GW129" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY129">
+        <f>GS129/GT129-1</f>
+        <v/>
+      </c>
+      <c r="GZ129">
+        <f>GU129/GT129-1</f>
+        <v/>
+      </c>
+      <c r="HB129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HC129" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HF129" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH129">
+        <f>HB129/HC129-1</f>
+        <v/>
+      </c>
+      <c r="HI129">
+        <f>HD129/HC129-1</f>
+        <v/>
+      </c>
+      <c r="HK129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HL129" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HO129" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ129">
+        <f>HK129/HL129-1</f>
+        <v/>
+      </c>
+      <c r="HR129">
+        <f>HM129/HL129-1</f>
+        <v/>
+      </c>
+      <c r="HT129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HU129" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HX129" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ129">
+        <f>HT129/HU129-1</f>
+        <v/>
+      </c>
+      <c r="IA129">
+        <f>HV129/HU129-1</f>
+        <v/>
+      </c>
+      <c r="IC129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ID129" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IG129" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II129">
+        <f>IC129/ID129-1</f>
+        <v/>
+      </c>
+      <c r="IJ129">
+        <f>IE129/ID129-1</f>
+        <v/>
+      </c>
+      <c r="IL129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IM129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IP129" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR129">
+        <f>IL129/IM129-1</f>
+        <v/>
+      </c>
+      <c r="IS129">
+        <f>IN129/IM129-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS129"/>
+  <dimension ref="A1:IS130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -79039,6 +79039,749 @@
         <v/>
       </c>
     </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>23 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I130">
+        <f>C130/D130-1</f>
+        <v/>
+      </c>
+      <c r="J130">
+        <f>E130/D130-1</f>
+        <v/>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M130" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R130">
+        <f>L130/M130-1</f>
+        <v/>
+      </c>
+      <c r="S130">
+        <f>N130/M130-1</f>
+        <v/>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V130" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA130">
+        <f>U130/V130-1</f>
+        <v/>
+      </c>
+      <c r="AB130">
+        <f>W130/V130-1</f>
+        <v/>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE130" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ130">
+        <f>AD130/AE130-1</f>
+        <v/>
+      </c>
+      <c r="AK130">
+        <f>AF130/AE130-1</f>
+        <v/>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN130" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS130">
+        <f>AM130/AN130-1</f>
+        <v/>
+      </c>
+      <c r="AT130">
+        <f>AO130/AN130-1</f>
+        <v/>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BB130">
+        <f>AV130/AW130-1</f>
+        <v/>
+      </c>
+      <c r="BC130">
+        <f>AX130/AW130-1</f>
+        <v/>
+      </c>
+      <c r="BE130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF130" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI130" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK130">
+        <f>BE130/BF130-1</f>
+        <v/>
+      </c>
+      <c r="BL130">
+        <f>BG130/BF130-1</f>
+        <v/>
+      </c>
+      <c r="BN130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO130" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR130" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT130">
+        <f>BN130/BO130-1</f>
+        <v/>
+      </c>
+      <c r="BU130">
+        <f>BP130/BO130-1</f>
+        <v/>
+      </c>
+      <c r="BW130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BZ130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC130">
+        <f>BW130/BX130-1</f>
+        <v/>
+      </c>
+      <c r="CD130">
+        <f>BY130/BX130-1</f>
+        <v/>
+      </c>
+      <c r="CF130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG130" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ130" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL130">
+        <f>CF130/CG130-1</f>
+        <v/>
+      </c>
+      <c r="CM130">
+        <f>CH130/CG130-1</f>
+        <v/>
+      </c>
+      <c r="CO130" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP130" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR130" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS130" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU130">
+        <f>CO130/CP130-1</f>
+        <v/>
+      </c>
+      <c r="CV130">
+        <f>CQ130/CP130-1</f>
+        <v/>
+      </c>
+      <c r="CX130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DA130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DD130">
+        <f>CX130/CY130-1</f>
+        <v/>
+      </c>
+      <c r="DE130">
+        <f>CZ130/CY130-1</f>
+        <v/>
+      </c>
+      <c r="DG130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH130" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK130" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM130">
+        <f>DG130/DH130-1</f>
+        <v/>
+      </c>
+      <c r="DN130">
+        <f>DI130/DH130-1</f>
+        <v/>
+      </c>
+      <c r="DP130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ130" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT130" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV130">
+        <f>DP130/DQ130-1</f>
+        <v/>
+      </c>
+      <c r="DW130">
+        <f>DR130/DQ130-1</f>
+        <v/>
+      </c>
+      <c r="DY130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ130" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC130" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE130">
+        <f>DY130/DZ130-1</f>
+        <v/>
+      </c>
+      <c r="EF130">
+        <f>EA130/DZ130-1</f>
+        <v/>
+      </c>
+      <c r="EH130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI130" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL130" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN130">
+        <f>EH130/EI130-1</f>
+        <v/>
+      </c>
+      <c r="EO130">
+        <f>EJ130/EI130-1</f>
+        <v/>
+      </c>
+      <c r="EQ130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER130" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU130" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW130">
+        <f>EQ130/ER130-1</f>
+        <v/>
+      </c>
+      <c r="EX130">
+        <f>ES130/ER130-1</f>
+        <v/>
+      </c>
+      <c r="EZ130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA130" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD130" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF130">
+        <f>EZ130/FA130-1</f>
+        <v/>
+      </c>
+      <c r="FG130">
+        <f>FB130/FA130-1</f>
+        <v/>
+      </c>
+      <c r="FI130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FJ130" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FM130" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO130">
+        <f>FI130/FJ130-1</f>
+        <v/>
+      </c>
+      <c r="FP130">
+        <f>FK130/FJ130-1</f>
+        <v/>
+      </c>
+      <c r="FR130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FS130" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FV130" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX130">
+        <f>FR130/FS130-1</f>
+        <v/>
+      </c>
+      <c r="FY130">
+        <f>FT130/FS130-1</f>
+        <v/>
+      </c>
+      <c r="GA130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GB130" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GE130" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG130">
+        <f>GA130/GB130-1</f>
+        <v/>
+      </c>
+      <c r="GH130">
+        <f>GC130/GB130-1</f>
+        <v/>
+      </c>
+      <c r="GJ130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GK130" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GN130" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP130">
+        <f>GJ130/GK130-1</f>
+        <v/>
+      </c>
+      <c r="GQ130">
+        <f>GL130/GK130-1</f>
+        <v/>
+      </c>
+      <c r="GS130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GT130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GV130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GW130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GY130">
+        <f>GS130/GT130-1</f>
+        <v/>
+      </c>
+      <c r="GZ130">
+        <f>GU130/GT130-1</f>
+        <v/>
+      </c>
+      <c r="HB130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HC130" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HF130" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH130">
+        <f>HB130/HC130-1</f>
+        <v/>
+      </c>
+      <c r="HI130">
+        <f>HD130/HC130-1</f>
+        <v/>
+      </c>
+      <c r="HK130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HL130" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HO130" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ130">
+        <f>HK130/HL130-1</f>
+        <v/>
+      </c>
+      <c r="HR130">
+        <f>HM130/HL130-1</f>
+        <v/>
+      </c>
+      <c r="HT130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HU130" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HX130" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ130">
+        <f>HT130/HU130-1</f>
+        <v/>
+      </c>
+      <c r="IA130">
+        <f>HV130/HU130-1</f>
+        <v/>
+      </c>
+      <c r="IC130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ID130" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IG130" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II130">
+        <f>IC130/ID130-1</f>
+        <v/>
+      </c>
+      <c r="IJ130">
+        <f>IE130/ID130-1</f>
+        <v/>
+      </c>
+      <c r="IL130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IM130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IP130" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR130">
+        <f>IL130/IM130-1</f>
+        <v/>
+      </c>
+      <c r="IS130">
+        <f>IN130/IM130-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS130"/>
+  <dimension ref="A1:IS131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -79782,6 +79782,741 @@
         <v/>
       </c>
     </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>24 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I131">
+        <f>C131/D131-1</f>
+        <v/>
+      </c>
+      <c r="J131">
+        <f>E131/D131-1</f>
+        <v/>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M131" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R131">
+        <f>L131/M131-1</f>
+        <v/>
+      </c>
+      <c r="S131">
+        <f>N131/M131-1</f>
+        <v/>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V131" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA131">
+        <f>U131/V131-1</f>
+        <v/>
+      </c>
+      <c r="AB131">
+        <f>W131/V131-1</f>
+        <v/>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE131" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ131">
+        <f>AD131/AE131-1</f>
+        <v/>
+      </c>
+      <c r="AK131">
+        <f>AF131/AE131-1</f>
+        <v/>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN131" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS131">
+        <f>AM131/AN131-1</f>
+        <v/>
+      </c>
+      <c r="AT131">
+        <f>AO131/AN131-1</f>
+        <v/>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW131" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB131">
+        <f>AV131/AW131-1</f>
+        <v/>
+      </c>
+      <c r="BC131">
+        <f>AX131/AW131-1</f>
+        <v/>
+      </c>
+      <c r="BE131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF131" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI131" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK131">
+        <f>BE131/BF131-1</f>
+        <v/>
+      </c>
+      <c r="BL131">
+        <f>BG131/BF131-1</f>
+        <v/>
+      </c>
+      <c r="BN131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO131" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR131" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT131">
+        <f>BN131/BO131-1</f>
+        <v/>
+      </c>
+      <c r="BU131">
+        <f>BP131/BO131-1</f>
+        <v/>
+      </c>
+      <c r="BW131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX131" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA131" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC131">
+        <f>BW131/BX131-1</f>
+        <v/>
+      </c>
+      <c r="CD131">
+        <f>BY131/BX131-1</f>
+        <v/>
+      </c>
+      <c r="CF131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG131" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ131" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL131">
+        <f>CF131/CG131-1</f>
+        <v/>
+      </c>
+      <c r="CM131">
+        <f>CH131/CG131-1</f>
+        <v/>
+      </c>
+      <c r="CO131" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP131" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR131" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS131" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU131">
+        <f>CO131/CP131-1</f>
+        <v/>
+      </c>
+      <c r="CV131">
+        <f>CQ131/CP131-1</f>
+        <v/>
+      </c>
+      <c r="CX131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY131" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB131" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD131">
+        <f>CX131/CY131-1</f>
+        <v/>
+      </c>
+      <c r="DE131">
+        <f>CZ131/CY131-1</f>
+        <v/>
+      </c>
+      <c r="DG131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH131" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK131" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM131">
+        <f>DG131/DH131-1</f>
+        <v/>
+      </c>
+      <c r="DN131">
+        <f>DI131/DH131-1</f>
+        <v/>
+      </c>
+      <c r="DP131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ131" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT131" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV131">
+        <f>DP131/DQ131-1</f>
+        <v/>
+      </c>
+      <c r="DW131">
+        <f>DR131/DQ131-1</f>
+        <v/>
+      </c>
+      <c r="DY131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ131" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC131" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE131">
+        <f>DY131/DZ131-1</f>
+        <v/>
+      </c>
+      <c r="EF131">
+        <f>EA131/DZ131-1</f>
+        <v/>
+      </c>
+      <c r="EH131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI131" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL131" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN131">
+        <f>EH131/EI131-1</f>
+        <v/>
+      </c>
+      <c r="EO131">
+        <f>EJ131/EI131-1</f>
+        <v/>
+      </c>
+      <c r="EQ131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER131" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU131" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW131">
+        <f>EQ131/ER131-1</f>
+        <v/>
+      </c>
+      <c r="EX131">
+        <f>ES131/ER131-1</f>
+        <v/>
+      </c>
+      <c r="EZ131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA131" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD131" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF131">
+        <f>EZ131/FA131-1</f>
+        <v/>
+      </c>
+      <c r="FG131">
+        <f>FB131/FA131-1</f>
+        <v/>
+      </c>
+      <c r="FI131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FJ131" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FM131" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO131">
+        <f>FI131/FJ131-1</f>
+        <v/>
+      </c>
+      <c r="FP131">
+        <f>FK131/FJ131-1</f>
+        <v/>
+      </c>
+      <c r="FR131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FS131" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FV131" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX131">
+        <f>FR131/FS131-1</f>
+        <v/>
+      </c>
+      <c r="FY131">
+        <f>FT131/FS131-1</f>
+        <v/>
+      </c>
+      <c r="GA131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GB131" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GE131" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG131">
+        <f>GA131/GB131-1</f>
+        <v/>
+      </c>
+      <c r="GH131">
+        <f>GC131/GB131-1</f>
+        <v/>
+      </c>
+      <c r="GJ131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GK131" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GN131" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP131">
+        <f>GJ131/GK131-1</f>
+        <v/>
+      </c>
+      <c r="GQ131">
+        <f>GL131/GK131-1</f>
+        <v/>
+      </c>
+      <c r="GS131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GT131" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GW131" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY131">
+        <f>GS131/GT131-1</f>
+        <v/>
+      </c>
+      <c r="GZ131">
+        <f>GU131/GT131-1</f>
+        <v/>
+      </c>
+      <c r="HB131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HC131" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HF131" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH131">
+        <f>HB131/HC131-1</f>
+        <v/>
+      </c>
+      <c r="HI131">
+        <f>HD131/HC131-1</f>
+        <v/>
+      </c>
+      <c r="HK131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HL131" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HO131" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ131">
+        <f>HK131/HL131-1</f>
+        <v/>
+      </c>
+      <c r="HR131">
+        <f>HM131/HL131-1</f>
+        <v/>
+      </c>
+      <c r="HT131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HU131" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HX131" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ131">
+        <f>HT131/HU131-1</f>
+        <v/>
+      </c>
+      <c r="IA131">
+        <f>HV131/HU131-1</f>
+        <v/>
+      </c>
+      <c r="IC131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ID131" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IG131" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II131">
+        <f>IC131/ID131-1</f>
+        <v/>
+      </c>
+      <c r="IJ131">
+        <f>IE131/ID131-1</f>
+        <v/>
+      </c>
+      <c r="IL131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IM131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IP131" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR131">
+        <f>IL131/IM131-1</f>
+        <v/>
+      </c>
+      <c r="IS131">
+        <f>IN131/IM131-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS131"/>
+  <dimension ref="A1:IS132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -80517,6 +80517,691 @@
         <v/>
       </c>
     </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>24 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I132">
+        <f>C132/D132-1</f>
+        <v/>
+      </c>
+      <c r="J132">
+        <f>E132/D132-1</f>
+        <v/>
+      </c>
+      <c r="L132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R132">
+        <f>L132/M132-1</f>
+        <v/>
+      </c>
+      <c r="S132">
+        <f>N132/M132-1</f>
+        <v/>
+      </c>
+      <c r="U132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA132">
+        <f>U132/V132-1</f>
+        <v/>
+      </c>
+      <c r="AB132">
+        <f>W132/V132-1</f>
+        <v/>
+      </c>
+      <c r="AD132" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE132" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ132">
+        <f>AD132/AE132-1</f>
+        <v/>
+      </c>
+      <c r="AK132">
+        <f>AF132/AE132-1</f>
+        <v/>
+      </c>
+      <c r="AM132" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN132" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS132">
+        <f>AM132/AN132-1</f>
+        <v/>
+      </c>
+      <c r="AT132">
+        <f>AO132/AN132-1</f>
+        <v/>
+      </c>
+      <c r="AV132" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW132" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB132">
+        <f>AV132/AW132-1</f>
+        <v/>
+      </c>
+      <c r="BC132">
+        <f>AX132/AW132-1</f>
+        <v/>
+      </c>
+      <c r="BE132" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF132" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH132" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI132" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK132">
+        <f>BE132/BF132-1</f>
+        <v/>
+      </c>
+      <c r="BL132">
+        <f>BG132/BF132-1</f>
+        <v/>
+      </c>
+      <c r="BN132" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO132" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ132" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR132" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT132">
+        <f>BN132/BO132-1</f>
+        <v/>
+      </c>
+      <c r="BU132">
+        <f>BP132/BO132-1</f>
+        <v/>
+      </c>
+      <c r="BW132" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX132" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ132" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA132" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC132">
+        <f>BW132/BX132-1</f>
+        <v/>
+      </c>
+      <c r="CD132">
+        <f>BY132/BX132-1</f>
+        <v/>
+      </c>
+      <c r="CF132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI132" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ132" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL132">
+        <f>CF132/CG132-1</f>
+        <v/>
+      </c>
+      <c r="CM132">
+        <f>CH132/CG132-1</f>
+        <v/>
+      </c>
+      <c r="CO132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR132" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS132" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU132">
+        <f>CO132/CP132-1</f>
+        <v/>
+      </c>
+      <c r="CV132">
+        <f>CQ132/CP132-1</f>
+        <v/>
+      </c>
+      <c r="CX132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY132" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA132" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB132" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD132">
+        <f>CX132/CY132-1</f>
+        <v/>
+      </c>
+      <c r="DE132">
+        <f>CZ132/CY132-1</f>
+        <v/>
+      </c>
+      <c r="DG132" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH132" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ132" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK132" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM132">
+        <f>DG132/DH132-1</f>
+        <v/>
+      </c>
+      <c r="DN132">
+        <f>DI132/DH132-1</f>
+        <v/>
+      </c>
+      <c r="DP132" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ132" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS132" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT132" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV132">
+        <f>DP132/DQ132-1</f>
+        <v/>
+      </c>
+      <c r="DW132">
+        <f>DR132/DQ132-1</f>
+        <v/>
+      </c>
+      <c r="DY132" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ132" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB132" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC132" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE132">
+        <f>DY132/DZ132-1</f>
+        <v/>
+      </c>
+      <c r="EF132">
+        <f>EA132/DZ132-1</f>
+        <v/>
+      </c>
+      <c r="EH132" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI132" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK132" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL132" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN132">
+        <f>EH132/EI132-1</f>
+        <v/>
+      </c>
+      <c r="EO132">
+        <f>EJ132/EI132-1</f>
+        <v/>
+      </c>
+      <c r="EQ132" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER132" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET132" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU132" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW132">
+        <f>EQ132/ER132-1</f>
+        <v/>
+      </c>
+      <c r="EX132">
+        <f>ES132/ER132-1</f>
+        <v/>
+      </c>
+      <c r="EZ132" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA132" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC132" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD132" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF132">
+        <f>EZ132/FA132-1</f>
+        <v/>
+      </c>
+      <c r="FG132">
+        <f>FB132/FA132-1</f>
+        <v/>
+      </c>
+      <c r="FI132" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ132" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL132" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM132" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO132">
+        <f>FI132/FJ132-1</f>
+        <v/>
+      </c>
+      <c r="FP132">
+        <f>FK132/FJ132-1</f>
+        <v/>
+      </c>
+      <c r="FR132" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS132" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU132" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV132" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX132">
+        <f>FR132/FS132-1</f>
+        <v/>
+      </c>
+      <c r="FY132">
+        <f>FT132/FS132-1</f>
+        <v/>
+      </c>
+      <c r="GA132" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB132" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD132" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE132" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG132">
+        <f>GA132/GB132-1</f>
+        <v/>
+      </c>
+      <c r="GH132">
+        <f>GC132/GB132-1</f>
+        <v/>
+      </c>
+      <c r="GJ132" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK132" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GM132" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN132" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GP132">
+        <f>GJ132/GK132-1</f>
+        <v/>
+      </c>
+      <c r="GQ132">
+        <f>GL132/GK132-1</f>
+        <v/>
+      </c>
+      <c r="GS132" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT132" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV132" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW132" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY132">
+        <f>GS132/GT132-1</f>
+        <v/>
+      </c>
+      <c r="GZ132">
+        <f>GU132/GT132-1</f>
+        <v/>
+      </c>
+      <c r="HB132" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC132" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE132" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF132" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH132">
+        <f>HB132/HC132-1</f>
+        <v/>
+      </c>
+      <c r="HI132">
+        <f>HD132/HC132-1</f>
+        <v/>
+      </c>
+      <c r="HK132" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL132" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN132" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO132" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ132">
+        <f>HK132/HL132-1</f>
+        <v/>
+      </c>
+      <c r="HR132">
+        <f>HM132/HL132-1</f>
+        <v/>
+      </c>
+      <c r="HT132" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU132" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW132" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX132" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ132">
+        <f>HT132/HU132-1</f>
+        <v/>
+      </c>
+      <c r="IA132">
+        <f>HV132/HU132-1</f>
+        <v/>
+      </c>
+      <c r="IC132" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID132" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF132" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG132" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II132">
+        <f>IC132/ID132-1</f>
+        <v/>
+      </c>
+      <c r="IJ132">
+        <f>IE132/ID132-1</f>
+        <v/>
+      </c>
+      <c r="IL132" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM132" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO132" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP132" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR132">
+        <f>IL132/IM132-1</f>
+        <v/>
+      </c>
+      <c r="IS132">
+        <f>IN132/IM132-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS132"/>
+  <dimension ref="A1:IS133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -81202,6 +81202,689 @@
         <v/>
       </c>
     </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>24 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I133">
+        <f>C133/D133-1</f>
+        <v/>
+      </c>
+      <c r="J133">
+        <f>E133/D133-1</f>
+        <v/>
+      </c>
+      <c r="L133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R133">
+        <f>L133/M133-1</f>
+        <v/>
+      </c>
+      <c r="S133">
+        <f>N133/M133-1</f>
+        <v/>
+      </c>
+      <c r="U133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA133">
+        <f>U133/V133-1</f>
+        <v/>
+      </c>
+      <c r="AB133">
+        <f>W133/V133-1</f>
+        <v/>
+      </c>
+      <c r="AD133" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE133" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ133">
+        <f>AD133/AE133-1</f>
+        <v/>
+      </c>
+      <c r="AK133">
+        <f>AF133/AE133-1</f>
+        <v/>
+      </c>
+      <c r="AM133" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN133" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS133">
+        <f>AM133/AN133-1</f>
+        <v/>
+      </c>
+      <c r="AT133">
+        <f>AO133/AN133-1</f>
+        <v/>
+      </c>
+      <c r="AV133" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW133" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB133">
+        <f>AV133/AW133-1</f>
+        <v/>
+      </c>
+      <c r="BC133">
+        <f>AX133/AW133-1</f>
+        <v/>
+      </c>
+      <c r="BE133" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF133" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH133" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI133" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK133">
+        <f>BE133/BF133-1</f>
+        <v/>
+      </c>
+      <c r="BL133">
+        <f>BG133/BF133-1</f>
+        <v/>
+      </c>
+      <c r="BN133" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO133" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ133" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR133" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT133">
+        <f>BN133/BO133-1</f>
+        <v/>
+      </c>
+      <c r="BU133">
+        <f>BP133/BO133-1</f>
+        <v/>
+      </c>
+      <c r="BW133" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX133" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ133" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA133" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC133">
+        <f>BW133/BX133-1</f>
+        <v/>
+      </c>
+      <c r="CD133">
+        <f>BY133/BX133-1</f>
+        <v/>
+      </c>
+      <c r="CF133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI133" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ133" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL133">
+        <f>CF133/CG133-1</f>
+        <v/>
+      </c>
+      <c r="CM133">
+        <f>CH133/CG133-1</f>
+        <v/>
+      </c>
+      <c r="CO133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR133" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS133" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU133">
+        <f>CO133/CP133-1</f>
+        <v/>
+      </c>
+      <c r="CV133">
+        <f>CQ133/CP133-1</f>
+        <v/>
+      </c>
+      <c r="CX133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY133" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA133" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB133" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD133">
+        <f>CX133/CY133-1</f>
+        <v/>
+      </c>
+      <c r="DE133">
+        <f>CZ133/CY133-1</f>
+        <v/>
+      </c>
+      <c r="DG133" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH133" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ133" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK133" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM133">
+        <f>DG133/DH133-1</f>
+        <v/>
+      </c>
+      <c r="DN133">
+        <f>DI133/DH133-1</f>
+        <v/>
+      </c>
+      <c r="DP133" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ133" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS133" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT133" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV133">
+        <f>DP133/DQ133-1</f>
+        <v/>
+      </c>
+      <c r="DW133">
+        <f>DR133/DQ133-1</f>
+        <v/>
+      </c>
+      <c r="DY133" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ133" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB133" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC133" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE133">
+        <f>DY133/DZ133-1</f>
+        <v/>
+      </c>
+      <c r="EF133">
+        <f>EA133/DZ133-1</f>
+        <v/>
+      </c>
+      <c r="EH133" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI133" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK133" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL133" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN133">
+        <f>EH133/EI133-1</f>
+        <v/>
+      </c>
+      <c r="EO133">
+        <f>EJ133/EI133-1</f>
+        <v/>
+      </c>
+      <c r="EQ133" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER133" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET133" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU133" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW133">
+        <f>EQ133/ER133-1</f>
+        <v/>
+      </c>
+      <c r="EX133">
+        <f>ES133/ER133-1</f>
+        <v/>
+      </c>
+      <c r="EZ133" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA133" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC133" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD133" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF133">
+        <f>EZ133/FA133-1</f>
+        <v/>
+      </c>
+      <c r="FG133">
+        <f>FB133/FA133-1</f>
+        <v/>
+      </c>
+      <c r="FI133" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ133" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL133" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM133" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO133">
+        <f>FI133/FJ133-1</f>
+        <v/>
+      </c>
+      <c r="FP133">
+        <f>FK133/FJ133-1</f>
+        <v/>
+      </c>
+      <c r="FR133" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS133" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU133" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV133" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX133">
+        <f>FR133/FS133-1</f>
+        <v/>
+      </c>
+      <c r="FY133">
+        <f>FT133/FS133-1</f>
+        <v/>
+      </c>
+      <c r="GA133" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB133" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD133" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE133" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG133">
+        <f>GA133/GB133-1</f>
+        <v/>
+      </c>
+      <c r="GH133">
+        <f>GC133/GB133-1</f>
+        <v/>
+      </c>
+      <c r="GJ133" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK133" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM133" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN133" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP133">
+        <f>GJ133/GK133-1</f>
+        <v/>
+      </c>
+      <c r="GQ133">
+        <f>GL133/GK133-1</f>
+        <v/>
+      </c>
+      <c r="GS133" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT133" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV133" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW133" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY133">
+        <f>GS133/GT133-1</f>
+        <v/>
+      </c>
+      <c r="GZ133">
+        <f>GU133/GT133-1</f>
+        <v/>
+      </c>
+      <c r="HB133" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC133" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE133" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF133" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH133">
+        <f>HB133/HC133-1</f>
+        <v/>
+      </c>
+      <c r="HI133">
+        <f>HD133/HC133-1</f>
+        <v/>
+      </c>
+      <c r="HK133" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL133" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN133" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO133" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ133">
+        <f>HK133/HL133-1</f>
+        <v/>
+      </c>
+      <c r="HR133">
+        <f>HM133/HL133-1</f>
+        <v/>
+      </c>
+      <c r="HT133" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU133" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW133" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX133" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ133">
+        <f>HT133/HU133-1</f>
+        <v/>
+      </c>
+      <c r="IA133">
+        <f>HV133/HU133-1</f>
+        <v/>
+      </c>
+      <c r="IC133" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID133" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF133" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG133" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II133">
+        <f>IC133/ID133-1</f>
+        <v/>
+      </c>
+      <c r="IJ133">
+        <f>IE133/ID133-1</f>
+        <v/>
+      </c>
+      <c r="IL133" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM133" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO133" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP133" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR133">
+        <f>IL133/IM133-1</f>
+        <v/>
+      </c>
+      <c r="IS133">
+        <f>IN133/IM133-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS133"/>
+  <dimension ref="A1:IS134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -81885,6 +81885,691 @@
         <v/>
       </c>
     </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>24 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D134" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I134">
+        <f>C134/D134-1</f>
+        <v/>
+      </c>
+      <c r="J134">
+        <f>E134/D134-1</f>
+        <v/>
+      </c>
+      <c r="L134" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M134" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R134">
+        <f>L134/M134-1</f>
+        <v/>
+      </c>
+      <c r="S134">
+        <f>N134/M134-1</f>
+        <v/>
+      </c>
+      <c r="U134" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V134" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA134">
+        <f>U134/V134-1</f>
+        <v/>
+      </c>
+      <c r="AB134">
+        <f>W134/V134-1</f>
+        <v/>
+      </c>
+      <c r="AD134" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE134" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ134">
+        <f>AD134/AE134-1</f>
+        <v/>
+      </c>
+      <c r="AK134">
+        <f>AF134/AE134-1</f>
+        <v/>
+      </c>
+      <c r="AM134" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN134" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS134">
+        <f>AM134/AN134-1</f>
+        <v/>
+      </c>
+      <c r="AT134">
+        <f>AO134/AN134-1</f>
+        <v/>
+      </c>
+      <c r="AV134" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW134" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB134">
+        <f>AV134/AW134-1</f>
+        <v/>
+      </c>
+      <c r="BC134">
+        <f>AX134/AW134-1</f>
+        <v/>
+      </c>
+      <c r="BE134" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF134" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH134" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI134" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK134">
+        <f>BE134/BF134-1</f>
+        <v/>
+      </c>
+      <c r="BL134">
+        <f>BG134/BF134-1</f>
+        <v/>
+      </c>
+      <c r="BN134" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO134" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ134" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR134" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT134">
+        <f>BN134/BO134-1</f>
+        <v/>
+      </c>
+      <c r="BU134">
+        <f>BP134/BO134-1</f>
+        <v/>
+      </c>
+      <c r="BW134" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX134" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ134" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA134" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC134">
+        <f>BW134/BX134-1</f>
+        <v/>
+      </c>
+      <c r="CD134">
+        <f>BY134/BX134-1</f>
+        <v/>
+      </c>
+      <c r="CF134" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG134" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI134" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ134" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL134">
+        <f>CF134/CG134-1</f>
+        <v/>
+      </c>
+      <c r="CM134">
+        <f>CH134/CG134-1</f>
+        <v/>
+      </c>
+      <c r="CO134" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP134" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CR134" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS134" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CU134">
+        <f>CO134/CP134-1</f>
+        <v/>
+      </c>
+      <c r="CV134">
+        <f>CQ134/CP134-1</f>
+        <v/>
+      </c>
+      <c r="CX134" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY134" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA134" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB134" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD134">
+        <f>CX134/CY134-1</f>
+        <v/>
+      </c>
+      <c r="DE134">
+        <f>CZ134/CY134-1</f>
+        <v/>
+      </c>
+      <c r="DG134" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH134" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ134" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK134" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM134">
+        <f>DG134/DH134-1</f>
+        <v/>
+      </c>
+      <c r="DN134">
+        <f>DI134/DH134-1</f>
+        <v/>
+      </c>
+      <c r="DP134" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ134" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS134" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT134" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV134">
+        <f>DP134/DQ134-1</f>
+        <v/>
+      </c>
+      <c r="DW134">
+        <f>DR134/DQ134-1</f>
+        <v/>
+      </c>
+      <c r="DY134" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ134" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB134" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC134" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE134">
+        <f>DY134/DZ134-1</f>
+        <v/>
+      </c>
+      <c r="EF134">
+        <f>EA134/DZ134-1</f>
+        <v/>
+      </c>
+      <c r="EH134" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI134" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK134" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL134" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN134">
+        <f>EH134/EI134-1</f>
+        <v/>
+      </c>
+      <c r="EO134">
+        <f>EJ134/EI134-1</f>
+        <v/>
+      </c>
+      <c r="EQ134" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER134" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET134" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU134" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW134">
+        <f>EQ134/ER134-1</f>
+        <v/>
+      </c>
+      <c r="EX134">
+        <f>ES134/ER134-1</f>
+        <v/>
+      </c>
+      <c r="EZ134" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA134" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC134" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD134" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF134">
+        <f>EZ134/FA134-1</f>
+        <v/>
+      </c>
+      <c r="FG134">
+        <f>FB134/FA134-1</f>
+        <v/>
+      </c>
+      <c r="FI134" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ134" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL134" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM134" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO134">
+        <f>FI134/FJ134-1</f>
+        <v/>
+      </c>
+      <c r="FP134">
+        <f>FK134/FJ134-1</f>
+        <v/>
+      </c>
+      <c r="FR134" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS134" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU134" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV134" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX134">
+        <f>FR134/FS134-1</f>
+        <v/>
+      </c>
+      <c r="FY134">
+        <f>FT134/FS134-1</f>
+        <v/>
+      </c>
+      <c r="GA134" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB134" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD134" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE134" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG134">
+        <f>GA134/GB134-1</f>
+        <v/>
+      </c>
+      <c r="GH134">
+        <f>GC134/GB134-1</f>
+        <v/>
+      </c>
+      <c r="GJ134" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK134" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM134" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN134" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP134">
+        <f>GJ134/GK134-1</f>
+        <v/>
+      </c>
+      <c r="GQ134">
+        <f>GL134/GK134-1</f>
+        <v/>
+      </c>
+      <c r="GS134" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT134" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV134" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW134" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY134">
+        <f>GS134/GT134-1</f>
+        <v/>
+      </c>
+      <c r="GZ134">
+        <f>GU134/GT134-1</f>
+        <v/>
+      </c>
+      <c r="HB134" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC134" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE134" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF134" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH134">
+        <f>HB134/HC134-1</f>
+        <v/>
+      </c>
+      <c r="HI134">
+        <f>HD134/HC134-1</f>
+        <v/>
+      </c>
+      <c r="HK134" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL134" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN134" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO134" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ134">
+        <f>HK134/HL134-1</f>
+        <v/>
+      </c>
+      <c r="HR134">
+        <f>HM134/HL134-1</f>
+        <v/>
+      </c>
+      <c r="HT134" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU134" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW134" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX134" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ134">
+        <f>HT134/HU134-1</f>
+        <v/>
+      </c>
+      <c r="IA134">
+        <f>HV134/HU134-1</f>
+        <v/>
+      </c>
+      <c r="IC134" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID134" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF134" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG134" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II134">
+        <f>IC134/ID134-1</f>
+        <v/>
+      </c>
+      <c r="IJ134">
+        <f>IE134/ID134-1</f>
+        <v/>
+      </c>
+      <c r="IL134" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM134" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO134" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP134" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR134">
+        <f>IL134/IM134-1</f>
+        <v/>
+      </c>
+      <c r="IS134">
+        <f>IN134/IM134-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS134"/>
+  <dimension ref="A1:IS135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -82570,6 +82570,695 @@
         <v/>
       </c>
     </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>25 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D135" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I135">
+        <f>C135/D135-1</f>
+        <v/>
+      </c>
+      <c r="J135">
+        <f>E135/D135-1</f>
+        <v/>
+      </c>
+      <c r="L135" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M135" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R135">
+        <f>L135/M135-1</f>
+        <v/>
+      </c>
+      <c r="S135">
+        <f>N135/M135-1</f>
+        <v/>
+      </c>
+      <c r="U135" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AA135">
+        <f>U135/V135-1</f>
+        <v/>
+      </c>
+      <c r="AB135">
+        <f>W135/V135-1</f>
+        <v/>
+      </c>
+      <c r="AD135" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE135" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ135">
+        <f>AD135/AE135-1</f>
+        <v/>
+      </c>
+      <c r="AK135">
+        <f>AF135/AE135-1</f>
+        <v/>
+      </c>
+      <c r="AM135" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN135" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS135">
+        <f>AM135/AN135-1</f>
+        <v/>
+      </c>
+      <c r="AT135">
+        <f>AO135/AN135-1</f>
+        <v/>
+      </c>
+      <c r="AV135" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW135" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB135">
+        <f>AV135/AW135-1</f>
+        <v/>
+      </c>
+      <c r="BC135">
+        <f>AX135/AW135-1</f>
+        <v/>
+      </c>
+      <c r="BE135" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF135" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH135" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI135" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK135">
+        <f>BE135/BF135-1</f>
+        <v/>
+      </c>
+      <c r="BL135">
+        <f>BG135/BF135-1</f>
+        <v/>
+      </c>
+      <c r="BN135" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO135" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BQ135" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR135" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BT135">
+        <f>BN135/BO135-1</f>
+        <v/>
+      </c>
+      <c r="BU135">
+        <f>BP135/BO135-1</f>
+        <v/>
+      </c>
+      <c r="BW135" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX135" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ135" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA135" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC135">
+        <f>BW135/BX135-1</f>
+        <v/>
+      </c>
+      <c r="CD135">
+        <f>BY135/BX135-1</f>
+        <v/>
+      </c>
+      <c r="CF135" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG135" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI135" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ135" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL135">
+        <f>CF135/CG135-1</f>
+        <v/>
+      </c>
+      <c r="CM135">
+        <f>CH135/CG135-1</f>
+        <v/>
+      </c>
+      <c r="CO135" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP135" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR135" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS135" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU135">
+        <f>CO135/CP135-1</f>
+        <v/>
+      </c>
+      <c r="CV135">
+        <f>CQ135/CP135-1</f>
+        <v/>
+      </c>
+      <c r="CX135" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY135" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA135" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB135" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD135">
+        <f>CX135/CY135-1</f>
+        <v/>
+      </c>
+      <c r="DE135">
+        <f>CZ135/CY135-1</f>
+        <v/>
+      </c>
+      <c r="DG135" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH135" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ135" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK135" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM135">
+        <f>DG135/DH135-1</f>
+        <v/>
+      </c>
+      <c r="DN135">
+        <f>DI135/DH135-1</f>
+        <v/>
+      </c>
+      <c r="DP135" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ135" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS135" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT135" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV135">
+        <f>DP135/DQ135-1</f>
+        <v/>
+      </c>
+      <c r="DW135">
+        <f>DR135/DQ135-1</f>
+        <v/>
+      </c>
+      <c r="DY135" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ135" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB135" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC135" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE135">
+        <f>DY135/DZ135-1</f>
+        <v/>
+      </c>
+      <c r="EF135">
+        <f>EA135/DZ135-1</f>
+        <v/>
+      </c>
+      <c r="EH135" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI135" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK135" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL135" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN135">
+        <f>EH135/EI135-1</f>
+        <v/>
+      </c>
+      <c r="EO135">
+        <f>EJ135/EI135-1</f>
+        <v/>
+      </c>
+      <c r="EQ135" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER135" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET135" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU135" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW135">
+        <f>EQ135/ER135-1</f>
+        <v/>
+      </c>
+      <c r="EX135">
+        <f>ES135/ER135-1</f>
+        <v/>
+      </c>
+      <c r="EZ135" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA135" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC135" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD135" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF135">
+        <f>EZ135/FA135-1</f>
+        <v/>
+      </c>
+      <c r="FG135">
+        <f>FB135/FA135-1</f>
+        <v/>
+      </c>
+      <c r="FI135" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ135" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL135" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM135" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO135">
+        <f>FI135/FJ135-1</f>
+        <v/>
+      </c>
+      <c r="FP135">
+        <f>FK135/FJ135-1</f>
+        <v/>
+      </c>
+      <c r="FR135" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS135" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU135" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV135" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX135">
+        <f>FR135/FS135-1</f>
+        <v/>
+      </c>
+      <c r="FY135">
+        <f>FT135/FS135-1</f>
+        <v/>
+      </c>
+      <c r="GA135" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB135" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD135" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE135" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG135">
+        <f>GA135/GB135-1</f>
+        <v/>
+      </c>
+      <c r="GH135">
+        <f>GC135/GB135-1</f>
+        <v/>
+      </c>
+      <c r="GJ135" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK135" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GM135" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN135" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GP135">
+        <f>GJ135/GK135-1</f>
+        <v/>
+      </c>
+      <c r="GQ135">
+        <f>GL135/GK135-1</f>
+        <v/>
+      </c>
+      <c r="GS135" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT135" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV135" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW135" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY135">
+        <f>GS135/GT135-1</f>
+        <v/>
+      </c>
+      <c r="GZ135">
+        <f>GU135/GT135-1</f>
+        <v/>
+      </c>
+      <c r="HB135" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC135" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE135" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF135" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH135">
+        <f>HB135/HC135-1</f>
+        <v/>
+      </c>
+      <c r="HI135">
+        <f>HD135/HC135-1</f>
+        <v/>
+      </c>
+      <c r="HK135" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL135" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN135" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO135" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ135">
+        <f>HK135/HL135-1</f>
+        <v/>
+      </c>
+      <c r="HR135">
+        <f>HM135/HL135-1</f>
+        <v/>
+      </c>
+      <c r="HT135" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU135" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW135" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX135" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ135">
+        <f>HT135/HU135-1</f>
+        <v/>
+      </c>
+      <c r="IA135">
+        <f>HV135/HU135-1</f>
+        <v/>
+      </c>
+      <c r="IC135" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID135" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF135" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG135" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II135">
+        <f>IC135/ID135-1</f>
+        <v/>
+      </c>
+      <c r="IJ135">
+        <f>IE135/ID135-1</f>
+        <v/>
+      </c>
+      <c r="IL135" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM135" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO135" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP135" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR135">
+        <f>IL135/IM135-1</f>
+        <v/>
+      </c>
+      <c r="IS135">
+        <f>IN135/IM135-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS135"/>
+  <dimension ref="A1:IS136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -83259,6 +83259,727 @@
         <v/>
       </c>
     </row>
+    <row r="136">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>25 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I136">
+        <f>C136/D136-1</f>
+        <v/>
+      </c>
+      <c r="J136">
+        <f>E136/D136-1</f>
+        <v/>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M136" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R136">
+        <f>L136/M136-1</f>
+        <v/>
+      </c>
+      <c r="S136">
+        <f>N136/M136-1</f>
+        <v/>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V136" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA136">
+        <f>U136/V136-1</f>
+        <v/>
+      </c>
+      <c r="AB136">
+        <f>W136/V136-1</f>
+        <v/>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE136" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ136">
+        <f>AD136/AE136-1</f>
+        <v/>
+      </c>
+      <c r="AK136">
+        <f>AF136/AE136-1</f>
+        <v/>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN136" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS136">
+        <f>AM136/AN136-1</f>
+        <v/>
+      </c>
+      <c r="AT136">
+        <f>AO136/AN136-1</f>
+        <v/>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BB136">
+        <f>AV136/AW136-1</f>
+        <v/>
+      </c>
+      <c r="BC136">
+        <f>AX136/AW136-1</f>
+        <v/>
+      </c>
+      <c r="BE136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF136" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI136" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK136">
+        <f>BE136/BF136-1</f>
+        <v/>
+      </c>
+      <c r="BL136">
+        <f>BG136/BF136-1</f>
+        <v/>
+      </c>
+      <c r="BN136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO136" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR136" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT136">
+        <f>BN136/BO136-1</f>
+        <v/>
+      </c>
+      <c r="BU136">
+        <f>BP136/BO136-1</f>
+        <v/>
+      </c>
+      <c r="BW136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX136" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA136" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC136">
+        <f>BW136/BX136-1</f>
+        <v/>
+      </c>
+      <c r="CD136">
+        <f>BY136/BX136-1</f>
+        <v/>
+      </c>
+      <c r="CF136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG136" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ136" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL136">
+        <f>CF136/CG136-1</f>
+        <v/>
+      </c>
+      <c r="CM136">
+        <f>CH136/CG136-1</f>
+        <v/>
+      </c>
+      <c r="CO136" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP136" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR136" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS136" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU136">
+        <f>CO136/CP136-1</f>
+        <v/>
+      </c>
+      <c r="CV136">
+        <f>CQ136/CP136-1</f>
+        <v/>
+      </c>
+      <c r="CX136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY136" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB136" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD136">
+        <f>CX136/CY136-1</f>
+        <v/>
+      </c>
+      <c r="DE136">
+        <f>CZ136/CY136-1</f>
+        <v/>
+      </c>
+      <c r="DG136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH136" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK136" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM136">
+        <f>DG136/DH136-1</f>
+        <v/>
+      </c>
+      <c r="DN136">
+        <f>DI136/DH136-1</f>
+        <v/>
+      </c>
+      <c r="DP136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ136" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT136" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV136">
+        <f>DP136/DQ136-1</f>
+        <v/>
+      </c>
+      <c r="DW136">
+        <f>DR136/DQ136-1</f>
+        <v/>
+      </c>
+      <c r="DY136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ136" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC136" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE136">
+        <f>DY136/DZ136-1</f>
+        <v/>
+      </c>
+      <c r="EF136">
+        <f>EA136/DZ136-1</f>
+        <v/>
+      </c>
+      <c r="EH136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI136" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL136" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN136">
+        <f>EH136/EI136-1</f>
+        <v/>
+      </c>
+      <c r="EO136">
+        <f>EJ136/EI136-1</f>
+        <v/>
+      </c>
+      <c r="EQ136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER136" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU136" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW136">
+        <f>EQ136/ER136-1</f>
+        <v/>
+      </c>
+      <c r="EX136">
+        <f>ES136/ER136-1</f>
+        <v/>
+      </c>
+      <c r="EZ136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA136" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD136" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF136">
+        <f>EZ136/FA136-1</f>
+        <v/>
+      </c>
+      <c r="FG136">
+        <f>FB136/FA136-1</f>
+        <v/>
+      </c>
+      <c r="FI136" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ136" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL136" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM136" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO136">
+        <f>FI136/FJ136-1</f>
+        <v/>
+      </c>
+      <c r="FP136">
+        <f>FK136/FJ136-1</f>
+        <v/>
+      </c>
+      <c r="FR136" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FU136" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FX136">
+        <f>FR136/FS136-1</f>
+        <v/>
+      </c>
+      <c r="FY136">
+        <f>FT136/FS136-1</f>
+        <v/>
+      </c>
+      <c r="GA136" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB136" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD136" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE136" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG136">
+        <f>GA136/GB136-1</f>
+        <v/>
+      </c>
+      <c r="GH136">
+        <f>GC136/GB136-1</f>
+        <v/>
+      </c>
+      <c r="GJ136" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GM136" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GP136">
+        <f>GJ136/GK136-1</f>
+        <v/>
+      </c>
+      <c r="GQ136">
+        <f>GL136/GK136-1</f>
+        <v/>
+      </c>
+      <c r="GS136" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT136" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV136" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW136" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY136">
+        <f>GS136/GT136-1</f>
+        <v/>
+      </c>
+      <c r="GZ136">
+        <f>GU136/GT136-1</f>
+        <v/>
+      </c>
+      <c r="HB136" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC136" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE136" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF136" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH136">
+        <f>HB136/HC136-1</f>
+        <v/>
+      </c>
+      <c r="HI136">
+        <f>HD136/HC136-1</f>
+        <v/>
+      </c>
+      <c r="HK136" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL136" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN136" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO136" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ136">
+        <f>HK136/HL136-1</f>
+        <v/>
+      </c>
+      <c r="HR136">
+        <f>HM136/HL136-1</f>
+        <v/>
+      </c>
+      <c r="HT136" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU136" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW136" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX136" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ136">
+        <f>HT136/HU136-1</f>
+        <v/>
+      </c>
+      <c r="IA136">
+        <f>HV136/HU136-1</f>
+        <v/>
+      </c>
+      <c r="IC136" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID136" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF136" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG136" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II136">
+        <f>IC136/ID136-1</f>
+        <v/>
+      </c>
+      <c r="IJ136">
+        <f>IE136/ID136-1</f>
+        <v/>
+      </c>
+      <c r="IL136" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO136" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP136" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR136">
+        <f>IL136/IM136-1</f>
+        <v/>
+      </c>
+      <c r="IS136">
+        <f>IN136/IM136-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS136"/>
+  <dimension ref="A1:IS137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -83980,6 +83980,731 @@
         <v/>
       </c>
     </row>
+    <row r="137">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>25 Aug 2026, 12:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I137">
+        <f>C137/D137-1</f>
+        <v/>
+      </c>
+      <c r="J137">
+        <f>E137/D137-1</f>
+        <v/>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R137">
+        <f>L137/M137-1</f>
+        <v/>
+      </c>
+      <c r="S137">
+        <f>N137/M137-1</f>
+        <v/>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V137" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA137">
+        <f>U137/V137-1</f>
+        <v/>
+      </c>
+      <c r="AB137">
+        <f>W137/V137-1</f>
+        <v/>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE137" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ137">
+        <f>AD137/AE137-1</f>
+        <v/>
+      </c>
+      <c r="AK137">
+        <f>AF137/AE137-1</f>
+        <v/>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN137" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS137">
+        <f>AM137/AN137-1</f>
+        <v/>
+      </c>
+      <c r="AT137">
+        <f>AO137/AN137-1</f>
+        <v/>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW137" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB137">
+        <f>AV137/AW137-1</f>
+        <v/>
+      </c>
+      <c r="BC137">
+        <f>AX137/AW137-1</f>
+        <v/>
+      </c>
+      <c r="BE137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF137" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI137" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK137">
+        <f>BE137/BF137-1</f>
+        <v/>
+      </c>
+      <c r="BL137">
+        <f>BG137/BF137-1</f>
+        <v/>
+      </c>
+      <c r="BN137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO137" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR137" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT137">
+        <f>BN137/BO137-1</f>
+        <v/>
+      </c>
+      <c r="BU137">
+        <f>BP137/BO137-1</f>
+        <v/>
+      </c>
+      <c r="BW137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX137" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA137" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC137">
+        <f>BW137/BX137-1</f>
+        <v/>
+      </c>
+      <c r="CD137">
+        <f>BY137/BX137-1</f>
+        <v/>
+      </c>
+      <c r="CF137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG137" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ137" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL137">
+        <f>CF137/CG137-1</f>
+        <v/>
+      </c>
+      <c r="CM137">
+        <f>CH137/CG137-1</f>
+        <v/>
+      </c>
+      <c r="CO137" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP137" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR137" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS137" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU137">
+        <f>CO137/CP137-1</f>
+        <v/>
+      </c>
+      <c r="CV137">
+        <f>CQ137/CP137-1</f>
+        <v/>
+      </c>
+      <c r="CX137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY137" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB137" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD137">
+        <f>CX137/CY137-1</f>
+        <v/>
+      </c>
+      <c r="DE137">
+        <f>CZ137/CY137-1</f>
+        <v/>
+      </c>
+      <c r="DG137" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH137" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ137" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK137" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM137">
+        <f>DG137/DH137-1</f>
+        <v/>
+      </c>
+      <c r="DN137">
+        <f>DI137/DH137-1</f>
+        <v/>
+      </c>
+      <c r="DP137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ137" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT137" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV137">
+        <f>DP137/DQ137-1</f>
+        <v/>
+      </c>
+      <c r="DW137">
+        <f>DR137/DQ137-1</f>
+        <v/>
+      </c>
+      <c r="DY137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ137" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC137" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE137">
+        <f>DY137/DZ137-1</f>
+        <v/>
+      </c>
+      <c r="EF137">
+        <f>EA137/DZ137-1</f>
+        <v/>
+      </c>
+      <c r="EH137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI137" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL137" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN137">
+        <f>EH137/EI137-1</f>
+        <v/>
+      </c>
+      <c r="EO137">
+        <f>EJ137/EI137-1</f>
+        <v/>
+      </c>
+      <c r="EQ137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER137" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU137" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW137">
+        <f>EQ137/ER137-1</f>
+        <v/>
+      </c>
+      <c r="EX137">
+        <f>ES137/ER137-1</f>
+        <v/>
+      </c>
+      <c r="EZ137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA137" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD137" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF137">
+        <f>EZ137/FA137-1</f>
+        <v/>
+      </c>
+      <c r="FG137">
+        <f>FB137/FA137-1</f>
+        <v/>
+      </c>
+      <c r="FI137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FJ137" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FM137" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO137">
+        <f>FI137/FJ137-1</f>
+        <v/>
+      </c>
+      <c r="FP137">
+        <f>FK137/FJ137-1</f>
+        <v/>
+      </c>
+      <c r="FR137" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS137" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU137" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV137" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX137">
+        <f>FR137/FS137-1</f>
+        <v/>
+      </c>
+      <c r="FY137">
+        <f>FT137/FS137-1</f>
+        <v/>
+      </c>
+      <c r="GA137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GB137" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GE137" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG137">
+        <f>GA137/GB137-1</f>
+        <v/>
+      </c>
+      <c r="GH137">
+        <f>GC137/GB137-1</f>
+        <v/>
+      </c>
+      <c r="GJ137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GK137" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GN137" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP137">
+        <f>GJ137/GK137-1</f>
+        <v/>
+      </c>
+      <c r="GQ137">
+        <f>GL137/GK137-1</f>
+        <v/>
+      </c>
+      <c r="GS137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GT137" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GW137" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY137">
+        <f>GS137/GT137-1</f>
+        <v/>
+      </c>
+      <c r="GZ137">
+        <f>GU137/GT137-1</f>
+        <v/>
+      </c>
+      <c r="HB137" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC137" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE137" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF137" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH137">
+        <f>HB137/HC137-1</f>
+        <v/>
+      </c>
+      <c r="HI137">
+        <f>HD137/HC137-1</f>
+        <v/>
+      </c>
+      <c r="HK137" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL137" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN137" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO137" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ137">
+        <f>HK137/HL137-1</f>
+        <v/>
+      </c>
+      <c r="HR137">
+        <f>HM137/HL137-1</f>
+        <v/>
+      </c>
+      <c r="HT137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HU137" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="HX137" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ137">
+        <f>HT137/HU137-1</f>
+        <v/>
+      </c>
+      <c r="IA137">
+        <f>HV137/HU137-1</f>
+        <v/>
+      </c>
+      <c r="IC137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ID137" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IG137" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II137">
+        <f>IC137/ID137-1</f>
+        <v/>
+      </c>
+      <c r="IJ137">
+        <f>IE137/ID137-1</f>
+        <v/>
+      </c>
+      <c r="IL137" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO137" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP137" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR137">
+        <f>IL137/IM137-1</f>
+        <v/>
+      </c>
+      <c r="IS137">
+        <f>IN137/IM137-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS137"/>
+  <dimension ref="A1:IS138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -84705,6 +84705,725 @@
         <v/>
       </c>
     </row>
+    <row r="138">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>25 Aug 2026, 18:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I138">
+        <f>C138/D138-1</f>
+        <v/>
+      </c>
+      <c r="J138">
+        <f>E138/D138-1</f>
+        <v/>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M138" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R138">
+        <f>L138/M138-1</f>
+        <v/>
+      </c>
+      <c r="S138">
+        <f>N138/M138-1</f>
+        <v/>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V138" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA138">
+        <f>U138/V138-1</f>
+        <v/>
+      </c>
+      <c r="AB138">
+        <f>W138/V138-1</f>
+        <v/>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE138" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ138">
+        <f>AD138/AE138-1</f>
+        <v/>
+      </c>
+      <c r="AK138">
+        <f>AF138/AE138-1</f>
+        <v/>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AS138">
+        <f>AM138/AN138-1</f>
+        <v/>
+      </c>
+      <c r="AT138">
+        <f>AO138/AN138-1</f>
+        <v/>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AW138" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB138">
+        <f>AV138/AW138-1</f>
+        <v/>
+      </c>
+      <c r="BC138">
+        <f>AX138/AW138-1</f>
+        <v/>
+      </c>
+      <c r="BE138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF138" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI138" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK138">
+        <f>BE138/BF138-1</f>
+        <v/>
+      </c>
+      <c r="BL138">
+        <f>BG138/BF138-1</f>
+        <v/>
+      </c>
+      <c r="BN138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO138" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR138" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT138">
+        <f>BN138/BO138-1</f>
+        <v/>
+      </c>
+      <c r="BU138">
+        <f>BP138/BO138-1</f>
+        <v/>
+      </c>
+      <c r="BW138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX138" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA138" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC138">
+        <f>BW138/BX138-1</f>
+        <v/>
+      </c>
+      <c r="CD138">
+        <f>BY138/BX138-1</f>
+        <v/>
+      </c>
+      <c r="CF138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG138" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ138" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL138">
+        <f>CF138/CG138-1</f>
+        <v/>
+      </c>
+      <c r="CM138">
+        <f>CH138/CG138-1</f>
+        <v/>
+      </c>
+      <c r="CO138" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP138" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR138" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS138" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU138">
+        <f>CO138/CP138-1</f>
+        <v/>
+      </c>
+      <c r="CV138">
+        <f>CQ138/CP138-1</f>
+        <v/>
+      </c>
+      <c r="CX138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CY138" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DB138" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD138">
+        <f>CX138/CY138-1</f>
+        <v/>
+      </c>
+      <c r="DE138">
+        <f>CZ138/CY138-1</f>
+        <v/>
+      </c>
+      <c r="DG138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH138" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK138" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM138">
+        <f>DG138/DH138-1</f>
+        <v/>
+      </c>
+      <c r="DN138">
+        <f>DI138/DH138-1</f>
+        <v/>
+      </c>
+      <c r="DP138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ138" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT138" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV138">
+        <f>DP138/DQ138-1</f>
+        <v/>
+      </c>
+      <c r="DW138">
+        <f>DR138/DQ138-1</f>
+        <v/>
+      </c>
+      <c r="DY138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ138" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC138" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE138">
+        <f>DY138/DZ138-1</f>
+        <v/>
+      </c>
+      <c r="EF138">
+        <f>EA138/DZ138-1</f>
+        <v/>
+      </c>
+      <c r="EH138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI138" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL138" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN138">
+        <f>EH138/EI138-1</f>
+        <v/>
+      </c>
+      <c r="EO138">
+        <f>EJ138/EI138-1</f>
+        <v/>
+      </c>
+      <c r="EQ138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER138" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU138" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW138">
+        <f>EQ138/ER138-1</f>
+        <v/>
+      </c>
+      <c r="EX138">
+        <f>ES138/ER138-1</f>
+        <v/>
+      </c>
+      <c r="EZ138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FA138" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="FD138" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF138">
+        <f>EZ138/FA138-1</f>
+        <v/>
+      </c>
+      <c r="FG138">
+        <f>FB138/FA138-1</f>
+        <v/>
+      </c>
+      <c r="FI138" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ138" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL138" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM138" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO138">
+        <f>FI138/FJ138-1</f>
+        <v/>
+      </c>
+      <c r="FP138">
+        <f>FK138/FJ138-1</f>
+        <v/>
+      </c>
+      <c r="FR138" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS138" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU138" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV138" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX138">
+        <f>FR138/FS138-1</f>
+        <v/>
+      </c>
+      <c r="FY138">
+        <f>FT138/FS138-1</f>
+        <v/>
+      </c>
+      <c r="GA138" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GB138" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD138" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE138" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG138">
+        <f>GA138/GB138-1</f>
+        <v/>
+      </c>
+      <c r="GH138">
+        <f>GC138/GB138-1</f>
+        <v/>
+      </c>
+      <c r="GJ138" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GM138" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="GP138">
+        <f>GJ138/GK138-1</f>
+        <v/>
+      </c>
+      <c r="GQ138">
+        <f>GL138/GK138-1</f>
+        <v/>
+      </c>
+      <c r="GS138" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT138" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV138" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW138" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY138">
+        <f>GS138/GT138-1</f>
+        <v/>
+      </c>
+      <c r="GZ138">
+        <f>GU138/GT138-1</f>
+        <v/>
+      </c>
+      <c r="HB138" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC138" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE138" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF138" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH138">
+        <f>HB138/HC138-1</f>
+        <v/>
+      </c>
+      <c r="HI138">
+        <f>HD138/HC138-1</f>
+        <v/>
+      </c>
+      <c r="HK138" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL138" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN138" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO138" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ138">
+        <f>HK138/HL138-1</f>
+        <v/>
+      </c>
+      <c r="HR138">
+        <f>HM138/HL138-1</f>
+        <v/>
+      </c>
+      <c r="HT138" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU138" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW138" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX138" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ138">
+        <f>HT138/HU138-1</f>
+        <v/>
+      </c>
+      <c r="IA138">
+        <f>HV138/HU138-1</f>
+        <v/>
+      </c>
+      <c r="IC138" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID138" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF138" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG138" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II138">
+        <f>IC138/ID138-1</f>
+        <v/>
+      </c>
+      <c r="IJ138">
+        <f>IE138/ID138-1</f>
+        <v/>
+      </c>
+      <c r="IL138" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO138" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP138" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR138">
+        <f>IL138/IM138-1</f>
+        <v/>
+      </c>
+      <c r="IS138">
+        <f>IN138/IM138-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS138"/>
+  <dimension ref="A1:IS139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -85424,6 +85424,719 @@
         <v/>
       </c>
     </row>
+    <row r="139">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>26 Aug 2026, 00:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I139">
+        <f>C139/D139-1</f>
+        <v/>
+      </c>
+      <c r="J139">
+        <f>E139/D139-1</f>
+        <v/>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R139">
+        <f>L139/M139-1</f>
+        <v/>
+      </c>
+      <c r="S139">
+        <f>N139/M139-1</f>
+        <v/>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="V139" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA139">
+        <f>U139/V139-1</f>
+        <v/>
+      </c>
+      <c r="AB139">
+        <f>W139/V139-1</f>
+        <v/>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AE139" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ139">
+        <f>AD139/AE139-1</f>
+        <v/>
+      </c>
+      <c r="AK139">
+        <f>AF139/AE139-1</f>
+        <v/>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AN139" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS139">
+        <f>AM139/AN139-1</f>
+        <v/>
+      </c>
+      <c r="AT139">
+        <f>AO139/AN139-1</f>
+        <v/>
+      </c>
+      <c r="AV139" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW139" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB139">
+        <f>AV139/AW139-1</f>
+        <v/>
+      </c>
+      <c r="BC139">
+        <f>AX139/AW139-1</f>
+        <v/>
+      </c>
+      <c r="BE139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BF139" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BI139" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK139">
+        <f>BE139/BF139-1</f>
+        <v/>
+      </c>
+      <c r="BL139">
+        <f>BG139/BF139-1</f>
+        <v/>
+      </c>
+      <c r="BN139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BO139" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BR139" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT139">
+        <f>BN139/BO139-1</f>
+        <v/>
+      </c>
+      <c r="BU139">
+        <f>BP139/BO139-1</f>
+        <v/>
+      </c>
+      <c r="BW139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="BX139" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CA139" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC139">
+        <f>BW139/BX139-1</f>
+        <v/>
+      </c>
+      <c r="CD139">
+        <f>BY139/BX139-1</f>
+        <v/>
+      </c>
+      <c r="CF139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CG139" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CJ139" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL139">
+        <f>CF139/CG139-1</f>
+        <v/>
+      </c>
+      <c r="CM139">
+        <f>CH139/CG139-1</f>
+        <v/>
+      </c>
+      <c r="CO139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CP139" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CS139" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU139">
+        <f>CO139/CP139-1</f>
+        <v/>
+      </c>
+      <c r="CV139">
+        <f>CQ139/CP139-1</f>
+        <v/>
+      </c>
+      <c r="CX139" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY139" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA139" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB139" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD139">
+        <f>CX139/CY139-1</f>
+        <v/>
+      </c>
+      <c r="DE139">
+        <f>CZ139/CY139-1</f>
+        <v/>
+      </c>
+      <c r="DG139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DH139" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DK139" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM139">
+        <f>DG139/DH139-1</f>
+        <v/>
+      </c>
+      <c r="DN139">
+        <f>DI139/DH139-1</f>
+        <v/>
+      </c>
+      <c r="DP139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DQ139" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DT139" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV139">
+        <f>DP139/DQ139-1</f>
+        <v/>
+      </c>
+      <c r="DW139">
+        <f>DR139/DQ139-1</f>
+        <v/>
+      </c>
+      <c r="DY139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="DZ139" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EC139" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE139">
+        <f>DY139/DZ139-1</f>
+        <v/>
+      </c>
+      <c r="EF139">
+        <f>EA139/DZ139-1</f>
+        <v/>
+      </c>
+      <c r="EH139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EI139" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EL139" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN139">
+        <f>EH139/EI139-1</f>
+        <v/>
+      </c>
+      <c r="EO139">
+        <f>EJ139/EI139-1</f>
+        <v/>
+      </c>
+      <c r="EQ139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ET139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EW139">
+        <f>EQ139/ER139-1</f>
+        <v/>
+      </c>
+      <c r="EX139">
+        <f>ES139/ER139-1</f>
+        <v/>
+      </c>
+      <c r="EZ139" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA139" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC139" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD139" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF139">
+        <f>EZ139/FA139-1</f>
+        <v/>
+      </c>
+      <c r="FG139">
+        <f>FB139/FA139-1</f>
+        <v/>
+      </c>
+      <c r="FI139" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ139" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL139" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM139" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO139">
+        <f>FI139/FJ139-1</f>
+        <v/>
+      </c>
+      <c r="FP139">
+        <f>FK139/FJ139-1</f>
+        <v/>
+      </c>
+      <c r="FR139" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS139" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU139" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV139" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX139">
+        <f>FR139/FS139-1</f>
+        <v/>
+      </c>
+      <c r="FY139">
+        <f>FT139/FS139-1</f>
+        <v/>
+      </c>
+      <c r="GA139" s="11" t="n">
+        <v>374.99</v>
+      </c>
+      <c r="GB139" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD139" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE139" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG139">
+        <f>GA139/GB139-1</f>
+        <v/>
+      </c>
+      <c r="GH139">
+        <f>GC139/GB139-1</f>
+        <v/>
+      </c>
+      <c r="GJ139" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK139" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM139" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN139" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP139">
+        <f>GJ139/GK139-1</f>
+        <v/>
+      </c>
+      <c r="GQ139">
+        <f>GL139/GK139-1</f>
+        <v/>
+      </c>
+      <c r="GS139" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT139" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV139" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW139" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY139">
+        <f>GS139/GT139-1</f>
+        <v/>
+      </c>
+      <c r="GZ139">
+        <f>GU139/GT139-1</f>
+        <v/>
+      </c>
+      <c r="HB139" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC139" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE139" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF139" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH139">
+        <f>HB139/HC139-1</f>
+        <v/>
+      </c>
+      <c r="HI139">
+        <f>HD139/HC139-1</f>
+        <v/>
+      </c>
+      <c r="HK139" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL139" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN139" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO139" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ139">
+        <f>HK139/HL139-1</f>
+        <v/>
+      </c>
+      <c r="HR139">
+        <f>HM139/HL139-1</f>
+        <v/>
+      </c>
+      <c r="HT139" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU139" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW139" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX139" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ139">
+        <f>HT139/HU139-1</f>
+        <v/>
+      </c>
+      <c r="IA139">
+        <f>HV139/HU139-1</f>
+        <v/>
+      </c>
+      <c r="IC139" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID139" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF139" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG139" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II139">
+        <f>IC139/ID139-1</f>
+        <v/>
+      </c>
+      <c r="IJ139">
+        <f>IE139/ID139-1</f>
+        <v/>
+      </c>
+      <c r="IL139" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO139" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP139" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR139">
+        <f>IL139/IM139-1</f>
+        <v/>
+      </c>
+      <c r="IS139">
+        <f>IN139/IM139-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/results.xlsx
+++ b/outputs/results.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IS139"/>
+  <dimension ref="A1:IS140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -86137,6 +86137,689 @@
         <v/>
       </c>
     </row>
+    <row r="140">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>26 Aug 2026, 06:00</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="D140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>SM-F976UZVAXAA</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>sm-f976uzvaxaa</t>
+        </is>
+      </c>
+      <c r="I140">
+        <f>C140/D140-1</f>
+        <v/>
+      </c>
+      <c r="J140">
+        <f>E140/D140-1</f>
+        <v/>
+      </c>
+      <c r="L140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="M140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>SM-F976UZWAXAA</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>sm-f976uzwaxaa</t>
+        </is>
+      </c>
+      <c r="R140">
+        <f>L140/M140-1</f>
+        <v/>
+      </c>
+      <c r="S140">
+        <f>N140/M140-1</f>
+        <v/>
+      </c>
+      <c r="U140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="V140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>SM-F976UZKAXAA</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>sm-f976uzkaxaa</t>
+        </is>
+      </c>
+      <c r="AA140">
+        <f>U140/V140-1</f>
+        <v/>
+      </c>
+      <c r="AB140">
+        <f>W140/V140-1</f>
+        <v/>
+      </c>
+      <c r="AD140" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AE140" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>SM-F976UZVEXAA</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>sm-f976uzvexaa</t>
+        </is>
+      </c>
+      <c r="AJ140">
+        <f>AD140/AE140-1</f>
+        <v/>
+      </c>
+      <c r="AK140">
+        <f>AF140/AE140-1</f>
+        <v/>
+      </c>
+      <c r="AM140" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AN140" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>SM-F976UZWEXAA</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>sm-f976uzwexaa</t>
+        </is>
+      </c>
+      <c r="AS140">
+        <f>AM140/AN140-1</f>
+        <v/>
+      </c>
+      <c r="AT140">
+        <f>AO140/AN140-1</f>
+        <v/>
+      </c>
+      <c r="AV140" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AW140" s="11" t="n">
+        <v>2299.99</v>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>SM-F976UZKEXAA</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>sm-f976uzkexaa</t>
+        </is>
+      </c>
+      <c r="BB140">
+        <f>AV140/AW140-1</f>
+        <v/>
+      </c>
+      <c r="BC140">
+        <f>AX140/AW140-1</f>
+        <v/>
+      </c>
+      <c r="BE140" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BF140" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BH140" t="inlineStr">
+        <is>
+          <t>SM-F971ULVAXAA</t>
+        </is>
+      </c>
+      <c r="BI140" t="inlineStr">
+        <is>
+          <t>sm-f971ulvaxaa</t>
+        </is>
+      </c>
+      <c r="BK140">
+        <f>BE140/BF140-1</f>
+        <v/>
+      </c>
+      <c r="BL140">
+        <f>BG140/BF140-1</f>
+        <v/>
+      </c>
+      <c r="BN140" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BO140" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BQ140" t="inlineStr">
+        <is>
+          <t>SM-F971UZWAXAA</t>
+        </is>
+      </c>
+      <c r="BR140" t="inlineStr">
+        <is>
+          <t>sm-f971uzwaxaa</t>
+        </is>
+      </c>
+      <c r="BT140">
+        <f>BN140/BO140-1</f>
+        <v/>
+      </c>
+      <c r="BU140">
+        <f>BP140/BO140-1</f>
+        <v/>
+      </c>
+      <c r="BW140" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BX140" s="11" t="n">
+        <v>1899.99</v>
+      </c>
+      <c r="BZ140" t="inlineStr">
+        <is>
+          <t>SM-F971UZKAXAA</t>
+        </is>
+      </c>
+      <c r="CA140" t="inlineStr">
+        <is>
+          <t>sm-f971uzkaxaa</t>
+        </is>
+      </c>
+      <c r="CC140">
+        <f>BW140/BX140-1</f>
+        <v/>
+      </c>
+      <c r="CD140">
+        <f>BY140/BX140-1</f>
+        <v/>
+      </c>
+      <c r="CF140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CG140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CI140" t="inlineStr">
+        <is>
+          <t>SM-F971ULVEXAA</t>
+        </is>
+      </c>
+      <c r="CJ140" t="inlineStr">
+        <is>
+          <t>sm-f971ulvexaa</t>
+        </is>
+      </c>
+      <c r="CL140">
+        <f>CF140/CG140-1</f>
+        <v/>
+      </c>
+      <c r="CM140">
+        <f>CH140/CG140-1</f>
+        <v/>
+      </c>
+      <c r="CO140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CP140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CR140" t="inlineStr">
+        <is>
+          <t>SM-F971UZWEXAA</t>
+        </is>
+      </c>
+      <c r="CS140" t="inlineStr">
+        <is>
+          <t>sm-f971uzwexaa</t>
+        </is>
+      </c>
+      <c r="CU140">
+        <f>CO140/CP140-1</f>
+        <v/>
+      </c>
+      <c r="CV140">
+        <f>CQ140/CP140-1</f>
+        <v/>
+      </c>
+      <c r="CX140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="CY140" s="11" t="n">
+        <v>2099.99</v>
+      </c>
+      <c r="DA140" t="inlineStr">
+        <is>
+          <t>SM-F971UZKEXAA</t>
+        </is>
+      </c>
+      <c r="DB140" t="inlineStr">
+        <is>
+          <t>sm-f971uzkexaa</t>
+        </is>
+      </c>
+      <c r="DD140">
+        <f>CX140/CY140-1</f>
+        <v/>
+      </c>
+      <c r="DE140">
+        <f>CZ140/CY140-1</f>
+        <v/>
+      </c>
+      <c r="DG140" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DH140" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DJ140" t="inlineStr">
+        <is>
+          <t>SM-F776ULIAXAA</t>
+        </is>
+      </c>
+      <c r="DK140" t="inlineStr">
+        <is>
+          <t>sm-f776uliaxaa</t>
+        </is>
+      </c>
+      <c r="DM140">
+        <f>DG140/DH140-1</f>
+        <v/>
+      </c>
+      <c r="DN140">
+        <f>DI140/DH140-1</f>
+        <v/>
+      </c>
+      <c r="DP140" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DQ140" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DS140" t="inlineStr">
+        <is>
+          <t>SM-F776UZWAXAA</t>
+        </is>
+      </c>
+      <c r="DT140" t="inlineStr">
+        <is>
+          <t>sm-f776uzwaxaa</t>
+        </is>
+      </c>
+      <c r="DV140">
+        <f>DP140/DQ140-1</f>
+        <v/>
+      </c>
+      <c r="DW140">
+        <f>DR140/DQ140-1</f>
+        <v/>
+      </c>
+      <c r="DY140" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="DZ140" s="11" t="n">
+        <v>1199.99</v>
+      </c>
+      <c r="EB140" t="inlineStr">
+        <is>
+          <t>SM-F776UZKAXAA</t>
+        </is>
+      </c>
+      <c r="EC140" t="inlineStr">
+        <is>
+          <t>sm-f776uzkaxaa</t>
+        </is>
+      </c>
+      <c r="EE140">
+        <f>DY140/DZ140-1</f>
+        <v/>
+      </c>
+      <c r="EF140">
+        <f>EA140/DZ140-1</f>
+        <v/>
+      </c>
+      <c r="EH140" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EI140" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="EK140" t="inlineStr">
+        <is>
+          <t>SM-F776ULIEXAA</t>
+        </is>
+      </c>
+      <c r="EL140" t="inlineStr">
+        <is>
+          <t>sm-f776uliexaa</t>
+        </is>
+      </c>
+      <c r="EN140">
+        <f>EH140/EI140-1</f>
+        <v/>
+      </c>
+      <c r="EO140">
+        <f>EJ140/EI140-1</f>
+        <v/>
+      </c>
+      <c r="EQ140" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="ER140" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="ET140" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="EU140" t="inlineStr">
+        <is>
+          <t>sm-f776uzwexaa</t>
+        </is>
+      </c>
+      <c r="EW140">
+        <f>EQ140/ER140-1</f>
+        <v/>
+      </c>
+      <c r="EX140">
+        <f>ES140/ER140-1</f>
+        <v/>
+      </c>
+      <c r="EZ140" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FA140" s="11" t="n">
+        <v>1399.99</v>
+      </c>
+      <c r="FC140" t="inlineStr">
+        <is>
+          <t>SM-F776UZKEXAA</t>
+        </is>
+      </c>
+      <c r="FD140" t="inlineStr">
+        <is>
+          <t>sm-f776uzkexaa</t>
+        </is>
+      </c>
+      <c r="FF140">
+        <f>EZ140/FA140-1</f>
+        <v/>
+      </c>
+      <c r="FG140">
+        <f>FB140/FA140-1</f>
+        <v/>
+      </c>
+      <c r="FI140" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FJ140" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="FL140" t="inlineStr">
+        <is>
+          <t>SM-L340NZEAXAA</t>
+        </is>
+      </c>
+      <c r="FM140" t="inlineStr">
+        <is>
+          <t>sm-l340nzeaxaa</t>
+        </is>
+      </c>
+      <c r="FO140">
+        <f>FI140/FJ140-1</f>
+        <v/>
+      </c>
+      <c r="FP140">
+        <f>FK140/FJ140-1</f>
+        <v/>
+      </c>
+      <c r="FR140" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FS140" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="FU140" t="inlineStr">
+        <is>
+          <t>SM-L345UZEDXAA</t>
+        </is>
+      </c>
+      <c r="FV140" t="inlineStr">
+        <is>
+          <t>sm-l345uzedxaa</t>
+        </is>
+      </c>
+      <c r="FX140">
+        <f>FR140/FS140-1</f>
+        <v/>
+      </c>
+      <c r="FY140">
+        <f>FT140/FS140-1</f>
+        <v/>
+      </c>
+      <c r="GA140" s="11" t="n">
+        <v>374.99</v>
+      </c>
+      <c r="GB140" s="11" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="GD140" t="inlineStr">
+        <is>
+          <t>SM-L340NZKAXAA</t>
+        </is>
+      </c>
+      <c r="GE140" t="inlineStr">
+        <is>
+          <t>sm-l340nzkaxaa</t>
+        </is>
+      </c>
+      <c r="GG140">
+        <f>GA140/GB140-1</f>
+        <v/>
+      </c>
+      <c r="GH140">
+        <f>GC140/GB140-1</f>
+        <v/>
+      </c>
+      <c r="GJ140" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GK140" s="11" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="GM140" t="inlineStr">
+        <is>
+          <t>SM-L345UZKAXAA</t>
+        </is>
+      </c>
+      <c r="GN140" t="inlineStr">
+        <is>
+          <t>sm-l345uzkaxaa</t>
+        </is>
+      </c>
+      <c r="GP140">
+        <f>GJ140/GK140-1</f>
+        <v/>
+      </c>
+      <c r="GQ140">
+        <f>GL140/GK140-1</f>
+        <v/>
+      </c>
+      <c r="GS140" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GT140" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="GV140" t="inlineStr">
+        <is>
+          <t>SM-L350NZSAXAA</t>
+        </is>
+      </c>
+      <c r="GW140" t="inlineStr">
+        <is>
+          <t>sm-l350nzsaxaa</t>
+        </is>
+      </c>
+      <c r="GY140">
+        <f>GS140/GT140-1</f>
+        <v/>
+      </c>
+      <c r="GZ140">
+        <f>GU140/GT140-1</f>
+        <v/>
+      </c>
+      <c r="HB140" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HC140" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HE140" t="inlineStr">
+        <is>
+          <t>SM-L355UZSDXAA</t>
+        </is>
+      </c>
+      <c r="HF140" t="inlineStr">
+        <is>
+          <t>sm-l355uzsdxaa</t>
+        </is>
+      </c>
+      <c r="HH140">
+        <f>HB140/HC140-1</f>
+        <v/>
+      </c>
+      <c r="HI140">
+        <f>HD140/HC140-1</f>
+        <v/>
+      </c>
+      <c r="HK140" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HL140" s="11" t="n">
+        <v>409.99</v>
+      </c>
+      <c r="HN140" t="inlineStr">
+        <is>
+          <t>SM-L350NZKAXAA</t>
+        </is>
+      </c>
+      <c r="HO140" t="inlineStr">
+        <is>
+          <t>sm-l350nzkaxaa</t>
+        </is>
+      </c>
+      <c r="HQ140">
+        <f>HK140/HL140-1</f>
+        <v/>
+      </c>
+      <c r="HR140">
+        <f>HM140/HL140-1</f>
+        <v/>
+      </c>
+      <c r="HT140" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HU140" s="11" t="n">
+        <v>459.99</v>
+      </c>
+      <c r="HW140" t="inlineStr">
+        <is>
+          <t>SM-L355UZKDXAA</t>
+        </is>
+      </c>
+      <c r="HX140" t="inlineStr">
+        <is>
+          <t>sm-l355uzkdxaa</t>
+        </is>
+      </c>
+      <c r="HZ140">
+        <f>HT140/HU140-1</f>
+        <v/>
+      </c>
+      <c r="IA140">
+        <f>HV140/HU140-1</f>
+        <v/>
+      </c>
+      <c r="IC140" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="ID140" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IF140" t="inlineStr">
+        <is>
+          <t>SM-L715UZKAXAA</t>
+        </is>
+      </c>
+      <c r="IG140" t="inlineStr">
+        <is>
+          <t>sm-l715uzkaxaa</t>
+        </is>
+      </c>
+      <c r="II140">
+        <f>IC140/ID140-1</f>
+        <v/>
+      </c>
+      <c r="IJ140">
+        <f>IE140/ID140-1</f>
+        <v/>
+      </c>
+      <c r="IL140" s="11" t="n">
+        <v>699.99</v>
+      </c>
+      <c r="IM140" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IO140" t="inlineStr">
+        <is>
+          <t>SM-L715UZSAXAA</t>
+        </is>
+      </c>
+      <c r="IP140" t="inlineStr">
+        <is>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="IR140">
+        <f>IL140/IM140-1</f>
+        <v/>
+      </c>
+      <c r="IS140">
+        <f>IN140/IM140-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
